--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B31AC30-2F57-42A5-A66C-235975CEA9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="29920" windowHeight="12420"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,9 +149,6 @@
     <t>newProcess</t>
   </si>
   <si>
-    <t>{"id":"NEW","order":1,"flow":"NEW","isSubProcess":false,"label":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"screens":[{"order":1,"name":"consentdet","label":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"caption":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"ara":"الاسم الكامل الكامل الكامل","fra":"J'ai lu et j'accepte les termes et conditions pour partager mes PII","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"ara":"لغة الإخطار","fra":"Langue de notification","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"caption":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"fields":[{"id":"fullName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Full Name","label":{"ara":"الاسم الكامل","fra":"Nom complet","eng":"Full Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"name"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"ara":"الاسم الكامل","fra":"DOB","eng":"DOB"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"ara":"جنس","fra":"Le genre","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"ara":"الاسم الكامل","fra":"line1","eng":"line1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"ara":"الاسم الكامل","fra":"line2","eng":"line2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"addressLine3","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine3","label":{"ara":"الاسم الكامل","fra":"line3","eng":"line3"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine3"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"ara":"الاسم الكامل","fra":"Reside Status","eng":"Residence Status"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"referenceIdentityNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"referenceIdentityNumber","label":{"ara":"الاسم الكامل","fra":"Reference Identity Number","eng":"Reference Identity Number"},"controlType":"textbox","fieldType":"default","format":"kyc","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ReferenceIdentityNumber","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"none"},{"id":"region","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"region","label":{"ara":"الاسم الكامل","fra":"Region","eng":"Region"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Region"},{"id":"province","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"province","label":{"ara":"الاسم الكامل","fra":"Province","eng":"Province"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Province"},{"id":"city","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"city","label":{"ara":"الاسم الكامل","fra":"City","eng":"City"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"City"},{"id":"zone","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"zone","label":{"ara":"الاسم الكامل","fra":"Zone","eng":"Zone"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":null,"group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Zone"},{"id":"postalCode","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"postalCode","label":{"ara":"الاسم الكامل","fra":"Postal","eng":"Postal"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[(?i)A-Z0-9]{5}$|^NA$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Postal Code"},{"id":"phone","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"phone","label":{"ara":"الاسم الكامل","fra":"Phone","eng":"Phone"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[+]*([0-9]{1})([0-9]{9})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Phone"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"ara":"الاسم الكامل","fra":"Email","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"ara":"اسم المُعرّف","fra":"nom del'introducteur","eng":"Introducer Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"ara":"مقدم RID","fra":"Introducteur RID","eng":"Introducer RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"ara":"مقدم في","fra":"Introducteur UIN","eng":"Introducer UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"}],"layoutTemplate":null,"preRegFetchRequired":true,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","fra":"Des documents","eng":"Document Upload"},"caption":{"ara":"وثائق","fra":"Des documents","eng":"Documents"},"fields":[{"id":"proofOfAddress","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfAddress","label":{"ara":"إثبات العنوان","fra":"Address Proof","eng":"Address Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POA"},{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"ara":"إثبات الهوية","fra":"Identity Proof","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"ara":"إثبات العلاقة","fra":"Relationship Proof","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"ara":"دليل DOB","fra":"DOB Proof","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"ara":"إثبات الاستثناء","fra":"Exception Proof","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"caption":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"القياسات الحيوية الفردية","fra":"Applicant Biometrics","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"مقدم القياسات الحيوية","fra":"Introducteur Biométrie","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false}],"caption":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"icon":"NewReg.png","isActive":true,"autoSelectedGroups":null}</t>
-  </si>
-  <si>
     <t>703796d8-085f-4778-80be-df298c1b8367</t>
   </si>
   <si>
@@ -181,18 +184,15 @@
   <si>
     <t xml:space="preserve">{"id":"BIOMETRIC_CORRECTION","order":4,"flow":"CORRECTION","isSubProcess":false,"label":{"eng":"Biometric correction","ara":"التصحيح البيومتري","fra":"Correction biométrique"},"screens":[{"order":1,"name":"consentdet","label":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"caption":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"fields":[{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"ara":"الاسم الكامل الكامل الكامل","fra":"J'ai lu et j'accepte les termes et conditions pour partager mes PII","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"ara":"لغة الإخطار","fra":"Langue de notification","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":2,"name":"BiometricDetails","label":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"caption":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"القياسات الحيوية الفردية","fra":"Applicant Biometrics","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"proofOfException","inputRequired":false,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"ara":"إثبات الاستثناء","fra":"Exception Proof","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":true,"active":false}],"caption":{"eng":"Biometric correction","ara":"التصحيح البيومتري","fra":"Correction biométrique"},"icon":"UINUpdate.png","isActive":true,"autoSelectedGroups":null} </t>
   </si>
+  <si>
+    <t>{"id":"NEW","order":1,"flow":"NEW","isSubProcess":false,"label":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"screens":[{"order":1,"name":"consentdet","label":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"caption":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"ara":"الاسم الكامل الكامل الكامل","fra":"J'ai lu et j'accepte les termes et conditions pour partager mes PII","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"ara":"لغة الإخطار","fra":"Langue de notification","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"caption":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"fields":[{"id":"fullName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Full Name","label":{"ara":"الاسم الكامل","fra":"Nom complet","eng":"Full Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"name"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"ara":"الاسم الكامل","fra":"DOB","eng":"DOB"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"ara":"جنس","fra":"Le genre","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"ara":"الاسم الكامل","fra":"line1","eng":"line1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"ara":"الاسم الكامل","fra":"line2","eng":"line2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"addressLine3","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine3","label":{"ara":"الاسم الكامل","fra":"line3","eng":"line3"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine3"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"ara":"الاسم الكامل","fra":"Reside Status","eng":"Residence Status"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"referenceIdentityNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"referenceIdentityNumber","label":{"ara":"الاسم الكامل","fra":"Reference Identity Number","eng":"Reference Identity Number"},"controlType":"textbox","fieldType":"default","format":"kyc","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ReferenceIdentityNumber","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"none"},{"id":"region","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"region","label":{"ara":"الاسم الكامل","fra":"Region","eng":"Region"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Region"},{"id":"province","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"province","label":{"ara":"الاسم الكامل","fra":"Province","eng":"Province"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Province"},{"id":"city","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"city","label":{"ara":"الاسم الكامل","fra":"City","eng":"City"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"City"},{"id":"zone","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"zone","label":{"ara":"الاسم الكامل","fra":"Zone","eng":"Zone"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":null,"group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Zone"},{"id":"postalCode","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"postalCode","label":{"ara":"الاسم الكامل","fra":"Postal","eng":"Postal"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[(?i)A-Z0-9]{5}$|^NA$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Postal Code"},{"id":"phone","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"phone","label":{"ara":"الاسم الكامل","fra":"Phone","eng":"Phone"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[+]*([0-9]{1})([0-9]{9})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Phone"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"ara":"الاسم الكامل","fra":"Email","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"ara":"اسم المُعرّف","fra":"nom del'introducteur","eng":"Introducer Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"ara":"مقدم RID","fra":"Introducteur RID","eng":"Introducer RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"ara":"مقدم في","fra":"Introducteur UIN","eng":"Introducer UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"}],"layoutTemplate":null,"preRegFetchRequired":true,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","fra":"Des documents","eng":"Document Upload"},"caption":{"ara":"وثائق","fra":"Des documents","eng":"Documents"},"fields":[{"id":"proofOfAddress","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfAddress","label":{"ara":"إثبات العنوان","fra":"Address Proof","eng":"Address Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POA"},{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"ara":"إثبات الهوية","fra":"Identity Proof","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"ara":"إثبات العلاقة","fra":"Relationship Proof","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"ara":"دليل DOB","fra":"DOB Proof","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"ara":"إثبات الاستثناء","fra":"Exception Proof","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"caption":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"القياسات الحيوية الفردية","fra":"Applicant Biometrics","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"bioAttributes":["face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"مقدم القياسات الحيوية","fra":"Introducteur Biométrie","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["face"]}],"required":false,"bioAttributes":["face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false}],"caption":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"icon":"NewReg.png","isActive":true,"autoSelectedGroups":null}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -217,353 +217,16 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -586,326 +249,40 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1110,31 +487,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="8.5703125" customWidth="1"/>
     <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="30.2890625" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.4296875" customWidth="1"/>
-    <col min="7" max="7" width="45.859375" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="45.85546875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="14.140625" customWidth="1"/>
     <col min="11" max="11" width="10.140625" customWidth="1"/>
     <col min="12" max="15" width="8.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.859375" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" customWidth="1"/>
     <col min="17" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:18">
+    <row r="1" spans="1:26" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,7 +567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1" spans="1:18">
+    <row r="2" spans="1:26" ht="13.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1244,7 +621,7 @@
       </c>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" ht="30.75" customHeight="1" spans="1:18">
+    <row r="3" spans="1:26" ht="30.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -1298,7 +675,7 @@
       </c>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" ht="29.25" customHeight="1" spans="1:26">
+    <row r="4" spans="1:26" ht="29.25" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
@@ -1318,7 +695,7 @@
         <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2">
         <v>1001</v>
@@ -1360,9 +737,9 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1" spans="1:26">
+    <row r="5" spans="1:26" ht="13.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2">
         <v>0.1</v>
@@ -1371,16 +748,16 @@
         <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H5" s="2">
         <v>1001</v>
@@ -1422,9 +799,9 @@
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" spans="1:26">
+    <row r="6" spans="1:26" ht="13.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2">
         <v>0.1</v>
@@ -1433,16 +810,16 @@
         <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="H6" s="2">
         <v>1001</v>
@@ -1484,9 +861,9 @@
       <c r="Y6" s="6"/>
       <c r="Z6" s="6"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1" spans="1:26">
+    <row r="7" spans="1:26" ht="13.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2">
         <v>0.1</v>
@@ -1495,16 +872,16 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="H7" s="2">
         <v>1001</v>
@@ -1546,7 +923,7 @@
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1" spans="1:26">
+    <row r="8" spans="1:26" ht="13.5" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1574,7 +951,7 @@
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:26">
+    <row r="9" spans="1:26" ht="13.5" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1602,7 +979,7 @@
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
     </row>
-    <row r="10" ht="13.5" customHeight="1" spans="1:18">
+    <row r="10" spans="1:26" ht="13.5" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1622,7 +999,7 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" ht="13.5" customHeight="1" spans="1:18">
+    <row r="11" spans="1:26" ht="13.5" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1642,7 +1019,7 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" ht="13.5" customHeight="1" spans="1:18">
+    <row r="12" spans="1:26" ht="13.5" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1662,7 +1039,7 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" ht="13.5" customHeight="1" spans="1:18">
+    <row r="13" spans="1:26" ht="13.5" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1682,7 +1059,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" ht="13.5" customHeight="1" spans="1:18">
+    <row r="14" spans="1:26" ht="13.5" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1702,7 +1079,7 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1" spans="1:18">
+    <row r="15" spans="1:26" ht="13.5" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1722,7 +1099,7 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1" spans="1:18">
+    <row r="16" spans="1:26" ht="13.5" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1742,7 +1119,7 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1" spans="1:18">
+    <row r="17" spans="1:18" ht="13.5" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1762,7 +1139,7 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" ht="13.5" customHeight="1" spans="1:18">
+    <row r="18" spans="1:18" ht="13.5" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1782,7 +1159,7 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" ht="13.5" customHeight="1" spans="1:18">
+    <row r="19" spans="1:18" ht="13.5" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1802,7 +1179,7 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" ht="13.5" customHeight="1" spans="1:18">
+    <row r="20" spans="1:18" ht="13.5" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1822,7 +1199,7 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" ht="13.5" customHeight="1" spans="1:18">
+    <row r="21" spans="1:18" ht="13.5" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1842,7 +1219,7 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" ht="13.5" customHeight="1" spans="1:18">
+    <row r="22" spans="1:18" ht="13.5" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1862,7 +1239,7 @@
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="23" ht="13.5" customHeight="1" spans="1:18">
+    <row r="23" spans="1:18" ht="13.5" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1882,7 +1259,7 @@
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
     </row>
-    <row r="24" ht="13.5" customHeight="1" spans="1:18">
+    <row r="24" spans="1:18" ht="13.5" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1902,7 +1279,7 @@
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
     </row>
-    <row r="25" ht="13.5" customHeight="1" spans="1:18">
+    <row r="25" spans="1:18" ht="13.5" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1922,7 +1299,7 @@
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
     </row>
-    <row r="26" ht="13.5" customHeight="1" spans="1:18">
+    <row r="26" spans="1:18" ht="13.5" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1942,7 +1319,7 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
     </row>
-    <row r="27" ht="13.5" customHeight="1" spans="1:18">
+    <row r="27" spans="1:18" ht="13.5" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1962,7 +1339,7 @@
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
     </row>
-    <row r="28" ht="13.5" customHeight="1" spans="1:18">
+    <row r="28" spans="1:18" ht="13.5" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1982,7 +1359,7 @@
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1" spans="1:18">
+    <row r="29" spans="1:18" ht="13.5" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2002,7 +1379,7 @@
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
     </row>
-    <row r="30" ht="13.5" customHeight="1" spans="1:18">
+    <row r="30" spans="1:18" ht="13.5" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2022,7 +1399,7 @@
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
     </row>
-    <row r="31" ht="13.5" customHeight="1" spans="1:18">
+    <row r="31" spans="1:18" ht="13.5" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2042,7 +1419,7 @@
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
     </row>
-    <row r="32" ht="13.5" customHeight="1" spans="1:18">
+    <row r="32" spans="1:18" ht="13.5" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2062,7 +1439,7 @@
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
     </row>
-    <row r="33" ht="13.5" customHeight="1" spans="1:18">
+    <row r="33" spans="1:18" ht="13.5" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2082,7 +1459,7 @@
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
     </row>
-    <row r="34" ht="13.5" customHeight="1" spans="1:18">
+    <row r="34" spans="1:18" ht="13.5" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2102,7 +1479,7 @@
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
     </row>
-    <row r="35" ht="13.5" customHeight="1" spans="1:18">
+    <row r="35" spans="1:18" ht="13.5" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2122,7 +1499,7 @@
       <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
     </row>
-    <row r="36" ht="13.5" customHeight="1" spans="1:18">
+    <row r="36" spans="1:18" ht="13.5" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2142,7 +1519,7 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" ht="13.5" customHeight="1" spans="1:18">
+    <row r="37" spans="1:18" ht="13.5" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2162,7 +1539,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" ht="13.5" customHeight="1" spans="1:18">
+    <row r="38" spans="1:18" ht="13.5" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2182,7 +1559,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" ht="13.5" customHeight="1" spans="1:18">
+    <row r="39" spans="1:18" ht="13.5" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2202,7 +1579,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" ht="13.5" customHeight="1" spans="1:18">
+    <row r="40" spans="1:18" ht="13.5" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2222,7 +1599,7 @@
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
     </row>
-    <row r="41" ht="13.5" customHeight="1" spans="1:18">
+    <row r="41" spans="1:18" ht="13.5" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2242,7 +1619,7 @@
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
     </row>
-    <row r="42" ht="13.5" customHeight="1" spans="1:18">
+    <row r="42" spans="1:18" ht="13.5" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2262,7 +1639,7 @@
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
     </row>
-    <row r="43" ht="13.5" customHeight="1" spans="1:18">
+    <row r="43" spans="1:18" ht="13.5" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -2282,7 +1659,7 @@
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
     </row>
-    <row r="44" ht="13.5" customHeight="1" spans="1:18">
+    <row r="44" spans="1:18" ht="13.5" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -2302,7 +1679,7 @@
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
     </row>
-    <row r="45" ht="13.5" customHeight="1" spans="1:18">
+    <row r="45" spans="1:18" ht="13.5" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2322,7 +1699,7 @@
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
     </row>
-    <row r="46" ht="13.5" customHeight="1" spans="1:18">
+    <row r="46" spans="1:18" ht="13.5" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2342,7 +1719,7 @@
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
     </row>
-    <row r="47" ht="13.5" customHeight="1" spans="1:18">
+    <row r="47" spans="1:18" ht="13.5" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2362,7 +1739,7 @@
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
     </row>
-    <row r="48" ht="13.5" customHeight="1" spans="1:18">
+    <row r="48" spans="1:18" ht="13.5" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2382,7 +1759,7 @@
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
     </row>
-    <row r="49" ht="13.5" customHeight="1" spans="1:18">
+    <row r="49" spans="1:18" ht="13.5" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2402,7 +1779,7 @@
       <c r="Q49" s="4"/>
       <c r="R49" s="4"/>
     </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:18">
+    <row r="50" spans="1:18" ht="13.5" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2422,7 +1799,7 @@
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
     </row>
-    <row r="51" ht="13.5" customHeight="1" spans="1:18">
+    <row r="51" spans="1:18" ht="13.5" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -2442,7 +1819,7 @@
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1" spans="1:18">
+    <row r="52" spans="1:18" ht="13.5" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2462,7 +1839,7 @@
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
     </row>
-    <row r="53" ht="13.5" customHeight="1" spans="1:18">
+    <row r="53" spans="1:18" ht="13.5" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2482,7 +1859,7 @@
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
     </row>
-    <row r="54" ht="13.5" customHeight="1" spans="1:18">
+    <row r="54" spans="1:18" ht="13.5" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2502,7 +1879,7 @@
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
     </row>
-    <row r="55" ht="13.5" customHeight="1" spans="1:18">
+    <row r="55" spans="1:18" ht="13.5" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2522,7 +1899,7 @@
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
     </row>
-    <row r="56" ht="13.5" customHeight="1" spans="1:18">
+    <row r="56" spans="1:18" ht="13.5" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2542,7 +1919,7 @@
       <c r="Q56" s="4"/>
       <c r="R56" s="4"/>
     </row>
-    <row r="57" ht="13.5" customHeight="1" spans="1:18">
+    <row r="57" spans="1:18" ht="13.5" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2562,7 +1939,7 @@
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
     </row>
-    <row r="58" ht="13.5" customHeight="1" spans="1:18">
+    <row r="58" spans="1:18" ht="13.5" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2582,7 +1959,7 @@
       <c r="Q58" s="4"/>
       <c r="R58" s="4"/>
     </row>
-    <row r="59" ht="13.5" customHeight="1" spans="1:18">
+    <row r="59" spans="1:18" ht="13.5" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2602,7 +1979,7 @@
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
     </row>
-    <row r="60" ht="13.5" customHeight="1" spans="1:18">
+    <row r="60" spans="1:18" ht="13.5" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2622,7 +1999,7 @@
       <c r="Q60" s="4"/>
       <c r="R60" s="4"/>
     </row>
-    <row r="61" ht="13.5" customHeight="1" spans="1:18">
+    <row r="61" spans="1:18" ht="13.5" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2642,7 +2019,7 @@
       <c r="Q61" s="4"/>
       <c r="R61" s="4"/>
     </row>
-    <row r="62" ht="13.5" customHeight="1" spans="1:18">
+    <row r="62" spans="1:18" ht="13.5" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2662,7 +2039,7 @@
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
     </row>
-    <row r="63" ht="13.5" customHeight="1" spans="1:18">
+    <row r="63" spans="1:18" ht="13.5" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2682,7 +2059,7 @@
       <c r="Q63" s="4"/>
       <c r="R63" s="4"/>
     </row>
-    <row r="64" ht="13.5" customHeight="1" spans="1:18">
+    <row r="64" spans="1:18" ht="13.5" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2702,7 +2079,7 @@
       <c r="Q64" s="4"/>
       <c r="R64" s="4"/>
     </row>
-    <row r="65" ht="13.5" customHeight="1" spans="1:18">
+    <row r="65" spans="1:18" ht="13.5" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2722,7 +2099,7 @@
       <c r="Q65" s="4"/>
       <c r="R65" s="4"/>
     </row>
-    <row r="66" ht="13.5" customHeight="1" spans="1:18">
+    <row r="66" spans="1:18" ht="13.5" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2742,7 +2119,7 @@
       <c r="Q66" s="4"/>
       <c r="R66" s="4"/>
     </row>
-    <row r="67" ht="13.5" customHeight="1" spans="1:18">
+    <row r="67" spans="1:18" ht="13.5" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2762,7 +2139,7 @@
       <c r="Q67" s="4"/>
       <c r="R67" s="4"/>
     </row>
-    <row r="68" ht="13.5" customHeight="1" spans="1:18">
+    <row r="68" spans="1:18" ht="13.5" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2782,7 +2159,7 @@
       <c r="Q68" s="4"/>
       <c r="R68" s="4"/>
     </row>
-    <row r="69" ht="13.5" customHeight="1" spans="1:18">
+    <row r="69" spans="1:18" ht="13.5" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2802,7 +2179,7 @@
       <c r="Q69" s="4"/>
       <c r="R69" s="4"/>
     </row>
-    <row r="70" ht="13.5" customHeight="1" spans="1:18">
+    <row r="70" spans="1:18" ht="13.5" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2822,7 +2199,7 @@
       <c r="Q70" s="4"/>
       <c r="R70" s="4"/>
     </row>
-    <row r="71" ht="13.5" customHeight="1" spans="1:18">
+    <row r="71" spans="1:18" ht="13.5" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2842,7 +2219,7 @@
       <c r="Q71" s="4"/>
       <c r="R71" s="4"/>
     </row>
-    <row r="72" ht="13.5" customHeight="1" spans="1:18">
+    <row r="72" spans="1:18" ht="13.5" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2862,7 +2239,7 @@
       <c r="Q72" s="4"/>
       <c r="R72" s="4"/>
     </row>
-    <row r="73" ht="13.5" customHeight="1" spans="1:18">
+    <row r="73" spans="1:18" ht="13.5" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2882,7 +2259,7 @@
       <c r="Q73" s="4"/>
       <c r="R73" s="4"/>
     </row>
-    <row r="74" ht="13.5" customHeight="1" spans="1:18">
+    <row r="74" spans="1:18" ht="13.5" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2902,7 +2279,7 @@
       <c r="Q74" s="4"/>
       <c r="R74" s="4"/>
     </row>
-    <row r="75" ht="13.5" customHeight="1" spans="1:18">
+    <row r="75" spans="1:18" ht="13.5" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2922,7 +2299,7 @@
       <c r="Q75" s="4"/>
       <c r="R75" s="4"/>
     </row>
-    <row r="76" ht="13.5" customHeight="1" spans="1:18">
+    <row r="76" spans="1:18" ht="13.5" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2942,7 +2319,7 @@
       <c r="Q76" s="4"/>
       <c r="R76" s="4"/>
     </row>
-    <row r="77" ht="13.5" customHeight="1" spans="1:18">
+    <row r="77" spans="1:18" ht="13.5" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2962,7 +2339,7 @@
       <c r="Q77" s="4"/>
       <c r="R77" s="4"/>
     </row>
-    <row r="78" ht="13.5" customHeight="1" spans="1:18">
+    <row r="78" spans="1:18" ht="13.5" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2982,7 +2359,7 @@
       <c r="Q78" s="4"/>
       <c r="R78" s="4"/>
     </row>
-    <row r="79" ht="13.5" customHeight="1" spans="1:18">
+    <row r="79" spans="1:18" ht="13.5" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3002,7 +2379,7 @@
       <c r="Q79" s="4"/>
       <c r="R79" s="4"/>
     </row>
-    <row r="80" ht="13.5" customHeight="1" spans="1:18">
+    <row r="80" spans="1:18" ht="13.5" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3022,7 +2399,7 @@
       <c r="Q80" s="4"/>
       <c r="R80" s="4"/>
     </row>
-    <row r="81" ht="13.5" customHeight="1" spans="1:18">
+    <row r="81" spans="1:18" ht="13.5" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -3042,7 +2419,7 @@
       <c r="Q81" s="4"/>
       <c r="R81" s="4"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1" spans="1:18">
+    <row r="82" spans="1:18" ht="13.5" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3062,7 +2439,7 @@
       <c r="Q82" s="4"/>
       <c r="R82" s="4"/>
     </row>
-    <row r="83" ht="13.5" customHeight="1" spans="1:18">
+    <row r="83" spans="1:18" ht="13.5" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3082,7 +2459,7 @@
       <c r="Q83" s="4"/>
       <c r="R83" s="4"/>
     </row>
-    <row r="84" ht="13.5" customHeight="1" spans="1:18">
+    <row r="84" spans="1:18" ht="13.5" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3102,7 +2479,7 @@
       <c r="Q84" s="4"/>
       <c r="R84" s="4"/>
     </row>
-    <row r="85" ht="13.5" customHeight="1" spans="1:18">
+    <row r="85" spans="1:18" ht="13.5" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3122,7 +2499,7 @@
       <c r="Q85" s="4"/>
       <c r="R85" s="4"/>
     </row>
-    <row r="86" ht="13.5" customHeight="1" spans="1:18">
+    <row r="86" spans="1:18" ht="13.5" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3142,7 +2519,7 @@
       <c r="Q86" s="4"/>
       <c r="R86" s="4"/>
     </row>
-    <row r="87" ht="13.5" customHeight="1" spans="1:18">
+    <row r="87" spans="1:18" ht="13.5" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -3162,7 +2539,7 @@
       <c r="Q87" s="4"/>
       <c r="R87" s="4"/>
     </row>
-    <row r="88" ht="13.5" customHeight="1" spans="1:18">
+    <row r="88" spans="1:18" ht="13.5" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3182,7 +2559,7 @@
       <c r="Q88" s="4"/>
       <c r="R88" s="4"/>
     </row>
-    <row r="89" ht="13.5" customHeight="1" spans="1:18">
+    <row r="89" spans="1:18" ht="13.5" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -3202,7 +2579,7 @@
       <c r="Q89" s="4"/>
       <c r="R89" s="4"/>
     </row>
-    <row r="90" ht="13.5" customHeight="1" spans="1:18">
+    <row r="90" spans="1:18" ht="13.5" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -3222,7 +2599,7 @@
       <c r="Q90" s="4"/>
       <c r="R90" s="4"/>
     </row>
-    <row r="91" ht="13.5" customHeight="1" spans="1:18">
+    <row r="91" spans="1:18" ht="13.5" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -3242,7 +2619,7 @@
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
     </row>
-    <row r="92" ht="13.5" customHeight="1" spans="1:18">
+    <row r="92" spans="1:18" ht="13.5" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -3262,7 +2639,7 @@
       <c r="Q92" s="4"/>
       <c r="R92" s="4"/>
     </row>
-    <row r="93" ht="13.5" customHeight="1" spans="1:18">
+    <row r="93" spans="1:18" ht="13.5" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -3282,7 +2659,7 @@
       <c r="Q93" s="4"/>
       <c r="R93" s="4"/>
     </row>
-    <row r="94" ht="13.5" customHeight="1" spans="1:18">
+    <row r="94" spans="1:18" ht="13.5" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3302,7 +2679,7 @@
       <c r="Q94" s="4"/>
       <c r="R94" s="4"/>
     </row>
-    <row r="95" ht="13.5" customHeight="1" spans="1:18">
+    <row r="95" spans="1:18" ht="13.5" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3322,7 +2699,7 @@
       <c r="Q95" s="4"/>
       <c r="R95" s="4"/>
     </row>
-    <row r="96" ht="13.5" customHeight="1" spans="1:18">
+    <row r="96" spans="1:18" ht="13.5" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3342,7 +2719,7 @@
       <c r="Q96" s="4"/>
       <c r="R96" s="4"/>
     </row>
-    <row r="97" ht="13.5" customHeight="1" spans="1:18">
+    <row r="97" spans="1:18" ht="13.5" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3362,7 +2739,7 @@
       <c r="Q97" s="4"/>
       <c r="R97" s="4"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1" spans="1:18">
+    <row r="98" spans="1:18" ht="13.5" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3382,7 +2759,7 @@
       <c r="Q98" s="4"/>
       <c r="R98" s="4"/>
     </row>
-    <row r="99" ht="13.5" customHeight="1" spans="1:18">
+    <row r="99" spans="1:18" ht="13.5" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3402,7 +2779,7 @@
       <c r="Q99" s="4"/>
       <c r="R99" s="4"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1" spans="1:18">
+    <row r="100" spans="1:18" ht="13.5" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3422,7 +2799,7 @@
       <c r="Q100" s="4"/>
       <c r="R100" s="4"/>
     </row>
-    <row r="101" ht="13.5" customHeight="1" spans="1:18">
+    <row r="101" spans="1:18" ht="13.5" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3442,7 +2819,7 @@
       <c r="Q101" s="4"/>
       <c r="R101" s="4"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1" spans="1:18">
+    <row r="102" spans="1:18" ht="13.5" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3462,7 +2839,7 @@
       <c r="Q102" s="4"/>
       <c r="R102" s="4"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1" spans="1:18">
+    <row r="103" spans="1:18" ht="13.5" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3482,7 +2859,7 @@
       <c r="Q103" s="4"/>
       <c r="R103" s="4"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1" spans="1:18">
+    <row r="104" spans="1:18" ht="13.5" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3502,7 +2879,7 @@
       <c r="Q104" s="4"/>
       <c r="R104" s="4"/>
     </row>
-    <row r="105" ht="13.5" customHeight="1" spans="1:18">
+    <row r="105" spans="1:18" ht="13.5" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3522,7 +2899,7 @@
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1" spans="1:18">
+    <row r="106" spans="1:18" ht="13.5" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3542,7 +2919,7 @@
       <c r="Q106" s="4"/>
       <c r="R106" s="4"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1" spans="1:18">
+    <row r="107" spans="1:18" ht="13.5" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3562,7 +2939,7 @@
       <c r="Q107" s="4"/>
       <c r="R107" s="4"/>
     </row>
-    <row r="108" ht="13.5" customHeight="1" spans="1:18">
+    <row r="108" spans="1:18" ht="13.5" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -3582,7 +2959,7 @@
       <c r="Q108" s="4"/>
       <c r="R108" s="4"/>
     </row>
-    <row r="109" ht="13.5" customHeight="1" spans="1:18">
+    <row r="109" spans="1:18" ht="13.5" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -3602,7 +2979,7 @@
       <c r="Q109" s="4"/>
       <c r="R109" s="4"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1" spans="1:18">
+    <row r="110" spans="1:18" ht="13.5" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -3622,7 +2999,7 @@
       <c r="Q110" s="4"/>
       <c r="R110" s="4"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1" spans="1:18">
+    <row r="111" spans="1:18" ht="13.5" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3642,7 +3019,7 @@
       <c r="Q111" s="4"/>
       <c r="R111" s="4"/>
     </row>
-    <row r="112" ht="13.5" customHeight="1" spans="1:18">
+    <row r="112" spans="1:18" ht="13.5" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3662,7 +3039,7 @@
       <c r="Q112" s="4"/>
       <c r="R112" s="4"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1" spans="1:18">
+    <row r="113" spans="1:18" ht="13.5" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3682,7 +3059,7 @@
       <c r="Q113" s="4"/>
       <c r="R113" s="4"/>
     </row>
-    <row r="114" ht="13.5" customHeight="1" spans="1:18">
+    <row r="114" spans="1:18" ht="13.5" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3702,7 +3079,7 @@
       <c r="Q114" s="4"/>
       <c r="R114" s="4"/>
     </row>
-    <row r="115" ht="13.5" customHeight="1" spans="1:18">
+    <row r="115" spans="1:18" ht="13.5" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3722,7 +3099,7 @@
       <c r="Q115" s="4"/>
       <c r="R115" s="4"/>
     </row>
-    <row r="116" ht="13.5" customHeight="1" spans="1:18">
+    <row r="116" spans="1:18" ht="13.5" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3742,7 +3119,7 @@
       <c r="Q116" s="4"/>
       <c r="R116" s="4"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1" spans="1:18">
+    <row r="117" spans="1:18" ht="13.5" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3762,7 +3139,7 @@
       <c r="Q117" s="4"/>
       <c r="R117" s="4"/>
     </row>
-    <row r="118" ht="13.5" customHeight="1" spans="1:18">
+    <row r="118" spans="1:18" ht="13.5" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3782,7 +3159,7 @@
       <c r="Q118" s="4"/>
       <c r="R118" s="4"/>
     </row>
-    <row r="119" ht="13.5" customHeight="1" spans="1:18">
+    <row r="119" spans="1:18" ht="13.5" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3802,7 +3179,7 @@
       <c r="Q119" s="4"/>
       <c r="R119" s="4"/>
     </row>
-    <row r="120" ht="13.5" customHeight="1" spans="1:18">
+    <row r="120" spans="1:18" ht="13.5" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3822,7 +3199,7 @@
       <c r="Q120" s="4"/>
       <c r="R120" s="4"/>
     </row>
-    <row r="121" ht="13.5" customHeight="1" spans="1:18">
+    <row r="121" spans="1:18" ht="13.5" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3842,7 +3219,7 @@
       <c r="Q121" s="4"/>
       <c r="R121" s="4"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1" spans="1:18">
+    <row r="122" spans="1:18" ht="13.5" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3862,7 +3239,7 @@
       <c r="Q122" s="4"/>
       <c r="R122" s="4"/>
     </row>
-    <row r="123" ht="13.5" customHeight="1" spans="1:18">
+    <row r="123" spans="1:18" ht="13.5" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3882,7 +3259,7 @@
       <c r="Q123" s="4"/>
       <c r="R123" s="4"/>
     </row>
-    <row r="124" ht="13.5" customHeight="1" spans="1:18">
+    <row r="124" spans="1:18" ht="13.5" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3902,7 +3279,7 @@
       <c r="Q124" s="4"/>
       <c r="R124" s="4"/>
     </row>
-    <row r="125" ht="13.5" customHeight="1" spans="1:18">
+    <row r="125" spans="1:18" ht="13.5" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3922,7 +3299,7 @@
       <c r="Q125" s="4"/>
       <c r="R125" s="4"/>
     </row>
-    <row r="126" ht="13.5" customHeight="1" spans="1:18">
+    <row r="126" spans="1:18" ht="13.5" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3942,7 +3319,7 @@
       <c r="Q126" s="4"/>
       <c r="R126" s="4"/>
     </row>
-    <row r="127" ht="13.5" customHeight="1" spans="1:18">
+    <row r="127" spans="1:18" ht="13.5" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3962,7 +3339,7 @@
       <c r="Q127" s="4"/>
       <c r="R127" s="4"/>
     </row>
-    <row r="128" ht="13.5" customHeight="1" spans="1:18">
+    <row r="128" spans="1:18" ht="13.5" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3982,7 +3359,7 @@
       <c r="Q128" s="4"/>
       <c r="R128" s="4"/>
     </row>
-    <row r="129" ht="13.5" customHeight="1" spans="1:18">
+    <row r="129" spans="1:18" ht="13.5" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4002,7 +3379,7 @@
       <c r="Q129" s="4"/>
       <c r="R129" s="4"/>
     </row>
-    <row r="130" ht="13.5" customHeight="1" spans="1:18">
+    <row r="130" spans="1:18" ht="13.5" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4022,7 +3399,7 @@
       <c r="Q130" s="4"/>
       <c r="R130" s="4"/>
     </row>
-    <row r="131" ht="13.5" customHeight="1" spans="1:18">
+    <row r="131" spans="1:18" ht="13.5" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4042,7 +3419,7 @@
       <c r="Q131" s="4"/>
       <c r="R131" s="4"/>
     </row>
-    <row r="132" ht="13.5" customHeight="1" spans="1:18">
+    <row r="132" spans="1:18" ht="13.5" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4062,7 +3439,7 @@
       <c r="Q132" s="4"/>
       <c r="R132" s="4"/>
     </row>
-    <row r="133" ht="13.5" customHeight="1" spans="1:18">
+    <row r="133" spans="1:18" ht="13.5" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4082,7 +3459,7 @@
       <c r="Q133" s="4"/>
       <c r="R133" s="4"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1" spans="1:18">
+    <row r="134" spans="1:18" ht="13.5" customHeight="1">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4102,7 +3479,7 @@
       <c r="Q134" s="4"/>
       <c r="R134" s="4"/>
     </row>
-    <row r="135" ht="13.5" customHeight="1" spans="1:18">
+    <row r="135" spans="1:18" ht="13.5" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4122,7 +3499,7 @@
       <c r="Q135" s="4"/>
       <c r="R135" s="4"/>
     </row>
-    <row r="136" ht="13.5" customHeight="1" spans="1:18">
+    <row r="136" spans="1:18" ht="13.5" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4142,7 +3519,7 @@
       <c r="Q136" s="4"/>
       <c r="R136" s="4"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1" spans="1:18">
+    <row r="137" spans="1:18" ht="13.5" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4162,7 +3539,7 @@
       <c r="Q137" s="4"/>
       <c r="R137" s="4"/>
     </row>
-    <row r="138" ht="13.5" customHeight="1" spans="1:18">
+    <row r="138" spans="1:18" ht="13.5" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4182,7 +3559,7 @@
       <c r="Q138" s="4"/>
       <c r="R138" s="4"/>
     </row>
-    <row r="139" ht="13.5" customHeight="1" spans="1:18">
+    <row r="139" spans="1:18" ht="13.5" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4202,7 +3579,7 @@
       <c r="Q139" s="4"/>
       <c r="R139" s="4"/>
     </row>
-    <row r="140" ht="13.5" customHeight="1" spans="1:18">
+    <row r="140" spans="1:18" ht="13.5" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4222,7 +3599,7 @@
       <c r="Q140" s="4"/>
       <c r="R140" s="4"/>
     </row>
-    <row r="141" ht="13.5" customHeight="1" spans="1:18">
+    <row r="141" spans="1:18" ht="13.5" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -4242,7 +3619,7 @@
       <c r="Q141" s="4"/>
       <c r="R141" s="4"/>
     </row>
-    <row r="142" ht="13.5" customHeight="1" spans="1:18">
+    <row r="142" spans="1:18" ht="13.5" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -4262,7 +3639,7 @@
       <c r="Q142" s="4"/>
       <c r="R142" s="4"/>
     </row>
-    <row r="143" ht="13.5" customHeight="1" spans="1:18">
+    <row r="143" spans="1:18" ht="13.5" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -4282,7 +3659,7 @@
       <c r="Q143" s="4"/>
       <c r="R143" s="4"/>
     </row>
-    <row r="144" ht="13.5" customHeight="1" spans="1:18">
+    <row r="144" spans="1:18" ht="13.5" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -4302,7 +3679,7 @@
       <c r="Q144" s="4"/>
       <c r="R144" s="4"/>
     </row>
-    <row r="145" ht="13.5" customHeight="1" spans="1:18">
+    <row r="145" spans="1:18" ht="13.5" customHeight="1">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -4322,7 +3699,7 @@
       <c r="Q145" s="4"/>
       <c r="R145" s="4"/>
     </row>
-    <row r="146" ht="13.5" customHeight="1" spans="1:18">
+    <row r="146" spans="1:18" ht="13.5" customHeight="1">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -4342,7 +3719,7 @@
       <c r="Q146" s="4"/>
       <c r="R146" s="4"/>
     </row>
-    <row r="147" ht="13.5" customHeight="1" spans="1:18">
+    <row r="147" spans="1:18" ht="13.5" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -4362,7 +3739,7 @@
       <c r="Q147" s="4"/>
       <c r="R147" s="4"/>
     </row>
-    <row r="148" ht="13.5" customHeight="1" spans="1:18">
+    <row r="148" spans="1:18" ht="13.5" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4382,7 +3759,7 @@
       <c r="Q148" s="4"/>
       <c r="R148" s="4"/>
     </row>
-    <row r="149" ht="13.5" customHeight="1" spans="1:18">
+    <row r="149" spans="1:18" ht="13.5" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -4402,7 +3779,7 @@
       <c r="Q149" s="4"/>
       <c r="R149" s="4"/>
     </row>
-    <row r="150" ht="13.5" customHeight="1" spans="1:18">
+    <row r="150" spans="1:18" ht="13.5" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -4422,7 +3799,7 @@
       <c r="Q150" s="4"/>
       <c r="R150" s="4"/>
     </row>
-    <row r="151" ht="13.5" customHeight="1" spans="1:18">
+    <row r="151" spans="1:18" ht="13.5" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -4442,7 +3819,7 @@
       <c r="Q151" s="4"/>
       <c r="R151" s="4"/>
     </row>
-    <row r="152" ht="13.5" customHeight="1" spans="1:18">
+    <row r="152" spans="1:18" ht="13.5" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -4462,7 +3839,7 @@
       <c r="Q152" s="4"/>
       <c r="R152" s="4"/>
     </row>
-    <row r="153" ht="13.5" customHeight="1" spans="1:18">
+    <row r="153" spans="1:18" ht="13.5" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -4482,7 +3859,7 @@
       <c r="Q153" s="4"/>
       <c r="R153" s="4"/>
     </row>
-    <row r="154" ht="13.5" customHeight="1" spans="1:18">
+    <row r="154" spans="1:18" ht="13.5" customHeight="1">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -4502,7 +3879,7 @@
       <c r="Q154" s="4"/>
       <c r="R154" s="4"/>
     </row>
-    <row r="155" ht="13.5" customHeight="1" spans="1:18">
+    <row r="155" spans="1:18" ht="13.5" customHeight="1">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -4522,7 +3899,7 @@
       <c r="Q155" s="4"/>
       <c r="R155" s="4"/>
     </row>
-    <row r="156" ht="13.5" customHeight="1" spans="1:18">
+    <row r="156" spans="1:18" ht="13.5" customHeight="1">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -4542,7 +3919,7 @@
       <c r="Q156" s="4"/>
       <c r="R156" s="4"/>
     </row>
-    <row r="157" ht="13.5" customHeight="1" spans="1:18">
+    <row r="157" spans="1:18" ht="13.5" customHeight="1">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -4562,7 +3939,7 @@
       <c r="Q157" s="4"/>
       <c r="R157" s="4"/>
     </row>
-    <row r="158" ht="13.5" customHeight="1" spans="1:18">
+    <row r="158" spans="1:18" ht="13.5" customHeight="1">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -4582,7 +3959,7 @@
       <c r="Q158" s="4"/>
       <c r="R158" s="4"/>
     </row>
-    <row r="159" ht="13.5" customHeight="1" spans="1:18">
+    <row r="159" spans="1:18" ht="13.5" customHeight="1">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -4602,7 +3979,7 @@
       <c r="Q159" s="4"/>
       <c r="R159" s="4"/>
     </row>
-    <row r="160" ht="13.5" customHeight="1" spans="1:18">
+    <row r="160" spans="1:18" ht="13.5" customHeight="1">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -4622,7 +3999,7 @@
       <c r="Q160" s="4"/>
       <c r="R160" s="4"/>
     </row>
-    <row r="161" ht="13.5" customHeight="1" spans="1:18">
+    <row r="161" spans="1:18" ht="13.5" customHeight="1">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -4642,7 +4019,7 @@
       <c r="Q161" s="4"/>
       <c r="R161" s="4"/>
     </row>
-    <row r="162" ht="13.5" customHeight="1" spans="1:18">
+    <row r="162" spans="1:18" ht="13.5" customHeight="1">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -4662,7 +4039,7 @@
       <c r="Q162" s="4"/>
       <c r="R162" s="4"/>
     </row>
-    <row r="163" ht="13.5" customHeight="1" spans="1:18">
+    <row r="163" spans="1:18" ht="13.5" customHeight="1">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -4682,7 +4059,7 @@
       <c r="Q163" s="4"/>
       <c r="R163" s="4"/>
     </row>
-    <row r="164" ht="13.5" customHeight="1" spans="1:18">
+    <row r="164" spans="1:18" ht="13.5" customHeight="1">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -4702,7 +4079,7 @@
       <c r="Q164" s="4"/>
       <c r="R164" s="4"/>
     </row>
-    <row r="165" ht="13.5" customHeight="1" spans="1:18">
+    <row r="165" spans="1:18" ht="13.5" customHeight="1">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -4722,7 +4099,7 @@
       <c r="Q165" s="4"/>
       <c r="R165" s="4"/>
     </row>
-    <row r="166" ht="13.5" customHeight="1" spans="1:18">
+    <row r="166" spans="1:18" ht="13.5" customHeight="1">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -4742,7 +4119,7 @@
       <c r="Q166" s="4"/>
       <c r="R166" s="4"/>
     </row>
-    <row r="167" ht="13.5" customHeight="1" spans="1:18">
+    <row r="167" spans="1:18" ht="13.5" customHeight="1">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -4762,7 +4139,7 @@
       <c r="Q167" s="4"/>
       <c r="R167" s="4"/>
     </row>
-    <row r="168" ht="13.5" customHeight="1" spans="1:18">
+    <row r="168" spans="1:18" ht="13.5" customHeight="1">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -4782,7 +4159,7 @@
       <c r="Q168" s="4"/>
       <c r="R168" s="4"/>
     </row>
-    <row r="169" ht="13.5" customHeight="1" spans="1:18">
+    <row r="169" spans="1:18" ht="13.5" customHeight="1">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -4802,7 +4179,7 @@
       <c r="Q169" s="4"/>
       <c r="R169" s="4"/>
     </row>
-    <row r="170" ht="13.5" customHeight="1" spans="1:18">
+    <row r="170" spans="1:18" ht="13.5" customHeight="1">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -4822,7 +4199,7 @@
       <c r="Q170" s="4"/>
       <c r="R170" s="4"/>
     </row>
-    <row r="171" ht="13.5" customHeight="1" spans="1:18">
+    <row r="171" spans="1:18" ht="13.5" customHeight="1">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -4842,7 +4219,7 @@
       <c r="Q171" s="4"/>
       <c r="R171" s="4"/>
     </row>
-    <row r="172" ht="13.5" customHeight="1" spans="1:18">
+    <row r="172" spans="1:18" ht="13.5" customHeight="1">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -4862,7 +4239,7 @@
       <c r="Q172" s="4"/>
       <c r="R172" s="4"/>
     </row>
-    <row r="173" ht="13.5" customHeight="1" spans="1:18">
+    <row r="173" spans="1:18" ht="13.5" customHeight="1">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -4882,7 +4259,7 @@
       <c r="Q173" s="4"/>
       <c r="R173" s="4"/>
     </row>
-    <row r="174" ht="13.5" customHeight="1" spans="1:18">
+    <row r="174" spans="1:18" ht="13.5" customHeight="1">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -4902,7 +4279,7 @@
       <c r="Q174" s="4"/>
       <c r="R174" s="4"/>
     </row>
-    <row r="175" ht="13.5" customHeight="1" spans="1:18">
+    <row r="175" spans="1:18" ht="13.5" customHeight="1">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -4922,7 +4299,7 @@
       <c r="Q175" s="4"/>
       <c r="R175" s="4"/>
     </row>
-    <row r="176" ht="13.5" customHeight="1" spans="1:18">
+    <row r="176" spans="1:18" ht="13.5" customHeight="1">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -4942,7 +4319,7 @@
       <c r="Q176" s="4"/>
       <c r="R176" s="4"/>
     </row>
-    <row r="177" ht="13.5" customHeight="1" spans="1:18">
+    <row r="177" spans="1:18" ht="13.5" customHeight="1">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -4962,7 +4339,7 @@
       <c r="Q177" s="4"/>
       <c r="R177" s="4"/>
     </row>
-    <row r="178" ht="13.5" customHeight="1" spans="1:18">
+    <row r="178" spans="1:18" ht="13.5" customHeight="1">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -4982,7 +4359,7 @@
       <c r="Q178" s="4"/>
       <c r="R178" s="4"/>
     </row>
-    <row r="179" ht="13.5" customHeight="1" spans="1:18">
+    <row r="179" spans="1:18" ht="13.5" customHeight="1">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -5002,7 +4379,7 @@
       <c r="Q179" s="4"/>
       <c r="R179" s="4"/>
     </row>
-    <row r="180" ht="13.5" customHeight="1" spans="1:18">
+    <row r="180" spans="1:18" ht="13.5" customHeight="1">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -5022,7 +4399,7 @@
       <c r="Q180" s="4"/>
       <c r="R180" s="4"/>
     </row>
-    <row r="181" ht="13.5" customHeight="1" spans="1:18">
+    <row r="181" spans="1:18" ht="13.5" customHeight="1">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5042,7 +4419,7 @@
       <c r="Q181" s="4"/>
       <c r="R181" s="4"/>
     </row>
-    <row r="182" ht="13.5" customHeight="1" spans="1:18">
+    <row r="182" spans="1:18" ht="13.5" customHeight="1">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5062,7 +4439,7 @@
       <c r="Q182" s="4"/>
       <c r="R182" s="4"/>
     </row>
-    <row r="183" ht="13.5" customHeight="1" spans="1:18">
+    <row r="183" spans="1:18" ht="13.5" customHeight="1">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -5082,7 +4459,7 @@
       <c r="Q183" s="4"/>
       <c r="R183" s="4"/>
     </row>
-    <row r="184" ht="13.5" customHeight="1" spans="1:18">
+    <row r="184" spans="1:18" ht="13.5" customHeight="1">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5102,7 +4479,7 @@
       <c r="Q184" s="4"/>
       <c r="R184" s="4"/>
     </row>
-    <row r="185" ht="13.5" customHeight="1" spans="1:18">
+    <row r="185" spans="1:18" ht="13.5" customHeight="1">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5122,7 +4499,7 @@
       <c r="Q185" s="4"/>
       <c r="R185" s="4"/>
     </row>
-    <row r="186" ht="13.5" customHeight="1" spans="1:18">
+    <row r="186" spans="1:18" ht="13.5" customHeight="1">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -5142,7 +4519,7 @@
       <c r="Q186" s="4"/>
       <c r="R186" s="4"/>
     </row>
-    <row r="187" ht="13.5" customHeight="1" spans="1:18">
+    <row r="187" spans="1:18" ht="13.5" customHeight="1">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -5162,7 +4539,7 @@
       <c r="Q187" s="4"/>
       <c r="R187" s="4"/>
     </row>
-    <row r="188" ht="13.5" customHeight="1" spans="1:18">
+    <row r="188" spans="1:18" ht="13.5" customHeight="1">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -5182,7 +4559,7 @@
       <c r="Q188" s="4"/>
       <c r="R188" s="4"/>
     </row>
-    <row r="189" ht="13.5" customHeight="1" spans="1:18">
+    <row r="189" spans="1:18" ht="13.5" customHeight="1">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -5202,7 +4579,7 @@
       <c r="Q189" s="4"/>
       <c r="R189" s="4"/>
     </row>
-    <row r="190" ht="13.5" customHeight="1" spans="1:18">
+    <row r="190" spans="1:18" ht="13.5" customHeight="1">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -5222,7 +4599,7 @@
       <c r="Q190" s="4"/>
       <c r="R190" s="4"/>
     </row>
-    <row r="191" ht="13.5" customHeight="1" spans="1:18">
+    <row r="191" spans="1:18" ht="13.5" customHeight="1">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5242,7 +4619,7 @@
       <c r="Q191" s="4"/>
       <c r="R191" s="4"/>
     </row>
-    <row r="192" ht="13.5" customHeight="1" spans="1:18">
+    <row r="192" spans="1:18" ht="13.5" customHeight="1">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -5262,7 +4639,7 @@
       <c r="Q192" s="4"/>
       <c r="R192" s="4"/>
     </row>
-    <row r="193" ht="13.5" customHeight="1" spans="1:18">
+    <row r="193" spans="1:18" ht="13.5" customHeight="1">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5282,7 +4659,7 @@
       <c r="Q193" s="4"/>
       <c r="R193" s="4"/>
     </row>
-    <row r="194" ht="13.5" customHeight="1" spans="1:18">
+    <row r="194" spans="1:18" ht="13.5" customHeight="1">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5302,7 +4679,7 @@
       <c r="Q194" s="4"/>
       <c r="R194" s="4"/>
     </row>
-    <row r="195" ht="13.5" customHeight="1" spans="1:18">
+    <row r="195" spans="1:18" ht="13.5" customHeight="1">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5322,7 +4699,7 @@
       <c r="Q195" s="4"/>
       <c r="R195" s="4"/>
     </row>
-    <row r="196" ht="13.5" customHeight="1" spans="1:18">
+    <row r="196" spans="1:18" ht="13.5" customHeight="1">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -5342,7 +4719,7 @@
       <c r="Q196" s="4"/>
       <c r="R196" s="4"/>
     </row>
-    <row r="197" ht="13.5" customHeight="1" spans="1:18">
+    <row r="197" spans="1:18" ht="13.5" customHeight="1">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -5362,7 +4739,7 @@
       <c r="Q197" s="4"/>
       <c r="R197" s="4"/>
     </row>
-    <row r="198" ht="13.5" customHeight="1" spans="1:18">
+    <row r="198" spans="1:18" ht="13.5" customHeight="1">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -5382,7 +4759,7 @@
       <c r="Q198" s="4"/>
       <c r="R198" s="4"/>
     </row>
-    <row r="199" ht="13.5" customHeight="1" spans="1:18">
+    <row r="199" spans="1:18" ht="13.5" customHeight="1">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -5402,7 +4779,7 @@
       <c r="Q199" s="4"/>
       <c r="R199" s="4"/>
     </row>
-    <row r="200" ht="13.5" customHeight="1" spans="1:18">
+    <row r="200" spans="1:18" ht="13.5" customHeight="1">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -5422,7 +4799,7 @@
       <c r="Q200" s="4"/>
       <c r="R200" s="4"/>
     </row>
-    <row r="201" ht="13.5" customHeight="1" spans="1:18">
+    <row r="201" spans="1:18" ht="13.5" customHeight="1">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -5442,7 +4819,7 @@
       <c r="Q201" s="4"/>
       <c r="R201" s="4"/>
     </row>
-    <row r="202" ht="13.5" customHeight="1" spans="1:18">
+    <row r="202" spans="1:18" ht="13.5" customHeight="1">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -5462,7 +4839,7 @@
       <c r="Q202" s="4"/>
       <c r="R202" s="4"/>
     </row>
-    <row r="203" ht="13.5" customHeight="1" spans="1:18">
+    <row r="203" spans="1:18" ht="13.5" customHeight="1">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -5482,7 +4859,7 @@
       <c r="Q203" s="4"/>
       <c r="R203" s="4"/>
     </row>
-    <row r="204" ht="13.5" customHeight="1" spans="1:18">
+    <row r="204" spans="1:18" ht="13.5" customHeight="1">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -5502,7 +4879,7 @@
       <c r="Q204" s="4"/>
       <c r="R204" s="4"/>
     </row>
-    <row r="205" ht="13.5" customHeight="1" spans="1:18">
+    <row r="205" spans="1:18" ht="13.5" customHeight="1">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -5522,7 +4899,7 @@
       <c r="Q205" s="4"/>
       <c r="R205" s="4"/>
     </row>
-    <row r="206" ht="13.5" customHeight="1" spans="1:18">
+    <row r="206" spans="1:18" ht="13.5" customHeight="1">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -5542,7 +4919,7 @@
       <c r="Q206" s="4"/>
       <c r="R206" s="4"/>
     </row>
-    <row r="207" ht="13.5" customHeight="1" spans="1:18">
+    <row r="207" spans="1:18" ht="13.5" customHeight="1">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -5562,7 +4939,7 @@
       <c r="Q207" s="4"/>
       <c r="R207" s="4"/>
     </row>
-    <row r="208" ht="13.5" customHeight="1" spans="1:18">
+    <row r="208" spans="1:18" ht="13.5" customHeight="1">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -5582,7 +4959,7 @@
       <c r="Q208" s="4"/>
       <c r="R208" s="4"/>
     </row>
-    <row r="209" ht="13.5" customHeight="1" spans="1:18">
+    <row r="209" spans="1:18" ht="13.5" customHeight="1">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -5602,7 +4979,7 @@
       <c r="Q209" s="4"/>
       <c r="R209" s="4"/>
     </row>
-    <row r="210" ht="13.5" customHeight="1" spans="1:18">
+    <row r="210" spans="1:18" ht="13.5" customHeight="1">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -5622,7 +4999,7 @@
       <c r="Q210" s="4"/>
       <c r="R210" s="4"/>
     </row>
-    <row r="211" ht="13.5" customHeight="1" spans="1:18">
+    <row r="211" spans="1:18" ht="13.5" customHeight="1">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -5642,7 +5019,7 @@
       <c r="Q211" s="4"/>
       <c r="R211" s="4"/>
     </row>
-    <row r="212" ht="13.5" customHeight="1" spans="1:18">
+    <row r="212" spans="1:18" ht="13.5" customHeight="1">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -5662,7 +5039,7 @@
       <c r="Q212" s="4"/>
       <c r="R212" s="4"/>
     </row>
-    <row r="213" ht="13.5" customHeight="1" spans="1:18">
+    <row r="213" spans="1:18" ht="13.5" customHeight="1">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -5682,7 +5059,7 @@
       <c r="Q213" s="4"/>
       <c r="R213" s="4"/>
     </row>
-    <row r="214" ht="13.5" customHeight="1" spans="1:18">
+    <row r="214" spans="1:18" ht="13.5" customHeight="1">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -5702,7 +5079,7 @@
       <c r="Q214" s="4"/>
       <c r="R214" s="4"/>
     </row>
-    <row r="215" ht="13.5" customHeight="1" spans="1:18">
+    <row r="215" spans="1:18" ht="13.5" customHeight="1">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -5722,7 +5099,7 @@
       <c r="Q215" s="4"/>
       <c r="R215" s="4"/>
     </row>
-    <row r="216" ht="13.5" customHeight="1" spans="1:18">
+    <row r="216" spans="1:18" ht="13.5" customHeight="1">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -5742,7 +5119,7 @@
       <c r="Q216" s="4"/>
       <c r="R216" s="4"/>
     </row>
-    <row r="217" ht="13.5" customHeight="1" spans="1:18">
+    <row r="217" spans="1:18" ht="13.5" customHeight="1">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -5762,7 +5139,7 @@
       <c r="Q217" s="4"/>
       <c r="R217" s="4"/>
     </row>
-    <row r="218" ht="13.5" customHeight="1" spans="1:18">
+    <row r="218" spans="1:18" ht="13.5" customHeight="1">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -5782,7 +5159,7 @@
       <c r="Q218" s="4"/>
       <c r="R218" s="4"/>
     </row>
-    <row r="219" ht="13.5" customHeight="1" spans="1:18">
+    <row r="219" spans="1:18" ht="13.5" customHeight="1">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -5802,7 +5179,7 @@
       <c r="Q219" s="4"/>
       <c r="R219" s="4"/>
     </row>
-    <row r="220" ht="13.5" customHeight="1" spans="1:18">
+    <row r="220" spans="1:18" ht="13.5" customHeight="1">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -5822,7 +5199,7 @@
       <c r="Q220" s="4"/>
       <c r="R220" s="4"/>
     </row>
-    <row r="221" ht="13.5" customHeight="1" spans="1:18">
+    <row r="221" spans="1:18" ht="13.5" customHeight="1">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -5842,7 +5219,7 @@
       <c r="Q221" s="4"/>
       <c r="R221" s="4"/>
     </row>
-    <row r="222" ht="13.5" customHeight="1" spans="1:18">
+    <row r="222" spans="1:18" ht="13.5" customHeight="1">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -5862,7 +5239,7 @@
       <c r="Q222" s="4"/>
       <c r="R222" s="4"/>
     </row>
-    <row r="223" ht="13.5" customHeight="1" spans="1:18">
+    <row r="223" spans="1:18" ht="13.5" customHeight="1">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -5882,7 +5259,7 @@
       <c r="Q223" s="4"/>
       <c r="R223" s="4"/>
     </row>
-    <row r="224" ht="13.5" customHeight="1" spans="1:18">
+    <row r="224" spans="1:18" ht="13.5" customHeight="1">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -5902,7 +5279,7 @@
       <c r="Q224" s="4"/>
       <c r="R224" s="4"/>
     </row>
-    <row r="225" ht="13.5" customHeight="1" spans="1:18">
+    <row r="225" spans="1:18" ht="13.5" customHeight="1">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -5922,7 +5299,7 @@
       <c r="Q225" s="4"/>
       <c r="R225" s="4"/>
     </row>
-    <row r="226" ht="13.5" customHeight="1" spans="1:18">
+    <row r="226" spans="1:18" ht="13.5" customHeight="1">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -5942,7 +5319,7 @@
       <c r="Q226" s="4"/>
       <c r="R226" s="4"/>
     </row>
-    <row r="227" ht="13.5" customHeight="1" spans="1:18">
+    <row r="227" spans="1:18" ht="13.5" customHeight="1">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -5962,7 +5339,7 @@
       <c r="Q227" s="4"/>
       <c r="R227" s="4"/>
     </row>
-    <row r="228" ht="13.5" customHeight="1" spans="1:18">
+    <row r="228" spans="1:18" ht="13.5" customHeight="1">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -5982,7 +5359,7 @@
       <c r="Q228" s="4"/>
       <c r="R228" s="4"/>
     </row>
-    <row r="229" ht="13.5" customHeight="1" spans="1:18">
+    <row r="229" spans="1:18" ht="13.5" customHeight="1">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -6002,7 +5379,7 @@
       <c r="Q229" s="4"/>
       <c r="R229" s="4"/>
     </row>
-    <row r="230" ht="13.5" customHeight="1" spans="1:18">
+    <row r="230" spans="1:18" ht="13.5" customHeight="1">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -6022,7 +5399,7 @@
       <c r="Q230" s="4"/>
       <c r="R230" s="4"/>
     </row>
-    <row r="231" ht="13.5" customHeight="1" spans="1:18">
+    <row r="231" spans="1:18" ht="13.5" customHeight="1">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -6042,7 +5419,7 @@
       <c r="Q231" s="4"/>
       <c r="R231" s="4"/>
     </row>
-    <row r="232" ht="13.5" customHeight="1" spans="1:18">
+    <row r="232" spans="1:18" ht="13.5" customHeight="1">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -6062,7 +5439,7 @@
       <c r="Q232" s="4"/>
       <c r="R232" s="4"/>
     </row>
-    <row r="233" ht="13.5" customHeight="1" spans="1:18">
+    <row r="233" spans="1:18" ht="13.5" customHeight="1">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -6082,7 +5459,7 @@
       <c r="Q233" s="4"/>
       <c r="R233" s="4"/>
     </row>
-    <row r="234" ht="13.5" customHeight="1" spans="1:18">
+    <row r="234" spans="1:18" ht="13.5" customHeight="1">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -6102,7 +5479,7 @@
       <c r="Q234" s="4"/>
       <c r="R234" s="4"/>
     </row>
-    <row r="235" ht="13.5" customHeight="1" spans="1:18">
+    <row r="235" spans="1:18" ht="13.5" customHeight="1">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -6122,7 +5499,7 @@
       <c r="Q235" s="4"/>
       <c r="R235" s="4"/>
     </row>
-    <row r="236" ht="13.5" customHeight="1" spans="1:18">
+    <row r="236" spans="1:18" ht="13.5" customHeight="1">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -6142,7 +5519,7 @@
       <c r="Q236" s="4"/>
       <c r="R236" s="4"/>
     </row>
-    <row r="237" ht="13.5" customHeight="1" spans="1:18">
+    <row r="237" spans="1:18" ht="13.5" customHeight="1">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -6162,7 +5539,7 @@
       <c r="Q237" s="4"/>
       <c r="R237" s="4"/>
     </row>
-    <row r="238" ht="13.5" customHeight="1" spans="1:18">
+    <row r="238" spans="1:18" ht="13.5" customHeight="1">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -6182,7 +5559,7 @@
       <c r="Q238" s="4"/>
       <c r="R238" s="4"/>
     </row>
-    <row r="239" ht="13.5" customHeight="1" spans="1:18">
+    <row r="239" spans="1:18" ht="13.5" customHeight="1">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -6202,7 +5579,7 @@
       <c r="Q239" s="4"/>
       <c r="R239" s="4"/>
     </row>
-    <row r="240" ht="13.5" customHeight="1" spans="1:18">
+    <row r="240" spans="1:18" ht="13.5" customHeight="1">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -6222,7 +5599,7 @@
       <c r="Q240" s="4"/>
       <c r="R240" s="4"/>
     </row>
-    <row r="241" ht="13.5" customHeight="1" spans="1:18">
+    <row r="241" spans="1:18" ht="13.5" customHeight="1">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -6242,7 +5619,7 @@
       <c r="Q241" s="4"/>
       <c r="R241" s="4"/>
     </row>
-    <row r="242" ht="13.5" customHeight="1" spans="1:18">
+    <row r="242" spans="1:18" ht="13.5" customHeight="1">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -6262,7 +5639,7 @@
       <c r="Q242" s="4"/>
       <c r="R242" s="4"/>
     </row>
-    <row r="243" ht="13.5" customHeight="1" spans="1:18">
+    <row r="243" spans="1:18" ht="13.5" customHeight="1">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -6282,7 +5659,7 @@
       <c r="Q243" s="4"/>
       <c r="R243" s="4"/>
     </row>
-    <row r="244" ht="13.5" customHeight="1" spans="1:18">
+    <row r="244" spans="1:18" ht="13.5" customHeight="1">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -6302,7 +5679,7 @@
       <c r="Q244" s="4"/>
       <c r="R244" s="4"/>
     </row>
-    <row r="245" ht="13.5" customHeight="1" spans="1:18">
+    <row r="245" spans="1:18" ht="13.5" customHeight="1">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -6322,7 +5699,7 @@
       <c r="Q245" s="4"/>
       <c r="R245" s="4"/>
     </row>
-    <row r="246" ht="13.5" customHeight="1" spans="1:18">
+    <row r="246" spans="1:18" ht="13.5" customHeight="1">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -6342,7 +5719,7 @@
       <c r="Q246" s="4"/>
       <c r="R246" s="4"/>
     </row>
-    <row r="247" ht="13.5" customHeight="1" spans="1:18">
+    <row r="247" spans="1:18" ht="13.5" customHeight="1">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -6362,7 +5739,7 @@
       <c r="Q247" s="4"/>
       <c r="R247" s="4"/>
     </row>
-    <row r="248" ht="13.5" customHeight="1" spans="1:18">
+    <row r="248" spans="1:18" ht="13.5" customHeight="1">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -6382,7 +5759,7 @@
       <c r="Q248" s="4"/>
       <c r="R248" s="4"/>
     </row>
-    <row r="249" ht="13.5" customHeight="1" spans="1:18">
+    <row r="249" spans="1:18" ht="13.5" customHeight="1">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -6402,7 +5779,7 @@
       <c r="Q249" s="4"/>
       <c r="R249" s="4"/>
     </row>
-    <row r="250" ht="13.5" customHeight="1" spans="1:18">
+    <row r="250" spans="1:18" ht="13.5" customHeight="1">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -6422,7 +5799,7 @@
       <c r="Q250" s="4"/>
       <c r="R250" s="4"/>
     </row>
-    <row r="251" ht="13.5" customHeight="1" spans="1:18">
+    <row r="251" spans="1:18" ht="13.5" customHeight="1">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -6442,7 +5819,7 @@
       <c r="Q251" s="4"/>
       <c r="R251" s="4"/>
     </row>
-    <row r="252" ht="13.5" customHeight="1" spans="1:18">
+    <row r="252" spans="1:18" ht="13.5" customHeight="1">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -6462,7 +5839,7 @@
       <c r="Q252" s="4"/>
       <c r="R252" s="4"/>
     </row>
-    <row r="253" ht="13.5" customHeight="1" spans="1:18">
+    <row r="253" spans="1:18" ht="13.5" customHeight="1">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -6482,7 +5859,7 @@
       <c r="Q253" s="4"/>
       <c r="R253" s="4"/>
     </row>
-    <row r="254" ht="13.5" customHeight="1" spans="1:18">
+    <row r="254" spans="1:18" ht="13.5" customHeight="1">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -6502,7 +5879,7 @@
       <c r="Q254" s="4"/>
       <c r="R254" s="4"/>
     </row>
-    <row r="255" ht="13.5" customHeight="1" spans="1:18">
+    <row r="255" spans="1:18" ht="13.5" customHeight="1">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -6522,7 +5899,7 @@
       <c r="Q255" s="4"/>
       <c r="R255" s="4"/>
     </row>
-    <row r="256" ht="13.5" customHeight="1" spans="1:18">
+    <row r="256" spans="1:18" ht="13.5" customHeight="1">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -6542,7 +5919,7 @@
       <c r="Q256" s="4"/>
       <c r="R256" s="4"/>
     </row>
-    <row r="257" ht="13.5" customHeight="1" spans="1:18">
+    <row r="257" spans="1:18" ht="13.5" customHeight="1">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -6562,7 +5939,7 @@
       <c r="Q257" s="4"/>
       <c r="R257" s="4"/>
     </row>
-    <row r="258" ht="13.5" customHeight="1" spans="1:18">
+    <row r="258" spans="1:18" ht="13.5" customHeight="1">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -6582,7 +5959,7 @@
       <c r="Q258" s="4"/>
       <c r="R258" s="4"/>
     </row>
-    <row r="259" ht="13.5" customHeight="1" spans="1:18">
+    <row r="259" spans="1:18" ht="13.5" customHeight="1">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -6602,7 +5979,7 @@
       <c r="Q259" s="4"/>
       <c r="R259" s="4"/>
     </row>
-    <row r="260" ht="13.5" customHeight="1" spans="1:18">
+    <row r="260" spans="1:18" ht="13.5" customHeight="1">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -6622,7 +5999,7 @@
       <c r="Q260" s="4"/>
       <c r="R260" s="4"/>
     </row>
-    <row r="261" ht="13.5" customHeight="1" spans="1:18">
+    <row r="261" spans="1:18" ht="13.5" customHeight="1">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -6642,7 +6019,7 @@
       <c r="Q261" s="4"/>
       <c r="R261" s="4"/>
     </row>
-    <row r="262" ht="13.5" customHeight="1" spans="1:18">
+    <row r="262" spans="1:18" ht="13.5" customHeight="1">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -6662,7 +6039,7 @@
       <c r="Q262" s="4"/>
       <c r="R262" s="4"/>
     </row>
-    <row r="263" ht="13.5" customHeight="1" spans="1:18">
+    <row r="263" spans="1:18" ht="13.5" customHeight="1">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -6682,7 +6059,7 @@
       <c r="Q263" s="4"/>
       <c r="R263" s="4"/>
     </row>
-    <row r="264" ht="13.5" customHeight="1" spans="1:18">
+    <row r="264" spans="1:18" ht="13.5" customHeight="1">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -6702,7 +6079,7 @@
       <c r="Q264" s="4"/>
       <c r="R264" s="4"/>
     </row>
-    <row r="265" ht="13.5" customHeight="1" spans="1:18">
+    <row r="265" spans="1:18" ht="13.5" customHeight="1">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -6722,7 +6099,7 @@
       <c r="Q265" s="4"/>
       <c r="R265" s="4"/>
     </row>
-    <row r="266" ht="13.5" customHeight="1" spans="1:18">
+    <row r="266" spans="1:18" ht="13.5" customHeight="1">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -6742,7 +6119,7 @@
       <c r="Q266" s="4"/>
       <c r="R266" s="4"/>
     </row>
-    <row r="267" ht="13.5" customHeight="1" spans="1:18">
+    <row r="267" spans="1:18" ht="13.5" customHeight="1">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -6762,7 +6139,7 @@
       <c r="Q267" s="4"/>
       <c r="R267" s="4"/>
     </row>
-    <row r="268" ht="13.5" customHeight="1" spans="1:18">
+    <row r="268" spans="1:18" ht="13.5" customHeight="1">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -6782,7 +6159,7 @@
       <c r="Q268" s="4"/>
       <c r="R268" s="4"/>
     </row>
-    <row r="269" ht="13.5" customHeight="1" spans="1:18">
+    <row r="269" spans="1:18" ht="13.5" customHeight="1">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -6802,7 +6179,7 @@
       <c r="Q269" s="4"/>
       <c r="R269" s="4"/>
     </row>
-    <row r="270" ht="13.5" customHeight="1" spans="1:18">
+    <row r="270" spans="1:18" ht="13.5" customHeight="1">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -6822,7 +6199,7 @@
       <c r="Q270" s="4"/>
       <c r="R270" s="4"/>
     </row>
-    <row r="271" ht="13.5" customHeight="1" spans="1:18">
+    <row r="271" spans="1:18" ht="13.5" customHeight="1">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -6842,7 +6219,7 @@
       <c r="Q271" s="4"/>
       <c r="R271" s="4"/>
     </row>
-    <row r="272" ht="13.5" customHeight="1" spans="1:18">
+    <row r="272" spans="1:18" ht="13.5" customHeight="1">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -6862,7 +6239,7 @@
       <c r="Q272" s="4"/>
       <c r="R272" s="4"/>
     </row>
-    <row r="273" ht="13.5" customHeight="1" spans="1:18">
+    <row r="273" spans="1:18" ht="13.5" customHeight="1">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -6882,7 +6259,7 @@
       <c r="Q273" s="4"/>
       <c r="R273" s="4"/>
     </row>
-    <row r="274" ht="13.5" customHeight="1" spans="1:18">
+    <row r="274" spans="1:18" ht="13.5" customHeight="1">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -6902,7 +6279,7 @@
       <c r="Q274" s="4"/>
       <c r="R274" s="4"/>
     </row>
-    <row r="275" ht="13.5" customHeight="1" spans="1:18">
+    <row r="275" spans="1:18" ht="13.5" customHeight="1">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -6922,7 +6299,7 @@
       <c r="Q275" s="4"/>
       <c r="R275" s="4"/>
     </row>
-    <row r="276" ht="13.5" customHeight="1" spans="1:18">
+    <row r="276" spans="1:18" ht="13.5" customHeight="1">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -6942,7 +6319,7 @@
       <c r="Q276" s="4"/>
       <c r="R276" s="4"/>
     </row>
-    <row r="277" ht="13.5" customHeight="1" spans="1:18">
+    <row r="277" spans="1:18" ht="13.5" customHeight="1">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -6962,7 +6339,7 @@
       <c r="Q277" s="4"/>
       <c r="R277" s="4"/>
     </row>
-    <row r="278" ht="13.5" customHeight="1" spans="1:18">
+    <row r="278" spans="1:18" ht="13.5" customHeight="1">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -6982,7 +6359,7 @@
       <c r="Q278" s="4"/>
       <c r="R278" s="4"/>
     </row>
-    <row r="279" ht="13.5" customHeight="1" spans="1:18">
+    <row r="279" spans="1:18" ht="13.5" customHeight="1">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -7002,7 +6379,7 @@
       <c r="Q279" s="4"/>
       <c r="R279" s="4"/>
     </row>
-    <row r="280" ht="13.5" customHeight="1" spans="1:18">
+    <row r="280" spans="1:18" ht="13.5" customHeight="1">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -7022,7 +6399,7 @@
       <c r="Q280" s="4"/>
       <c r="R280" s="4"/>
     </row>
-    <row r="281" ht="13.5" customHeight="1" spans="1:18">
+    <row r="281" spans="1:18" ht="13.5" customHeight="1">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -7042,7 +6419,7 @@
       <c r="Q281" s="4"/>
       <c r="R281" s="4"/>
     </row>
-    <row r="282" ht="13.5" customHeight="1" spans="1:18">
+    <row r="282" spans="1:18" ht="13.5" customHeight="1">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -7062,7 +6439,7 @@
       <c r="Q282" s="4"/>
       <c r="R282" s="4"/>
     </row>
-    <row r="283" ht="13.5" customHeight="1" spans="1:18">
+    <row r="283" spans="1:18" ht="13.5" customHeight="1">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -7082,7 +6459,7 @@
       <c r="Q283" s="4"/>
       <c r="R283" s="4"/>
     </row>
-    <row r="284" ht="13.5" customHeight="1" spans="1:18">
+    <row r="284" spans="1:18" ht="13.5" customHeight="1">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -7102,7 +6479,7 @@
       <c r="Q284" s="4"/>
       <c r="R284" s="4"/>
     </row>
-    <row r="285" ht="13.5" customHeight="1" spans="1:18">
+    <row r="285" spans="1:18" ht="13.5" customHeight="1">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -7122,7 +6499,7 @@
       <c r="Q285" s="4"/>
       <c r="R285" s="4"/>
     </row>
-    <row r="286" ht="13.5" customHeight="1" spans="1:18">
+    <row r="286" spans="1:18" ht="13.5" customHeight="1">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -7142,7 +6519,7 @@
       <c r="Q286" s="4"/>
       <c r="R286" s="4"/>
     </row>
-    <row r="287" ht="13.5" customHeight="1" spans="1:18">
+    <row r="287" spans="1:18" ht="13.5" customHeight="1">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -7162,7 +6539,7 @@
       <c r="Q287" s="4"/>
       <c r="R287" s="4"/>
     </row>
-    <row r="288" ht="13.5" customHeight="1" spans="1:18">
+    <row r="288" spans="1:18" ht="13.5" customHeight="1">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -7182,7 +6559,7 @@
       <c r="Q288" s="4"/>
       <c r="R288" s="4"/>
     </row>
-    <row r="289" ht="13.5" customHeight="1" spans="1:18">
+    <row r="289" spans="1:18" ht="13.5" customHeight="1">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -7202,7 +6579,7 @@
       <c r="Q289" s="4"/>
       <c r="R289" s="4"/>
     </row>
-    <row r="290" ht="13.5" customHeight="1" spans="1:18">
+    <row r="290" spans="1:18" ht="13.5" customHeight="1">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -7222,7 +6599,7 @@
       <c r="Q290" s="4"/>
       <c r="R290" s="4"/>
     </row>
-    <row r="291" ht="13.5" customHeight="1" spans="1:18">
+    <row r="291" spans="1:18" ht="13.5" customHeight="1">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -7242,7 +6619,7 @@
       <c r="Q291" s="4"/>
       <c r="R291" s="4"/>
     </row>
-    <row r="292" ht="13.5" customHeight="1" spans="1:18">
+    <row r="292" spans="1:18" ht="13.5" customHeight="1">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -7262,7 +6639,7 @@
       <c r="Q292" s="4"/>
       <c r="R292" s="4"/>
     </row>
-    <row r="293" ht="13.5" customHeight="1" spans="1:18">
+    <row r="293" spans="1:18" ht="13.5" customHeight="1">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -7282,7 +6659,7 @@
       <c r="Q293" s="4"/>
       <c r="R293" s="4"/>
     </row>
-    <row r="294" ht="13.5" customHeight="1" spans="1:18">
+    <row r="294" spans="1:18" ht="13.5" customHeight="1">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -7302,7 +6679,7 @@
       <c r="Q294" s="4"/>
       <c r="R294" s="4"/>
     </row>
-    <row r="295" ht="13.5" customHeight="1" spans="1:18">
+    <row r="295" spans="1:18" ht="13.5" customHeight="1">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -7322,7 +6699,7 @@
       <c r="Q295" s="4"/>
       <c r="R295" s="4"/>
     </row>
-    <row r="296" ht="13.5" customHeight="1" spans="1:18">
+    <row r="296" spans="1:18" ht="13.5" customHeight="1">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -7342,7 +6719,7 @@
       <c r="Q296" s="4"/>
       <c r="R296" s="4"/>
     </row>
-    <row r="297" ht="13.5" customHeight="1" spans="1:18">
+    <row r="297" spans="1:18" ht="13.5" customHeight="1">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -7362,7 +6739,7 @@
       <c r="Q297" s="4"/>
       <c r="R297" s="4"/>
     </row>
-    <row r="298" ht="13.5" customHeight="1" spans="1:18">
+    <row r="298" spans="1:18" ht="13.5" customHeight="1">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -7382,7 +6759,7 @@
       <c r="Q298" s="4"/>
       <c r="R298" s="4"/>
     </row>
-    <row r="299" ht="13.5" customHeight="1" spans="1:18">
+    <row r="299" spans="1:18" ht="13.5" customHeight="1">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -7402,7 +6779,7 @@
       <c r="Q299" s="4"/>
       <c r="R299" s="4"/>
     </row>
-    <row r="300" ht="13.5" customHeight="1" spans="1:18">
+    <row r="300" spans="1:18" ht="13.5" customHeight="1">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -7422,7 +6799,7 @@
       <c r="Q300" s="4"/>
       <c r="R300" s="4"/>
     </row>
-    <row r="301" ht="13.5" customHeight="1" spans="1:18">
+    <row r="301" spans="1:18" ht="13.5" customHeight="1">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -7442,7 +6819,7 @@
       <c r="Q301" s="4"/>
       <c r="R301" s="4"/>
     </row>
-    <row r="302" ht="13.5" customHeight="1" spans="1:18">
+    <row r="302" spans="1:18" ht="13.5" customHeight="1">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -7462,7 +6839,7 @@
       <c r="Q302" s="4"/>
       <c r="R302" s="4"/>
     </row>
-    <row r="303" ht="13.5" customHeight="1" spans="1:18">
+    <row r="303" spans="1:18" ht="13.5" customHeight="1">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -7482,7 +6859,7 @@
       <c r="Q303" s="4"/>
       <c r="R303" s="4"/>
     </row>
-    <row r="304" ht="13.5" customHeight="1" spans="1:18">
+    <row r="304" spans="1:18" ht="13.5" customHeight="1">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -7502,7 +6879,7 @@
       <c r="Q304" s="4"/>
       <c r="R304" s="4"/>
     </row>
-    <row r="305" ht="13.5" customHeight="1" spans="1:18">
+    <row r="305" spans="1:18" ht="13.5" customHeight="1">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -7522,7 +6899,7 @@
       <c r="Q305" s="4"/>
       <c r="R305" s="4"/>
     </row>
-    <row r="306" ht="13.5" customHeight="1" spans="1:18">
+    <row r="306" spans="1:18" ht="13.5" customHeight="1">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -7542,7 +6919,7 @@
       <c r="Q306" s="4"/>
       <c r="R306" s="4"/>
     </row>
-    <row r="307" ht="13.5" customHeight="1" spans="1:18">
+    <row r="307" spans="1:18" ht="13.5" customHeight="1">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -7562,7 +6939,7 @@
       <c r="Q307" s="4"/>
       <c r="R307" s="4"/>
     </row>
-    <row r="308" ht="13.5" customHeight="1" spans="1:18">
+    <row r="308" spans="1:18" ht="13.5" customHeight="1">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -7582,7 +6959,7 @@
       <c r="Q308" s="4"/>
       <c r="R308" s="4"/>
     </row>
-    <row r="309" ht="13.5" customHeight="1" spans="1:18">
+    <row r="309" spans="1:18" ht="13.5" customHeight="1">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -7602,7 +6979,7 @@
       <c r="Q309" s="4"/>
       <c r="R309" s="4"/>
     </row>
-    <row r="310" ht="13.5" customHeight="1" spans="1:18">
+    <row r="310" spans="1:18" ht="13.5" customHeight="1">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -7622,7 +6999,7 @@
       <c r="Q310" s="4"/>
       <c r="R310" s="4"/>
     </row>
-    <row r="311" ht="13.5" customHeight="1" spans="1:18">
+    <row r="311" spans="1:18" ht="13.5" customHeight="1">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -7642,7 +7019,7 @@
       <c r="Q311" s="4"/>
       <c r="R311" s="4"/>
     </row>
-    <row r="312" ht="13.5" customHeight="1" spans="1:18">
+    <row r="312" spans="1:18" ht="13.5" customHeight="1">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -7662,7 +7039,7 @@
       <c r="Q312" s="4"/>
       <c r="R312" s="4"/>
     </row>
-    <row r="313" ht="13.5" customHeight="1" spans="1:18">
+    <row r="313" spans="1:18" ht="13.5" customHeight="1">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -7682,7 +7059,7 @@
       <c r="Q313" s="4"/>
       <c r="R313" s="4"/>
     </row>
-    <row r="314" ht="13.5" customHeight="1" spans="1:18">
+    <row r="314" spans="1:18" ht="13.5" customHeight="1">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -7702,7 +7079,7 @@
       <c r="Q314" s="4"/>
       <c r="R314" s="4"/>
     </row>
-    <row r="315" ht="13.5" customHeight="1" spans="1:18">
+    <row r="315" spans="1:18" ht="13.5" customHeight="1">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -7722,7 +7099,7 @@
       <c r="Q315" s="4"/>
       <c r="R315" s="4"/>
     </row>
-    <row r="316" ht="13.5" customHeight="1" spans="1:18">
+    <row r="316" spans="1:18" ht="13.5" customHeight="1">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -7742,7 +7119,7 @@
       <c r="Q316" s="4"/>
       <c r="R316" s="4"/>
     </row>
-    <row r="317" ht="13.5" customHeight="1" spans="1:18">
+    <row r="317" spans="1:18" ht="13.5" customHeight="1">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -7762,7 +7139,7 @@
       <c r="Q317" s="4"/>
       <c r="R317" s="4"/>
     </row>
-    <row r="318" ht="13.5" customHeight="1" spans="1:18">
+    <row r="318" spans="1:18" ht="13.5" customHeight="1">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -7782,7 +7159,7 @@
       <c r="Q318" s="4"/>
       <c r="R318" s="4"/>
     </row>
-    <row r="319" ht="13.5" customHeight="1" spans="1:18">
+    <row r="319" spans="1:18" ht="13.5" customHeight="1">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -7802,7 +7179,7 @@
       <c r="Q319" s="4"/>
       <c r="R319" s="4"/>
     </row>
-    <row r="320" ht="13.5" customHeight="1" spans="1:18">
+    <row r="320" spans="1:18" ht="13.5" customHeight="1">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -7822,7 +7199,7 @@
       <c r="Q320" s="4"/>
       <c r="R320" s="4"/>
     </row>
-    <row r="321" ht="13.5" customHeight="1" spans="1:18">
+    <row r="321" spans="1:18" ht="13.5" customHeight="1">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -7842,7 +7219,7 @@
       <c r="Q321" s="4"/>
       <c r="R321" s="4"/>
     </row>
-    <row r="322" ht="13.5" customHeight="1" spans="1:18">
+    <row r="322" spans="1:18" ht="13.5" customHeight="1">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -7862,7 +7239,7 @@
       <c r="Q322" s="4"/>
       <c r="R322" s="4"/>
     </row>
-    <row r="323" ht="13.5" customHeight="1" spans="1:18">
+    <row r="323" spans="1:18" ht="13.5" customHeight="1">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -7882,7 +7259,7 @@
       <c r="Q323" s="4"/>
       <c r="R323" s="4"/>
     </row>
-    <row r="324" ht="13.5" customHeight="1" spans="1:18">
+    <row r="324" spans="1:18" ht="13.5" customHeight="1">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -7902,7 +7279,7 @@
       <c r="Q324" s="4"/>
       <c r="R324" s="4"/>
     </row>
-    <row r="325" ht="13.5" customHeight="1" spans="1:18">
+    <row r="325" spans="1:18" ht="13.5" customHeight="1">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -7922,7 +7299,7 @@
       <c r="Q325" s="4"/>
       <c r="R325" s="4"/>
     </row>
-    <row r="326" ht="13.5" customHeight="1" spans="1:18">
+    <row r="326" spans="1:18" ht="13.5" customHeight="1">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -7942,7 +7319,7 @@
       <c r="Q326" s="4"/>
       <c r="R326" s="4"/>
     </row>
-    <row r="327" ht="13.5" customHeight="1" spans="1:18">
+    <row r="327" spans="1:18" ht="13.5" customHeight="1">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -7962,7 +7339,7 @@
       <c r="Q327" s="4"/>
       <c r="R327" s="4"/>
     </row>
-    <row r="328" ht="13.5" customHeight="1" spans="1:18">
+    <row r="328" spans="1:18" ht="13.5" customHeight="1">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -7982,7 +7359,7 @@
       <c r="Q328" s="4"/>
       <c r="R328" s="4"/>
     </row>
-    <row r="329" ht="13.5" customHeight="1" spans="1:18">
+    <row r="329" spans="1:18" ht="13.5" customHeight="1">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -8002,7 +7379,7 @@
       <c r="Q329" s="4"/>
       <c r="R329" s="4"/>
     </row>
-    <row r="330" ht="13.5" customHeight="1" spans="1:18">
+    <row r="330" spans="1:18" ht="13.5" customHeight="1">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -8022,7 +7399,7 @@
       <c r="Q330" s="4"/>
       <c r="R330" s="4"/>
     </row>
-    <row r="331" ht="13.5" customHeight="1" spans="1:18">
+    <row r="331" spans="1:18" ht="13.5" customHeight="1">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -8042,7 +7419,7 @@
       <c r="Q331" s="4"/>
       <c r="R331" s="4"/>
     </row>
-    <row r="332" ht="13.5" customHeight="1" spans="1:18">
+    <row r="332" spans="1:18" ht="13.5" customHeight="1">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -8062,7 +7439,7 @@
       <c r="Q332" s="4"/>
       <c r="R332" s="4"/>
     </row>
-    <row r="333" ht="13.5" customHeight="1" spans="1:18">
+    <row r="333" spans="1:18" ht="13.5" customHeight="1">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -8082,7 +7459,7 @@
       <c r="Q333" s="4"/>
       <c r="R333" s="4"/>
     </row>
-    <row r="334" ht="13.5" customHeight="1" spans="1:18">
+    <row r="334" spans="1:18" ht="13.5" customHeight="1">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -8102,7 +7479,7 @@
       <c r="Q334" s="4"/>
       <c r="R334" s="4"/>
     </row>
-    <row r="335" ht="13.5" customHeight="1" spans="1:18">
+    <row r="335" spans="1:18" ht="13.5" customHeight="1">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -8122,7 +7499,7 @@
       <c r="Q335" s="4"/>
       <c r="R335" s="4"/>
     </row>
-    <row r="336" ht="13.5" customHeight="1" spans="1:18">
+    <row r="336" spans="1:18" ht="13.5" customHeight="1">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -8142,7 +7519,7 @@
       <c r="Q336" s="4"/>
       <c r="R336" s="4"/>
     </row>
-    <row r="337" ht="13.5" customHeight="1" spans="1:18">
+    <row r="337" spans="1:18" ht="13.5" customHeight="1">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -8162,7 +7539,7 @@
       <c r="Q337" s="4"/>
       <c r="R337" s="4"/>
     </row>
-    <row r="338" ht="13.5" customHeight="1" spans="1:18">
+    <row r="338" spans="1:18" ht="13.5" customHeight="1">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -8182,7 +7559,7 @@
       <c r="Q338" s="4"/>
       <c r="R338" s="4"/>
     </row>
-    <row r="339" ht="13.5" customHeight="1" spans="1:18">
+    <row r="339" spans="1:18" ht="13.5" customHeight="1">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -8202,7 +7579,7 @@
       <c r="Q339" s="4"/>
       <c r="R339" s="4"/>
     </row>
-    <row r="340" ht="13.5" customHeight="1" spans="1:18">
+    <row r="340" spans="1:18" ht="13.5" customHeight="1">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -8222,7 +7599,7 @@
       <c r="Q340" s="4"/>
       <c r="R340" s="4"/>
     </row>
-    <row r="341" ht="13.5" customHeight="1" spans="1:18">
+    <row r="341" spans="1:18" ht="13.5" customHeight="1">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -8242,7 +7619,7 @@
       <c r="Q341" s="4"/>
       <c r="R341" s="4"/>
     </row>
-    <row r="342" ht="13.5" customHeight="1" spans="1:18">
+    <row r="342" spans="1:18" ht="13.5" customHeight="1">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -8262,7 +7639,7 @@
       <c r="Q342" s="4"/>
       <c r="R342" s="4"/>
     </row>
-    <row r="343" ht="13.5" customHeight="1" spans="1:18">
+    <row r="343" spans="1:18" ht="13.5" customHeight="1">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -8282,7 +7659,7 @@
       <c r="Q343" s="4"/>
       <c r="R343" s="4"/>
     </row>
-    <row r="344" ht="13.5" customHeight="1" spans="1:18">
+    <row r="344" spans="1:18" ht="13.5" customHeight="1">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -8302,7 +7679,7 @@
       <c r="Q344" s="4"/>
       <c r="R344" s="4"/>
     </row>
-    <row r="345" ht="13.5" customHeight="1" spans="1:18">
+    <row r="345" spans="1:18" ht="13.5" customHeight="1">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -8322,7 +7699,7 @@
       <c r="Q345" s="4"/>
       <c r="R345" s="4"/>
     </row>
-    <row r="346" ht="13.5" customHeight="1" spans="1:18">
+    <row r="346" spans="1:18" ht="13.5" customHeight="1">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -8342,7 +7719,7 @@
       <c r="Q346" s="4"/>
       <c r="R346" s="4"/>
     </row>
-    <row r="347" ht="13.5" customHeight="1" spans="1:18">
+    <row r="347" spans="1:18" ht="13.5" customHeight="1">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -8362,7 +7739,7 @@
       <c r="Q347" s="4"/>
       <c r="R347" s="4"/>
     </row>
-    <row r="348" ht="13.5" customHeight="1" spans="1:18">
+    <row r="348" spans="1:18" ht="13.5" customHeight="1">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -8382,7 +7759,7 @@
       <c r="Q348" s="4"/>
       <c r="R348" s="4"/>
     </row>
-    <row r="349" ht="13.5" customHeight="1" spans="1:18">
+    <row r="349" spans="1:18" ht="13.5" customHeight="1">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -8402,7 +7779,7 @@
       <c r="Q349" s="4"/>
       <c r="R349" s="4"/>
     </row>
-    <row r="350" ht="13.5" customHeight="1" spans="1:18">
+    <row r="350" spans="1:18" ht="13.5" customHeight="1">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -8422,7 +7799,7 @@
       <c r="Q350" s="4"/>
       <c r="R350" s="4"/>
     </row>
-    <row r="351" ht="13.5" customHeight="1" spans="1:18">
+    <row r="351" spans="1:18" ht="13.5" customHeight="1">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -8442,7 +7819,7 @@
       <c r="Q351" s="4"/>
       <c r="R351" s="4"/>
     </row>
-    <row r="352" ht="13.5" customHeight="1" spans="1:18">
+    <row r="352" spans="1:18" ht="13.5" customHeight="1">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -8462,7 +7839,7 @@
       <c r="Q352" s="4"/>
       <c r="R352" s="4"/>
     </row>
-    <row r="353" ht="13.5" customHeight="1" spans="1:18">
+    <row r="353" spans="1:18" ht="13.5" customHeight="1">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -8482,7 +7859,7 @@
       <c r="Q353" s="4"/>
       <c r="R353" s="4"/>
     </row>
-    <row r="354" ht="13.5" customHeight="1" spans="1:18">
+    <row r="354" spans="1:18" ht="13.5" customHeight="1">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -8502,7 +7879,7 @@
       <c r="Q354" s="4"/>
       <c r="R354" s="4"/>
     </row>
-    <row r="355" ht="13.5" customHeight="1" spans="1:18">
+    <row r="355" spans="1:18" ht="13.5" customHeight="1">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -8522,7 +7899,7 @@
       <c r="Q355" s="4"/>
       <c r="R355" s="4"/>
     </row>
-    <row r="356" ht="13.5" customHeight="1" spans="1:18">
+    <row r="356" spans="1:18" ht="13.5" customHeight="1">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -8542,7 +7919,7 @@
       <c r="Q356" s="4"/>
       <c r="R356" s="4"/>
     </row>
-    <row r="357" ht="13.5" customHeight="1" spans="1:18">
+    <row r="357" spans="1:18" ht="13.5" customHeight="1">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -8562,7 +7939,7 @@
       <c r="Q357" s="4"/>
       <c r="R357" s="4"/>
     </row>
-    <row r="358" ht="13.5" customHeight="1" spans="1:18">
+    <row r="358" spans="1:18" ht="13.5" customHeight="1">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -8582,7 +7959,7 @@
       <c r="Q358" s="4"/>
       <c r="R358" s="4"/>
     </row>
-    <row r="359" ht="13.5" customHeight="1" spans="1:18">
+    <row r="359" spans="1:18" ht="13.5" customHeight="1">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -8602,7 +7979,7 @@
       <c r="Q359" s="4"/>
       <c r="R359" s="4"/>
     </row>
-    <row r="360" ht="13.5" customHeight="1" spans="1:18">
+    <row r="360" spans="1:18" ht="13.5" customHeight="1">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -8622,7 +7999,7 @@
       <c r="Q360" s="4"/>
       <c r="R360" s="4"/>
     </row>
-    <row r="361" ht="13.5" customHeight="1" spans="1:18">
+    <row r="361" spans="1:18" ht="13.5" customHeight="1">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -8642,7 +8019,7 @@
       <c r="Q361" s="4"/>
       <c r="R361" s="4"/>
     </row>
-    <row r="362" ht="13.5" customHeight="1" spans="1:18">
+    <row r="362" spans="1:18" ht="13.5" customHeight="1">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -8662,7 +8039,7 @@
       <c r="Q362" s="4"/>
       <c r="R362" s="4"/>
     </row>
-    <row r="363" ht="13.5" customHeight="1" spans="1:18">
+    <row r="363" spans="1:18" ht="13.5" customHeight="1">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -8682,7 +8059,7 @@
       <c r="Q363" s="4"/>
       <c r="R363" s="4"/>
     </row>
-    <row r="364" ht="13.5" customHeight="1" spans="1:18">
+    <row r="364" spans="1:18" ht="13.5" customHeight="1">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -8702,7 +8079,7 @@
       <c r="Q364" s="4"/>
       <c r="R364" s="4"/>
     </row>
-    <row r="365" ht="13.5" customHeight="1" spans="1:18">
+    <row r="365" spans="1:18" ht="13.5" customHeight="1">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -8722,7 +8099,7 @@
       <c r="Q365" s="4"/>
       <c r="R365" s="4"/>
     </row>
-    <row r="366" ht="13.5" customHeight="1" spans="1:18">
+    <row r="366" spans="1:18" ht="13.5" customHeight="1">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -8742,7 +8119,7 @@
       <c r="Q366" s="4"/>
       <c r="R366" s="4"/>
     </row>
-    <row r="367" ht="13.5" customHeight="1" spans="1:18">
+    <row r="367" spans="1:18" ht="13.5" customHeight="1">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -8762,7 +8139,7 @@
       <c r="Q367" s="4"/>
       <c r="R367" s="4"/>
     </row>
-    <row r="368" ht="13.5" customHeight="1" spans="1:18">
+    <row r="368" spans="1:18" ht="13.5" customHeight="1">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -8782,7 +8159,7 @@
       <c r="Q368" s="4"/>
       <c r="R368" s="4"/>
     </row>
-    <row r="369" ht="13.5" customHeight="1" spans="1:18">
+    <row r="369" spans="1:18" ht="13.5" customHeight="1">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -8802,7 +8179,7 @@
       <c r="Q369" s="4"/>
       <c r="R369" s="4"/>
     </row>
-    <row r="370" ht="13.5" customHeight="1" spans="1:18">
+    <row r="370" spans="1:18" ht="13.5" customHeight="1">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -8822,7 +8199,7 @@
       <c r="Q370" s="4"/>
       <c r="R370" s="4"/>
     </row>
-    <row r="371" ht="13.5" customHeight="1" spans="1:18">
+    <row r="371" spans="1:18" ht="13.5" customHeight="1">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -8842,7 +8219,7 @@
       <c r="Q371" s="4"/>
       <c r="R371" s="4"/>
     </row>
-    <row r="372" ht="13.5" customHeight="1" spans="1:18">
+    <row r="372" spans="1:18" ht="13.5" customHeight="1">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -8862,7 +8239,7 @@
       <c r="Q372" s="4"/>
       <c r="R372" s="4"/>
     </row>
-    <row r="373" ht="13.5" customHeight="1" spans="1:18">
+    <row r="373" spans="1:18" ht="13.5" customHeight="1">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -8882,7 +8259,7 @@
       <c r="Q373" s="4"/>
       <c r="R373" s="4"/>
     </row>
-    <row r="374" ht="13.5" customHeight="1" spans="1:18">
+    <row r="374" spans="1:18" ht="13.5" customHeight="1">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -8902,7 +8279,7 @@
       <c r="Q374" s="4"/>
       <c r="R374" s="4"/>
     </row>
-    <row r="375" ht="13.5" customHeight="1" spans="1:18">
+    <row r="375" spans="1:18" ht="13.5" customHeight="1">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -8922,7 +8299,7 @@
       <c r="Q375" s="4"/>
       <c r="R375" s="4"/>
     </row>
-    <row r="376" ht="13.5" customHeight="1" spans="1:18">
+    <row r="376" spans="1:18" ht="13.5" customHeight="1">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -8942,7 +8319,7 @@
       <c r="Q376" s="4"/>
       <c r="R376" s="4"/>
     </row>
-    <row r="377" ht="13.5" customHeight="1" spans="1:18">
+    <row r="377" spans="1:18" ht="13.5" customHeight="1">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -8962,7 +8339,7 @@
       <c r="Q377" s="4"/>
       <c r="R377" s="4"/>
     </row>
-    <row r="378" ht="13.5" customHeight="1" spans="1:18">
+    <row r="378" spans="1:18" ht="13.5" customHeight="1">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -8982,7 +8359,7 @@
       <c r="Q378" s="4"/>
       <c r="R378" s="4"/>
     </row>
-    <row r="379" ht="13.5" customHeight="1" spans="1:18">
+    <row r="379" spans="1:18" ht="13.5" customHeight="1">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -9002,7 +8379,7 @@
       <c r="Q379" s="4"/>
       <c r="R379" s="4"/>
     </row>
-    <row r="380" ht="13.5" customHeight="1" spans="1:18">
+    <row r="380" spans="1:18" ht="13.5" customHeight="1">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -9022,7 +8399,7 @@
       <c r="Q380" s="4"/>
       <c r="R380" s="4"/>
     </row>
-    <row r="381" ht="13.5" customHeight="1" spans="1:18">
+    <row r="381" spans="1:18" ht="13.5" customHeight="1">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -9042,7 +8419,7 @@
       <c r="Q381" s="4"/>
       <c r="R381" s="4"/>
     </row>
-    <row r="382" ht="13.5" customHeight="1" spans="1:18">
+    <row r="382" spans="1:18" ht="13.5" customHeight="1">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -9062,7 +8439,7 @@
       <c r="Q382" s="4"/>
       <c r="R382" s="4"/>
     </row>
-    <row r="383" ht="13.5" customHeight="1" spans="1:18">
+    <row r="383" spans="1:18" ht="13.5" customHeight="1">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -9082,7 +8459,7 @@
       <c r="Q383" s="4"/>
       <c r="R383" s="4"/>
     </row>
-    <row r="384" ht="13.5" customHeight="1" spans="1:18">
+    <row r="384" spans="1:18" ht="13.5" customHeight="1">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -9102,7 +8479,7 @@
       <c r="Q384" s="4"/>
       <c r="R384" s="4"/>
     </row>
-    <row r="385" ht="13.5" customHeight="1" spans="1:18">
+    <row r="385" spans="1:18" ht="13.5" customHeight="1">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -9122,7 +8499,7 @@
       <c r="Q385" s="4"/>
       <c r="R385" s="4"/>
     </row>
-    <row r="386" ht="13.5" customHeight="1" spans="1:18">
+    <row r="386" spans="1:18" ht="13.5" customHeight="1">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -9142,7 +8519,7 @@
       <c r="Q386" s="4"/>
       <c r="R386" s="4"/>
     </row>
-    <row r="387" ht="13.5" customHeight="1" spans="1:18">
+    <row r="387" spans="1:18" ht="13.5" customHeight="1">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -9162,7 +8539,7 @@
       <c r="Q387" s="4"/>
       <c r="R387" s="4"/>
     </row>
-    <row r="388" ht="13.5" customHeight="1" spans="1:18">
+    <row r="388" spans="1:18" ht="13.5" customHeight="1">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -9182,7 +8559,7 @@
       <c r="Q388" s="4"/>
       <c r="R388" s="4"/>
     </row>
-    <row r="389" ht="13.5" customHeight="1" spans="1:18">
+    <row r="389" spans="1:18" ht="13.5" customHeight="1">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -9202,7 +8579,7 @@
       <c r="Q389" s="4"/>
       <c r="R389" s="4"/>
     </row>
-    <row r="390" ht="13.5" customHeight="1" spans="1:18">
+    <row r="390" spans="1:18" ht="13.5" customHeight="1">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -9222,7 +8599,7 @@
       <c r="Q390" s="4"/>
       <c r="R390" s="4"/>
     </row>
-    <row r="391" ht="13.5" customHeight="1" spans="1:18">
+    <row r="391" spans="1:18" ht="13.5" customHeight="1">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -9242,7 +8619,7 @@
       <c r="Q391" s="4"/>
       <c r="R391" s="4"/>
     </row>
-    <row r="392" ht="13.5" customHeight="1" spans="1:18">
+    <row r="392" spans="1:18" ht="13.5" customHeight="1">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -9262,7 +8639,7 @@
       <c r="Q392" s="4"/>
       <c r="R392" s="4"/>
     </row>
-    <row r="393" ht="13.5" customHeight="1" spans="1:18">
+    <row r="393" spans="1:18" ht="13.5" customHeight="1">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -9282,7 +8659,7 @@
       <c r="Q393" s="4"/>
       <c r="R393" s="4"/>
     </row>
-    <row r="394" ht="13.5" customHeight="1" spans="1:18">
+    <row r="394" spans="1:18" ht="13.5" customHeight="1">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -9302,7 +8679,7 @@
       <c r="Q394" s="4"/>
       <c r="R394" s="4"/>
     </row>
-    <row r="395" ht="13.5" customHeight="1" spans="1:18">
+    <row r="395" spans="1:18" ht="13.5" customHeight="1">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -9322,7 +8699,7 @@
       <c r="Q395" s="4"/>
       <c r="R395" s="4"/>
     </row>
-    <row r="396" ht="13.5" customHeight="1" spans="1:18">
+    <row r="396" spans="1:18" ht="13.5" customHeight="1">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -9342,7 +8719,7 @@
       <c r="Q396" s="4"/>
       <c r="R396" s="4"/>
     </row>
-    <row r="397" ht="13.5" customHeight="1" spans="1:18">
+    <row r="397" spans="1:18" ht="13.5" customHeight="1">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -9362,7 +8739,7 @@
       <c r="Q397" s="4"/>
       <c r="R397" s="4"/>
     </row>
-    <row r="398" ht="13.5" customHeight="1" spans="1:18">
+    <row r="398" spans="1:18" ht="13.5" customHeight="1">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -9382,7 +8759,7 @@
       <c r="Q398" s="4"/>
       <c r="R398" s="4"/>
     </row>
-    <row r="399" ht="13.5" customHeight="1" spans="1:18">
+    <row r="399" spans="1:18" ht="13.5" customHeight="1">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -9402,7 +8779,7 @@
       <c r="Q399" s="4"/>
       <c r="R399" s="4"/>
     </row>
-    <row r="400" ht="13.5" customHeight="1" spans="1:18">
+    <row r="400" spans="1:18" ht="13.5" customHeight="1">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -9422,7 +8799,7 @@
       <c r="Q400" s="4"/>
       <c r="R400" s="4"/>
     </row>
-    <row r="401" ht="13.5" customHeight="1" spans="1:18">
+    <row r="401" spans="1:18" ht="13.5" customHeight="1">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -9442,7 +8819,7 @@
       <c r="Q401" s="4"/>
       <c r="R401" s="4"/>
     </row>
-    <row r="402" ht="13.5" customHeight="1" spans="1:18">
+    <row r="402" spans="1:18" ht="13.5" customHeight="1">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -9462,7 +8839,7 @@
       <c r="Q402" s="4"/>
       <c r="R402" s="4"/>
     </row>
-    <row r="403" ht="13.5" customHeight="1" spans="1:18">
+    <row r="403" spans="1:18" ht="13.5" customHeight="1">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -9482,7 +8859,7 @@
       <c r="Q403" s="4"/>
       <c r="R403" s="4"/>
     </row>
-    <row r="404" ht="13.5" customHeight="1" spans="1:18">
+    <row r="404" spans="1:18" ht="13.5" customHeight="1">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -9502,7 +8879,7 @@
       <c r="Q404" s="4"/>
       <c r="R404" s="4"/>
     </row>
-    <row r="405" ht="13.5" customHeight="1" spans="1:18">
+    <row r="405" spans="1:18" ht="13.5" customHeight="1">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -9522,7 +8899,7 @@
       <c r="Q405" s="4"/>
       <c r="R405" s="4"/>
     </row>
-    <row r="406" ht="13.5" customHeight="1" spans="1:18">
+    <row r="406" spans="1:18" ht="13.5" customHeight="1">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -9542,7 +8919,7 @@
       <c r="Q406" s="4"/>
       <c r="R406" s="4"/>
     </row>
-    <row r="407" ht="13.5" customHeight="1" spans="1:18">
+    <row r="407" spans="1:18" ht="13.5" customHeight="1">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -9562,7 +8939,7 @@
       <c r="Q407" s="4"/>
       <c r="R407" s="4"/>
     </row>
-    <row r="408" ht="13.5" customHeight="1" spans="1:18">
+    <row r="408" spans="1:18" ht="13.5" customHeight="1">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -9582,7 +8959,7 @@
       <c r="Q408" s="4"/>
       <c r="R408" s="4"/>
     </row>
-    <row r="409" ht="13.5" customHeight="1" spans="1:18">
+    <row r="409" spans="1:18" ht="13.5" customHeight="1">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -9602,7 +8979,7 @@
       <c r="Q409" s="4"/>
       <c r="R409" s="4"/>
     </row>
-    <row r="410" ht="13.5" customHeight="1" spans="1:18">
+    <row r="410" spans="1:18" ht="13.5" customHeight="1">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -9622,7 +8999,7 @@
       <c r="Q410" s="4"/>
       <c r="R410" s="4"/>
     </row>
-    <row r="411" ht="13.5" customHeight="1" spans="1:18">
+    <row r="411" spans="1:18" ht="13.5" customHeight="1">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -9642,7 +9019,7 @@
       <c r="Q411" s="4"/>
       <c r="R411" s="4"/>
     </row>
-    <row r="412" ht="13.5" customHeight="1" spans="1:18">
+    <row r="412" spans="1:18" ht="13.5" customHeight="1">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -9662,7 +9039,7 @@
       <c r="Q412" s="4"/>
       <c r="R412" s="4"/>
     </row>
-    <row r="413" ht="13.5" customHeight="1" spans="1:18">
+    <row r="413" spans="1:18" ht="13.5" customHeight="1">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -9682,7 +9059,7 @@
       <c r="Q413" s="4"/>
       <c r="R413" s="4"/>
     </row>
-    <row r="414" ht="13.5" customHeight="1" spans="1:18">
+    <row r="414" spans="1:18" ht="13.5" customHeight="1">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -9702,7 +9079,7 @@
       <c r="Q414" s="4"/>
       <c r="R414" s="4"/>
     </row>
-    <row r="415" ht="13.5" customHeight="1" spans="1:18">
+    <row r="415" spans="1:18" ht="13.5" customHeight="1">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -9722,7 +9099,7 @@
       <c r="Q415" s="4"/>
       <c r="R415" s="4"/>
     </row>
-    <row r="416" ht="13.5" customHeight="1" spans="1:18">
+    <row r="416" spans="1:18" ht="13.5" customHeight="1">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -9742,7 +9119,7 @@
       <c r="Q416" s="4"/>
       <c r="R416" s="4"/>
     </row>
-    <row r="417" ht="13.5" customHeight="1" spans="1:18">
+    <row r="417" spans="1:18" ht="13.5" customHeight="1">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -9762,7 +9139,7 @@
       <c r="Q417" s="4"/>
       <c r="R417" s="4"/>
     </row>
-    <row r="418" ht="13.5" customHeight="1" spans="1:18">
+    <row r="418" spans="1:18" ht="13.5" customHeight="1">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -9782,7 +9159,7 @@
       <c r="Q418" s="4"/>
       <c r="R418" s="4"/>
     </row>
-    <row r="419" ht="13.5" customHeight="1" spans="1:18">
+    <row r="419" spans="1:18" ht="13.5" customHeight="1">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -9802,7 +9179,7 @@
       <c r="Q419" s="4"/>
       <c r="R419" s="4"/>
     </row>
-    <row r="420" ht="13.5" customHeight="1" spans="1:18">
+    <row r="420" spans="1:18" ht="13.5" customHeight="1">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -9822,7 +9199,7 @@
       <c r="Q420" s="4"/>
       <c r="R420" s="4"/>
     </row>
-    <row r="421" ht="13.5" customHeight="1" spans="1:18">
+    <row r="421" spans="1:18" ht="13.5" customHeight="1">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -9842,7 +9219,7 @@
       <c r="Q421" s="4"/>
       <c r="R421" s="4"/>
     </row>
-    <row r="422" ht="13.5" customHeight="1" spans="1:18">
+    <row r="422" spans="1:18" ht="13.5" customHeight="1">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -9862,7 +9239,7 @@
       <c r="Q422" s="4"/>
       <c r="R422" s="4"/>
     </row>
-    <row r="423" ht="13.5" customHeight="1" spans="1:18">
+    <row r="423" spans="1:18" ht="13.5" customHeight="1">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -9882,7 +9259,7 @@
       <c r="Q423" s="4"/>
       <c r="R423" s="4"/>
     </row>
-    <row r="424" ht="13.5" customHeight="1" spans="1:18">
+    <row r="424" spans="1:18" ht="13.5" customHeight="1">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -9902,7 +9279,7 @@
       <c r="Q424" s="4"/>
       <c r="R424" s="4"/>
     </row>
-    <row r="425" ht="13.5" customHeight="1" spans="1:18">
+    <row r="425" spans="1:18" ht="13.5" customHeight="1">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -9922,7 +9299,7 @@
       <c r="Q425" s="4"/>
       <c r="R425" s="4"/>
     </row>
-    <row r="426" ht="13.5" customHeight="1" spans="1:18">
+    <row r="426" spans="1:18" ht="13.5" customHeight="1">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -9942,7 +9319,7 @@
       <c r="Q426" s="4"/>
       <c r="R426" s="4"/>
     </row>
-    <row r="427" ht="13.5" customHeight="1" spans="1:18">
+    <row r="427" spans="1:18" ht="13.5" customHeight="1">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -9962,7 +9339,7 @@
       <c r="Q427" s="4"/>
       <c r="R427" s="4"/>
     </row>
-    <row r="428" ht="13.5" customHeight="1" spans="1:18">
+    <row r="428" spans="1:18" ht="13.5" customHeight="1">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -9982,7 +9359,7 @@
       <c r="Q428" s="4"/>
       <c r="R428" s="4"/>
     </row>
-    <row r="429" ht="13.5" customHeight="1" spans="1:18">
+    <row r="429" spans="1:18" ht="13.5" customHeight="1">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -10002,7 +9379,7 @@
       <c r="Q429" s="4"/>
       <c r="R429" s="4"/>
     </row>
-    <row r="430" ht="13.5" customHeight="1" spans="1:18">
+    <row r="430" spans="1:18" ht="13.5" customHeight="1">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -10022,7 +9399,7 @@
       <c r="Q430" s="4"/>
       <c r="R430" s="4"/>
     </row>
-    <row r="431" ht="13.5" customHeight="1" spans="1:18">
+    <row r="431" spans="1:18" ht="13.5" customHeight="1">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -10042,7 +9419,7 @@
       <c r="Q431" s="4"/>
       <c r="R431" s="4"/>
     </row>
-    <row r="432" ht="13.5" customHeight="1" spans="1:18">
+    <row r="432" spans="1:18" ht="13.5" customHeight="1">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -10062,7 +9439,7 @@
       <c r="Q432" s="4"/>
       <c r="R432" s="4"/>
     </row>
-    <row r="433" ht="13.5" customHeight="1" spans="1:18">
+    <row r="433" spans="1:18" ht="13.5" customHeight="1">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -10082,7 +9459,7 @@
       <c r="Q433" s="4"/>
       <c r="R433" s="4"/>
     </row>
-    <row r="434" ht="13.5" customHeight="1" spans="1:18">
+    <row r="434" spans="1:18" ht="13.5" customHeight="1">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -10102,7 +9479,7 @@
       <c r="Q434" s="4"/>
       <c r="R434" s="4"/>
     </row>
-    <row r="435" ht="13.5" customHeight="1" spans="1:18">
+    <row r="435" spans="1:18" ht="13.5" customHeight="1">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -10122,7 +9499,7 @@
       <c r="Q435" s="4"/>
       <c r="R435" s="4"/>
     </row>
-    <row r="436" ht="13.5" customHeight="1" spans="1:18">
+    <row r="436" spans="1:18" ht="13.5" customHeight="1">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -10142,7 +9519,7 @@
       <c r="Q436" s="4"/>
       <c r="R436" s="4"/>
     </row>
-    <row r="437" ht="13.5" customHeight="1" spans="1:18">
+    <row r="437" spans="1:18" ht="13.5" customHeight="1">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -10162,7 +9539,7 @@
       <c r="Q437" s="4"/>
       <c r="R437" s="4"/>
     </row>
-    <row r="438" ht="13.5" customHeight="1" spans="1:18">
+    <row r="438" spans="1:18" ht="13.5" customHeight="1">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -10182,7 +9559,7 @@
       <c r="Q438" s="4"/>
       <c r="R438" s="4"/>
     </row>
-    <row r="439" ht="13.5" customHeight="1" spans="1:18">
+    <row r="439" spans="1:18" ht="13.5" customHeight="1">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -10202,7 +9579,7 @@
       <c r="Q439" s="4"/>
       <c r="R439" s="4"/>
     </row>
-    <row r="440" ht="13.5" customHeight="1" spans="1:18">
+    <row r="440" spans="1:18" ht="13.5" customHeight="1">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -10222,7 +9599,7 @@
       <c r="Q440" s="4"/>
       <c r="R440" s="4"/>
     </row>
-    <row r="441" ht="13.5" customHeight="1" spans="1:18">
+    <row r="441" spans="1:18" ht="13.5" customHeight="1">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -10242,7 +9619,7 @@
       <c r="Q441" s="4"/>
       <c r="R441" s="4"/>
     </row>
-    <row r="442" ht="13.5" customHeight="1" spans="1:18">
+    <row r="442" spans="1:18" ht="13.5" customHeight="1">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -10262,7 +9639,7 @@
       <c r="Q442" s="4"/>
       <c r="R442" s="4"/>
     </row>
-    <row r="443" ht="13.5" customHeight="1" spans="1:18">
+    <row r="443" spans="1:18" ht="13.5" customHeight="1">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -10282,7 +9659,7 @@
       <c r="Q443" s="4"/>
       <c r="R443" s="4"/>
     </row>
-    <row r="444" ht="13.5" customHeight="1" spans="1:18">
+    <row r="444" spans="1:18" ht="13.5" customHeight="1">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -10302,7 +9679,7 @@
       <c r="Q444" s="4"/>
       <c r="R444" s="4"/>
     </row>
-    <row r="445" ht="13.5" customHeight="1" spans="1:18">
+    <row r="445" spans="1:18" ht="13.5" customHeight="1">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -10322,7 +9699,7 @@
       <c r="Q445" s="4"/>
       <c r="R445" s="4"/>
     </row>
-    <row r="446" ht="13.5" customHeight="1" spans="1:18">
+    <row r="446" spans="1:18" ht="13.5" customHeight="1">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -10342,7 +9719,7 @@
       <c r="Q446" s="4"/>
       <c r="R446" s="4"/>
     </row>
-    <row r="447" ht="13.5" customHeight="1" spans="1:18">
+    <row r="447" spans="1:18" ht="13.5" customHeight="1">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -10362,7 +9739,7 @@
       <c r="Q447" s="4"/>
       <c r="R447" s="4"/>
     </row>
-    <row r="448" ht="13.5" customHeight="1" spans="1:18">
+    <row r="448" spans="1:18" ht="13.5" customHeight="1">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -10382,7 +9759,7 @@
       <c r="Q448" s="4"/>
       <c r="R448" s="4"/>
     </row>
-    <row r="449" ht="13.5" customHeight="1" spans="1:18">
+    <row r="449" spans="1:18" ht="13.5" customHeight="1">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -10402,7 +9779,7 @@
       <c r="Q449" s="4"/>
       <c r="R449" s="4"/>
     </row>
-    <row r="450" ht="13.5" customHeight="1" spans="1:18">
+    <row r="450" spans="1:18" ht="13.5" customHeight="1">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -10422,7 +9799,7 @@
       <c r="Q450" s="4"/>
       <c r="R450" s="4"/>
     </row>
-    <row r="451" ht="13.5" customHeight="1" spans="1:18">
+    <row r="451" spans="1:18" ht="13.5" customHeight="1">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -10442,7 +9819,7 @@
       <c r="Q451" s="4"/>
       <c r="R451" s="4"/>
     </row>
-    <row r="452" ht="13.5" customHeight="1" spans="1:18">
+    <row r="452" spans="1:18" ht="13.5" customHeight="1">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -10462,7 +9839,7 @@
       <c r="Q452" s="4"/>
       <c r="R452" s="4"/>
     </row>
-    <row r="453" ht="13.5" customHeight="1" spans="1:18">
+    <row r="453" spans="1:18" ht="13.5" customHeight="1">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -10482,7 +9859,7 @@
       <c r="Q453" s="4"/>
       <c r="R453" s="4"/>
     </row>
-    <row r="454" ht="13.5" customHeight="1" spans="1:18">
+    <row r="454" spans="1:18" ht="13.5" customHeight="1">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -10502,7 +9879,7 @@
       <c r="Q454" s="4"/>
       <c r="R454" s="4"/>
     </row>
-    <row r="455" ht="13.5" customHeight="1" spans="1:18">
+    <row r="455" spans="1:18" ht="13.5" customHeight="1">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -10522,7 +9899,7 @@
       <c r="Q455" s="4"/>
       <c r="R455" s="4"/>
     </row>
-    <row r="456" ht="13.5" customHeight="1" spans="1:18">
+    <row r="456" spans="1:18" ht="13.5" customHeight="1">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -10542,7 +9919,7 @@
       <c r="Q456" s="4"/>
       <c r="R456" s="4"/>
     </row>
-    <row r="457" ht="13.5" customHeight="1" spans="1:18">
+    <row r="457" spans="1:18" ht="13.5" customHeight="1">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -10562,7 +9939,7 @@
       <c r="Q457" s="4"/>
       <c r="R457" s="4"/>
     </row>
-    <row r="458" ht="13.5" customHeight="1" spans="1:18">
+    <row r="458" spans="1:18" ht="13.5" customHeight="1">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -10582,7 +9959,7 @@
       <c r="Q458" s="4"/>
       <c r="R458" s="4"/>
     </row>
-    <row r="459" ht="13.5" customHeight="1" spans="1:18">
+    <row r="459" spans="1:18" ht="13.5" customHeight="1">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -10602,7 +9979,7 @@
       <c r="Q459" s="4"/>
       <c r="R459" s="4"/>
     </row>
-    <row r="460" ht="13.5" customHeight="1" spans="1:18">
+    <row r="460" spans="1:18" ht="13.5" customHeight="1">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -10622,7 +9999,7 @@
       <c r="Q460" s="4"/>
       <c r="R460" s="4"/>
     </row>
-    <row r="461" ht="13.5" customHeight="1" spans="1:18">
+    <row r="461" spans="1:18" ht="13.5" customHeight="1">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -10642,7 +10019,7 @@
       <c r="Q461" s="4"/>
       <c r="R461" s="4"/>
     </row>
-    <row r="462" ht="13.5" customHeight="1" spans="1:18">
+    <row r="462" spans="1:18" ht="13.5" customHeight="1">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -10662,7 +10039,7 @@
       <c r="Q462" s="4"/>
       <c r="R462" s="4"/>
     </row>
-    <row r="463" ht="13.5" customHeight="1" spans="1:18">
+    <row r="463" spans="1:18" ht="13.5" customHeight="1">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -10682,7 +10059,7 @@
       <c r="Q463" s="4"/>
       <c r="R463" s="4"/>
     </row>
-    <row r="464" ht="13.5" customHeight="1" spans="1:18">
+    <row r="464" spans="1:18" ht="13.5" customHeight="1">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -10702,7 +10079,7 @@
       <c r="Q464" s="4"/>
       <c r="R464" s="4"/>
     </row>
-    <row r="465" ht="13.5" customHeight="1" spans="1:18">
+    <row r="465" spans="1:18" ht="13.5" customHeight="1">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -10722,7 +10099,7 @@
       <c r="Q465" s="4"/>
       <c r="R465" s="4"/>
     </row>
-    <row r="466" ht="13.5" customHeight="1" spans="1:18">
+    <row r="466" spans="1:18" ht="13.5" customHeight="1">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -10742,7 +10119,7 @@
       <c r="Q466" s="4"/>
       <c r="R466" s="4"/>
     </row>
-    <row r="467" ht="13.5" customHeight="1" spans="1:18">
+    <row r="467" spans="1:18" ht="13.5" customHeight="1">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -10762,7 +10139,7 @@
       <c r="Q467" s="4"/>
       <c r="R467" s="4"/>
     </row>
-    <row r="468" ht="13.5" customHeight="1" spans="1:18">
+    <row r="468" spans="1:18" ht="13.5" customHeight="1">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -10782,7 +10159,7 @@
       <c r="Q468" s="4"/>
       <c r="R468" s="4"/>
     </row>
-    <row r="469" ht="13.5" customHeight="1" spans="1:18">
+    <row r="469" spans="1:18" ht="13.5" customHeight="1">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -10802,7 +10179,7 @@
       <c r="Q469" s="4"/>
       <c r="R469" s="4"/>
     </row>
-    <row r="470" ht="13.5" customHeight="1" spans="1:18">
+    <row r="470" spans="1:18" ht="13.5" customHeight="1">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -10822,7 +10199,7 @@
       <c r="Q470" s="4"/>
       <c r="R470" s="4"/>
     </row>
-    <row r="471" ht="13.5" customHeight="1" spans="1:18">
+    <row r="471" spans="1:18" ht="13.5" customHeight="1">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -10842,7 +10219,7 @@
       <c r="Q471" s="4"/>
       <c r="R471" s="4"/>
     </row>
-    <row r="472" ht="13.5" customHeight="1" spans="1:18">
+    <row r="472" spans="1:18" ht="13.5" customHeight="1">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -10862,7 +10239,7 @@
       <c r="Q472" s="4"/>
       <c r="R472" s="4"/>
     </row>
-    <row r="473" ht="13.5" customHeight="1" spans="1:18">
+    <row r="473" spans="1:18" ht="13.5" customHeight="1">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -10882,7 +10259,7 @@
       <c r="Q473" s="4"/>
       <c r="R473" s="4"/>
     </row>
-    <row r="474" ht="13.5" customHeight="1" spans="1:18">
+    <row r="474" spans="1:18" ht="13.5" customHeight="1">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -10902,7 +10279,7 @@
       <c r="Q474" s="4"/>
       <c r="R474" s="4"/>
     </row>
-    <row r="475" ht="13.5" customHeight="1" spans="1:18">
+    <row r="475" spans="1:18" ht="13.5" customHeight="1">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -10922,7 +10299,7 @@
       <c r="Q475" s="4"/>
       <c r="R475" s="4"/>
     </row>
-    <row r="476" ht="13.5" customHeight="1" spans="1:18">
+    <row r="476" spans="1:18" ht="13.5" customHeight="1">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -10942,7 +10319,7 @@
       <c r="Q476" s="4"/>
       <c r="R476" s="4"/>
     </row>
-    <row r="477" ht="13.5" customHeight="1" spans="1:18">
+    <row r="477" spans="1:18" ht="13.5" customHeight="1">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -10962,7 +10339,7 @@
       <c r="Q477" s="4"/>
       <c r="R477" s="4"/>
     </row>
-    <row r="478" ht="13.5" customHeight="1" spans="1:18">
+    <row r="478" spans="1:18" ht="13.5" customHeight="1">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -10982,7 +10359,7 @@
       <c r="Q478" s="4"/>
       <c r="R478" s="4"/>
     </row>
-    <row r="479" ht="13.5" customHeight="1" spans="1:18">
+    <row r="479" spans="1:18" ht="13.5" customHeight="1">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -11002,7 +10379,7 @@
       <c r="Q479" s="4"/>
       <c r="R479" s="4"/>
     </row>
-    <row r="480" ht="13.5" customHeight="1" spans="1:18">
+    <row r="480" spans="1:18" ht="13.5" customHeight="1">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -11022,7 +10399,7 @@
       <c r="Q480" s="4"/>
       <c r="R480" s="4"/>
     </row>
-    <row r="481" ht="13.5" customHeight="1" spans="1:18">
+    <row r="481" spans="1:18" ht="13.5" customHeight="1">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -11042,7 +10419,7 @@
       <c r="Q481" s="4"/>
       <c r="R481" s="4"/>
     </row>
-    <row r="482" ht="13.5" customHeight="1" spans="1:18">
+    <row r="482" spans="1:18" ht="13.5" customHeight="1">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -11062,7 +10439,7 @@
       <c r="Q482" s="4"/>
       <c r="R482" s="4"/>
     </row>
-    <row r="483" ht="13.5" customHeight="1" spans="1:18">
+    <row r="483" spans="1:18" ht="13.5" customHeight="1">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -11082,7 +10459,7 @@
       <c r="Q483" s="4"/>
       <c r="R483" s="4"/>
     </row>
-    <row r="484" ht="13.5" customHeight="1" spans="1:18">
+    <row r="484" spans="1:18" ht="13.5" customHeight="1">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -11102,7 +10479,7 @@
       <c r="Q484" s="4"/>
       <c r="R484" s="4"/>
     </row>
-    <row r="485" ht="13.5" customHeight="1" spans="1:18">
+    <row r="485" spans="1:18" ht="13.5" customHeight="1">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -11122,7 +10499,7 @@
       <c r="Q485" s="4"/>
       <c r="R485" s="4"/>
     </row>
-    <row r="486" ht="13.5" customHeight="1" spans="1:18">
+    <row r="486" spans="1:18" ht="13.5" customHeight="1">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -11142,7 +10519,7 @@
       <c r="Q486" s="4"/>
       <c r="R486" s="4"/>
     </row>
-    <row r="487" ht="13.5" customHeight="1" spans="1:18">
+    <row r="487" spans="1:18" ht="13.5" customHeight="1">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -11162,7 +10539,7 @@
       <c r="Q487" s="4"/>
       <c r="R487" s="4"/>
     </row>
-    <row r="488" ht="13.5" customHeight="1" spans="1:18">
+    <row r="488" spans="1:18" ht="13.5" customHeight="1">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -11182,7 +10559,7 @@
       <c r="Q488" s="4"/>
       <c r="R488" s="4"/>
     </row>
-    <row r="489" ht="13.5" customHeight="1" spans="1:18">
+    <row r="489" spans="1:18" ht="13.5" customHeight="1">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -11202,7 +10579,7 @@
       <c r="Q489" s="4"/>
       <c r="R489" s="4"/>
     </row>
-    <row r="490" ht="13.5" customHeight="1" spans="1:18">
+    <row r="490" spans="1:18" ht="13.5" customHeight="1">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -11222,7 +10599,7 @@
       <c r="Q490" s="4"/>
       <c r="R490" s="4"/>
     </row>
-    <row r="491" ht="13.5" customHeight="1" spans="1:18">
+    <row r="491" spans="1:18" ht="13.5" customHeight="1">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -11242,7 +10619,7 @@
       <c r="Q491" s="4"/>
       <c r="R491" s="4"/>
     </row>
-    <row r="492" ht="13.5" customHeight="1" spans="1:18">
+    <row r="492" spans="1:18" ht="13.5" customHeight="1">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -11262,7 +10639,7 @@
       <c r="Q492" s="4"/>
       <c r="R492" s="4"/>
     </row>
-    <row r="493" ht="13.5" customHeight="1" spans="1:18">
+    <row r="493" spans="1:18" ht="13.5" customHeight="1">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -11282,7 +10659,7 @@
       <c r="Q493" s="4"/>
       <c r="R493" s="4"/>
     </row>
-    <row r="494" ht="13.5" customHeight="1" spans="1:18">
+    <row r="494" spans="1:18" ht="13.5" customHeight="1">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -11302,7 +10679,7 @@
       <c r="Q494" s="4"/>
       <c r="R494" s="4"/>
     </row>
-    <row r="495" ht="13.5" customHeight="1" spans="1:18">
+    <row r="495" spans="1:18" ht="13.5" customHeight="1">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -11322,7 +10699,7 @@
       <c r="Q495" s="4"/>
       <c r="R495" s="4"/>
     </row>
-    <row r="496" ht="13.5" customHeight="1" spans="1:18">
+    <row r="496" spans="1:18" ht="13.5" customHeight="1">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -11342,7 +10719,7 @@
       <c r="Q496" s="4"/>
       <c r="R496" s="4"/>
     </row>
-    <row r="497" ht="13.5" customHeight="1" spans="1:18">
+    <row r="497" spans="1:18" ht="13.5" customHeight="1">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -11362,7 +10739,7 @@
       <c r="Q497" s="4"/>
       <c r="R497" s="4"/>
     </row>
-    <row r="498" ht="13.5" customHeight="1" spans="1:18">
+    <row r="498" spans="1:18" ht="13.5" customHeight="1">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -11382,7 +10759,7 @@
       <c r="Q498" s="4"/>
       <c r="R498" s="4"/>
     </row>
-    <row r="499" ht="13.5" customHeight="1" spans="1:18">
+    <row r="499" spans="1:18" ht="13.5" customHeight="1">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -11402,7 +10779,7 @@
       <c r="Q499" s="4"/>
       <c r="R499" s="4"/>
     </row>
-    <row r="500" ht="13.5" customHeight="1" spans="1:18">
+    <row r="500" spans="1:18" ht="13.5" customHeight="1">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -11422,7 +10799,7 @@
       <c r="Q500" s="4"/>
       <c r="R500" s="4"/>
     </row>
-    <row r="501" ht="13.5" customHeight="1" spans="1:18">
+    <row r="501" spans="1:18" ht="13.5" customHeight="1">
       <c r="A501" s="4"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -11442,7 +10819,7 @@
       <c r="Q501" s="4"/>
       <c r="R501" s="4"/>
     </row>
-    <row r="502" ht="13.5" customHeight="1" spans="1:18">
+    <row r="502" spans="1:18" ht="13.5" customHeight="1">
       <c r="A502" s="4"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -11462,7 +10839,7 @@
       <c r="Q502" s="4"/>
       <c r="R502" s="4"/>
     </row>
-    <row r="503" ht="13.5" customHeight="1" spans="1:18">
+    <row r="503" spans="1:18" ht="13.5" customHeight="1">
       <c r="A503" s="4"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -11482,7 +10859,7 @@
       <c r="Q503" s="4"/>
       <c r="R503" s="4"/>
     </row>
-    <row r="504" ht="13.5" customHeight="1" spans="1:18">
+    <row r="504" spans="1:18" ht="13.5" customHeight="1">
       <c r="A504" s="4"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -11502,7 +10879,7 @@
       <c r="Q504" s="4"/>
       <c r="R504" s="4"/>
     </row>
-    <row r="505" ht="13.5" customHeight="1" spans="1:18">
+    <row r="505" spans="1:18" ht="13.5" customHeight="1">
       <c r="A505" s="4"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -11522,7 +10899,7 @@
       <c r="Q505" s="4"/>
       <c r="R505" s="4"/>
     </row>
-    <row r="506" ht="13.5" customHeight="1" spans="1:18">
+    <row r="506" spans="1:18" ht="13.5" customHeight="1">
       <c r="A506" s="4"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -11542,7 +10919,7 @@
       <c r="Q506" s="4"/>
       <c r="R506" s="4"/>
     </row>
-    <row r="507" ht="13.5" customHeight="1" spans="1:18">
+    <row r="507" spans="1:18" ht="13.5" customHeight="1">
       <c r="A507" s="4"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -11562,7 +10939,7 @@
       <c r="Q507" s="4"/>
       <c r="R507" s="4"/>
     </row>
-    <row r="508" ht="13.5" customHeight="1" spans="1:18">
+    <row r="508" spans="1:18" ht="13.5" customHeight="1">
       <c r="A508" s="4"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -11582,7 +10959,7 @@
       <c r="Q508" s="4"/>
       <c r="R508" s="4"/>
     </row>
-    <row r="509" ht="13.5" customHeight="1" spans="1:18">
+    <row r="509" spans="1:18" ht="13.5" customHeight="1">
       <c r="A509" s="4"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -11602,7 +10979,7 @@
       <c r="Q509" s="4"/>
       <c r="R509" s="4"/>
     </row>
-    <row r="510" ht="13.5" customHeight="1" spans="1:18">
+    <row r="510" spans="1:18" ht="13.5" customHeight="1">
       <c r="A510" s="4"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -11622,7 +10999,7 @@
       <c r="Q510" s="4"/>
       <c r="R510" s="4"/>
     </row>
-    <row r="511" ht="13.5" customHeight="1" spans="1:18">
+    <row r="511" spans="1:18" ht="13.5" customHeight="1">
       <c r="A511" s="4"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -11642,7 +11019,7 @@
       <c r="Q511" s="4"/>
       <c r="R511" s="4"/>
     </row>
-    <row r="512" ht="13.5" customHeight="1" spans="1:18">
+    <row r="512" spans="1:18" ht="13.5" customHeight="1">
       <c r="A512" s="4"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -11662,7 +11039,7 @@
       <c r="Q512" s="4"/>
       <c r="R512" s="4"/>
     </row>
-    <row r="513" ht="13.5" customHeight="1" spans="1:18">
+    <row r="513" spans="1:18" ht="13.5" customHeight="1">
       <c r="A513" s="4"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -11682,7 +11059,7 @@
       <c r="Q513" s="4"/>
       <c r="R513" s="4"/>
     </row>
-    <row r="514" ht="13.5" customHeight="1" spans="1:18">
+    <row r="514" spans="1:18" ht="13.5" customHeight="1">
       <c r="A514" s="4"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -11702,7 +11079,7 @@
       <c r="Q514" s="4"/>
       <c r="R514" s="4"/>
     </row>
-    <row r="515" ht="13.5" customHeight="1" spans="1:18">
+    <row r="515" spans="1:18" ht="13.5" customHeight="1">
       <c r="A515" s="4"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -11722,7 +11099,7 @@
       <c r="Q515" s="4"/>
       <c r="R515" s="4"/>
     </row>
-    <row r="516" ht="13.5" customHeight="1" spans="1:18">
+    <row r="516" spans="1:18" ht="13.5" customHeight="1">
       <c r="A516" s="4"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -11742,7 +11119,7 @@
       <c r="Q516" s="4"/>
       <c r="R516" s="4"/>
     </row>
-    <row r="517" ht="13.5" customHeight="1" spans="1:18">
+    <row r="517" spans="1:18" ht="13.5" customHeight="1">
       <c r="A517" s="4"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -11762,7 +11139,7 @@
       <c r="Q517" s="4"/>
       <c r="R517" s="4"/>
     </row>
-    <row r="518" ht="13.5" customHeight="1" spans="1:18">
+    <row r="518" spans="1:18" ht="13.5" customHeight="1">
       <c r="A518" s="4"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -11782,7 +11159,7 @@
       <c r="Q518" s="4"/>
       <c r="R518" s="4"/>
     </row>
-    <row r="519" ht="13.5" customHeight="1" spans="1:18">
+    <row r="519" spans="1:18" ht="13.5" customHeight="1">
       <c r="A519" s="4"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -11802,7 +11179,7 @@
       <c r="Q519" s="4"/>
       <c r="R519" s="4"/>
     </row>
-    <row r="520" ht="13.5" customHeight="1" spans="1:18">
+    <row r="520" spans="1:18" ht="13.5" customHeight="1">
       <c r="A520" s="4"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -11822,7 +11199,7 @@
       <c r="Q520" s="4"/>
       <c r="R520" s="4"/>
     </row>
-    <row r="521" ht="13.5" customHeight="1" spans="1:18">
+    <row r="521" spans="1:18" ht="13.5" customHeight="1">
       <c r="A521" s="4"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -11842,7 +11219,7 @@
       <c r="Q521" s="4"/>
       <c r="R521" s="4"/>
     </row>
-    <row r="522" ht="13.5" customHeight="1" spans="1:18">
+    <row r="522" spans="1:18" ht="13.5" customHeight="1">
       <c r="A522" s="4"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -11862,7 +11239,7 @@
       <c r="Q522" s="4"/>
       <c r="R522" s="4"/>
     </row>
-    <row r="523" ht="13.5" customHeight="1" spans="1:18">
+    <row r="523" spans="1:18" ht="13.5" customHeight="1">
       <c r="A523" s="4"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -11882,7 +11259,7 @@
       <c r="Q523" s="4"/>
       <c r="R523" s="4"/>
     </row>
-    <row r="524" ht="13.5" customHeight="1" spans="1:18">
+    <row r="524" spans="1:18" ht="13.5" customHeight="1">
       <c r="A524" s="4"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -11902,7 +11279,7 @@
       <c r="Q524" s="4"/>
       <c r="R524" s="4"/>
     </row>
-    <row r="525" ht="13.5" customHeight="1" spans="1:18">
+    <row r="525" spans="1:18" ht="13.5" customHeight="1">
       <c r="A525" s="4"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -11922,7 +11299,7 @@
       <c r="Q525" s="4"/>
       <c r="R525" s="4"/>
     </row>
-    <row r="526" ht="13.5" customHeight="1" spans="1:18">
+    <row r="526" spans="1:18" ht="13.5" customHeight="1">
       <c r="A526" s="4"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -11942,7 +11319,7 @@
       <c r="Q526" s="4"/>
       <c r="R526" s="4"/>
     </row>
-    <row r="527" ht="13.5" customHeight="1" spans="1:18">
+    <row r="527" spans="1:18" ht="13.5" customHeight="1">
       <c r="A527" s="4"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -11962,7 +11339,7 @@
       <c r="Q527" s="4"/>
       <c r="R527" s="4"/>
     </row>
-    <row r="528" ht="13.5" customHeight="1" spans="1:18">
+    <row r="528" spans="1:18" ht="13.5" customHeight="1">
       <c r="A528" s="4"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -11982,7 +11359,7 @@
       <c r="Q528" s="4"/>
       <c r="R528" s="4"/>
     </row>
-    <row r="529" ht="13.5" customHeight="1" spans="1:18">
+    <row r="529" spans="1:18" ht="13.5" customHeight="1">
       <c r="A529" s="4"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -12002,7 +11379,7 @@
       <c r="Q529" s="4"/>
       <c r="R529" s="4"/>
     </row>
-    <row r="530" ht="13.5" customHeight="1" spans="1:18">
+    <row r="530" spans="1:18" ht="13.5" customHeight="1">
       <c r="A530" s="4"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -12022,7 +11399,7 @@
       <c r="Q530" s="4"/>
       <c r="R530" s="4"/>
     </row>
-    <row r="531" ht="13.5" customHeight="1" spans="1:18">
+    <row r="531" spans="1:18" ht="13.5" customHeight="1">
       <c r="A531" s="4"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -12042,7 +11419,7 @@
       <c r="Q531" s="4"/>
       <c r="R531" s="4"/>
     </row>
-    <row r="532" ht="13.5" customHeight="1" spans="1:18">
+    <row r="532" spans="1:18" ht="13.5" customHeight="1">
       <c r="A532" s="4"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -12062,7 +11439,7 @@
       <c r="Q532" s="4"/>
       <c r="R532" s="4"/>
     </row>
-    <row r="533" ht="13.5" customHeight="1" spans="1:18">
+    <row r="533" spans="1:18" ht="13.5" customHeight="1">
       <c r="A533" s="4"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -12082,7 +11459,7 @@
       <c r="Q533" s="4"/>
       <c r="R533" s="4"/>
     </row>
-    <row r="534" ht="13.5" customHeight="1" spans="1:18">
+    <row r="534" spans="1:18" ht="13.5" customHeight="1">
       <c r="A534" s="4"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -12102,7 +11479,7 @@
       <c r="Q534" s="4"/>
       <c r="R534" s="4"/>
     </row>
-    <row r="535" ht="13.5" customHeight="1" spans="1:18">
+    <row r="535" spans="1:18" ht="13.5" customHeight="1">
       <c r="A535" s="4"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
@@ -12122,7 +11499,7 @@
       <c r="Q535" s="4"/>
       <c r="R535" s="4"/>
     </row>
-    <row r="536" ht="13.5" customHeight="1" spans="1:18">
+    <row r="536" spans="1:18" ht="13.5" customHeight="1">
       <c r="A536" s="4"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
@@ -12142,7 +11519,7 @@
       <c r="Q536" s="4"/>
       <c r="R536" s="4"/>
     </row>
-    <row r="537" ht="13.5" customHeight="1" spans="1:18">
+    <row r="537" spans="1:18" ht="13.5" customHeight="1">
       <c r="A537" s="4"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
@@ -12162,7 +11539,7 @@
       <c r="Q537" s="4"/>
       <c r="R537" s="4"/>
     </row>
-    <row r="538" ht="13.5" customHeight="1" spans="1:18">
+    <row r="538" spans="1:18" ht="13.5" customHeight="1">
       <c r="A538" s="4"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
@@ -12182,7 +11559,7 @@
       <c r="Q538" s="4"/>
       <c r="R538" s="4"/>
     </row>
-    <row r="539" ht="13.5" customHeight="1" spans="1:18">
+    <row r="539" spans="1:18" ht="13.5" customHeight="1">
       <c r="A539" s="4"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
@@ -12202,7 +11579,7 @@
       <c r="Q539" s="4"/>
       <c r="R539" s="4"/>
     </row>
-    <row r="540" ht="13.5" customHeight="1" spans="1:18">
+    <row r="540" spans="1:18" ht="13.5" customHeight="1">
       <c r="A540" s="4"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
@@ -12222,7 +11599,7 @@
       <c r="Q540" s="4"/>
       <c r="R540" s="4"/>
     </row>
-    <row r="541" ht="13.5" customHeight="1" spans="1:18">
+    <row r="541" spans="1:18" ht="13.5" customHeight="1">
       <c r="A541" s="4"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
@@ -12242,7 +11619,7 @@
       <c r="Q541" s="4"/>
       <c r="R541" s="4"/>
     </row>
-    <row r="542" ht="13.5" customHeight="1" spans="1:18">
+    <row r="542" spans="1:18" ht="13.5" customHeight="1">
       <c r="A542" s="4"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
@@ -12262,7 +11639,7 @@
       <c r="Q542" s="4"/>
       <c r="R542" s="4"/>
     </row>
-    <row r="543" ht="13.5" customHeight="1" spans="1:18">
+    <row r="543" spans="1:18" ht="13.5" customHeight="1">
       <c r="A543" s="4"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
@@ -12282,7 +11659,7 @@
       <c r="Q543" s="4"/>
       <c r="R543" s="4"/>
     </row>
-    <row r="544" ht="13.5" customHeight="1" spans="1:18">
+    <row r="544" spans="1:18" ht="13.5" customHeight="1">
       <c r="A544" s="4"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
@@ -12302,7 +11679,7 @@
       <c r="Q544" s="4"/>
       <c r="R544" s="4"/>
     </row>
-    <row r="545" ht="13.5" customHeight="1" spans="1:18">
+    <row r="545" spans="1:18" ht="13.5" customHeight="1">
       <c r="A545" s="4"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
@@ -12322,7 +11699,7 @@
       <c r="Q545" s="4"/>
       <c r="R545" s="4"/>
     </row>
-    <row r="546" ht="13.5" customHeight="1" spans="1:18">
+    <row r="546" spans="1:18" ht="13.5" customHeight="1">
       <c r="A546" s="4"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -12342,7 +11719,7 @@
       <c r="Q546" s="4"/>
       <c r="R546" s="4"/>
     </row>
-    <row r="547" ht="13.5" customHeight="1" spans="1:18">
+    <row r="547" spans="1:18" ht="13.5" customHeight="1">
       <c r="A547" s="4"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
@@ -12362,7 +11739,7 @@
       <c r="Q547" s="4"/>
       <c r="R547" s="4"/>
     </row>
-    <row r="548" ht="13.5" customHeight="1" spans="1:18">
+    <row r="548" spans="1:18" ht="13.5" customHeight="1">
       <c r="A548" s="4"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
@@ -12382,7 +11759,7 @@
       <c r="Q548" s="4"/>
       <c r="R548" s="4"/>
     </row>
-    <row r="549" ht="13.5" customHeight="1" spans="1:18">
+    <row r="549" spans="1:18" ht="13.5" customHeight="1">
       <c r="A549" s="4"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
@@ -12402,7 +11779,7 @@
       <c r="Q549" s="4"/>
       <c r="R549" s="4"/>
     </row>
-    <row r="550" ht="13.5" customHeight="1" spans="1:18">
+    <row r="550" spans="1:18" ht="13.5" customHeight="1">
       <c r="A550" s="4"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
@@ -12422,7 +11799,7 @@
       <c r="Q550" s="4"/>
       <c r="R550" s="4"/>
     </row>
-    <row r="551" ht="13.5" customHeight="1" spans="1:18">
+    <row r="551" spans="1:18" ht="13.5" customHeight="1">
       <c r="A551" s="4"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
@@ -12442,7 +11819,7 @@
       <c r="Q551" s="4"/>
       <c r="R551" s="4"/>
     </row>
-    <row r="552" ht="13.5" customHeight="1" spans="1:18">
+    <row r="552" spans="1:18" ht="13.5" customHeight="1">
       <c r="A552" s="4"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
@@ -12462,7 +11839,7 @@
       <c r="Q552" s="4"/>
       <c r="R552" s="4"/>
     </row>
-    <row r="553" ht="13.5" customHeight="1" spans="1:18">
+    <row r="553" spans="1:18" ht="13.5" customHeight="1">
       <c r="A553" s="4"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
@@ -12482,7 +11859,7 @@
       <c r="Q553" s="4"/>
       <c r="R553" s="4"/>
     </row>
-    <row r="554" ht="13.5" customHeight="1" spans="1:18">
+    <row r="554" spans="1:18" ht="13.5" customHeight="1">
       <c r="A554" s="4"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
@@ -12502,7 +11879,7 @@
       <c r="Q554" s="4"/>
       <c r="R554" s="4"/>
     </row>
-    <row r="555" ht="13.5" customHeight="1" spans="1:18">
+    <row r="555" spans="1:18" ht="13.5" customHeight="1">
       <c r="A555" s="4"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
@@ -12522,7 +11899,7 @@
       <c r="Q555" s="4"/>
       <c r="R555" s="4"/>
     </row>
-    <row r="556" ht="13.5" customHeight="1" spans="1:18">
+    <row r="556" spans="1:18" ht="13.5" customHeight="1">
       <c r="A556" s="4"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
@@ -12542,7 +11919,7 @@
       <c r="Q556" s="4"/>
       <c r="R556" s="4"/>
     </row>
-    <row r="557" ht="13.5" customHeight="1" spans="1:18">
+    <row r="557" spans="1:18" ht="13.5" customHeight="1">
       <c r="A557" s="4"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
@@ -12562,7 +11939,7 @@
       <c r="Q557" s="4"/>
       <c r="R557" s="4"/>
     </row>
-    <row r="558" ht="13.5" customHeight="1" spans="1:18">
+    <row r="558" spans="1:18" ht="13.5" customHeight="1">
       <c r="A558" s="4"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
@@ -12582,7 +11959,7 @@
       <c r="Q558" s="4"/>
       <c r="R558" s="4"/>
     </row>
-    <row r="559" ht="13.5" customHeight="1" spans="1:18">
+    <row r="559" spans="1:18" ht="13.5" customHeight="1">
       <c r="A559" s="4"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
@@ -12602,7 +11979,7 @@
       <c r="Q559" s="4"/>
       <c r="R559" s="4"/>
     </row>
-    <row r="560" ht="13.5" customHeight="1" spans="1:18">
+    <row r="560" spans="1:18" ht="13.5" customHeight="1">
       <c r="A560" s="4"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
@@ -12622,7 +11999,7 @@
       <c r="Q560" s="4"/>
       <c r="R560" s="4"/>
     </row>
-    <row r="561" ht="13.5" customHeight="1" spans="1:18">
+    <row r="561" spans="1:18" ht="13.5" customHeight="1">
       <c r="A561" s="4"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
@@ -12642,7 +12019,7 @@
       <c r="Q561" s="4"/>
       <c r="R561" s="4"/>
     </row>
-    <row r="562" ht="13.5" customHeight="1" spans="1:18">
+    <row r="562" spans="1:18" ht="13.5" customHeight="1">
       <c r="A562" s="4"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -12662,7 +12039,7 @@
       <c r="Q562" s="4"/>
       <c r="R562" s="4"/>
     </row>
-    <row r="563" ht="13.5" customHeight="1" spans="1:18">
+    <row r="563" spans="1:18" ht="13.5" customHeight="1">
       <c r="A563" s="4"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
@@ -12682,7 +12059,7 @@
       <c r="Q563" s="4"/>
       <c r="R563" s="4"/>
     </row>
-    <row r="564" ht="13.5" customHeight="1" spans="1:18">
+    <row r="564" spans="1:18" ht="13.5" customHeight="1">
       <c r="A564" s="4"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
@@ -12702,7 +12079,7 @@
       <c r="Q564" s="4"/>
       <c r="R564" s="4"/>
     </row>
-    <row r="565" ht="13.5" customHeight="1" spans="1:18">
+    <row r="565" spans="1:18" ht="13.5" customHeight="1">
       <c r="A565" s="4"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
@@ -12722,7 +12099,7 @@
       <c r="Q565" s="4"/>
       <c r="R565" s="4"/>
     </row>
-    <row r="566" ht="13.5" customHeight="1" spans="1:18">
+    <row r="566" spans="1:18" ht="13.5" customHeight="1">
       <c r="A566" s="4"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
@@ -12742,7 +12119,7 @@
       <c r="Q566" s="4"/>
       <c r="R566" s="4"/>
     </row>
-    <row r="567" ht="13.5" customHeight="1" spans="1:18">
+    <row r="567" spans="1:18" ht="13.5" customHeight="1">
       <c r="A567" s="4"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
@@ -12762,7 +12139,7 @@
       <c r="Q567" s="4"/>
       <c r="R567" s="4"/>
     </row>
-    <row r="568" ht="13.5" customHeight="1" spans="1:18">
+    <row r="568" spans="1:18" ht="13.5" customHeight="1">
       <c r="A568" s="4"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
@@ -12782,7 +12159,7 @@
       <c r="Q568" s="4"/>
       <c r="R568" s="4"/>
     </row>
-    <row r="569" ht="13.5" customHeight="1" spans="1:18">
+    <row r="569" spans="1:18" ht="13.5" customHeight="1">
       <c r="A569" s="4"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
@@ -12802,7 +12179,7 @@
       <c r="Q569" s="4"/>
       <c r="R569" s="4"/>
     </row>
-    <row r="570" ht="13.5" customHeight="1" spans="1:18">
+    <row r="570" spans="1:18" ht="13.5" customHeight="1">
       <c r="A570" s="4"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
@@ -12822,7 +12199,7 @@
       <c r="Q570" s="4"/>
       <c r="R570" s="4"/>
     </row>
-    <row r="571" ht="13.5" customHeight="1" spans="1:18">
+    <row r="571" spans="1:18" ht="13.5" customHeight="1">
       <c r="A571" s="4"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
@@ -12842,7 +12219,7 @@
       <c r="Q571" s="4"/>
       <c r="R571" s="4"/>
     </row>
-    <row r="572" ht="13.5" customHeight="1" spans="1:18">
+    <row r="572" spans="1:18" ht="13.5" customHeight="1">
       <c r="A572" s="4"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
@@ -12862,7 +12239,7 @@
       <c r="Q572" s="4"/>
       <c r="R572" s="4"/>
     </row>
-    <row r="573" ht="13.5" customHeight="1" spans="1:18">
+    <row r="573" spans="1:18" ht="13.5" customHeight="1">
       <c r="A573" s="4"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
@@ -12882,7 +12259,7 @@
       <c r="Q573" s="4"/>
       <c r="R573" s="4"/>
     </row>
-    <row r="574" ht="13.5" customHeight="1" spans="1:18">
+    <row r="574" spans="1:18" ht="13.5" customHeight="1">
       <c r="A574" s="4"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
@@ -12902,7 +12279,7 @@
       <c r="Q574" s="4"/>
       <c r="R574" s="4"/>
     </row>
-    <row r="575" ht="13.5" customHeight="1" spans="1:18">
+    <row r="575" spans="1:18" ht="13.5" customHeight="1">
       <c r="A575" s="4"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
@@ -12922,7 +12299,7 @@
       <c r="Q575" s="4"/>
       <c r="R575" s="4"/>
     </row>
-    <row r="576" ht="13.5" customHeight="1" spans="1:18">
+    <row r="576" spans="1:18" ht="13.5" customHeight="1">
       <c r="A576" s="4"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
@@ -12942,7 +12319,7 @@
       <c r="Q576" s="4"/>
       <c r="R576" s="4"/>
     </row>
-    <row r="577" ht="13.5" customHeight="1" spans="1:18">
+    <row r="577" spans="1:18" ht="13.5" customHeight="1">
       <c r="A577" s="4"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
@@ -12962,7 +12339,7 @@
       <c r="Q577" s="4"/>
       <c r="R577" s="4"/>
     </row>
-    <row r="578" ht="13.5" customHeight="1" spans="1:18">
+    <row r="578" spans="1:18" ht="13.5" customHeight="1">
       <c r="A578" s="4"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
@@ -12982,7 +12359,7 @@
       <c r="Q578" s="4"/>
       <c r="R578" s="4"/>
     </row>
-    <row r="579" ht="13.5" customHeight="1" spans="1:18">
+    <row r="579" spans="1:18" ht="13.5" customHeight="1">
       <c r="A579" s="4"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
@@ -13002,7 +12379,7 @@
       <c r="Q579" s="4"/>
       <c r="R579" s="4"/>
     </row>
-    <row r="580" ht="13.5" customHeight="1" spans="1:18">
+    <row r="580" spans="1:18" ht="13.5" customHeight="1">
       <c r="A580" s="4"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
@@ -13022,7 +12399,7 @@
       <c r="Q580" s="4"/>
       <c r="R580" s="4"/>
     </row>
-    <row r="581" ht="13.5" customHeight="1" spans="1:18">
+    <row r="581" spans="1:18" ht="13.5" customHeight="1">
       <c r="A581" s="4"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
@@ -13042,7 +12419,7 @@
       <c r="Q581" s="4"/>
       <c r="R581" s="4"/>
     </row>
-    <row r="582" ht="13.5" customHeight="1" spans="1:18">
+    <row r="582" spans="1:18" ht="13.5" customHeight="1">
       <c r="A582" s="4"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
@@ -13062,7 +12439,7 @@
       <c r="Q582" s="4"/>
       <c r="R582" s="4"/>
     </row>
-    <row r="583" ht="13.5" customHeight="1" spans="1:18">
+    <row r="583" spans="1:18" ht="13.5" customHeight="1">
       <c r="A583" s="4"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
@@ -13082,7 +12459,7 @@
       <c r="Q583" s="4"/>
       <c r="R583" s="4"/>
     </row>
-    <row r="584" ht="13.5" customHeight="1" spans="1:18">
+    <row r="584" spans="1:18" ht="13.5" customHeight="1">
       <c r="A584" s="4"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
@@ -13102,7 +12479,7 @@
       <c r="Q584" s="4"/>
       <c r="R584" s="4"/>
     </row>
-    <row r="585" ht="13.5" customHeight="1" spans="1:18">
+    <row r="585" spans="1:18" ht="13.5" customHeight="1">
       <c r="A585" s="4"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
@@ -13122,7 +12499,7 @@
       <c r="Q585" s="4"/>
       <c r="R585" s="4"/>
     </row>
-    <row r="586" ht="13.5" customHeight="1" spans="1:18">
+    <row r="586" spans="1:18" ht="13.5" customHeight="1">
       <c r="A586" s="4"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
@@ -13142,7 +12519,7 @@
       <c r="Q586" s="4"/>
       <c r="R586" s="4"/>
     </row>
-    <row r="587" ht="13.5" customHeight="1" spans="1:18">
+    <row r="587" spans="1:18" ht="13.5" customHeight="1">
       <c r="A587" s="4"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
@@ -13162,7 +12539,7 @@
       <c r="Q587" s="4"/>
       <c r="R587" s="4"/>
     </row>
-    <row r="588" ht="13.5" customHeight="1" spans="1:18">
+    <row r="588" spans="1:18" ht="13.5" customHeight="1">
       <c r="A588" s="4"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
@@ -13182,7 +12559,7 @@
       <c r="Q588" s="4"/>
       <c r="R588" s="4"/>
     </row>
-    <row r="589" ht="13.5" customHeight="1" spans="1:18">
+    <row r="589" spans="1:18" ht="13.5" customHeight="1">
       <c r="A589" s="4"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
@@ -13202,7 +12579,7 @@
       <c r="Q589" s="4"/>
       <c r="R589" s="4"/>
     </row>
-    <row r="590" ht="13.5" customHeight="1" spans="1:18">
+    <row r="590" spans="1:18" ht="13.5" customHeight="1">
       <c r="A590" s="4"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
@@ -13222,7 +12599,7 @@
       <c r="Q590" s="4"/>
       <c r="R590" s="4"/>
     </row>
-    <row r="591" ht="13.5" customHeight="1" spans="1:18">
+    <row r="591" spans="1:18" ht="13.5" customHeight="1">
       <c r="A591" s="4"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
@@ -13242,7 +12619,7 @@
       <c r="Q591" s="4"/>
       <c r="R591" s="4"/>
     </row>
-    <row r="592" ht="13.5" customHeight="1" spans="1:18">
+    <row r="592" spans="1:18" ht="13.5" customHeight="1">
       <c r="A592" s="4"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
@@ -13262,7 +12639,7 @@
       <c r="Q592" s="4"/>
       <c r="R592" s="4"/>
     </row>
-    <row r="593" ht="13.5" customHeight="1" spans="1:18">
+    <row r="593" spans="1:18" ht="13.5" customHeight="1">
       <c r="A593" s="4"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
@@ -13282,7 +12659,7 @@
       <c r="Q593" s="4"/>
       <c r="R593" s="4"/>
     </row>
-    <row r="594" ht="13.5" customHeight="1" spans="1:18">
+    <row r="594" spans="1:18" ht="13.5" customHeight="1">
       <c r="A594" s="4"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
@@ -13302,7 +12679,7 @@
       <c r="Q594" s="4"/>
       <c r="R594" s="4"/>
     </row>
-    <row r="595" ht="13.5" customHeight="1" spans="1:18">
+    <row r="595" spans="1:18" ht="13.5" customHeight="1">
       <c r="A595" s="4"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
@@ -13322,7 +12699,7 @@
       <c r="Q595" s="4"/>
       <c r="R595" s="4"/>
     </row>
-    <row r="596" ht="13.5" customHeight="1" spans="1:18">
+    <row r="596" spans="1:18" ht="13.5" customHeight="1">
       <c r="A596" s="4"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
@@ -13342,7 +12719,7 @@
       <c r="Q596" s="4"/>
       <c r="R596" s="4"/>
     </row>
-    <row r="597" ht="13.5" customHeight="1" spans="1:18">
+    <row r="597" spans="1:18" ht="13.5" customHeight="1">
       <c r="A597" s="4"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -13362,7 +12739,7 @@
       <c r="Q597" s="4"/>
       <c r="R597" s="4"/>
     </row>
-    <row r="598" ht="13.5" customHeight="1" spans="1:18">
+    <row r="598" spans="1:18" ht="13.5" customHeight="1">
       <c r="A598" s="4"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
@@ -13382,7 +12759,7 @@
       <c r="Q598" s="4"/>
       <c r="R598" s="4"/>
     </row>
-    <row r="599" ht="13.5" customHeight="1" spans="1:18">
+    <row r="599" spans="1:18" ht="13.5" customHeight="1">
       <c r="A599" s="4"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
@@ -13402,7 +12779,7 @@
       <c r="Q599" s="4"/>
       <c r="R599" s="4"/>
     </row>
-    <row r="600" ht="13.5" customHeight="1" spans="1:18">
+    <row r="600" spans="1:18" ht="13.5" customHeight="1">
       <c r="A600" s="4"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
@@ -13422,7 +12799,7 @@
       <c r="Q600" s="4"/>
       <c r="R600" s="4"/>
     </row>
-    <row r="601" ht="13.5" customHeight="1" spans="1:18">
+    <row r="601" spans="1:18" ht="13.5" customHeight="1">
       <c r="A601" s="4"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
@@ -13442,7 +12819,7 @@
       <c r="Q601" s="4"/>
       <c r="R601" s="4"/>
     </row>
-    <row r="602" ht="13.5" customHeight="1" spans="1:18">
+    <row r="602" spans="1:18" ht="13.5" customHeight="1">
       <c r="A602" s="4"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
@@ -13462,7 +12839,7 @@
       <c r="Q602" s="4"/>
       <c r="R602" s="4"/>
     </row>
-    <row r="603" ht="13.5" customHeight="1" spans="1:18">
+    <row r="603" spans="1:18" ht="13.5" customHeight="1">
       <c r="A603" s="4"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
@@ -13482,7 +12859,7 @@
       <c r="Q603" s="4"/>
       <c r="R603" s="4"/>
     </row>
-    <row r="604" ht="13.5" customHeight="1" spans="1:18">
+    <row r="604" spans="1:18" ht="13.5" customHeight="1">
       <c r="A604" s="4"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
@@ -13502,7 +12879,7 @@
       <c r="Q604" s="4"/>
       <c r="R604" s="4"/>
     </row>
-    <row r="605" ht="13.5" customHeight="1" spans="1:18">
+    <row r="605" spans="1:18" ht="13.5" customHeight="1">
       <c r="A605" s="4"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
@@ -13522,7 +12899,7 @@
       <c r="Q605" s="4"/>
       <c r="R605" s="4"/>
     </row>
-    <row r="606" ht="13.5" customHeight="1" spans="1:18">
+    <row r="606" spans="1:18" ht="13.5" customHeight="1">
       <c r="A606" s="4"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
@@ -13542,7 +12919,7 @@
       <c r="Q606" s="4"/>
       <c r="R606" s="4"/>
     </row>
-    <row r="607" ht="13.5" customHeight="1" spans="1:18">
+    <row r="607" spans="1:18" ht="13.5" customHeight="1">
       <c r="A607" s="4"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
@@ -13562,7 +12939,7 @@
       <c r="Q607" s="4"/>
       <c r="R607" s="4"/>
     </row>
-    <row r="608" ht="13.5" customHeight="1" spans="1:18">
+    <row r="608" spans="1:18" ht="13.5" customHeight="1">
       <c r="A608" s="4"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
@@ -13582,7 +12959,7 @@
       <c r="Q608" s="4"/>
       <c r="R608" s="4"/>
     </row>
-    <row r="609" ht="13.5" customHeight="1" spans="1:18">
+    <row r="609" spans="1:18" ht="13.5" customHeight="1">
       <c r="A609" s="4"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
@@ -13602,7 +12979,7 @@
       <c r="Q609" s="4"/>
       <c r="R609" s="4"/>
     </row>
-    <row r="610" ht="13.5" customHeight="1" spans="1:18">
+    <row r="610" spans="1:18" ht="13.5" customHeight="1">
       <c r="A610" s="4"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
@@ -13622,7 +12999,7 @@
       <c r="Q610" s="4"/>
       <c r="R610" s="4"/>
     </row>
-    <row r="611" ht="13.5" customHeight="1" spans="1:18">
+    <row r="611" spans="1:18" ht="13.5" customHeight="1">
       <c r="A611" s="4"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
@@ -13642,7 +13019,7 @@
       <c r="Q611" s="4"/>
       <c r="R611" s="4"/>
     </row>
-    <row r="612" ht="13.5" customHeight="1" spans="1:18">
+    <row r="612" spans="1:18" ht="13.5" customHeight="1">
       <c r="A612" s="4"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
@@ -13662,7 +13039,7 @@
       <c r="Q612" s="4"/>
       <c r="R612" s="4"/>
     </row>
-    <row r="613" ht="13.5" customHeight="1" spans="1:18">
+    <row r="613" spans="1:18" ht="13.5" customHeight="1">
       <c r="A613" s="4"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
@@ -13682,7 +13059,7 @@
       <c r="Q613" s="4"/>
       <c r="R613" s="4"/>
     </row>
-    <row r="614" ht="13.5" customHeight="1" spans="1:18">
+    <row r="614" spans="1:18" ht="13.5" customHeight="1">
       <c r="A614" s="4"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
@@ -13702,7 +13079,7 @@
       <c r="Q614" s="4"/>
       <c r="R614" s="4"/>
     </row>
-    <row r="615" ht="13.5" customHeight="1" spans="1:18">
+    <row r="615" spans="1:18" ht="13.5" customHeight="1">
       <c r="A615" s="4"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
@@ -13722,7 +13099,7 @@
       <c r="Q615" s="4"/>
       <c r="R615" s="4"/>
     </row>
-    <row r="616" ht="13.5" customHeight="1" spans="1:18">
+    <row r="616" spans="1:18" ht="13.5" customHeight="1">
       <c r="A616" s="4"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
@@ -13742,7 +13119,7 @@
       <c r="Q616" s="4"/>
       <c r="R616" s="4"/>
     </row>
-    <row r="617" ht="13.5" customHeight="1" spans="1:18">
+    <row r="617" spans="1:18" ht="13.5" customHeight="1">
       <c r="A617" s="4"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
@@ -13762,7 +13139,7 @@
       <c r="Q617" s="4"/>
       <c r="R617" s="4"/>
     </row>
-    <row r="618" ht="13.5" customHeight="1" spans="1:18">
+    <row r="618" spans="1:18" ht="13.5" customHeight="1">
       <c r="A618" s="4"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
@@ -13782,7 +13159,7 @@
       <c r="Q618" s="4"/>
       <c r="R618" s="4"/>
     </row>
-    <row r="619" ht="13.5" customHeight="1" spans="1:18">
+    <row r="619" spans="1:18" ht="13.5" customHeight="1">
       <c r="A619" s="4"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
@@ -13802,7 +13179,7 @@
       <c r="Q619" s="4"/>
       <c r="R619" s="4"/>
     </row>
-    <row r="620" ht="13.5" customHeight="1" spans="1:18">
+    <row r="620" spans="1:18" ht="13.5" customHeight="1">
       <c r="A620" s="4"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
@@ -13822,7 +13199,7 @@
       <c r="Q620" s="4"/>
       <c r="R620" s="4"/>
     </row>
-    <row r="621" ht="13.5" customHeight="1" spans="1:18">
+    <row r="621" spans="1:18" ht="13.5" customHeight="1">
       <c r="A621" s="4"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
@@ -13842,7 +13219,7 @@
       <c r="Q621" s="4"/>
       <c r="R621" s="4"/>
     </row>
-    <row r="622" ht="13.5" customHeight="1" spans="1:18">
+    <row r="622" spans="1:18" ht="13.5" customHeight="1">
       <c r="A622" s="4"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
@@ -13862,7 +13239,7 @@
       <c r="Q622" s="4"/>
       <c r="R622" s="4"/>
     </row>
-    <row r="623" ht="13.5" customHeight="1" spans="1:18">
+    <row r="623" spans="1:18" ht="13.5" customHeight="1">
       <c r="A623" s="4"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
@@ -13882,7 +13259,7 @@
       <c r="Q623" s="4"/>
       <c r="R623" s="4"/>
     </row>
-    <row r="624" ht="13.5" customHeight="1" spans="1:18">
+    <row r="624" spans="1:18" ht="13.5" customHeight="1">
       <c r="A624" s="4"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
@@ -13902,7 +13279,7 @@
       <c r="Q624" s="4"/>
       <c r="R624" s="4"/>
     </row>
-    <row r="625" ht="13.5" customHeight="1" spans="1:18">
+    <row r="625" spans="1:18" ht="13.5" customHeight="1">
       <c r="A625" s="4"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
@@ -13922,7 +13299,7 @@
       <c r="Q625" s="4"/>
       <c r="R625" s="4"/>
     </row>
-    <row r="626" ht="13.5" customHeight="1" spans="1:18">
+    <row r="626" spans="1:18" ht="13.5" customHeight="1">
       <c r="A626" s="4"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
@@ -13942,7 +13319,7 @@
       <c r="Q626" s="4"/>
       <c r="R626" s="4"/>
     </row>
-    <row r="627" ht="13.5" customHeight="1" spans="1:18">
+    <row r="627" spans="1:18" ht="13.5" customHeight="1">
       <c r="A627" s="4"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
@@ -13962,7 +13339,7 @@
       <c r="Q627" s="4"/>
       <c r="R627" s="4"/>
     </row>
-    <row r="628" ht="13.5" customHeight="1" spans="1:18">
+    <row r="628" spans="1:18" ht="13.5" customHeight="1">
       <c r="A628" s="4"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
@@ -13982,7 +13359,7 @@
       <c r="Q628" s="4"/>
       <c r="R628" s="4"/>
     </row>
-    <row r="629" ht="13.5" customHeight="1" spans="1:18">
+    <row r="629" spans="1:18" ht="13.5" customHeight="1">
       <c r="A629" s="4"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
@@ -14002,7 +13379,7 @@
       <c r="Q629" s="4"/>
       <c r="R629" s="4"/>
     </row>
-    <row r="630" ht="13.5" customHeight="1" spans="1:18">
+    <row r="630" spans="1:18" ht="13.5" customHeight="1">
       <c r="A630" s="4"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
@@ -14022,7 +13399,7 @@
       <c r="Q630" s="4"/>
       <c r="R630" s="4"/>
     </row>
-    <row r="631" ht="13.5" customHeight="1" spans="1:18">
+    <row r="631" spans="1:18" ht="13.5" customHeight="1">
       <c r="A631" s="4"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
@@ -14042,7 +13419,7 @@
       <c r="Q631" s="4"/>
       <c r="R631" s="4"/>
     </row>
-    <row r="632" ht="13.5" customHeight="1" spans="1:18">
+    <row r="632" spans="1:18" ht="13.5" customHeight="1">
       <c r="A632" s="4"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
@@ -14062,7 +13439,7 @@
       <c r="Q632" s="4"/>
       <c r="R632" s="4"/>
     </row>
-    <row r="633" ht="13.5" customHeight="1" spans="1:18">
+    <row r="633" spans="1:18" ht="13.5" customHeight="1">
       <c r="A633" s="4"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
@@ -14082,7 +13459,7 @@
       <c r="Q633" s="4"/>
       <c r="R633" s="4"/>
     </row>
-    <row r="634" ht="13.5" customHeight="1" spans="1:18">
+    <row r="634" spans="1:18" ht="13.5" customHeight="1">
       <c r="A634" s="4"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
@@ -14102,7 +13479,7 @@
       <c r="Q634" s="4"/>
       <c r="R634" s="4"/>
     </row>
-    <row r="635" ht="13.5" customHeight="1" spans="1:18">
+    <row r="635" spans="1:18" ht="13.5" customHeight="1">
       <c r="A635" s="4"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
@@ -14122,7 +13499,7 @@
       <c r="Q635" s="4"/>
       <c r="R635" s="4"/>
     </row>
-    <row r="636" ht="13.5" customHeight="1" spans="1:18">
+    <row r="636" spans="1:18" ht="13.5" customHeight="1">
       <c r="A636" s="4"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
@@ -14142,7 +13519,7 @@
       <c r="Q636" s="4"/>
       <c r="R636" s="4"/>
     </row>
-    <row r="637" ht="13.5" customHeight="1" spans="1:18">
+    <row r="637" spans="1:18" ht="13.5" customHeight="1">
       <c r="A637" s="4"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
@@ -14162,7 +13539,7 @@
       <c r="Q637" s="4"/>
       <c r="R637" s="4"/>
     </row>
-    <row r="638" ht="13.5" customHeight="1" spans="1:18">
+    <row r="638" spans="1:18" ht="13.5" customHeight="1">
       <c r="A638" s="4"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
@@ -14182,7 +13559,7 @@
       <c r="Q638" s="4"/>
       <c r="R638" s="4"/>
     </row>
-    <row r="639" ht="13.5" customHeight="1" spans="1:18">
+    <row r="639" spans="1:18" ht="13.5" customHeight="1">
       <c r="A639" s="4"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
@@ -14202,7 +13579,7 @@
       <c r="Q639" s="4"/>
       <c r="R639" s="4"/>
     </row>
-    <row r="640" ht="13.5" customHeight="1" spans="1:18">
+    <row r="640" spans="1:18" ht="13.5" customHeight="1">
       <c r="A640" s="4"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
@@ -14222,7 +13599,7 @@
       <c r="Q640" s="4"/>
       <c r="R640" s="4"/>
     </row>
-    <row r="641" ht="13.5" customHeight="1" spans="1:18">
+    <row r="641" spans="1:18" ht="13.5" customHeight="1">
       <c r="A641" s="4"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
@@ -14242,7 +13619,7 @@
       <c r="Q641" s="4"/>
       <c r="R641" s="4"/>
     </row>
-    <row r="642" ht="13.5" customHeight="1" spans="1:18">
+    <row r="642" spans="1:18" ht="13.5" customHeight="1">
       <c r="A642" s="4"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
@@ -14262,7 +13639,7 @@
       <c r="Q642" s="4"/>
       <c r="R642" s="4"/>
     </row>
-    <row r="643" ht="13.5" customHeight="1" spans="1:18">
+    <row r="643" spans="1:18" ht="13.5" customHeight="1">
       <c r="A643" s="4"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
@@ -14282,7 +13659,7 @@
       <c r="Q643" s="4"/>
       <c r="R643" s="4"/>
     </row>
-    <row r="644" ht="13.5" customHeight="1" spans="1:18">
+    <row r="644" spans="1:18" ht="13.5" customHeight="1">
       <c r="A644" s="4"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
@@ -14302,7 +13679,7 @@
       <c r="Q644" s="4"/>
       <c r="R644" s="4"/>
     </row>
-    <row r="645" ht="13.5" customHeight="1" spans="1:18">
+    <row r="645" spans="1:18" ht="13.5" customHeight="1">
       <c r="A645" s="4"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
@@ -14322,7 +13699,7 @@
       <c r="Q645" s="4"/>
       <c r="R645" s="4"/>
     </row>
-    <row r="646" ht="13.5" customHeight="1" spans="1:18">
+    <row r="646" spans="1:18" ht="13.5" customHeight="1">
       <c r="A646" s="4"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
@@ -14342,7 +13719,7 @@
       <c r="Q646" s="4"/>
       <c r="R646" s="4"/>
     </row>
-    <row r="647" ht="13.5" customHeight="1" spans="1:18">
+    <row r="647" spans="1:18" ht="13.5" customHeight="1">
       <c r="A647" s="4"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
@@ -14362,7 +13739,7 @@
       <c r="Q647" s="4"/>
       <c r="R647" s="4"/>
     </row>
-    <row r="648" ht="13.5" customHeight="1" spans="1:18">
+    <row r="648" spans="1:18" ht="13.5" customHeight="1">
       <c r="A648" s="4"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
@@ -14382,7 +13759,7 @@
       <c r="Q648" s="4"/>
       <c r="R648" s="4"/>
     </row>
-    <row r="649" ht="13.5" customHeight="1" spans="1:18">
+    <row r="649" spans="1:18" ht="13.5" customHeight="1">
       <c r="A649" s="4"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
@@ -14402,7 +13779,7 @@
       <c r="Q649" s="4"/>
       <c r="R649" s="4"/>
     </row>
-    <row r="650" ht="13.5" customHeight="1" spans="1:18">
+    <row r="650" spans="1:18" ht="13.5" customHeight="1">
       <c r="A650" s="4"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
@@ -14422,7 +13799,7 @@
       <c r="Q650" s="4"/>
       <c r="R650" s="4"/>
     </row>
-    <row r="651" ht="13.5" customHeight="1" spans="1:18">
+    <row r="651" spans="1:18" ht="13.5" customHeight="1">
       <c r="A651" s="4"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
@@ -14442,7 +13819,7 @@
       <c r="Q651" s="4"/>
       <c r="R651" s="4"/>
     </row>
-    <row r="652" ht="13.5" customHeight="1" spans="1:18">
+    <row r="652" spans="1:18" ht="13.5" customHeight="1">
       <c r="A652" s="4"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
@@ -14462,7 +13839,7 @@
       <c r="Q652" s="4"/>
       <c r="R652" s="4"/>
     </row>
-    <row r="653" ht="13.5" customHeight="1" spans="1:18">
+    <row r="653" spans="1:18" ht="13.5" customHeight="1">
       <c r="A653" s="4"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
@@ -14482,7 +13859,7 @@
       <c r="Q653" s="4"/>
       <c r="R653" s="4"/>
     </row>
-    <row r="654" ht="13.5" customHeight="1" spans="1:18">
+    <row r="654" spans="1:18" ht="13.5" customHeight="1">
       <c r="A654" s="4"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
@@ -14502,7 +13879,7 @@
       <c r="Q654" s="4"/>
       <c r="R654" s="4"/>
     </row>
-    <row r="655" ht="13.5" customHeight="1" spans="1:18">
+    <row r="655" spans="1:18" ht="13.5" customHeight="1">
       <c r="A655" s="4"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
@@ -14522,7 +13899,7 @@
       <c r="Q655" s="4"/>
       <c r="R655" s="4"/>
     </row>
-    <row r="656" ht="13.5" customHeight="1" spans="1:18">
+    <row r="656" spans="1:18" ht="13.5" customHeight="1">
       <c r="A656" s="4"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
@@ -14542,7 +13919,7 @@
       <c r="Q656" s="4"/>
       <c r="R656" s="4"/>
     </row>
-    <row r="657" ht="13.5" customHeight="1" spans="1:18">
+    <row r="657" spans="1:18" ht="13.5" customHeight="1">
       <c r="A657" s="4"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
@@ -14562,7 +13939,7 @@
       <c r="Q657" s="4"/>
       <c r="R657" s="4"/>
     </row>
-    <row r="658" ht="13.5" customHeight="1" spans="1:18">
+    <row r="658" spans="1:18" ht="13.5" customHeight="1">
       <c r="A658" s="4"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
@@ -14582,7 +13959,7 @@
       <c r="Q658" s="4"/>
       <c r="R658" s="4"/>
     </row>
-    <row r="659" ht="13.5" customHeight="1" spans="1:18">
+    <row r="659" spans="1:18" ht="13.5" customHeight="1">
       <c r="A659" s="4"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
@@ -14602,7 +13979,7 @@
       <c r="Q659" s="4"/>
       <c r="R659" s="4"/>
     </row>
-    <row r="660" ht="13.5" customHeight="1" spans="1:18">
+    <row r="660" spans="1:18" ht="13.5" customHeight="1">
       <c r="A660" s="4"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
@@ -14622,7 +13999,7 @@
       <c r="Q660" s="4"/>
       <c r="R660" s="4"/>
     </row>
-    <row r="661" ht="13.5" customHeight="1" spans="1:18">
+    <row r="661" spans="1:18" ht="13.5" customHeight="1">
       <c r="A661" s="4"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
@@ -14642,7 +14019,7 @@
       <c r="Q661" s="4"/>
       <c r="R661" s="4"/>
     </row>
-    <row r="662" ht="13.5" customHeight="1" spans="1:18">
+    <row r="662" spans="1:18" ht="13.5" customHeight="1">
       <c r="A662" s="4"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
@@ -14662,7 +14039,7 @@
       <c r="Q662" s="4"/>
       <c r="R662" s="4"/>
     </row>
-    <row r="663" ht="13.5" customHeight="1" spans="1:18">
+    <row r="663" spans="1:18" ht="13.5" customHeight="1">
       <c r="A663" s="4"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
@@ -14682,7 +14059,7 @@
       <c r="Q663" s="4"/>
       <c r="R663" s="4"/>
     </row>
-    <row r="664" ht="13.5" customHeight="1" spans="1:18">
+    <row r="664" spans="1:18" ht="13.5" customHeight="1">
       <c r="A664" s="4"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
@@ -14702,7 +14079,7 @@
       <c r="Q664" s="4"/>
       <c r="R664" s="4"/>
     </row>
-    <row r="665" ht="13.5" customHeight="1" spans="1:18">
+    <row r="665" spans="1:18" ht="13.5" customHeight="1">
       <c r="A665" s="4"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
@@ -14722,7 +14099,7 @@
       <c r="Q665" s="4"/>
       <c r="R665" s="4"/>
     </row>
-    <row r="666" ht="13.5" customHeight="1" spans="1:18">
+    <row r="666" spans="1:18" ht="13.5" customHeight="1">
       <c r="A666" s="4"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
@@ -14742,7 +14119,7 @@
       <c r="Q666" s="4"/>
       <c r="R666" s="4"/>
     </row>
-    <row r="667" ht="13.5" customHeight="1" spans="1:18">
+    <row r="667" spans="1:18" ht="13.5" customHeight="1">
       <c r="A667" s="4"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
@@ -14762,7 +14139,7 @@
       <c r="Q667" s="4"/>
       <c r="R667" s="4"/>
     </row>
-    <row r="668" ht="13.5" customHeight="1" spans="1:18">
+    <row r="668" spans="1:18" ht="13.5" customHeight="1">
       <c r="A668" s="4"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
@@ -14782,7 +14159,7 @@
       <c r="Q668" s="4"/>
       <c r="R668" s="4"/>
     </row>
-    <row r="669" ht="13.5" customHeight="1" spans="1:18">
+    <row r="669" spans="1:18" ht="13.5" customHeight="1">
       <c r="A669" s="4"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
@@ -14802,7 +14179,7 @@
       <c r="Q669" s="4"/>
       <c r="R669" s="4"/>
     </row>
-    <row r="670" ht="13.5" customHeight="1" spans="1:18">
+    <row r="670" spans="1:18" ht="13.5" customHeight="1">
       <c r="A670" s="4"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
@@ -14822,7 +14199,7 @@
       <c r="Q670" s="4"/>
       <c r="R670" s="4"/>
     </row>
-    <row r="671" ht="13.5" customHeight="1" spans="1:18">
+    <row r="671" spans="1:18" ht="13.5" customHeight="1">
       <c r="A671" s="4"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
@@ -14842,7 +14219,7 @@
       <c r="Q671" s="4"/>
       <c r="R671" s="4"/>
     </row>
-    <row r="672" ht="13.5" customHeight="1" spans="1:18">
+    <row r="672" spans="1:18" ht="13.5" customHeight="1">
       <c r="A672" s="4"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
@@ -14862,7 +14239,7 @@
       <c r="Q672" s="4"/>
       <c r="R672" s="4"/>
     </row>
-    <row r="673" ht="13.5" customHeight="1" spans="1:18">
+    <row r="673" spans="1:18" ht="13.5" customHeight="1">
       <c r="A673" s="4"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
@@ -14882,7 +14259,7 @@
       <c r="Q673" s="4"/>
       <c r="R673" s="4"/>
     </row>
-    <row r="674" ht="13.5" customHeight="1" spans="1:18">
+    <row r="674" spans="1:18" ht="13.5" customHeight="1">
       <c r="A674" s="4"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
@@ -14902,7 +14279,7 @@
       <c r="Q674" s="4"/>
       <c r="R674" s="4"/>
     </row>
-    <row r="675" ht="13.5" customHeight="1" spans="1:18">
+    <row r="675" spans="1:18" ht="13.5" customHeight="1">
       <c r="A675" s="4"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
@@ -14922,7 +14299,7 @@
       <c r="Q675" s="4"/>
       <c r="R675" s="4"/>
     </row>
-    <row r="676" ht="13.5" customHeight="1" spans="1:18">
+    <row r="676" spans="1:18" ht="13.5" customHeight="1">
       <c r="A676" s="4"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
@@ -14942,7 +14319,7 @@
       <c r="Q676" s="4"/>
       <c r="R676" s="4"/>
     </row>
-    <row r="677" ht="13.5" customHeight="1" spans="1:18">
+    <row r="677" spans="1:18" ht="13.5" customHeight="1">
       <c r="A677" s="4"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
@@ -14962,7 +14339,7 @@
       <c r="Q677" s="4"/>
       <c r="R677" s="4"/>
     </row>
-    <row r="678" ht="13.5" customHeight="1" spans="1:18">
+    <row r="678" spans="1:18" ht="13.5" customHeight="1">
       <c r="A678" s="4"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
@@ -14982,7 +14359,7 @@
       <c r="Q678" s="4"/>
       <c r="R678" s="4"/>
     </row>
-    <row r="679" ht="13.5" customHeight="1" spans="1:18">
+    <row r="679" spans="1:18" ht="13.5" customHeight="1">
       <c r="A679" s="4"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
@@ -15002,7 +14379,7 @@
       <c r="Q679" s="4"/>
       <c r="R679" s="4"/>
     </row>
-    <row r="680" ht="13.5" customHeight="1" spans="1:18">
+    <row r="680" spans="1:18" ht="13.5" customHeight="1">
       <c r="A680" s="4"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
@@ -15022,7 +14399,7 @@
       <c r="Q680" s="4"/>
       <c r="R680" s="4"/>
     </row>
-    <row r="681" ht="13.5" customHeight="1" spans="1:18">
+    <row r="681" spans="1:18" ht="13.5" customHeight="1">
       <c r="A681" s="4"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
@@ -15042,7 +14419,7 @@
       <c r="Q681" s="4"/>
       <c r="R681" s="4"/>
     </row>
-    <row r="682" ht="13.5" customHeight="1" spans="1:18">
+    <row r="682" spans="1:18" ht="13.5" customHeight="1">
       <c r="A682" s="4"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
@@ -15062,7 +14439,7 @@
       <c r="Q682" s="4"/>
       <c r="R682" s="4"/>
     </row>
-    <row r="683" ht="13.5" customHeight="1" spans="1:18">
+    <row r="683" spans="1:18" ht="13.5" customHeight="1">
       <c r="A683" s="4"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
@@ -15082,7 +14459,7 @@
       <c r="Q683" s="4"/>
       <c r="R683" s="4"/>
     </row>
-    <row r="684" ht="13.5" customHeight="1" spans="1:18">
+    <row r="684" spans="1:18" ht="13.5" customHeight="1">
       <c r="A684" s="4"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
@@ -15102,7 +14479,7 @@
       <c r="Q684" s="4"/>
       <c r="R684" s="4"/>
     </row>
-    <row r="685" ht="13.5" customHeight="1" spans="1:18">
+    <row r="685" spans="1:18" ht="13.5" customHeight="1">
       <c r="A685" s="4"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
@@ -15122,7 +14499,7 @@
       <c r="Q685" s="4"/>
       <c r="R685" s="4"/>
     </row>
-    <row r="686" ht="13.5" customHeight="1" spans="1:18">
+    <row r="686" spans="1:18" ht="13.5" customHeight="1">
       <c r="A686" s="4"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
@@ -15142,7 +14519,7 @@
       <c r="Q686" s="4"/>
       <c r="R686" s="4"/>
     </row>
-    <row r="687" ht="13.5" customHeight="1" spans="1:18">
+    <row r="687" spans="1:18" ht="13.5" customHeight="1">
       <c r="A687" s="4"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
@@ -15162,7 +14539,7 @@
       <c r="Q687" s="4"/>
       <c r="R687" s="4"/>
     </row>
-    <row r="688" ht="13.5" customHeight="1" spans="1:18">
+    <row r="688" spans="1:18" ht="13.5" customHeight="1">
       <c r="A688" s="4"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
@@ -15182,7 +14559,7 @@
       <c r="Q688" s="4"/>
       <c r="R688" s="4"/>
     </row>
-    <row r="689" ht="13.5" customHeight="1" spans="1:18">
+    <row r="689" spans="1:18" ht="13.5" customHeight="1">
       <c r="A689" s="4"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
@@ -15202,7 +14579,7 @@
       <c r="Q689" s="4"/>
       <c r="R689" s="4"/>
     </row>
-    <row r="690" ht="13.5" customHeight="1" spans="1:18">
+    <row r="690" spans="1:18" ht="13.5" customHeight="1">
       <c r="A690" s="4"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
@@ -15222,7 +14599,7 @@
       <c r="Q690" s="4"/>
       <c r="R690" s="4"/>
     </row>
-    <row r="691" ht="13.5" customHeight="1" spans="1:18">
+    <row r="691" spans="1:18" ht="13.5" customHeight="1">
       <c r="A691" s="4"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
@@ -15242,7 +14619,7 @@
       <c r="Q691" s="4"/>
       <c r="R691" s="4"/>
     </row>
-    <row r="692" ht="13.5" customHeight="1" spans="1:18">
+    <row r="692" spans="1:18" ht="13.5" customHeight="1">
       <c r="A692" s="4"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
@@ -15262,7 +14639,7 @@
       <c r="Q692" s="4"/>
       <c r="R692" s="4"/>
     </row>
-    <row r="693" ht="13.5" customHeight="1" spans="1:18">
+    <row r="693" spans="1:18" ht="13.5" customHeight="1">
       <c r="A693" s="4"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
@@ -15282,7 +14659,7 @@
       <c r="Q693" s="4"/>
       <c r="R693" s="4"/>
     </row>
-    <row r="694" ht="13.5" customHeight="1" spans="1:18">
+    <row r="694" spans="1:18" ht="13.5" customHeight="1">
       <c r="A694" s="4"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
@@ -15302,7 +14679,7 @@
       <c r="Q694" s="4"/>
       <c r="R694" s="4"/>
     </row>
-    <row r="695" ht="13.5" customHeight="1" spans="1:18">
+    <row r="695" spans="1:18" ht="13.5" customHeight="1">
       <c r="A695" s="4"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
@@ -15322,7 +14699,7 @@
       <c r="Q695" s="4"/>
       <c r="R695" s="4"/>
     </row>
-    <row r="696" ht="13.5" customHeight="1" spans="1:18">
+    <row r="696" spans="1:18" ht="13.5" customHeight="1">
       <c r="A696" s="4"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
@@ -15342,7 +14719,7 @@
       <c r="Q696" s="4"/>
       <c r="R696" s="4"/>
     </row>
-    <row r="697" ht="13.5" customHeight="1" spans="1:18">
+    <row r="697" spans="1:18" ht="13.5" customHeight="1">
       <c r="A697" s="4"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
@@ -15362,7 +14739,7 @@
       <c r="Q697" s="4"/>
       <c r="R697" s="4"/>
     </row>
-    <row r="698" ht="13.5" customHeight="1" spans="1:18">
+    <row r="698" spans="1:18" ht="13.5" customHeight="1">
       <c r="A698" s="4"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
@@ -15382,7 +14759,7 @@
       <c r="Q698" s="4"/>
       <c r="R698" s="4"/>
     </row>
-    <row r="699" ht="13.5" customHeight="1" spans="1:18">
+    <row r="699" spans="1:18" ht="13.5" customHeight="1">
       <c r="A699" s="4"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
@@ -15402,7 +14779,7 @@
       <c r="Q699" s="4"/>
       <c r="R699" s="4"/>
     </row>
-    <row r="700" ht="13.5" customHeight="1" spans="1:18">
+    <row r="700" spans="1:18" ht="13.5" customHeight="1">
       <c r="A700" s="4"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
@@ -15422,7 +14799,7 @@
       <c r="Q700" s="4"/>
       <c r="R700" s="4"/>
     </row>
-    <row r="701" ht="13.5" customHeight="1" spans="1:18">
+    <row r="701" spans="1:18" ht="13.5" customHeight="1">
       <c r="A701" s="4"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
@@ -15442,7 +14819,7 @@
       <c r="Q701" s="4"/>
       <c r="R701" s="4"/>
     </row>
-    <row r="702" ht="13.5" customHeight="1" spans="1:18">
+    <row r="702" spans="1:18" ht="13.5" customHeight="1">
       <c r="A702" s="4"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
@@ -15462,7 +14839,7 @@
       <c r="Q702" s="4"/>
       <c r="R702" s="4"/>
     </row>
-    <row r="703" ht="13.5" customHeight="1" spans="1:18">
+    <row r="703" spans="1:18" ht="13.5" customHeight="1">
       <c r="A703" s="4"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
@@ -15482,7 +14859,7 @@
       <c r="Q703" s="4"/>
       <c r="R703" s="4"/>
     </row>
-    <row r="704" ht="13.5" customHeight="1" spans="1:18">
+    <row r="704" spans="1:18" ht="13.5" customHeight="1">
       <c r="A704" s="4"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
@@ -15502,7 +14879,7 @@
       <c r="Q704" s="4"/>
       <c r="R704" s="4"/>
     </row>
-    <row r="705" ht="13.5" customHeight="1" spans="1:18">
+    <row r="705" spans="1:18" ht="13.5" customHeight="1">
       <c r="A705" s="4"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
@@ -15522,7 +14899,7 @@
       <c r="Q705" s="4"/>
       <c r="R705" s="4"/>
     </row>
-    <row r="706" ht="13.5" customHeight="1" spans="1:18">
+    <row r="706" spans="1:18" ht="13.5" customHeight="1">
       <c r="A706" s="4"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
@@ -15542,7 +14919,7 @@
       <c r="Q706" s="4"/>
       <c r="R706" s="4"/>
     </row>
-    <row r="707" ht="13.5" customHeight="1" spans="1:18">
+    <row r="707" spans="1:18" ht="13.5" customHeight="1">
       <c r="A707" s="4"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
@@ -15562,7 +14939,7 @@
       <c r="Q707" s="4"/>
       <c r="R707" s="4"/>
     </row>
-    <row r="708" ht="13.5" customHeight="1" spans="1:18">
+    <row r="708" spans="1:18" ht="13.5" customHeight="1">
       <c r="A708" s="4"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
@@ -15582,7 +14959,7 @@
       <c r="Q708" s="4"/>
       <c r="R708" s="4"/>
     </row>
-    <row r="709" ht="13.5" customHeight="1" spans="1:18">
+    <row r="709" spans="1:18" ht="13.5" customHeight="1">
       <c r="A709" s="4"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
@@ -15602,7 +14979,7 @@
       <c r="Q709" s="4"/>
       <c r="R709" s="4"/>
     </row>
-    <row r="710" ht="13.5" customHeight="1" spans="1:18">
+    <row r="710" spans="1:18" ht="13.5" customHeight="1">
       <c r="A710" s="4"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
@@ -15622,7 +14999,7 @@
       <c r="Q710" s="4"/>
       <c r="R710" s="4"/>
     </row>
-    <row r="711" ht="13.5" customHeight="1" spans="1:18">
+    <row r="711" spans="1:18" ht="13.5" customHeight="1">
       <c r="A711" s="4"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
@@ -15642,7 +15019,7 @@
       <c r="Q711" s="4"/>
       <c r="R711" s="4"/>
     </row>
-    <row r="712" ht="13.5" customHeight="1" spans="1:18">
+    <row r="712" spans="1:18" ht="13.5" customHeight="1">
       <c r="A712" s="4"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
@@ -15662,7 +15039,7 @@
       <c r="Q712" s="4"/>
       <c r="R712" s="4"/>
     </row>
-    <row r="713" ht="13.5" customHeight="1" spans="1:18">
+    <row r="713" spans="1:18" ht="13.5" customHeight="1">
       <c r="A713" s="4"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
@@ -15682,7 +15059,7 @@
       <c r="Q713" s="4"/>
       <c r="R713" s="4"/>
     </row>
-    <row r="714" ht="13.5" customHeight="1" spans="1:18">
+    <row r="714" spans="1:18" ht="13.5" customHeight="1">
       <c r="A714" s="4"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
@@ -15702,7 +15079,7 @@
       <c r="Q714" s="4"/>
       <c r="R714" s="4"/>
     </row>
-    <row r="715" ht="13.5" customHeight="1" spans="1:18">
+    <row r="715" spans="1:18" ht="13.5" customHeight="1">
       <c r="A715" s="4"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
@@ -15722,7 +15099,7 @@
       <c r="Q715" s="4"/>
       <c r="R715" s="4"/>
     </row>
-    <row r="716" ht="13.5" customHeight="1" spans="1:18">
+    <row r="716" spans="1:18" ht="13.5" customHeight="1">
       <c r="A716" s="4"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
@@ -15742,7 +15119,7 @@
       <c r="Q716" s="4"/>
       <c r="R716" s="4"/>
     </row>
-    <row r="717" ht="13.5" customHeight="1" spans="1:18">
+    <row r="717" spans="1:18" ht="13.5" customHeight="1">
       <c r="A717" s="4"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
@@ -15762,7 +15139,7 @@
       <c r="Q717" s="4"/>
       <c r="R717" s="4"/>
     </row>
-    <row r="718" ht="13.5" customHeight="1" spans="1:18">
+    <row r="718" spans="1:18" ht="13.5" customHeight="1">
       <c r="A718" s="4"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
@@ -15782,7 +15159,7 @@
       <c r="Q718" s="4"/>
       <c r="R718" s="4"/>
     </row>
-    <row r="719" ht="13.5" customHeight="1" spans="1:18">
+    <row r="719" spans="1:18" ht="13.5" customHeight="1">
       <c r="A719" s="4"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
@@ -15802,7 +15179,7 @@
       <c r="Q719" s="4"/>
       <c r="R719" s="4"/>
     </row>
-    <row r="720" ht="13.5" customHeight="1" spans="1:18">
+    <row r="720" spans="1:18" ht="13.5" customHeight="1">
       <c r="A720" s="4"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
@@ -15822,7 +15199,7 @@
       <c r="Q720" s="4"/>
       <c r="R720" s="4"/>
     </row>
-    <row r="721" ht="13.5" customHeight="1" spans="1:18">
+    <row r="721" spans="1:18" ht="13.5" customHeight="1">
       <c r="A721" s="4"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
@@ -15842,7 +15219,7 @@
       <c r="Q721" s="4"/>
       <c r="R721" s="4"/>
     </row>
-    <row r="722" ht="13.5" customHeight="1" spans="1:18">
+    <row r="722" spans="1:18" ht="13.5" customHeight="1">
       <c r="A722" s="4"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
@@ -15862,7 +15239,7 @@
       <c r="Q722" s="4"/>
       <c r="R722" s="4"/>
     </row>
-    <row r="723" ht="13.5" customHeight="1" spans="1:18">
+    <row r="723" spans="1:18" ht="13.5" customHeight="1">
       <c r="A723" s="4"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
@@ -15882,7 +15259,7 @@
       <c r="Q723" s="4"/>
       <c r="R723" s="4"/>
     </row>
-    <row r="724" ht="13.5" customHeight="1" spans="1:18">
+    <row r="724" spans="1:18" ht="13.5" customHeight="1">
       <c r="A724" s="4"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
@@ -15902,7 +15279,7 @@
       <c r="Q724" s="4"/>
       <c r="R724" s="4"/>
     </row>
-    <row r="725" ht="13.5" customHeight="1" spans="1:18">
+    <row r="725" spans="1:18" ht="13.5" customHeight="1">
       <c r="A725" s="4"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
@@ -15922,7 +15299,7 @@
       <c r="Q725" s="4"/>
       <c r="R725" s="4"/>
     </row>
-    <row r="726" ht="13.5" customHeight="1" spans="1:18">
+    <row r="726" spans="1:18" ht="13.5" customHeight="1">
       <c r="A726" s="4"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
@@ -15942,7 +15319,7 @@
       <c r="Q726" s="4"/>
       <c r="R726" s="4"/>
     </row>
-    <row r="727" ht="13.5" customHeight="1" spans="1:18">
+    <row r="727" spans="1:18" ht="13.5" customHeight="1">
       <c r="A727" s="4"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
@@ -15962,7 +15339,7 @@
       <c r="Q727" s="4"/>
       <c r="R727" s="4"/>
     </row>
-    <row r="728" ht="13.5" customHeight="1" spans="1:18">
+    <row r="728" spans="1:18" ht="13.5" customHeight="1">
       <c r="A728" s="4"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
@@ -15982,7 +15359,7 @@
       <c r="Q728" s="4"/>
       <c r="R728" s="4"/>
     </row>
-    <row r="729" ht="13.5" customHeight="1" spans="1:18">
+    <row r="729" spans="1:18" ht="13.5" customHeight="1">
       <c r="A729" s="4"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
@@ -16002,7 +15379,7 @@
       <c r="Q729" s="4"/>
       <c r="R729" s="4"/>
     </row>
-    <row r="730" ht="13.5" customHeight="1" spans="1:18">
+    <row r="730" spans="1:18" ht="13.5" customHeight="1">
       <c r="A730" s="4"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
@@ -16022,7 +15399,7 @@
       <c r="Q730" s="4"/>
       <c r="R730" s="4"/>
     </row>
-    <row r="731" ht="13.5" customHeight="1" spans="1:18">
+    <row r="731" spans="1:18" ht="13.5" customHeight="1">
       <c r="A731" s="4"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
@@ -16042,7 +15419,7 @@
       <c r="Q731" s="4"/>
       <c r="R731" s="4"/>
     </row>
-    <row r="732" ht="13.5" customHeight="1" spans="1:18">
+    <row r="732" spans="1:18" ht="13.5" customHeight="1">
       <c r="A732" s="4"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
@@ -16062,7 +15439,7 @@
       <c r="Q732" s="4"/>
       <c r="R732" s="4"/>
     </row>
-    <row r="733" ht="13.5" customHeight="1" spans="1:18">
+    <row r="733" spans="1:18" ht="13.5" customHeight="1">
       <c r="A733" s="4"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
@@ -16082,7 +15459,7 @@
       <c r="Q733" s="4"/>
       <c r="R733" s="4"/>
     </row>
-    <row r="734" ht="13.5" customHeight="1" spans="1:18">
+    <row r="734" spans="1:18" ht="13.5" customHeight="1">
       <c r="A734" s="4"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
@@ -16102,7 +15479,7 @@
       <c r="Q734" s="4"/>
       <c r="R734" s="4"/>
     </row>
-    <row r="735" ht="13.5" customHeight="1" spans="1:18">
+    <row r="735" spans="1:18" ht="13.5" customHeight="1">
       <c r="A735" s="4"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
@@ -16122,7 +15499,7 @@
       <c r="Q735" s="4"/>
       <c r="R735" s="4"/>
     </row>
-    <row r="736" ht="13.5" customHeight="1" spans="1:18">
+    <row r="736" spans="1:18" ht="13.5" customHeight="1">
       <c r="A736" s="4"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
@@ -16142,7 +15519,7 @@
       <c r="Q736" s="4"/>
       <c r="R736" s="4"/>
     </row>
-    <row r="737" ht="13.5" customHeight="1" spans="1:18">
+    <row r="737" spans="1:18" ht="13.5" customHeight="1">
       <c r="A737" s="4"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
@@ -16162,7 +15539,7 @@
       <c r="Q737" s="4"/>
       <c r="R737" s="4"/>
     </row>
-    <row r="738" ht="13.5" customHeight="1" spans="1:18">
+    <row r="738" spans="1:18" ht="13.5" customHeight="1">
       <c r="A738" s="4"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
@@ -16182,7 +15559,7 @@
       <c r="Q738" s="4"/>
       <c r="R738" s="4"/>
     </row>
-    <row r="739" ht="13.5" customHeight="1" spans="1:18">
+    <row r="739" spans="1:18" ht="13.5" customHeight="1">
       <c r="A739" s="4"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
@@ -16202,7 +15579,7 @@
       <c r="Q739" s="4"/>
       <c r="R739" s="4"/>
     </row>
-    <row r="740" ht="13.5" customHeight="1" spans="1:18">
+    <row r="740" spans="1:18" ht="13.5" customHeight="1">
       <c r="A740" s="4"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
@@ -16222,7 +15599,7 @@
       <c r="Q740" s="4"/>
       <c r="R740" s="4"/>
     </row>
-    <row r="741" ht="13.5" customHeight="1" spans="1:18">
+    <row r="741" spans="1:18" ht="13.5" customHeight="1">
       <c r="A741" s="4"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
@@ -16242,7 +15619,7 @@
       <c r="Q741" s="4"/>
       <c r="R741" s="4"/>
     </row>
-    <row r="742" ht="13.5" customHeight="1" spans="1:18">
+    <row r="742" spans="1:18" ht="13.5" customHeight="1">
       <c r="A742" s="4"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
@@ -16262,7 +15639,7 @@
       <c r="Q742" s="4"/>
       <c r="R742" s="4"/>
     </row>
-    <row r="743" ht="13.5" customHeight="1" spans="1:18">
+    <row r="743" spans="1:18" ht="13.5" customHeight="1">
       <c r="A743" s="4"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
@@ -16282,7 +15659,7 @@
       <c r="Q743" s="4"/>
       <c r="R743" s="4"/>
     </row>
-    <row r="744" ht="13.5" customHeight="1" spans="1:18">
+    <row r="744" spans="1:18" ht="13.5" customHeight="1">
       <c r="A744" s="4"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
@@ -16302,7 +15679,7 @@
       <c r="Q744" s="4"/>
       <c r="R744" s="4"/>
     </row>
-    <row r="745" ht="13.5" customHeight="1" spans="1:18">
+    <row r="745" spans="1:18" ht="13.5" customHeight="1">
       <c r="A745" s="4"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
@@ -16322,7 +15699,7 @@
       <c r="Q745" s="4"/>
       <c r="R745" s="4"/>
     </row>
-    <row r="746" ht="13.5" customHeight="1" spans="1:18">
+    <row r="746" spans="1:18" ht="13.5" customHeight="1">
       <c r="A746" s="4"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
@@ -16342,7 +15719,7 @@
       <c r="Q746" s="4"/>
       <c r="R746" s="4"/>
     </row>
-    <row r="747" ht="13.5" customHeight="1" spans="1:18">
+    <row r="747" spans="1:18" ht="13.5" customHeight="1">
       <c r="A747" s="4"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
@@ -16362,7 +15739,7 @@
       <c r="Q747" s="4"/>
       <c r="R747" s="4"/>
     </row>
-    <row r="748" ht="13.5" customHeight="1" spans="1:18">
+    <row r="748" spans="1:18" ht="13.5" customHeight="1">
       <c r="A748" s="4"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
@@ -16382,7 +15759,7 @@
       <c r="Q748" s="4"/>
       <c r="R748" s="4"/>
     </row>
-    <row r="749" ht="13.5" customHeight="1" spans="1:18">
+    <row r="749" spans="1:18" ht="13.5" customHeight="1">
       <c r="A749" s="4"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
@@ -16402,7 +15779,7 @@
       <c r="Q749" s="4"/>
       <c r="R749" s="4"/>
     </row>
-    <row r="750" ht="13.5" customHeight="1" spans="1:18">
+    <row r="750" spans="1:18" ht="13.5" customHeight="1">
       <c r="A750" s="4"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
@@ -16422,7 +15799,7 @@
       <c r="Q750" s="4"/>
       <c r="R750" s="4"/>
     </row>
-    <row r="751" ht="13.5" customHeight="1" spans="1:18">
+    <row r="751" spans="1:18" ht="13.5" customHeight="1">
       <c r="A751" s="4"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
@@ -16442,7 +15819,7 @@
       <c r="Q751" s="4"/>
       <c r="R751" s="4"/>
     </row>
-    <row r="752" ht="13.5" customHeight="1" spans="1:18">
+    <row r="752" spans="1:18" ht="13.5" customHeight="1">
       <c r="A752" s="4"/>
       <c r="B752" s="4"/>
       <c r="C752" s="4"/>
@@ -16462,7 +15839,7 @@
       <c r="Q752" s="4"/>
       <c r="R752" s="4"/>
     </row>
-    <row r="753" ht="13.5" customHeight="1" spans="1:18">
+    <row r="753" spans="1:18" ht="13.5" customHeight="1">
       <c r="A753" s="4"/>
       <c r="B753" s="4"/>
       <c r="C753" s="4"/>
@@ -16482,7 +15859,7 @@
       <c r="Q753" s="4"/>
       <c r="R753" s="4"/>
     </row>
-    <row r="754" ht="13.5" customHeight="1" spans="1:18">
+    <row r="754" spans="1:18" ht="13.5" customHeight="1">
       <c r="A754" s="4"/>
       <c r="B754" s="4"/>
       <c r="C754" s="4"/>
@@ -16502,7 +15879,7 @@
       <c r="Q754" s="4"/>
       <c r="R754" s="4"/>
     </row>
-    <row r="755" ht="13.5" customHeight="1" spans="1:18">
+    <row r="755" spans="1:18" ht="13.5" customHeight="1">
       <c r="A755" s="4"/>
       <c r="B755" s="4"/>
       <c r="C755" s="4"/>
@@ -16522,7 +15899,7 @@
       <c r="Q755" s="4"/>
       <c r="R755" s="4"/>
     </row>
-    <row r="756" ht="13.5" customHeight="1" spans="1:18">
+    <row r="756" spans="1:18" ht="13.5" customHeight="1">
       <c r="A756" s="4"/>
       <c r="B756" s="4"/>
       <c r="C756" s="4"/>
@@ -16542,7 +15919,7 @@
       <c r="Q756" s="4"/>
       <c r="R756" s="4"/>
     </row>
-    <row r="757" ht="13.5" customHeight="1" spans="1:18">
+    <row r="757" spans="1:18" ht="13.5" customHeight="1">
       <c r="A757" s="4"/>
       <c r="B757" s="4"/>
       <c r="C757" s="4"/>
@@ -16562,7 +15939,7 @@
       <c r="Q757" s="4"/>
       <c r="R757" s="4"/>
     </row>
-    <row r="758" ht="13.5" customHeight="1" spans="1:18">
+    <row r="758" spans="1:18" ht="13.5" customHeight="1">
       <c r="A758" s="4"/>
       <c r="B758" s="4"/>
       <c r="C758" s="4"/>
@@ -16582,7 +15959,7 @@
       <c r="Q758" s="4"/>
       <c r="R758" s="4"/>
     </row>
-    <row r="759" ht="13.5" customHeight="1" spans="1:18">
+    <row r="759" spans="1:18" ht="13.5" customHeight="1">
       <c r="A759" s="4"/>
       <c r="B759" s="4"/>
       <c r="C759" s="4"/>
@@ -16602,7 +15979,7 @@
       <c r="Q759" s="4"/>
       <c r="R759" s="4"/>
     </row>
-    <row r="760" ht="13.5" customHeight="1" spans="1:18">
+    <row r="760" spans="1:18" ht="13.5" customHeight="1">
       <c r="A760" s="4"/>
       <c r="B760" s="4"/>
       <c r="C760" s="4"/>
@@ -16622,7 +15999,7 @@
       <c r="Q760" s="4"/>
       <c r="R760" s="4"/>
     </row>
-    <row r="761" ht="13.5" customHeight="1" spans="1:18">
+    <row r="761" spans="1:18" ht="13.5" customHeight="1">
       <c r="A761" s="4"/>
       <c r="B761" s="4"/>
       <c r="C761" s="4"/>
@@ -16642,7 +16019,7 @@
       <c r="Q761" s="4"/>
       <c r="R761" s="4"/>
     </row>
-    <row r="762" ht="13.5" customHeight="1" spans="1:18">
+    <row r="762" spans="1:18" ht="13.5" customHeight="1">
       <c r="A762" s="4"/>
       <c r="B762" s="4"/>
       <c r="C762" s="4"/>
@@ -16662,7 +16039,7 @@
       <c r="Q762" s="4"/>
       <c r="R762" s="4"/>
     </row>
-    <row r="763" ht="13.5" customHeight="1" spans="1:18">
+    <row r="763" spans="1:18" ht="13.5" customHeight="1">
       <c r="A763" s="4"/>
       <c r="B763" s="4"/>
       <c r="C763" s="4"/>
@@ -16682,7 +16059,7 @@
       <c r="Q763" s="4"/>
       <c r="R763" s="4"/>
     </row>
-    <row r="764" ht="13.5" customHeight="1" spans="1:18">
+    <row r="764" spans="1:18" ht="13.5" customHeight="1">
       <c r="A764" s="4"/>
       <c r="B764" s="4"/>
       <c r="C764" s="4"/>
@@ -16702,7 +16079,7 @@
       <c r="Q764" s="4"/>
       <c r="R764" s="4"/>
     </row>
-    <row r="765" ht="13.5" customHeight="1" spans="1:18">
+    <row r="765" spans="1:18" ht="13.5" customHeight="1">
       <c r="A765" s="4"/>
       <c r="B765" s="4"/>
       <c r="C765" s="4"/>
@@ -16722,7 +16099,7 @@
       <c r="Q765" s="4"/>
       <c r="R765" s="4"/>
     </row>
-    <row r="766" ht="13.5" customHeight="1" spans="1:18">
+    <row r="766" spans="1:18" ht="13.5" customHeight="1">
       <c r="A766" s="4"/>
       <c r="B766" s="4"/>
       <c r="C766" s="4"/>
@@ -16742,7 +16119,7 @@
       <c r="Q766" s="4"/>
       <c r="R766" s="4"/>
     </row>
-    <row r="767" ht="13.5" customHeight="1" spans="1:18">
+    <row r="767" spans="1:18" ht="13.5" customHeight="1">
       <c r="A767" s="4"/>
       <c r="B767" s="4"/>
       <c r="C767" s="4"/>
@@ -16762,7 +16139,7 @@
       <c r="Q767" s="4"/>
       <c r="R767" s="4"/>
     </row>
-    <row r="768" ht="13.5" customHeight="1" spans="1:18">
+    <row r="768" spans="1:18" ht="13.5" customHeight="1">
       <c r="A768" s="4"/>
       <c r="B768" s="4"/>
       <c r="C768" s="4"/>
@@ -16782,7 +16159,7 @@
       <c r="Q768" s="4"/>
       <c r="R768" s="4"/>
     </row>
-    <row r="769" ht="13.5" customHeight="1" spans="1:18">
+    <row r="769" spans="1:18" ht="13.5" customHeight="1">
       <c r="A769" s="4"/>
       <c r="B769" s="4"/>
       <c r="C769" s="4"/>
@@ -16802,7 +16179,7 @@
       <c r="Q769" s="4"/>
       <c r="R769" s="4"/>
     </row>
-    <row r="770" ht="13.5" customHeight="1" spans="1:18">
+    <row r="770" spans="1:18" ht="13.5" customHeight="1">
       <c r="A770" s="4"/>
       <c r="B770" s="4"/>
       <c r="C770" s="4"/>
@@ -16822,7 +16199,7 @@
       <c r="Q770" s="4"/>
       <c r="R770" s="4"/>
     </row>
-    <row r="771" ht="13.5" customHeight="1" spans="1:18">
+    <row r="771" spans="1:18" ht="13.5" customHeight="1">
       <c r="A771" s="4"/>
       <c r="B771" s="4"/>
       <c r="C771" s="4"/>
@@ -16842,7 +16219,7 @@
       <c r="Q771" s="4"/>
       <c r="R771" s="4"/>
     </row>
-    <row r="772" ht="13.5" customHeight="1" spans="1:18">
+    <row r="772" spans="1:18" ht="13.5" customHeight="1">
       <c r="A772" s="4"/>
       <c r="B772" s="4"/>
       <c r="C772" s="4"/>
@@ -16862,7 +16239,7 @@
       <c r="Q772" s="4"/>
       <c r="R772" s="4"/>
     </row>
-    <row r="773" ht="13.5" customHeight="1" spans="1:18">
+    <row r="773" spans="1:18" ht="13.5" customHeight="1">
       <c r="A773" s="4"/>
       <c r="B773" s="4"/>
       <c r="C773" s="4"/>
@@ -16882,7 +16259,7 @@
       <c r="Q773" s="4"/>
       <c r="R773" s="4"/>
     </row>
-    <row r="774" ht="13.5" customHeight="1" spans="1:18">
+    <row r="774" spans="1:18" ht="13.5" customHeight="1">
       <c r="A774" s="4"/>
       <c r="B774" s="4"/>
       <c r="C774" s="4"/>
@@ -16902,7 +16279,7 @@
       <c r="Q774" s="4"/>
       <c r="R774" s="4"/>
     </row>
-    <row r="775" ht="13.5" customHeight="1" spans="1:18">
+    <row r="775" spans="1:18" ht="13.5" customHeight="1">
       <c r="A775" s="4"/>
       <c r="B775" s="4"/>
       <c r="C775" s="4"/>
@@ -16922,7 +16299,7 @@
       <c r="Q775" s="4"/>
       <c r="R775" s="4"/>
     </row>
-    <row r="776" ht="13.5" customHeight="1" spans="1:18">
+    <row r="776" spans="1:18" ht="13.5" customHeight="1">
       <c r="A776" s="4"/>
       <c r="B776" s="4"/>
       <c r="C776" s="4"/>
@@ -16942,7 +16319,7 @@
       <c r="Q776" s="4"/>
       <c r="R776" s="4"/>
     </row>
-    <row r="777" ht="13.5" customHeight="1" spans="1:18">
+    <row r="777" spans="1:18" ht="13.5" customHeight="1">
       <c r="A777" s="4"/>
       <c r="B777" s="4"/>
       <c r="C777" s="4"/>
@@ -16962,7 +16339,7 @@
       <c r="Q777" s="4"/>
       <c r="R777" s="4"/>
     </row>
-    <row r="778" ht="13.5" customHeight="1" spans="1:18">
+    <row r="778" spans="1:18" ht="13.5" customHeight="1">
       <c r="A778" s="4"/>
       <c r="B778" s="4"/>
       <c r="C778" s="4"/>
@@ -16982,7 +16359,7 @@
       <c r="Q778" s="4"/>
       <c r="R778" s="4"/>
     </row>
-    <row r="779" ht="13.5" customHeight="1" spans="1:18">
+    <row r="779" spans="1:18" ht="13.5" customHeight="1">
       <c r="A779" s="4"/>
       <c r="B779" s="4"/>
       <c r="C779" s="4"/>
@@ -17002,7 +16379,7 @@
       <c r="Q779" s="4"/>
       <c r="R779" s="4"/>
     </row>
-    <row r="780" ht="13.5" customHeight="1" spans="1:18">
+    <row r="780" spans="1:18" ht="13.5" customHeight="1">
       <c r="A780" s="4"/>
       <c r="B780" s="4"/>
       <c r="C780" s="4"/>
@@ -17022,7 +16399,7 @@
       <c r="Q780" s="4"/>
       <c r="R780" s="4"/>
     </row>
-    <row r="781" ht="13.5" customHeight="1" spans="1:18">
+    <row r="781" spans="1:18" ht="13.5" customHeight="1">
       <c r="A781" s="4"/>
       <c r="B781" s="4"/>
       <c r="C781" s="4"/>
@@ -17042,7 +16419,7 @@
       <c r="Q781" s="4"/>
       <c r="R781" s="4"/>
     </row>
-    <row r="782" ht="13.5" customHeight="1" spans="1:18">
+    <row r="782" spans="1:18" ht="13.5" customHeight="1">
       <c r="A782" s="4"/>
       <c r="B782" s="4"/>
       <c r="C782" s="4"/>
@@ -17062,7 +16439,7 @@
       <c r="Q782" s="4"/>
       <c r="R782" s="4"/>
     </row>
-    <row r="783" ht="13.5" customHeight="1" spans="1:18">
+    <row r="783" spans="1:18" ht="13.5" customHeight="1">
       <c r="A783" s="4"/>
       <c r="B783" s="4"/>
       <c r="C783" s="4"/>
@@ -17082,7 +16459,7 @@
       <c r="Q783" s="4"/>
       <c r="R783" s="4"/>
     </row>
-    <row r="784" ht="13.5" customHeight="1" spans="1:18">
+    <row r="784" spans="1:18" ht="13.5" customHeight="1">
       <c r="A784" s="4"/>
       <c r="B784" s="4"/>
       <c r="C784" s="4"/>
@@ -17102,7 +16479,7 @@
       <c r="Q784" s="4"/>
       <c r="R784" s="4"/>
     </row>
-    <row r="785" ht="13.5" customHeight="1" spans="1:18">
+    <row r="785" spans="1:18" ht="13.5" customHeight="1">
       <c r="A785" s="4"/>
       <c r="B785" s="4"/>
       <c r="C785" s="4"/>
@@ -17122,7 +16499,7 @@
       <c r="Q785" s="4"/>
       <c r="R785" s="4"/>
     </row>
-    <row r="786" ht="13.5" customHeight="1" spans="1:18">
+    <row r="786" spans="1:18" ht="13.5" customHeight="1">
       <c r="A786" s="4"/>
       <c r="B786" s="4"/>
       <c r="C786" s="4"/>
@@ -17142,7 +16519,7 @@
       <c r="Q786" s="4"/>
       <c r="R786" s="4"/>
     </row>
-    <row r="787" ht="13.5" customHeight="1" spans="1:18">
+    <row r="787" spans="1:18" ht="13.5" customHeight="1">
       <c r="A787" s="4"/>
       <c r="B787" s="4"/>
       <c r="C787" s="4"/>
@@ -17162,7 +16539,7 @@
       <c r="Q787" s="4"/>
       <c r="R787" s="4"/>
     </row>
-    <row r="788" ht="13.5" customHeight="1" spans="1:18">
+    <row r="788" spans="1:18" ht="13.5" customHeight="1">
       <c r="A788" s="4"/>
       <c r="B788" s="4"/>
       <c r="C788" s="4"/>
@@ -17182,7 +16559,7 @@
       <c r="Q788" s="4"/>
       <c r="R788" s="4"/>
     </row>
-    <row r="789" ht="13.5" customHeight="1" spans="1:18">
+    <row r="789" spans="1:18" ht="13.5" customHeight="1">
       <c r="A789" s="4"/>
       <c r="B789" s="4"/>
       <c r="C789" s="4"/>
@@ -17202,7 +16579,7 @@
       <c r="Q789" s="4"/>
       <c r="R789" s="4"/>
     </row>
-    <row r="790" ht="13.5" customHeight="1" spans="1:18">
+    <row r="790" spans="1:18" ht="13.5" customHeight="1">
       <c r="A790" s="4"/>
       <c r="B790" s="4"/>
       <c r="C790" s="4"/>
@@ -17222,7 +16599,7 @@
       <c r="Q790" s="4"/>
       <c r="R790" s="4"/>
     </row>
-    <row r="791" ht="13.5" customHeight="1" spans="1:18">
+    <row r="791" spans="1:18" ht="13.5" customHeight="1">
       <c r="A791" s="4"/>
       <c r="B791" s="4"/>
       <c r="C791" s="4"/>
@@ -17242,7 +16619,7 @@
       <c r="Q791" s="4"/>
       <c r="R791" s="4"/>
     </row>
-    <row r="792" ht="13.5" customHeight="1" spans="1:18">
+    <row r="792" spans="1:18" ht="13.5" customHeight="1">
       <c r="A792" s="4"/>
       <c r="B792" s="4"/>
       <c r="C792" s="4"/>
@@ -17262,7 +16639,7 @@
       <c r="Q792" s="4"/>
       <c r="R792" s="4"/>
     </row>
-    <row r="793" ht="13.5" customHeight="1" spans="1:18">
+    <row r="793" spans="1:18" ht="13.5" customHeight="1">
       <c r="A793" s="4"/>
       <c r="B793" s="4"/>
       <c r="C793" s="4"/>
@@ -17282,7 +16659,7 @@
       <c r="Q793" s="4"/>
       <c r="R793" s="4"/>
     </row>
-    <row r="794" ht="13.5" customHeight="1" spans="1:18">
+    <row r="794" spans="1:18" ht="13.5" customHeight="1">
       <c r="A794" s="4"/>
       <c r="B794" s="4"/>
       <c r="C794" s="4"/>
@@ -17302,7 +16679,7 @@
       <c r="Q794" s="4"/>
       <c r="R794" s="4"/>
     </row>
-    <row r="795" ht="13.5" customHeight="1" spans="1:18">
+    <row r="795" spans="1:18" ht="13.5" customHeight="1">
       <c r="A795" s="4"/>
       <c r="B795" s="4"/>
       <c r="C795" s="4"/>
@@ -17322,7 +16699,7 @@
       <c r="Q795" s="4"/>
       <c r="R795" s="4"/>
     </row>
-    <row r="796" ht="13.5" customHeight="1" spans="1:18">
+    <row r="796" spans="1:18" ht="13.5" customHeight="1">
       <c r="A796" s="4"/>
       <c r="B796" s="4"/>
       <c r="C796" s="4"/>
@@ -17342,7 +16719,7 @@
       <c r="Q796" s="4"/>
       <c r="R796" s="4"/>
     </row>
-    <row r="797" ht="13.5" customHeight="1" spans="1:18">
+    <row r="797" spans="1:18" ht="13.5" customHeight="1">
       <c r="A797" s="4"/>
       <c r="B797" s="4"/>
       <c r="C797" s="4"/>
@@ -17362,7 +16739,7 @@
       <c r="Q797" s="4"/>
       <c r="R797" s="4"/>
     </row>
-    <row r="798" ht="13.5" customHeight="1" spans="1:18">
+    <row r="798" spans="1:18" ht="13.5" customHeight="1">
       <c r="A798" s="4"/>
       <c r="B798" s="4"/>
       <c r="C798" s="4"/>
@@ -17382,7 +16759,7 @@
       <c r="Q798" s="4"/>
       <c r="R798" s="4"/>
     </row>
-    <row r="799" ht="13.5" customHeight="1" spans="1:18">
+    <row r="799" spans="1:18" ht="13.5" customHeight="1">
       <c r="A799" s="4"/>
       <c r="B799" s="4"/>
       <c r="C799" s="4"/>
@@ -17402,7 +16779,7 @@
       <c r="Q799" s="4"/>
       <c r="R799" s="4"/>
     </row>
-    <row r="800" ht="13.5" customHeight="1" spans="1:18">
+    <row r="800" spans="1:18" ht="13.5" customHeight="1">
       <c r="A800" s="4"/>
       <c r="B800" s="4"/>
       <c r="C800" s="4"/>
@@ -17422,7 +16799,7 @@
       <c r="Q800" s="4"/>
       <c r="R800" s="4"/>
     </row>
-    <row r="801" ht="13.5" customHeight="1" spans="1:18">
+    <row r="801" spans="1:18" ht="13.5" customHeight="1">
       <c r="A801" s="4"/>
       <c r="B801" s="4"/>
       <c r="C801" s="4"/>
@@ -17442,7 +16819,7 @@
       <c r="Q801" s="4"/>
       <c r="R801" s="4"/>
     </row>
-    <row r="802" ht="13.5" customHeight="1" spans="1:18">
+    <row r="802" spans="1:18" ht="13.5" customHeight="1">
       <c r="A802" s="4"/>
       <c r="B802" s="4"/>
       <c r="C802" s="4"/>
@@ -17462,7 +16839,7 @@
       <c r="Q802" s="4"/>
       <c r="R802" s="4"/>
     </row>
-    <row r="803" ht="13.5" customHeight="1" spans="1:18">
+    <row r="803" spans="1:18" ht="13.5" customHeight="1">
       <c r="A803" s="4"/>
       <c r="B803" s="4"/>
       <c r="C803" s="4"/>
@@ -17482,7 +16859,7 @@
       <c r="Q803" s="4"/>
       <c r="R803" s="4"/>
     </row>
-    <row r="804" ht="13.5" customHeight="1" spans="1:18">
+    <row r="804" spans="1:18" ht="13.5" customHeight="1">
       <c r="A804" s="4"/>
       <c r="B804" s="4"/>
       <c r="C804" s="4"/>
@@ -17502,7 +16879,7 @@
       <c r="Q804" s="4"/>
       <c r="R804" s="4"/>
     </row>
-    <row r="805" ht="13.5" customHeight="1" spans="1:18">
+    <row r="805" spans="1:18" ht="13.5" customHeight="1">
       <c r="A805" s="4"/>
       <c r="B805" s="4"/>
       <c r="C805" s="4"/>
@@ -17522,7 +16899,7 @@
       <c r="Q805" s="4"/>
       <c r="R805" s="4"/>
     </row>
-    <row r="806" ht="13.5" customHeight="1" spans="1:18">
+    <row r="806" spans="1:18" ht="13.5" customHeight="1">
       <c r="A806" s="4"/>
       <c r="B806" s="4"/>
       <c r="C806" s="4"/>
@@ -17542,7 +16919,7 @@
       <c r="Q806" s="4"/>
       <c r="R806" s="4"/>
     </row>
-    <row r="807" ht="13.5" customHeight="1" spans="1:18">
+    <row r="807" spans="1:18" ht="13.5" customHeight="1">
       <c r="A807" s="4"/>
       <c r="B807" s="4"/>
       <c r="C807" s="4"/>
@@ -17562,7 +16939,7 @@
       <c r="Q807" s="4"/>
       <c r="R807" s="4"/>
     </row>
-    <row r="808" ht="13.5" customHeight="1" spans="1:18">
+    <row r="808" spans="1:18" ht="13.5" customHeight="1">
       <c r="A808" s="4"/>
       <c r="B808" s="4"/>
       <c r="C808" s="4"/>
@@ -17582,7 +16959,7 @@
       <c r="Q808" s="4"/>
       <c r="R808" s="4"/>
     </row>
-    <row r="809" ht="13.5" customHeight="1" spans="1:18">
+    <row r="809" spans="1:18" ht="13.5" customHeight="1">
       <c r="A809" s="4"/>
       <c r="B809" s="4"/>
       <c r="C809" s="4"/>
@@ -17602,7 +16979,7 @@
       <c r="Q809" s="4"/>
       <c r="R809" s="4"/>
     </row>
-    <row r="810" ht="13.5" customHeight="1" spans="1:18">
+    <row r="810" spans="1:18" ht="13.5" customHeight="1">
       <c r="A810" s="4"/>
       <c r="B810" s="4"/>
       <c r="C810" s="4"/>
@@ -17622,7 +16999,7 @@
       <c r="Q810" s="4"/>
       <c r="R810" s="4"/>
     </row>
-    <row r="811" ht="13.5" customHeight="1" spans="1:18">
+    <row r="811" spans="1:18" ht="13.5" customHeight="1">
       <c r="A811" s="4"/>
       <c r="B811" s="4"/>
       <c r="C811" s="4"/>
@@ -17642,7 +17019,7 @@
       <c r="Q811" s="4"/>
       <c r="R811" s="4"/>
     </row>
-    <row r="812" ht="13.5" customHeight="1" spans="1:18">
+    <row r="812" spans="1:18" ht="13.5" customHeight="1">
       <c r="A812" s="4"/>
       <c r="B812" s="4"/>
       <c r="C812" s="4"/>
@@ -17662,7 +17039,7 @@
       <c r="Q812" s="4"/>
       <c r="R812" s="4"/>
     </row>
-    <row r="813" ht="13.5" customHeight="1" spans="1:18">
+    <row r="813" spans="1:18" ht="13.5" customHeight="1">
       <c r="A813" s="4"/>
       <c r="B813" s="4"/>
       <c r="C813" s="4"/>
@@ -17682,7 +17059,7 @@
       <c r="Q813" s="4"/>
       <c r="R813" s="4"/>
     </row>
-    <row r="814" ht="13.5" customHeight="1" spans="1:18">
+    <row r="814" spans="1:18" ht="13.5" customHeight="1">
       <c r="A814" s="4"/>
       <c r="B814" s="4"/>
       <c r="C814" s="4"/>
@@ -17702,7 +17079,7 @@
       <c r="Q814" s="4"/>
       <c r="R814" s="4"/>
     </row>
-    <row r="815" ht="13.5" customHeight="1" spans="1:18">
+    <row r="815" spans="1:18" ht="13.5" customHeight="1">
       <c r="A815" s="4"/>
       <c r="B815" s="4"/>
       <c r="C815" s="4"/>
@@ -17722,7 +17099,7 @@
       <c r="Q815" s="4"/>
       <c r="R815" s="4"/>
     </row>
-    <row r="816" ht="13.5" customHeight="1" spans="1:18">
+    <row r="816" spans="1:18" ht="13.5" customHeight="1">
       <c r="A816" s="4"/>
       <c r="B816" s="4"/>
       <c r="C816" s="4"/>
@@ -17742,7 +17119,7 @@
       <c r="Q816" s="4"/>
       <c r="R816" s="4"/>
     </row>
-    <row r="817" ht="13.5" customHeight="1" spans="1:18">
+    <row r="817" spans="1:18" ht="13.5" customHeight="1">
       <c r="A817" s="4"/>
       <c r="B817" s="4"/>
       <c r="C817" s="4"/>
@@ -17762,7 +17139,7 @@
       <c r="Q817" s="4"/>
       <c r="R817" s="4"/>
     </row>
-    <row r="818" ht="13.5" customHeight="1" spans="1:18">
+    <row r="818" spans="1:18" ht="13.5" customHeight="1">
       <c r="A818" s="4"/>
       <c r="B818" s="4"/>
       <c r="C818" s="4"/>
@@ -17782,7 +17159,7 @@
       <c r="Q818" s="4"/>
       <c r="R818" s="4"/>
     </row>
-    <row r="819" ht="13.5" customHeight="1" spans="1:18">
+    <row r="819" spans="1:18" ht="13.5" customHeight="1">
       <c r="A819" s="4"/>
       <c r="B819" s="4"/>
       <c r="C819" s="4"/>
@@ -17802,7 +17179,7 @@
       <c r="Q819" s="4"/>
       <c r="R819" s="4"/>
     </row>
-    <row r="820" ht="13.5" customHeight="1" spans="1:18">
+    <row r="820" spans="1:18" ht="13.5" customHeight="1">
       <c r="A820" s="4"/>
       <c r="B820" s="4"/>
       <c r="C820" s="4"/>
@@ -17822,7 +17199,7 @@
       <c r="Q820" s="4"/>
       <c r="R820" s="4"/>
     </row>
-    <row r="821" ht="13.5" customHeight="1" spans="1:18">
+    <row r="821" spans="1:18" ht="13.5" customHeight="1">
       <c r="A821" s="4"/>
       <c r="B821" s="4"/>
       <c r="C821" s="4"/>
@@ -17842,7 +17219,7 @@
       <c r="Q821" s="4"/>
       <c r="R821" s="4"/>
     </row>
-    <row r="822" ht="13.5" customHeight="1" spans="1:18">
+    <row r="822" spans="1:18" ht="13.5" customHeight="1">
       <c r="A822" s="4"/>
       <c r="B822" s="4"/>
       <c r="C822" s="4"/>
@@ -17862,7 +17239,7 @@
       <c r="Q822" s="4"/>
       <c r="R822" s="4"/>
     </row>
-    <row r="823" ht="13.5" customHeight="1" spans="1:18">
+    <row r="823" spans="1:18" ht="13.5" customHeight="1">
       <c r="A823" s="4"/>
       <c r="B823" s="4"/>
       <c r="C823" s="4"/>
@@ -17882,7 +17259,7 @@
       <c r="Q823" s="4"/>
       <c r="R823" s="4"/>
     </row>
-    <row r="824" ht="13.5" customHeight="1" spans="1:18">
+    <row r="824" spans="1:18" ht="13.5" customHeight="1">
       <c r="A824" s="4"/>
       <c r="B824" s="4"/>
       <c r="C824" s="4"/>
@@ -17902,7 +17279,7 @@
       <c r="Q824" s="4"/>
       <c r="R824" s="4"/>
     </row>
-    <row r="825" ht="13.5" customHeight="1" spans="1:18">
+    <row r="825" spans="1:18" ht="13.5" customHeight="1">
       <c r="A825" s="4"/>
       <c r="B825" s="4"/>
       <c r="C825" s="4"/>
@@ -17922,7 +17299,7 @@
       <c r="Q825" s="4"/>
       <c r="R825" s="4"/>
     </row>
-    <row r="826" ht="13.5" customHeight="1" spans="1:18">
+    <row r="826" spans="1:18" ht="13.5" customHeight="1">
       <c r="A826" s="4"/>
       <c r="B826" s="4"/>
       <c r="C826" s="4"/>
@@ -17942,7 +17319,7 @@
       <c r="Q826" s="4"/>
       <c r="R826" s="4"/>
     </row>
-    <row r="827" ht="13.5" customHeight="1" spans="1:18">
+    <row r="827" spans="1:18" ht="13.5" customHeight="1">
       <c r="A827" s="4"/>
       <c r="B827" s="4"/>
       <c r="C827" s="4"/>
@@ -17962,7 +17339,7 @@
       <c r="Q827" s="4"/>
       <c r="R827" s="4"/>
     </row>
-    <row r="828" ht="13.5" customHeight="1" spans="1:18">
+    <row r="828" spans="1:18" ht="13.5" customHeight="1">
       <c r="A828" s="4"/>
       <c r="B828" s="4"/>
       <c r="C828" s="4"/>
@@ -17982,7 +17359,7 @@
       <c r="Q828" s="4"/>
       <c r="R828" s="4"/>
     </row>
-    <row r="829" ht="13.5" customHeight="1" spans="1:18">
+    <row r="829" spans="1:18" ht="13.5" customHeight="1">
       <c r="A829" s="4"/>
       <c r="B829" s="4"/>
       <c r="C829" s="4"/>
@@ -18002,7 +17379,7 @@
       <c r="Q829" s="4"/>
       <c r="R829" s="4"/>
     </row>
-    <row r="830" ht="13.5" customHeight="1" spans="1:18">
+    <row r="830" spans="1:18" ht="13.5" customHeight="1">
       <c r="A830" s="4"/>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
@@ -18022,7 +17399,7 @@
       <c r="Q830" s="4"/>
       <c r="R830" s="4"/>
     </row>
-    <row r="831" ht="13.5" customHeight="1" spans="1:18">
+    <row r="831" spans="1:18" ht="13.5" customHeight="1">
       <c r="A831" s="4"/>
       <c r="B831" s="4"/>
       <c r="C831" s="4"/>
@@ -18042,7 +17419,7 @@
       <c r="Q831" s="4"/>
       <c r="R831" s="4"/>
     </row>
-    <row r="832" ht="13.5" customHeight="1" spans="1:18">
+    <row r="832" spans="1:18" ht="13.5" customHeight="1">
       <c r="A832" s="4"/>
       <c r="B832" s="4"/>
       <c r="C832" s="4"/>
@@ -18062,7 +17439,7 @@
       <c r="Q832" s="4"/>
       <c r="R832" s="4"/>
     </row>
-    <row r="833" ht="13.5" customHeight="1" spans="1:18">
+    <row r="833" spans="1:18" ht="13.5" customHeight="1">
       <c r="A833" s="4"/>
       <c r="B833" s="4"/>
       <c r="C833" s="4"/>
@@ -18082,7 +17459,7 @@
       <c r="Q833" s="4"/>
       <c r="R833" s="4"/>
     </row>
-    <row r="834" ht="13.5" customHeight="1" spans="1:18">
+    <row r="834" spans="1:18" ht="13.5" customHeight="1">
       <c r="A834" s="4"/>
       <c r="B834" s="4"/>
       <c r="C834" s="4"/>
@@ -18102,7 +17479,7 @@
       <c r="Q834" s="4"/>
       <c r="R834" s="4"/>
     </row>
-    <row r="835" ht="13.5" customHeight="1" spans="1:18">
+    <row r="835" spans="1:18" ht="13.5" customHeight="1">
       <c r="A835" s="4"/>
       <c r="B835" s="4"/>
       <c r="C835" s="4"/>
@@ -18122,7 +17499,7 @@
       <c r="Q835" s="4"/>
       <c r="R835" s="4"/>
     </row>
-    <row r="836" ht="13.5" customHeight="1" spans="1:18">
+    <row r="836" spans="1:18" ht="13.5" customHeight="1">
       <c r="A836" s="4"/>
       <c r="B836" s="4"/>
       <c r="C836" s="4"/>
@@ -18142,7 +17519,7 @@
       <c r="Q836" s="4"/>
       <c r="R836" s="4"/>
     </row>
-    <row r="837" ht="13.5" customHeight="1" spans="1:18">
+    <row r="837" spans="1:18" ht="13.5" customHeight="1">
       <c r="A837" s="4"/>
       <c r="B837" s="4"/>
       <c r="C837" s="4"/>
@@ -18162,7 +17539,7 @@
       <c r="Q837" s="4"/>
       <c r="R837" s="4"/>
     </row>
-    <row r="838" ht="13.5" customHeight="1" spans="1:18">
+    <row r="838" spans="1:18" ht="13.5" customHeight="1">
       <c r="A838" s="4"/>
       <c r="B838" s="4"/>
       <c r="C838" s="4"/>
@@ -18182,7 +17559,7 @@
       <c r="Q838" s="4"/>
       <c r="R838" s="4"/>
     </row>
-    <row r="839" ht="13.5" customHeight="1" spans="1:18">
+    <row r="839" spans="1:18" ht="13.5" customHeight="1">
       <c r="A839" s="4"/>
       <c r="B839" s="4"/>
       <c r="C839" s="4"/>
@@ -18202,7 +17579,7 @@
       <c r="Q839" s="4"/>
       <c r="R839" s="4"/>
     </row>
-    <row r="840" ht="13.5" customHeight="1" spans="1:18">
+    <row r="840" spans="1:18" ht="13.5" customHeight="1">
       <c r="A840" s="4"/>
       <c r="B840" s="4"/>
       <c r="C840" s="4"/>
@@ -18222,7 +17599,7 @@
       <c r="Q840" s="4"/>
       <c r="R840" s="4"/>
     </row>
-    <row r="841" ht="13.5" customHeight="1" spans="1:18">
+    <row r="841" spans="1:18" ht="13.5" customHeight="1">
       <c r="A841" s="4"/>
       <c r="B841" s="4"/>
       <c r="C841" s="4"/>
@@ -18242,7 +17619,7 @@
       <c r="Q841" s="4"/>
       <c r="R841" s="4"/>
     </row>
-    <row r="842" ht="13.5" customHeight="1" spans="1:18">
+    <row r="842" spans="1:18" ht="13.5" customHeight="1">
       <c r="A842" s="4"/>
       <c r="B842" s="4"/>
       <c r="C842" s="4"/>
@@ -18262,7 +17639,7 @@
       <c r="Q842" s="4"/>
       <c r="R842" s="4"/>
     </row>
-    <row r="843" ht="13.5" customHeight="1" spans="1:18">
+    <row r="843" spans="1:18" ht="13.5" customHeight="1">
       <c r="A843" s="4"/>
       <c r="B843" s="4"/>
       <c r="C843" s="4"/>
@@ -18282,7 +17659,7 @@
       <c r="Q843" s="4"/>
       <c r="R843" s="4"/>
     </row>
-    <row r="844" ht="13.5" customHeight="1" spans="1:18">
+    <row r="844" spans="1:18" ht="13.5" customHeight="1">
       <c r="A844" s="4"/>
       <c r="B844" s="4"/>
       <c r="C844" s="4"/>
@@ -18302,7 +17679,7 @@
       <c r="Q844" s="4"/>
       <c r="R844" s="4"/>
     </row>
-    <row r="845" ht="13.5" customHeight="1" spans="1:18">
+    <row r="845" spans="1:18" ht="13.5" customHeight="1">
       <c r="A845" s="4"/>
       <c r="B845" s="4"/>
       <c r="C845" s="4"/>
@@ -18322,7 +17699,7 @@
       <c r="Q845" s="4"/>
       <c r="R845" s="4"/>
     </row>
-    <row r="846" ht="13.5" customHeight="1" spans="1:18">
+    <row r="846" spans="1:18" ht="13.5" customHeight="1">
       <c r="A846" s="4"/>
       <c r="B846" s="4"/>
       <c r="C846" s="4"/>
@@ -18342,7 +17719,7 @@
       <c r="Q846" s="4"/>
       <c r="R846" s="4"/>
     </row>
-    <row r="847" ht="13.5" customHeight="1" spans="1:18">
+    <row r="847" spans="1:18" ht="13.5" customHeight="1">
       <c r="A847" s="4"/>
       <c r="B847" s="4"/>
       <c r="C847" s="4"/>
@@ -18362,7 +17739,7 @@
       <c r="Q847" s="4"/>
       <c r="R847" s="4"/>
     </row>
-    <row r="848" ht="13.5" customHeight="1" spans="1:18">
+    <row r="848" spans="1:18" ht="13.5" customHeight="1">
       <c r="A848" s="4"/>
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
@@ -18382,7 +17759,7 @@
       <c r="Q848" s="4"/>
       <c r="R848" s="4"/>
     </row>
-    <row r="849" ht="13.5" customHeight="1" spans="1:18">
+    <row r="849" spans="1:18" ht="13.5" customHeight="1">
       <c r="A849" s="4"/>
       <c r="B849" s="4"/>
       <c r="C849" s="4"/>
@@ -18402,7 +17779,7 @@
       <c r="Q849" s="4"/>
       <c r="R849" s="4"/>
     </row>
-    <row r="850" ht="13.5" customHeight="1" spans="1:18">
+    <row r="850" spans="1:18" ht="13.5" customHeight="1">
       <c r="A850" s="4"/>
       <c r="B850" s="4"/>
       <c r="C850" s="4"/>
@@ -18422,7 +17799,7 @@
       <c r="Q850" s="4"/>
       <c r="R850" s="4"/>
     </row>
-    <row r="851" ht="13.5" customHeight="1" spans="1:18">
+    <row r="851" spans="1:18" ht="13.5" customHeight="1">
       <c r="A851" s="4"/>
       <c r="B851" s="4"/>
       <c r="C851" s="4"/>
@@ -18442,7 +17819,7 @@
       <c r="Q851" s="4"/>
       <c r="R851" s="4"/>
     </row>
-    <row r="852" ht="13.5" customHeight="1" spans="1:18">
+    <row r="852" spans="1:18" ht="13.5" customHeight="1">
       <c r="A852" s="4"/>
       <c r="B852" s="4"/>
       <c r="C852" s="4"/>
@@ -18462,7 +17839,7 @@
       <c r="Q852" s="4"/>
       <c r="R852" s="4"/>
     </row>
-    <row r="853" ht="13.5" customHeight="1" spans="1:18">
+    <row r="853" spans="1:18" ht="13.5" customHeight="1">
       <c r="A853" s="4"/>
       <c r="B853" s="4"/>
       <c r="C853" s="4"/>
@@ -18482,7 +17859,7 @@
       <c r="Q853" s="4"/>
       <c r="R853" s="4"/>
     </row>
-    <row r="854" ht="13.5" customHeight="1" spans="1:18">
+    <row r="854" spans="1:18" ht="13.5" customHeight="1">
       <c r="A854" s="4"/>
       <c r="B854" s="4"/>
       <c r="C854" s="4"/>
@@ -18502,7 +17879,7 @@
       <c r="Q854" s="4"/>
       <c r="R854" s="4"/>
     </row>
-    <row r="855" ht="13.5" customHeight="1" spans="1:18">
+    <row r="855" spans="1:18" ht="13.5" customHeight="1">
       <c r="A855" s="4"/>
       <c r="B855" s="4"/>
       <c r="C855" s="4"/>
@@ -18522,7 +17899,7 @@
       <c r="Q855" s="4"/>
       <c r="R855" s="4"/>
     </row>
-    <row r="856" ht="13.5" customHeight="1" spans="1:18">
+    <row r="856" spans="1:18" ht="13.5" customHeight="1">
       <c r="A856" s="4"/>
       <c r="B856" s="4"/>
       <c r="C856" s="4"/>
@@ -18542,7 +17919,7 @@
       <c r="Q856" s="4"/>
       <c r="R856" s="4"/>
     </row>
-    <row r="857" ht="13.5" customHeight="1" spans="1:18">
+    <row r="857" spans="1:18" ht="13.5" customHeight="1">
       <c r="A857" s="4"/>
       <c r="B857" s="4"/>
       <c r="C857" s="4"/>
@@ -18562,7 +17939,7 @@
       <c r="Q857" s="4"/>
       <c r="R857" s="4"/>
     </row>
-    <row r="858" ht="13.5" customHeight="1" spans="1:18">
+    <row r="858" spans="1:18" ht="13.5" customHeight="1">
       <c r="A858" s="4"/>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
@@ -18582,7 +17959,7 @@
       <c r="Q858" s="4"/>
       <c r="R858" s="4"/>
     </row>
-    <row r="859" ht="13.5" customHeight="1" spans="1:18">
+    <row r="859" spans="1:18" ht="13.5" customHeight="1">
       <c r="A859" s="4"/>
       <c r="B859" s="4"/>
       <c r="C859" s="4"/>
@@ -18602,7 +17979,7 @@
       <c r="Q859" s="4"/>
       <c r="R859" s="4"/>
     </row>
-    <row r="860" ht="13.5" customHeight="1" spans="1:18">
+    <row r="860" spans="1:18" ht="13.5" customHeight="1">
       <c r="A860" s="4"/>
       <c r="B860" s="4"/>
       <c r="C860" s="4"/>
@@ -18622,7 +17999,7 @@
       <c r="Q860" s="4"/>
       <c r="R860" s="4"/>
     </row>
-    <row r="861" ht="13.5" customHeight="1" spans="1:18">
+    <row r="861" spans="1:18" ht="13.5" customHeight="1">
       <c r="A861" s="4"/>
       <c r="B861" s="4"/>
       <c r="C861" s="4"/>
@@ -18642,7 +18019,7 @@
       <c r="Q861" s="4"/>
       <c r="R861" s="4"/>
     </row>
-    <row r="862" ht="13.5" customHeight="1" spans="1:18">
+    <row r="862" spans="1:18" ht="13.5" customHeight="1">
       <c r="A862" s="4"/>
       <c r="B862" s="4"/>
       <c r="C862" s="4"/>
@@ -18662,7 +18039,7 @@
       <c r="Q862" s="4"/>
       <c r="R862" s="4"/>
     </row>
-    <row r="863" ht="13.5" customHeight="1" spans="1:18">
+    <row r="863" spans="1:18" ht="13.5" customHeight="1">
       <c r="A863" s="4"/>
       <c r="B863" s="4"/>
       <c r="C863" s="4"/>
@@ -18682,7 +18059,7 @@
       <c r="Q863" s="4"/>
       <c r="R863" s="4"/>
     </row>
-    <row r="864" ht="13.5" customHeight="1" spans="1:18">
+    <row r="864" spans="1:18" ht="13.5" customHeight="1">
       <c r="A864" s="4"/>
       <c r="B864" s="4"/>
       <c r="C864" s="4"/>
@@ -18702,7 +18079,7 @@
       <c r="Q864" s="4"/>
       <c r="R864" s="4"/>
     </row>
-    <row r="865" ht="13.5" customHeight="1" spans="1:18">
+    <row r="865" spans="1:18" ht="13.5" customHeight="1">
       <c r="A865" s="4"/>
       <c r="B865" s="4"/>
       <c r="C865" s="4"/>
@@ -18722,7 +18099,7 @@
       <c r="Q865" s="4"/>
       <c r="R865" s="4"/>
     </row>
-    <row r="866" ht="13.5" customHeight="1" spans="1:18">
+    <row r="866" spans="1:18" ht="13.5" customHeight="1">
       <c r="A866" s="4"/>
       <c r="B866" s="4"/>
       <c r="C866" s="4"/>
@@ -18742,7 +18119,7 @@
       <c r="Q866" s="4"/>
       <c r="R866" s="4"/>
     </row>
-    <row r="867" ht="13.5" customHeight="1" spans="1:18">
+    <row r="867" spans="1:18" ht="13.5" customHeight="1">
       <c r="A867" s="4"/>
       <c r="B867" s="4"/>
       <c r="C867" s="4"/>
@@ -18762,7 +18139,7 @@
       <c r="Q867" s="4"/>
       <c r="R867" s="4"/>
     </row>
-    <row r="868" ht="13.5" customHeight="1" spans="1:18">
+    <row r="868" spans="1:18" ht="13.5" customHeight="1">
       <c r="A868" s="4"/>
       <c r="B868" s="4"/>
       <c r="C868" s="4"/>
@@ -18782,7 +18159,7 @@
       <c r="Q868" s="4"/>
       <c r="R868" s="4"/>
     </row>
-    <row r="869" ht="13.5" customHeight="1" spans="1:18">
+    <row r="869" spans="1:18" ht="13.5" customHeight="1">
       <c r="A869" s="4"/>
       <c r="B869" s="4"/>
       <c r="C869" s="4"/>
@@ -18802,7 +18179,7 @@
       <c r="Q869" s="4"/>
       <c r="R869" s="4"/>
     </row>
-    <row r="870" ht="13.5" customHeight="1" spans="1:18">
+    <row r="870" spans="1:18" ht="13.5" customHeight="1">
       <c r="A870" s="4"/>
       <c r="B870" s="4"/>
       <c r="C870" s="4"/>
@@ -18822,7 +18199,7 @@
       <c r="Q870" s="4"/>
       <c r="R870" s="4"/>
     </row>
-    <row r="871" ht="13.5" customHeight="1" spans="1:18">
+    <row r="871" spans="1:18" ht="13.5" customHeight="1">
       <c r="A871" s="4"/>
       <c r="B871" s="4"/>
       <c r="C871" s="4"/>
@@ -18842,7 +18219,7 @@
       <c r="Q871" s="4"/>
       <c r="R871" s="4"/>
     </row>
-    <row r="872" ht="13.5" customHeight="1" spans="1:18">
+    <row r="872" spans="1:18" ht="13.5" customHeight="1">
       <c r="A872" s="4"/>
       <c r="B872" s="4"/>
       <c r="C872" s="4"/>
@@ -18862,7 +18239,7 @@
       <c r="Q872" s="4"/>
       <c r="R872" s="4"/>
     </row>
-    <row r="873" ht="13.5" customHeight="1" spans="1:18">
+    <row r="873" spans="1:18" ht="13.5" customHeight="1">
       <c r="A873" s="4"/>
       <c r="B873" s="4"/>
       <c r="C873" s="4"/>
@@ -18882,7 +18259,7 @@
       <c r="Q873" s="4"/>
       <c r="R873" s="4"/>
     </row>
-    <row r="874" ht="13.5" customHeight="1" spans="1:18">
+    <row r="874" spans="1:18" ht="13.5" customHeight="1">
       <c r="A874" s="4"/>
       <c r="B874" s="4"/>
       <c r="C874" s="4"/>
@@ -18902,7 +18279,7 @@
       <c r="Q874" s="4"/>
       <c r="R874" s="4"/>
     </row>
-    <row r="875" ht="13.5" customHeight="1" spans="1:18">
+    <row r="875" spans="1:18" ht="13.5" customHeight="1">
       <c r="A875" s="4"/>
       <c r="B875" s="4"/>
       <c r="C875" s="4"/>
@@ -18922,7 +18299,7 @@
       <c r="Q875" s="4"/>
       <c r="R875" s="4"/>
     </row>
-    <row r="876" ht="13.5" customHeight="1" spans="1:18">
+    <row r="876" spans="1:18" ht="13.5" customHeight="1">
       <c r="A876" s="4"/>
       <c r="B876" s="4"/>
       <c r="C876" s="4"/>
@@ -18942,7 +18319,7 @@
       <c r="Q876" s="4"/>
       <c r="R876" s="4"/>
     </row>
-    <row r="877" ht="13.5" customHeight="1" spans="1:18">
+    <row r="877" spans="1:18" ht="13.5" customHeight="1">
       <c r="A877" s="4"/>
       <c r="B877" s="4"/>
       <c r="C877" s="4"/>
@@ -18962,7 +18339,7 @@
       <c r="Q877" s="4"/>
       <c r="R877" s="4"/>
     </row>
-    <row r="878" ht="13.5" customHeight="1" spans="1:18">
+    <row r="878" spans="1:18" ht="13.5" customHeight="1">
       <c r="A878" s="4"/>
       <c r="B878" s="4"/>
       <c r="C878" s="4"/>
@@ -18982,7 +18359,7 @@
       <c r="Q878" s="4"/>
       <c r="R878" s="4"/>
     </row>
-    <row r="879" ht="13.5" customHeight="1" spans="1:18">
+    <row r="879" spans="1:18" ht="13.5" customHeight="1">
       <c r="A879" s="4"/>
       <c r="B879" s="4"/>
       <c r="C879" s="4"/>
@@ -19002,7 +18379,7 @@
       <c r="Q879" s="4"/>
       <c r="R879" s="4"/>
     </row>
-    <row r="880" ht="13.5" customHeight="1" spans="1:18">
+    <row r="880" spans="1:18" ht="13.5" customHeight="1">
       <c r="A880" s="4"/>
       <c r="B880" s="4"/>
       <c r="C880" s="4"/>
@@ -19022,7 +18399,7 @@
       <c r="Q880" s="4"/>
       <c r="R880" s="4"/>
     </row>
-    <row r="881" ht="13.5" customHeight="1" spans="1:18">
+    <row r="881" spans="1:18" ht="13.5" customHeight="1">
       <c r="A881" s="4"/>
       <c r="B881" s="4"/>
       <c r="C881" s="4"/>
@@ -19042,7 +18419,7 @@
       <c r="Q881" s="4"/>
       <c r="R881" s="4"/>
     </row>
-    <row r="882" ht="13.5" customHeight="1" spans="1:18">
+    <row r="882" spans="1:18" ht="13.5" customHeight="1">
       <c r="A882" s="4"/>
       <c r="B882" s="4"/>
       <c r="C882" s="4"/>
@@ -19062,7 +18439,7 @@
       <c r="Q882" s="4"/>
       <c r="R882" s="4"/>
     </row>
-    <row r="883" ht="13.5" customHeight="1" spans="1:18">
+    <row r="883" spans="1:18" ht="13.5" customHeight="1">
       <c r="A883" s="4"/>
       <c r="B883" s="4"/>
       <c r="C883" s="4"/>
@@ -19082,7 +18459,7 @@
       <c r="Q883" s="4"/>
       <c r="R883" s="4"/>
     </row>
-    <row r="884" ht="13.5" customHeight="1" spans="1:18">
+    <row r="884" spans="1:18" ht="13.5" customHeight="1">
       <c r="A884" s="4"/>
       <c r="B884" s="4"/>
       <c r="C884" s="4"/>
@@ -19102,7 +18479,7 @@
       <c r="Q884" s="4"/>
       <c r="R884" s="4"/>
     </row>
-    <row r="885" ht="13.5" customHeight="1" spans="1:18">
+    <row r="885" spans="1:18" ht="13.5" customHeight="1">
       <c r="A885" s="4"/>
       <c r="B885" s="4"/>
       <c r="C885" s="4"/>
@@ -19122,7 +18499,7 @@
       <c r="Q885" s="4"/>
       <c r="R885" s="4"/>
     </row>
-    <row r="886" ht="13.5" customHeight="1" spans="1:18">
+    <row r="886" spans="1:18" ht="13.5" customHeight="1">
       <c r="A886" s="4"/>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
@@ -19142,7 +18519,7 @@
       <c r="Q886" s="4"/>
       <c r="R886" s="4"/>
     </row>
-    <row r="887" ht="13.5" customHeight="1" spans="1:18">
+    <row r="887" spans="1:18" ht="13.5" customHeight="1">
       <c r="A887" s="4"/>
       <c r="B887" s="4"/>
       <c r="C887" s="4"/>
@@ -19162,7 +18539,7 @@
       <c r="Q887" s="4"/>
       <c r="R887" s="4"/>
     </row>
-    <row r="888" ht="13.5" customHeight="1" spans="1:18">
+    <row r="888" spans="1:18" ht="13.5" customHeight="1">
       <c r="A888" s="4"/>
       <c r="B888" s="4"/>
       <c r="C888" s="4"/>
@@ -19182,7 +18559,7 @@
       <c r="Q888" s="4"/>
       <c r="R888" s="4"/>
     </row>
-    <row r="889" ht="13.5" customHeight="1" spans="1:18">
+    <row r="889" spans="1:18" ht="13.5" customHeight="1">
       <c r="A889" s="4"/>
       <c r="B889" s="4"/>
       <c r="C889" s="4"/>
@@ -19202,7 +18579,7 @@
       <c r="Q889" s="4"/>
       <c r="R889" s="4"/>
     </row>
-    <row r="890" ht="13.5" customHeight="1" spans="1:18">
+    <row r="890" spans="1:18" ht="13.5" customHeight="1">
       <c r="A890" s="4"/>
       <c r="B890" s="4"/>
       <c r="C890" s="4"/>
@@ -19222,7 +18599,7 @@
       <c r="Q890" s="4"/>
       <c r="R890" s="4"/>
     </row>
-    <row r="891" ht="13.5" customHeight="1" spans="1:18">
+    <row r="891" spans="1:18" ht="13.5" customHeight="1">
       <c r="A891" s="4"/>
       <c r="B891" s="4"/>
       <c r="C891" s="4"/>
@@ -19242,7 +18619,7 @@
       <c r="Q891" s="4"/>
       <c r="R891" s="4"/>
     </row>
-    <row r="892" ht="13.5" customHeight="1" spans="1:18">
+    <row r="892" spans="1:18" ht="13.5" customHeight="1">
       <c r="A892" s="4"/>
       <c r="B892" s="4"/>
       <c r="C892" s="4"/>
@@ -19262,7 +18639,7 @@
       <c r="Q892" s="4"/>
       <c r="R892" s="4"/>
     </row>
-    <row r="893" ht="13.5" customHeight="1" spans="1:18">
+    <row r="893" spans="1:18" ht="13.5" customHeight="1">
       <c r="A893" s="4"/>
       <c r="B893" s="4"/>
       <c r="C893" s="4"/>
@@ -19282,7 +18659,7 @@
       <c r="Q893" s="4"/>
       <c r="R893" s="4"/>
     </row>
-    <row r="894" ht="13.5" customHeight="1" spans="1:18">
+    <row r="894" spans="1:18" ht="13.5" customHeight="1">
       <c r="A894" s="4"/>
       <c r="B894" s="4"/>
       <c r="C894" s="4"/>
@@ -19302,7 +18679,7 @@
       <c r="Q894" s="4"/>
       <c r="R894" s="4"/>
     </row>
-    <row r="895" ht="13.5" customHeight="1" spans="1:18">
+    <row r="895" spans="1:18" ht="13.5" customHeight="1">
       <c r="A895" s="4"/>
       <c r="B895" s="4"/>
       <c r="C895" s="4"/>
@@ -19322,7 +18699,7 @@
       <c r="Q895" s="4"/>
       <c r="R895" s="4"/>
     </row>
-    <row r="896" ht="13.5" customHeight="1" spans="1:18">
+    <row r="896" spans="1:18" ht="13.5" customHeight="1">
       <c r="A896" s="4"/>
       <c r="B896" s="4"/>
       <c r="C896" s="4"/>
@@ -19342,7 +18719,7 @@
       <c r="Q896" s="4"/>
       <c r="R896" s="4"/>
     </row>
-    <row r="897" ht="13.5" customHeight="1" spans="1:18">
+    <row r="897" spans="1:18" ht="13.5" customHeight="1">
       <c r="A897" s="4"/>
       <c r="B897" s="4"/>
       <c r="C897" s="4"/>
@@ -19362,7 +18739,7 @@
       <c r="Q897" s="4"/>
       <c r="R897" s="4"/>
     </row>
-    <row r="898" ht="13.5" customHeight="1" spans="1:18">
+    <row r="898" spans="1:18" ht="13.5" customHeight="1">
       <c r="A898" s="4"/>
       <c r="B898" s="4"/>
       <c r="C898" s="4"/>
@@ -19382,7 +18759,7 @@
       <c r="Q898" s="4"/>
       <c r="R898" s="4"/>
     </row>
-    <row r="899" ht="13.5" customHeight="1" spans="1:18">
+    <row r="899" spans="1:18" ht="13.5" customHeight="1">
       <c r="A899" s="4"/>
       <c r="B899" s="4"/>
       <c r="C899" s="4"/>
@@ -19402,7 +18779,7 @@
       <c r="Q899" s="4"/>
       <c r="R899" s="4"/>
     </row>
-    <row r="900" ht="13.5" customHeight="1" spans="1:18">
+    <row r="900" spans="1:18" ht="13.5" customHeight="1">
       <c r="A900" s="4"/>
       <c r="B900" s="4"/>
       <c r="C900" s="4"/>
@@ -19422,7 +18799,7 @@
       <c r="Q900" s="4"/>
       <c r="R900" s="4"/>
     </row>
-    <row r="901" ht="13.5" customHeight="1" spans="1:18">
+    <row r="901" spans="1:18" ht="13.5" customHeight="1">
       <c r="A901" s="4"/>
       <c r="B901" s="4"/>
       <c r="C901" s="4"/>
@@ -19442,7 +18819,7 @@
       <c r="Q901" s="4"/>
       <c r="R901" s="4"/>
     </row>
-    <row r="902" ht="13.5" customHeight="1" spans="1:18">
+    <row r="902" spans="1:18" ht="13.5" customHeight="1">
       <c r="A902" s="4"/>
       <c r="B902" s="4"/>
       <c r="C902" s="4"/>
@@ -19462,7 +18839,7 @@
       <c r="Q902" s="4"/>
       <c r="R902" s="4"/>
     </row>
-    <row r="903" ht="13.5" customHeight="1" spans="1:18">
+    <row r="903" spans="1:18" ht="13.5" customHeight="1">
       <c r="A903" s="4"/>
       <c r="B903" s="4"/>
       <c r="C903" s="4"/>
@@ -19482,7 +18859,7 @@
       <c r="Q903" s="4"/>
       <c r="R903" s="4"/>
     </row>
-    <row r="904" ht="13.5" customHeight="1" spans="1:18">
+    <row r="904" spans="1:18" ht="13.5" customHeight="1">
       <c r="A904" s="4"/>
       <c r="B904" s="4"/>
       <c r="C904" s="4"/>
@@ -19502,7 +18879,7 @@
       <c r="Q904" s="4"/>
       <c r="R904" s="4"/>
     </row>
-    <row r="905" ht="13.5" customHeight="1" spans="1:18">
+    <row r="905" spans="1:18" ht="13.5" customHeight="1">
       <c r="A905" s="4"/>
       <c r="B905" s="4"/>
       <c r="C905" s="4"/>
@@ -19522,7 +18899,7 @@
       <c r="Q905" s="4"/>
       <c r="R905" s="4"/>
     </row>
-    <row r="906" ht="13.5" customHeight="1" spans="1:18">
+    <row r="906" spans="1:18" ht="13.5" customHeight="1">
       <c r="A906" s="4"/>
       <c r="B906" s="4"/>
       <c r="C906" s="4"/>
@@ -19542,7 +18919,7 @@
       <c r="Q906" s="4"/>
       <c r="R906" s="4"/>
     </row>
-    <row r="907" ht="13.5" customHeight="1" spans="1:18">
+    <row r="907" spans="1:18" ht="13.5" customHeight="1">
       <c r="A907" s="4"/>
       <c r="B907" s="4"/>
       <c r="C907" s="4"/>
@@ -19562,7 +18939,7 @@
       <c r="Q907" s="4"/>
       <c r="R907" s="4"/>
     </row>
-    <row r="908" ht="13.5" customHeight="1" spans="1:18">
+    <row r="908" spans="1:18" ht="13.5" customHeight="1">
       <c r="A908" s="4"/>
       <c r="B908" s="4"/>
       <c r="C908" s="4"/>
@@ -19582,7 +18959,7 @@
       <c r="Q908" s="4"/>
       <c r="R908" s="4"/>
     </row>
-    <row r="909" ht="13.5" customHeight="1" spans="1:18">
+    <row r="909" spans="1:18" ht="13.5" customHeight="1">
       <c r="A909" s="4"/>
       <c r="B909" s="4"/>
       <c r="C909" s="4"/>
@@ -19602,7 +18979,7 @@
       <c r="Q909" s="4"/>
       <c r="R909" s="4"/>
     </row>
-    <row r="910" ht="13.5" customHeight="1" spans="1:18">
+    <row r="910" spans="1:18" ht="13.5" customHeight="1">
       <c r="A910" s="4"/>
       <c r="B910" s="4"/>
       <c r="C910" s="4"/>
@@ -19622,7 +18999,7 @@
       <c r="Q910" s="4"/>
       <c r="R910" s="4"/>
     </row>
-    <row r="911" ht="13.5" customHeight="1" spans="1:18">
+    <row r="911" spans="1:18" ht="13.5" customHeight="1">
       <c r="A911" s="4"/>
       <c r="B911" s="4"/>
       <c r="C911" s="4"/>
@@ -19642,7 +19019,7 @@
       <c r="Q911" s="4"/>
       <c r="R911" s="4"/>
     </row>
-    <row r="912" ht="13.5" customHeight="1" spans="1:18">
+    <row r="912" spans="1:18" ht="13.5" customHeight="1">
       <c r="A912" s="4"/>
       <c r="B912" s="4"/>
       <c r="C912" s="4"/>
@@ -19662,7 +19039,7 @@
       <c r="Q912" s="4"/>
       <c r="R912" s="4"/>
     </row>
-    <row r="913" ht="13.5" customHeight="1" spans="1:18">
+    <row r="913" spans="1:18" ht="13.5" customHeight="1">
       <c r="A913" s="4"/>
       <c r="B913" s="4"/>
       <c r="C913" s="4"/>
@@ -19682,7 +19059,7 @@
       <c r="Q913" s="4"/>
       <c r="R913" s="4"/>
     </row>
-    <row r="914" ht="13.5" customHeight="1" spans="1:18">
+    <row r="914" spans="1:18" ht="13.5" customHeight="1">
       <c r="A914" s="4"/>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
@@ -19702,7 +19079,7 @@
       <c r="Q914" s="4"/>
       <c r="R914" s="4"/>
     </row>
-    <row r="915" ht="13.5" customHeight="1" spans="1:18">
+    <row r="915" spans="1:18" ht="13.5" customHeight="1">
       <c r="A915" s="4"/>
       <c r="B915" s="4"/>
       <c r="C915" s="4"/>
@@ -19722,7 +19099,7 @@
       <c r="Q915" s="4"/>
       <c r="R915" s="4"/>
     </row>
-    <row r="916" ht="13.5" customHeight="1" spans="1:18">
+    <row r="916" spans="1:18" ht="13.5" customHeight="1">
       <c r="A916" s="4"/>
       <c r="B916" s="4"/>
       <c r="C916" s="4"/>
@@ -19742,7 +19119,7 @@
       <c r="Q916" s="4"/>
       <c r="R916" s="4"/>
     </row>
-    <row r="917" ht="13.5" customHeight="1" spans="1:18">
+    <row r="917" spans="1:18" ht="13.5" customHeight="1">
       <c r="A917" s="4"/>
       <c r="B917" s="4"/>
       <c r="C917" s="4"/>
@@ -19762,7 +19139,7 @@
       <c r="Q917" s="4"/>
       <c r="R917" s="4"/>
     </row>
-    <row r="918" ht="13.5" customHeight="1" spans="1:18">
+    <row r="918" spans="1:18" ht="13.5" customHeight="1">
       <c r="A918" s="4"/>
       <c r="B918" s="4"/>
       <c r="C918" s="4"/>
@@ -19782,7 +19159,7 @@
       <c r="Q918" s="4"/>
       <c r="R918" s="4"/>
     </row>
-    <row r="919" ht="13.5" customHeight="1" spans="1:18">
+    <row r="919" spans="1:18" ht="13.5" customHeight="1">
       <c r="A919" s="4"/>
       <c r="B919" s="4"/>
       <c r="C919" s="4"/>
@@ -19802,7 +19179,7 @@
       <c r="Q919" s="4"/>
       <c r="R919" s="4"/>
     </row>
-    <row r="920" ht="13.5" customHeight="1" spans="1:18">
+    <row r="920" spans="1:18" ht="13.5" customHeight="1">
       <c r="A920" s="4"/>
       <c r="B920" s="4"/>
       <c r="C920" s="4"/>
@@ -19822,7 +19199,7 @@
       <c r="Q920" s="4"/>
       <c r="R920" s="4"/>
     </row>
-    <row r="921" ht="13.5" customHeight="1" spans="1:18">
+    <row r="921" spans="1:18" ht="13.5" customHeight="1">
       <c r="A921" s="4"/>
       <c r="B921" s="4"/>
       <c r="C921" s="4"/>
@@ -19842,7 +19219,7 @@
       <c r="Q921" s="4"/>
       <c r="R921" s="4"/>
     </row>
-    <row r="922" ht="13.5" customHeight="1" spans="1:18">
+    <row r="922" spans="1:18" ht="13.5" customHeight="1">
       <c r="A922" s="4"/>
       <c r="B922" s="4"/>
       <c r="C922" s="4"/>
@@ -19862,7 +19239,7 @@
       <c r="Q922" s="4"/>
       <c r="R922" s="4"/>
     </row>
-    <row r="923" ht="13.5" customHeight="1" spans="1:18">
+    <row r="923" spans="1:18" ht="13.5" customHeight="1">
       <c r="A923" s="4"/>
       <c r="B923" s="4"/>
       <c r="C923" s="4"/>
@@ -19882,7 +19259,7 @@
       <c r="Q923" s="4"/>
       <c r="R923" s="4"/>
     </row>
-    <row r="924" ht="13.5" customHeight="1" spans="1:18">
+    <row r="924" spans="1:18" ht="13.5" customHeight="1">
       <c r="A924" s="4"/>
       <c r="B924" s="4"/>
       <c r="C924" s="4"/>
@@ -19902,7 +19279,7 @@
       <c r="Q924" s="4"/>
       <c r="R924" s="4"/>
     </row>
-    <row r="925" ht="13.5" customHeight="1" spans="1:18">
+    <row r="925" spans="1:18" ht="13.5" customHeight="1">
       <c r="A925" s="4"/>
       <c r="B925" s="4"/>
       <c r="C925" s="4"/>
@@ -19922,7 +19299,7 @@
       <c r="Q925" s="4"/>
       <c r="R925" s="4"/>
     </row>
-    <row r="926" ht="13.5" customHeight="1" spans="1:18">
+    <row r="926" spans="1:18" ht="13.5" customHeight="1">
       <c r="A926" s="4"/>
       <c r="B926" s="4"/>
       <c r="C926" s="4"/>
@@ -19942,7 +19319,7 @@
       <c r="Q926" s="4"/>
       <c r="R926" s="4"/>
     </row>
-    <row r="927" ht="13.5" customHeight="1" spans="1:18">
+    <row r="927" spans="1:18" ht="13.5" customHeight="1">
       <c r="A927" s="4"/>
       <c r="B927" s="4"/>
       <c r="C927" s="4"/>
@@ -19962,7 +19339,7 @@
       <c r="Q927" s="4"/>
       <c r="R927" s="4"/>
     </row>
-    <row r="928" ht="13.5" customHeight="1" spans="1:18">
+    <row r="928" spans="1:18" ht="13.5" customHeight="1">
       <c r="A928" s="4"/>
       <c r="B928" s="4"/>
       <c r="C928" s="4"/>
@@ -19982,7 +19359,7 @@
       <c r="Q928" s="4"/>
       <c r="R928" s="4"/>
     </row>
-    <row r="929" ht="13.5" customHeight="1" spans="1:18">
+    <row r="929" spans="1:18" ht="13.5" customHeight="1">
       <c r="A929" s="4"/>
       <c r="B929" s="4"/>
       <c r="C929" s="4"/>
@@ -20002,7 +19379,7 @@
       <c r="Q929" s="4"/>
       <c r="R929" s="4"/>
     </row>
-    <row r="930" ht="13.5" customHeight="1" spans="1:18">
+    <row r="930" spans="1:18" ht="13.5" customHeight="1">
       <c r="A930" s="4"/>
       <c r="B930" s="4"/>
       <c r="C930" s="4"/>
@@ -20022,7 +19399,7 @@
       <c r="Q930" s="4"/>
       <c r="R930" s="4"/>
     </row>
-    <row r="931" ht="13.5" customHeight="1" spans="1:18">
+    <row r="931" spans="1:18" ht="13.5" customHeight="1">
       <c r="A931" s="4"/>
       <c r="B931" s="4"/>
       <c r="C931" s="4"/>
@@ -20042,7 +19419,7 @@
       <c r="Q931" s="4"/>
       <c r="R931" s="4"/>
     </row>
-    <row r="932" ht="13.5" customHeight="1" spans="1:18">
+    <row r="932" spans="1:18" ht="13.5" customHeight="1">
       <c r="A932" s="4"/>
       <c r="B932" s="4"/>
       <c r="C932" s="4"/>
@@ -20062,7 +19439,7 @@
       <c r="Q932" s="4"/>
       <c r="R932" s="4"/>
     </row>
-    <row r="933" ht="13.5" customHeight="1" spans="1:18">
+    <row r="933" spans="1:18" ht="13.5" customHeight="1">
       <c r="A933" s="4"/>
       <c r="B933" s="4"/>
       <c r="C933" s="4"/>
@@ -20082,7 +19459,7 @@
       <c r="Q933" s="4"/>
       <c r="R933" s="4"/>
     </row>
-    <row r="934" ht="13.5" customHeight="1" spans="1:18">
+    <row r="934" spans="1:18" ht="13.5" customHeight="1">
       <c r="A934" s="4"/>
       <c r="B934" s="4"/>
       <c r="C934" s="4"/>
@@ -20102,7 +19479,7 @@
       <c r="Q934" s="4"/>
       <c r="R934" s="4"/>
     </row>
-    <row r="935" ht="13.5" customHeight="1" spans="1:18">
+    <row r="935" spans="1:18" ht="13.5" customHeight="1">
       <c r="A935" s="4"/>
       <c r="B935" s="4"/>
       <c r="C935" s="4"/>
@@ -20122,7 +19499,7 @@
       <c r="Q935" s="4"/>
       <c r="R935" s="4"/>
     </row>
-    <row r="936" ht="13.5" customHeight="1" spans="1:18">
+    <row r="936" spans="1:18" ht="13.5" customHeight="1">
       <c r="A936" s="4"/>
       <c r="B936" s="4"/>
       <c r="C936" s="4"/>
@@ -20142,7 +19519,7 @@
       <c r="Q936" s="4"/>
       <c r="R936" s="4"/>
     </row>
-    <row r="937" ht="13.5" customHeight="1" spans="1:18">
+    <row r="937" spans="1:18" ht="13.5" customHeight="1">
       <c r="A937" s="4"/>
       <c r="B937" s="4"/>
       <c r="C937" s="4"/>
@@ -20162,7 +19539,7 @@
       <c r="Q937" s="4"/>
       <c r="R937" s="4"/>
     </row>
-    <row r="938" ht="13.5" customHeight="1" spans="1:18">
+    <row r="938" spans="1:18" ht="13.5" customHeight="1">
       <c r="A938" s="4"/>
       <c r="B938" s="4"/>
       <c r="C938" s="4"/>
@@ -20182,7 +19559,7 @@
       <c r="Q938" s="4"/>
       <c r="R938" s="4"/>
     </row>
-    <row r="939" ht="13.5" customHeight="1" spans="1:18">
+    <row r="939" spans="1:18" ht="13.5" customHeight="1">
       <c r="A939" s="4"/>
       <c r="B939" s="4"/>
       <c r="C939" s="4"/>
@@ -20202,7 +19579,7 @@
       <c r="Q939" s="4"/>
       <c r="R939" s="4"/>
     </row>
-    <row r="940" ht="13.5" customHeight="1" spans="1:18">
+    <row r="940" spans="1:18" ht="13.5" customHeight="1">
       <c r="A940" s="4"/>
       <c r="B940" s="4"/>
       <c r="C940" s="4"/>
@@ -20222,7 +19599,7 @@
       <c r="Q940" s="4"/>
       <c r="R940" s="4"/>
     </row>
-    <row r="941" ht="13.5" customHeight="1" spans="1:18">
+    <row r="941" spans="1:18" ht="13.5" customHeight="1">
       <c r="A941" s="4"/>
       <c r="B941" s="4"/>
       <c r="C941" s="4"/>
@@ -20242,7 +19619,7 @@
       <c r="Q941" s="4"/>
       <c r="R941" s="4"/>
     </row>
-    <row r="942" ht="13.5" customHeight="1" spans="1:18">
+    <row r="942" spans="1:18" ht="13.5" customHeight="1">
       <c r="A942" s="4"/>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
@@ -20262,7 +19639,7 @@
       <c r="Q942" s="4"/>
       <c r="R942" s="4"/>
     </row>
-    <row r="943" ht="13.5" customHeight="1" spans="1:18">
+    <row r="943" spans="1:18" ht="13.5" customHeight="1">
       <c r="A943" s="4"/>
       <c r="B943" s="4"/>
       <c r="C943" s="4"/>
@@ -20282,7 +19659,7 @@
       <c r="Q943" s="4"/>
       <c r="R943" s="4"/>
     </row>
-    <row r="944" ht="13.5" customHeight="1" spans="1:18">
+    <row r="944" spans="1:18" ht="13.5" customHeight="1">
       <c r="A944" s="4"/>
       <c r="B944" s="4"/>
       <c r="C944" s="4"/>
@@ -20302,7 +19679,7 @@
       <c r="Q944" s="4"/>
       <c r="R944" s="4"/>
     </row>
-    <row r="945" ht="13.5" customHeight="1" spans="1:18">
+    <row r="945" spans="1:18" ht="13.5" customHeight="1">
       <c r="A945" s="4"/>
       <c r="B945" s="4"/>
       <c r="C945" s="4"/>
@@ -20322,7 +19699,7 @@
       <c r="Q945" s="4"/>
       <c r="R945" s="4"/>
     </row>
-    <row r="946" ht="13.5" customHeight="1" spans="1:18">
+    <row r="946" spans="1:18" ht="13.5" customHeight="1">
       <c r="A946" s="4"/>
       <c r="B946" s="4"/>
       <c r="C946" s="4"/>
@@ -20342,7 +19719,7 @@
       <c r="Q946" s="4"/>
       <c r="R946" s="4"/>
     </row>
-    <row r="947" ht="13.5" customHeight="1" spans="1:18">
+    <row r="947" spans="1:18" ht="13.5" customHeight="1">
       <c r="A947" s="4"/>
       <c r="B947" s="4"/>
       <c r="C947" s="4"/>
@@ -20362,7 +19739,7 @@
       <c r="Q947" s="4"/>
       <c r="R947" s="4"/>
     </row>
-    <row r="948" ht="13.5" customHeight="1" spans="1:18">
+    <row r="948" spans="1:18" ht="13.5" customHeight="1">
       <c r="A948" s="4"/>
       <c r="B948" s="4"/>
       <c r="C948" s="4"/>
@@ -20382,7 +19759,7 @@
       <c r="Q948" s="4"/>
       <c r="R948" s="4"/>
     </row>
-    <row r="949" ht="13.5" customHeight="1" spans="1:18">
+    <row r="949" spans="1:18" ht="13.5" customHeight="1">
       <c r="A949" s="4"/>
       <c r="B949" s="4"/>
       <c r="C949" s="4"/>
@@ -20402,7 +19779,7 @@
       <c r="Q949" s="4"/>
       <c r="R949" s="4"/>
     </row>
-    <row r="950" ht="13.5" customHeight="1" spans="1:18">
+    <row r="950" spans="1:18" ht="13.5" customHeight="1">
       <c r="A950" s="4"/>
       <c r="B950" s="4"/>
       <c r="C950" s="4"/>
@@ -20422,7 +19799,7 @@
       <c r="Q950" s="4"/>
       <c r="R950" s="4"/>
     </row>
-    <row r="951" ht="13.5" customHeight="1" spans="1:18">
+    <row r="951" spans="1:18" ht="13.5" customHeight="1">
       <c r="A951" s="4"/>
       <c r="B951" s="4"/>
       <c r="C951" s="4"/>
@@ -20442,7 +19819,7 @@
       <c r="Q951" s="4"/>
       <c r="R951" s="4"/>
     </row>
-    <row r="952" ht="13.5" customHeight="1" spans="1:18">
+    <row r="952" spans="1:18" ht="13.5" customHeight="1">
       <c r="A952" s="4"/>
       <c r="B952" s="4"/>
       <c r="C952" s="4"/>
@@ -20462,7 +19839,7 @@
       <c r="Q952" s="4"/>
       <c r="R952" s="4"/>
     </row>
-    <row r="953" ht="13.5" customHeight="1" spans="1:18">
+    <row r="953" spans="1:18" ht="13.5" customHeight="1">
       <c r="A953" s="4"/>
       <c r="B953" s="4"/>
       <c r="C953" s="4"/>
@@ -20482,7 +19859,7 @@
       <c r="Q953" s="4"/>
       <c r="R953" s="4"/>
     </row>
-    <row r="954" ht="13.5" customHeight="1" spans="1:18">
+    <row r="954" spans="1:18" ht="13.5" customHeight="1">
       <c r="A954" s="4"/>
       <c r="B954" s="4"/>
       <c r="C954" s="4"/>
@@ -20502,7 +19879,7 @@
       <c r="Q954" s="4"/>
       <c r="R954" s="4"/>
     </row>
-    <row r="955" ht="13.5" customHeight="1" spans="1:18">
+    <row r="955" spans="1:18" ht="13.5" customHeight="1">
       <c r="A955" s="4"/>
       <c r="B955" s="4"/>
       <c r="C955" s="4"/>
@@ -20522,7 +19899,7 @@
       <c r="Q955" s="4"/>
       <c r="R955" s="4"/>
     </row>
-    <row r="956" ht="13.5" customHeight="1" spans="1:18">
+    <row r="956" spans="1:18" ht="13.5" customHeight="1">
       <c r="A956" s="4"/>
       <c r="B956" s="4"/>
       <c r="C956" s="4"/>
@@ -20542,7 +19919,7 @@
       <c r="Q956" s="4"/>
       <c r="R956" s="4"/>
     </row>
-    <row r="957" ht="13.5" customHeight="1" spans="1:18">
+    <row r="957" spans="1:18" ht="13.5" customHeight="1">
       <c r="A957" s="4"/>
       <c r="B957" s="4"/>
       <c r="C957" s="4"/>
@@ -20562,7 +19939,7 @@
       <c r="Q957" s="4"/>
       <c r="R957" s="4"/>
     </row>
-    <row r="958" ht="13.5" customHeight="1" spans="1:18">
+    <row r="958" spans="1:18" ht="13.5" customHeight="1">
       <c r="A958" s="4"/>
       <c r="B958" s="4"/>
       <c r="C958" s="4"/>
@@ -20582,7 +19959,7 @@
       <c r="Q958" s="4"/>
       <c r="R958" s="4"/>
     </row>
-    <row r="959" ht="13.5" customHeight="1" spans="1:18">
+    <row r="959" spans="1:18" ht="13.5" customHeight="1">
       <c r="A959" s="4"/>
       <c r="B959" s="4"/>
       <c r="C959" s="4"/>
@@ -20602,7 +19979,7 @@
       <c r="Q959" s="4"/>
       <c r="R959" s="4"/>
     </row>
-    <row r="960" ht="13.5" customHeight="1" spans="1:18">
+    <row r="960" spans="1:18" ht="13.5" customHeight="1">
       <c r="A960" s="4"/>
       <c r="B960" s="4"/>
       <c r="C960" s="4"/>
@@ -20622,7 +19999,7 @@
       <c r="Q960" s="4"/>
       <c r="R960" s="4"/>
     </row>
-    <row r="961" ht="13.5" customHeight="1" spans="1:18">
+    <row r="961" spans="1:18" ht="13.5" customHeight="1">
       <c r="A961" s="4"/>
       <c r="B961" s="4"/>
       <c r="C961" s="4"/>
@@ -20642,7 +20019,7 @@
       <c r="Q961" s="4"/>
       <c r="R961" s="4"/>
     </row>
-    <row r="962" ht="13.5" customHeight="1" spans="1:18">
+    <row r="962" spans="1:18" ht="13.5" customHeight="1">
       <c r="A962" s="4"/>
       <c r="B962" s="4"/>
       <c r="C962" s="4"/>
@@ -20662,7 +20039,7 @@
       <c r="Q962" s="4"/>
       <c r="R962" s="4"/>
     </row>
-    <row r="963" ht="13.5" customHeight="1" spans="1:18">
+    <row r="963" spans="1:18" ht="13.5" customHeight="1">
       <c r="A963" s="4"/>
       <c r="B963" s="4"/>
       <c r="C963" s="4"/>
@@ -20682,7 +20059,7 @@
       <c r="Q963" s="4"/>
       <c r="R963" s="4"/>
     </row>
-    <row r="964" ht="13.5" customHeight="1" spans="1:18">
+    <row r="964" spans="1:18" ht="13.5" customHeight="1">
       <c r="A964" s="4"/>
       <c r="B964" s="4"/>
       <c r="C964" s="4"/>
@@ -20702,7 +20079,7 @@
       <c r="Q964" s="4"/>
       <c r="R964" s="4"/>
     </row>
-    <row r="965" ht="13.5" customHeight="1" spans="1:18">
+    <row r="965" spans="1:18" ht="13.5" customHeight="1">
       <c r="A965" s="4"/>
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
@@ -20722,7 +20099,7 @@
       <c r="Q965" s="4"/>
       <c r="R965" s="4"/>
     </row>
-    <row r="966" ht="13.5" customHeight="1" spans="1:18">
+    <row r="966" spans="1:18" ht="13.5" customHeight="1">
       <c r="A966" s="4"/>
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
@@ -20742,7 +20119,7 @@
       <c r="Q966" s="4"/>
       <c r="R966" s="4"/>
     </row>
-    <row r="967" ht="13.5" customHeight="1" spans="1:18">
+    <row r="967" spans="1:18" ht="13.5" customHeight="1">
       <c r="A967" s="4"/>
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
@@ -20762,7 +20139,7 @@
       <c r="Q967" s="4"/>
       <c r="R967" s="4"/>
     </row>
-    <row r="968" ht="13.5" customHeight="1" spans="1:18">
+    <row r="968" spans="1:18" ht="13.5" customHeight="1">
       <c r="A968" s="4"/>
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
@@ -20782,7 +20159,7 @@
       <c r="Q968" s="4"/>
       <c r="R968" s="4"/>
     </row>
-    <row r="969" ht="13.5" customHeight="1" spans="1:18">
+    <row r="969" spans="1:18" ht="13.5" customHeight="1">
       <c r="A969" s="4"/>
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
@@ -20802,7 +20179,7 @@
       <c r="Q969" s="4"/>
       <c r="R969" s="4"/>
     </row>
-    <row r="970" ht="13.5" customHeight="1" spans="1:18">
+    <row r="970" spans="1:18" ht="13.5" customHeight="1">
       <c r="A970" s="4"/>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
@@ -20822,7 +20199,7 @@
       <c r="Q970" s="4"/>
       <c r="R970" s="4"/>
     </row>
-    <row r="971" ht="13.5" customHeight="1" spans="1:18">
+    <row r="971" spans="1:18" ht="13.5" customHeight="1">
       <c r="A971" s="4"/>
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
@@ -20842,7 +20219,7 @@
       <c r="Q971" s="4"/>
       <c r="R971" s="4"/>
     </row>
-    <row r="972" ht="13.5" customHeight="1" spans="1:18">
+    <row r="972" spans="1:18" ht="13.5" customHeight="1">
       <c r="A972" s="4"/>
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
@@ -20862,7 +20239,7 @@
       <c r="Q972" s="4"/>
       <c r="R972" s="4"/>
     </row>
-    <row r="973" ht="13.5" customHeight="1" spans="1:18">
+    <row r="973" spans="1:18" ht="13.5" customHeight="1">
       <c r="A973" s="4"/>
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
@@ -20882,7 +20259,7 @@
       <c r="Q973" s="4"/>
       <c r="R973" s="4"/>
     </row>
-    <row r="974" ht="13.5" customHeight="1" spans="1:18">
+    <row r="974" spans="1:18" ht="13.5" customHeight="1">
       <c r="A974" s="4"/>
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
@@ -20902,7 +20279,7 @@
       <c r="Q974" s="4"/>
       <c r="R974" s="4"/>
     </row>
-    <row r="975" ht="13.5" customHeight="1" spans="1:18">
+    <row r="975" spans="1:18" ht="13.5" customHeight="1">
       <c r="A975" s="4"/>
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
@@ -20922,7 +20299,7 @@
       <c r="Q975" s="4"/>
       <c r="R975" s="4"/>
     </row>
-    <row r="976" ht="13.5" customHeight="1" spans="1:18">
+    <row r="976" spans="1:18" ht="13.5" customHeight="1">
       <c r="A976" s="4"/>
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
@@ -20942,7 +20319,7 @@
       <c r="Q976" s="4"/>
       <c r="R976" s="4"/>
     </row>
-    <row r="977" ht="13.5" customHeight="1" spans="1:18">
+    <row r="977" spans="1:18" ht="13.5" customHeight="1">
       <c r="A977" s="4"/>
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
@@ -20962,7 +20339,7 @@
       <c r="Q977" s="4"/>
       <c r="R977" s="4"/>
     </row>
-    <row r="978" ht="13.5" customHeight="1" spans="1:18">
+    <row r="978" spans="1:18" ht="13.5" customHeight="1">
       <c r="A978" s="4"/>
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
@@ -20982,7 +20359,7 @@
       <c r="Q978" s="4"/>
       <c r="R978" s="4"/>
     </row>
-    <row r="979" ht="13.5" customHeight="1" spans="1:18">
+    <row r="979" spans="1:18" ht="13.5" customHeight="1">
       <c r="A979" s="4"/>
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
@@ -21002,7 +20379,7 @@
       <c r="Q979" s="4"/>
       <c r="R979" s="4"/>
     </row>
-    <row r="980" ht="13.5" customHeight="1" spans="1:18">
+    <row r="980" spans="1:18" ht="13.5" customHeight="1">
       <c r="A980" s="4"/>
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
@@ -21022,7 +20399,7 @@
       <c r="Q980" s="4"/>
       <c r="R980" s="4"/>
     </row>
-    <row r="981" ht="13.5" customHeight="1" spans="1:18">
+    <row r="981" spans="1:18" ht="13.5" customHeight="1">
       <c r="A981" s="4"/>
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
@@ -21042,7 +20419,7 @@
       <c r="Q981" s="4"/>
       <c r="R981" s="4"/>
     </row>
-    <row r="982" ht="13.5" customHeight="1" spans="1:18">
+    <row r="982" spans="1:18" ht="13.5" customHeight="1">
       <c r="A982" s="4"/>
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
@@ -21062,7 +20439,7 @@
       <c r="Q982" s="4"/>
       <c r="R982" s="4"/>
     </row>
-    <row r="983" ht="13.5" customHeight="1" spans="1:18">
+    <row r="983" spans="1:18" ht="13.5" customHeight="1">
       <c r="A983" s="4"/>
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
@@ -21082,7 +20459,7 @@
       <c r="Q983" s="4"/>
       <c r="R983" s="4"/>
     </row>
-    <row r="984" ht="13.5" customHeight="1" spans="1:18">
+    <row r="984" spans="1:18" ht="13.5" customHeight="1">
       <c r="A984" s="4"/>
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
@@ -21102,7 +20479,7 @@
       <c r="Q984" s="4"/>
       <c r="R984" s="4"/>
     </row>
-    <row r="985" ht="13.5" customHeight="1" spans="1:18">
+    <row r="985" spans="1:18" ht="13.5" customHeight="1">
       <c r="A985" s="4"/>
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
@@ -21122,7 +20499,7 @@
       <c r="Q985" s="4"/>
       <c r="R985" s="4"/>
     </row>
-    <row r="986" ht="13.5" customHeight="1" spans="1:18">
+    <row r="986" spans="1:18" ht="13.5" customHeight="1">
       <c r="A986" s="4"/>
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
@@ -21142,7 +20519,7 @@
       <c r="Q986" s="4"/>
       <c r="R986" s="4"/>
     </row>
-    <row r="987" ht="13.5" customHeight="1" spans="1:18">
+    <row r="987" spans="1:18" ht="13.5" customHeight="1">
       <c r="A987" s="4"/>
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
@@ -21162,7 +20539,7 @@
       <c r="Q987" s="4"/>
       <c r="R987" s="4"/>
     </row>
-    <row r="988" ht="13.5" customHeight="1" spans="1:18">
+    <row r="988" spans="1:18" ht="13.5" customHeight="1">
       <c r="A988" s="4"/>
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
@@ -21182,7 +20559,7 @@
       <c r="Q988" s="4"/>
       <c r="R988" s="4"/>
     </row>
-    <row r="989" ht="13.5" customHeight="1" spans="1:18">
+    <row r="989" spans="1:18" ht="13.5" customHeight="1">
       <c r="A989" s="4"/>
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
@@ -21202,7 +20579,7 @@
       <c r="Q989" s="4"/>
       <c r="R989" s="4"/>
     </row>
-    <row r="990" ht="13.5" customHeight="1" spans="1:18">
+    <row r="990" spans="1:18" ht="13.5" customHeight="1">
       <c r="A990" s="4"/>
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
@@ -21222,7 +20599,7 @@
       <c r="Q990" s="4"/>
       <c r="R990" s="4"/>
     </row>
-    <row r="991" ht="13.5" customHeight="1" spans="1:18">
+    <row r="991" spans="1:18" ht="13.5" customHeight="1">
       <c r="A991" s="4"/>
       <c r="B991" s="4"/>
       <c r="C991" s="4"/>
@@ -21242,7 +20619,7 @@
       <c r="Q991" s="4"/>
       <c r="R991" s="4"/>
     </row>
-    <row r="992" ht="13.5" customHeight="1" spans="1:18">
+    <row r="992" spans="1:18" ht="13.5" customHeight="1">
       <c r="A992" s="4"/>
       <c r="B992" s="4"/>
       <c r="C992" s="4"/>
@@ -21262,7 +20639,7 @@
       <c r="Q992" s="4"/>
       <c r="R992" s="4"/>
     </row>
-    <row r="993" ht="13.5" customHeight="1" spans="1:18">
+    <row r="993" spans="1:18" ht="13.5" customHeight="1">
       <c r="A993" s="4"/>
       <c r="B993" s="4"/>
       <c r="C993" s="4"/>
@@ -21282,7 +20659,7 @@
       <c r="Q993" s="4"/>
       <c r="R993" s="4"/>
     </row>
-    <row r="994" ht="13.5" customHeight="1" spans="1:18">
+    <row r="994" spans="1:18" ht="13.5" customHeight="1">
       <c r="A994" s="4"/>
       <c r="B994" s="4"/>
       <c r="C994" s="4"/>
@@ -21302,7 +20679,7 @@
       <c r="Q994" s="4"/>
       <c r="R994" s="4"/>
     </row>
-    <row r="995" ht="13.5" customHeight="1" spans="1:18">
+    <row r="995" spans="1:18" ht="13.5" customHeight="1">
       <c r="A995" s="4"/>
       <c r="B995" s="4"/>
       <c r="C995" s="4"/>
@@ -21322,7 +20699,7 @@
       <c r="Q995" s="4"/>
       <c r="R995" s="4"/>
     </row>
-    <row r="996" ht="13.5" customHeight="1" spans="1:18">
+    <row r="996" spans="1:18" ht="13.5" customHeight="1">
       <c r="A996" s="4"/>
       <c r="B996" s="4"/>
       <c r="C996" s="4"/>
@@ -21342,7 +20719,7 @@
       <c r="Q996" s="4"/>
       <c r="R996" s="4"/>
     </row>
-    <row r="997" ht="13.5" customHeight="1" spans="1:18">
+    <row r="997" spans="1:18" ht="13.5" customHeight="1">
       <c r="A997" s="4"/>
       <c r="B997" s="4"/>
       <c r="C997" s="4"/>
@@ -21362,7 +20739,7 @@
       <c r="Q997" s="4"/>
       <c r="R997" s="4"/>
     </row>
-    <row r="998" ht="13.5" customHeight="1" spans="1:18">
+    <row r="998" spans="1:18" ht="13.5" customHeight="1">
       <c r="A998" s="4"/>
       <c r="B998" s="4"/>
       <c r="C998" s="4"/>
@@ -21385,6 +20762,5 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B31AC30-2F57-42A5-A66C-235975CEA9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="29920" windowHeight="12420"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -149,6 +143,9 @@
     <t>newProcess</t>
   </si>
   <si>
+    <t>{"id":"NEW","order":1,"flow":"NEW","isSubProcess":false,"label":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"screens":[{"order":1,"name":"consentdet","label":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"caption":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"ara":"الاسم الكامل الكامل الكامل","fra":"J'ai lu et j'accepte les termes et conditions pour partager mes PII","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"ara":"لغة الإخطار","fra":"Langue de notification","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"caption":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"fields":[{"id":"fullName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Full Name","label":{"ara":"الاسم الكامل","fra":"Nom complet","eng":"Full Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"name"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"ara":"الاسم الكامل","fra":"DOB","eng":"DOB"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"ara":"جنس","fra":"Le genre","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"ara":"الاسم الكامل","fra":"line1","eng":"line1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"ara":"الاسم الكامل","fra":"line2","eng":"line2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"addressLine3","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine3","label":{"ara":"الاسم الكامل","fra":"line3","eng":"line3"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine3"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"ara":"الاسم الكامل","fra":"Reside Status","eng":"Residence Status"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"referenceIdentityNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"referenceIdentityNumber","label":{"ara":"الاسم الكامل","fra":"Reference Identity Number","eng":"Reference Identity Number"},"controlType":"textbox","fieldType":"default","format":"kyc","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ReferenceIdentityNumber","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"none"},{"id":"region","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"region","label":{"ara":"الاسم الكامل","fra":"Region","eng":"Region"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Region"},{"id":"province","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"province","label":{"ara":"الاسم الكامل","fra":"Province","eng":"Province"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Province"},{"id":"city","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"city","label":{"ara":"الاسم الكامل","fra":"City","eng":"City"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"City"},{"id":"zone","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"zone","label":{"ara":"الاسم الكامل","fra":"Zone","eng":"Zone"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":null,"group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Zone"},{"id":"postalCode","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"postalCode","label":{"ara":"الاسم الكامل","fra":"Postal","eng":"Postal"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[(?i)A-Z0-9]{5}$|^NA$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Postal Code"},{"id":"phone","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"phone","label":{"ara":"الاسم الكامل","fra":"Phone","eng":"Phone"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[+]*([0-9]{1})([0-9]{9})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Phone"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"ara":"الاسم الكامل","fra":"Email","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"ara":"اسم المُعرّف","fra":"nom del'introducteur","eng":"Introducer Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"ara":"مقدم RID","fra":"Introducteur RID","eng":"Introducer RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"ara":"مقدم في","fra":"Introducteur UIN","eng":"Introducer UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"}],"layoutTemplate":null,"preRegFetchRequired":true,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","fra":"Des documents","eng":"Document Upload"},"caption":{"ara":"وثائق","fra":"Des documents","eng":"Documents"},"fields":[{"id":"proofOfAddress","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfAddress","label":{"ara":"إثبات العنوان","fra":"Address Proof","eng":"Address Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POA"},{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"ara":"إثبات الهوية","fra":"Identity Proof","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"ara":"إثبات العلاقة","fra":"Relationship Proof","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"ara":"دليل DOB","fra":"DOB Proof","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"ara":"إثبات الاستثناء","fra":"Exception Proof","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"caption":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"القياسات الحيوية الفردية","fra":"Applicant Biometrics","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"مقدم القياسات الحيوية","fra":"Introducteur Biométrie","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false}],"caption":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"icon":"NewReg.png","isActive":true,"autoSelectedGroups":null}</t>
+  </si>
+  <si>
     <t>703796d8-085f-4778-80be-df298c1b8367</t>
   </si>
   <si>
@@ -184,15 +181,18 @@
   <si>
     <t xml:space="preserve">{"id":"BIOMETRIC_CORRECTION","order":4,"flow":"CORRECTION","isSubProcess":false,"label":{"eng":"Biometric correction","ara":"التصحيح البيومتري","fra":"Correction biométrique"},"screens":[{"order":1,"name":"consentdet","label":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"caption":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"fields":[{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"ara":"الاسم الكامل الكامل الكامل","fra":"J'ai lu et j'accepte les termes et conditions pour partager mes PII","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"ara":"لغة الإخطار","fra":"Langue de notification","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":2,"name":"BiometricDetails","label":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"caption":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"القياسات الحيوية الفردية","fra":"Applicant Biometrics","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"proofOfException","inputRequired":false,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"ara":"إثبات الاستثناء","fra":"Exception Proof","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":true,"active":false}],"caption":{"eng":"Biometric correction","ara":"التصحيح البيومتري","fra":"Correction biométrique"},"icon":"UINUpdate.png","isActive":true,"autoSelectedGroups":null} </t>
   </si>
-  <si>
-    <t>{"id":"NEW","order":1,"flow":"NEW","isSubProcess":false,"label":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"screens":[{"order":1,"name":"consentdet","label":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"caption":{"ara":"موافقة","fra":"Consentement","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"ara":"الاسم الكامل الكامل الكامل","fra":"J'ai lu et j'accepte les termes et conditions pour partager mes PII","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"ara":"لغة الإخطار","fra":"Langue de notification","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"caption":{"ara":"التفاصيل الديموغرافية","fra":"Détails démographiques","eng":"Demographic Details"},"fields":[{"id":"fullName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Full Name","label":{"ara":"الاسم الكامل","fra":"Nom complet","eng":"Full Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"name"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"ara":"الاسم الكامل","fra":"DOB","eng":"DOB"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"ara":"جنس","fra":"Le genre","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"ara":"الاسم الكامل","fra":"line1","eng":"line1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"ara":"الاسم الكامل","fra":"line2","eng":"line2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"addressLine3","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine3","label":{"ara":"الاسم الكامل","fra":"line3","eng":"line3"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine3"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"ara":"الاسم الكامل","fra":"Reside Status","eng":"Residence Status"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"referenceIdentityNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"referenceIdentityNumber","label":{"ara":"الاسم الكامل","fra":"Reference Identity Number","eng":"Reference Identity Number"},"controlType":"textbox","fieldType":"default","format":"kyc","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ReferenceIdentityNumber","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"none"},{"id":"region","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"region","label":{"ara":"الاسم الكامل","fra":"Region","eng":"Region"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Region"},{"id":"province","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"province","label":{"ara":"الاسم الكامل","fra":"Province","eng":"Province"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Province"},{"id":"city","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"city","label":{"ara":"الاسم الكامل","fra":"City","eng":"City"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"City"},{"id":"zone","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"zone","label":{"ara":"الاسم الكامل","fra":"Zone","eng":"Zone"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":null,"group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Zone"},{"id":"postalCode","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"postalCode","label":{"ara":"الاسم الكامل","fra":"Postal","eng":"Postal"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[(?i)A-Z0-9]{5}$|^NA$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Postal Code"},{"id":"phone","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"phone","label":{"ara":"الاسم الكامل","fra":"Phone","eng":"Phone"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[+]*([0-9]{1})([0-9]{9})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Phone"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"ara":"الاسم الكامل","fra":"Email","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"ara":"اسم المُعرّف","fra":"nom del'introducteur","eng":"Introducer Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"ara":"مقدم RID","fra":"Introducteur RID","eng":"Introducer RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"ara":"مقدم في","fra":"Introducteur UIN","eng":"Introducer UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"}],"layoutTemplate":null,"preRegFetchRequired":true,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","fra":"Des documents","eng":"Document Upload"},"caption":{"ara":"وثائق","fra":"Des documents","eng":"Documents"},"fields":[{"id":"proofOfAddress","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfAddress","label":{"ara":"إثبات العنوان","fra":"Address Proof","eng":"Address Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POA"},{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"ara":"إثبات الهوية","fra":"Identity Proof","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"ara":"إثبات العلاقة","fra":"Relationship Proof","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"ara":"دليل DOB","fra":"DOB Proof","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"ara":"إثبات الاستثناء","fra":"Exception Proof","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"caption":{"ara":"التفاصيل البيومترية","fra":"Détails biométriques","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"القياسات الحيوية الفردية","fra":"Applicant Biometrics","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"bioAttributes":["face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"ara":"مقدم القياسات الحيوية","fra":"Introducteur Biométrie","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["face"]}],"required":false,"bioAttributes":["face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false}],"caption":{"eng":"New Registration","ara":"تسجيل جديد","fra":"Nouvelle inscription"},"icon":"NewReg.png","isActive":true,"autoSelectedGroups":null}</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -217,16 +217,353 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -249,40 +586,326 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -487,31 +1110,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="8.5703125" customWidth="1"/>
     <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.2890625" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="45.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.4296875" customWidth="1"/>
+    <col min="7" max="7" width="45.859375" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="14.140625" customWidth="1"/>
     <col min="11" max="11" width="10.140625" customWidth="1"/>
     <col min="12" max="15" width="8.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" customWidth="1"/>
+    <col min="16" max="16" width="12.859375" customWidth="1"/>
     <col min="17" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="13.5" customHeight="1">
+    <row r="1" ht="13.5" customHeight="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +1190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="13.5" customHeight="1">
+    <row r="2" ht="13.5" customHeight="1" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -621,7 +1244,7 @@
       </c>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="30.75" customHeight="1">
+    <row r="3" ht="30.75" customHeight="1" spans="1:18">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -675,7 +1298,7 @@
       </c>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="29.25" customHeight="1">
+    <row r="4" ht="29.25" customHeight="1" spans="1:26">
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
@@ -695,7 +1318,7 @@
         <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2">
         <v>1001</v>
@@ -737,9 +1360,9 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
     </row>
-    <row r="5" spans="1:26" ht="13.5" customHeight="1">
+    <row r="5" ht="13.5" customHeight="1" spans="1:26">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2">
         <v>0.1</v>
@@ -748,16 +1371,16 @@
         <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2">
         <v>1001</v>
@@ -799,9 +1422,9 @@
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
     </row>
-    <row r="6" spans="1:26" ht="13.5" customHeight="1">
+    <row r="6" ht="13.5" customHeight="1" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2">
         <v>0.1</v>
@@ -810,16 +1433,16 @@
         <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2">
         <v>1001</v>
@@ -861,9 +1484,9 @@
       <c r="Y6" s="6"/>
       <c r="Z6" s="6"/>
     </row>
-    <row r="7" spans="1:26" ht="13.5" customHeight="1">
+    <row r="7" ht="13.5" customHeight="1" spans="1:26">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2">
         <v>0.1</v>
@@ -872,16 +1495,16 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2">
         <v>1001</v>
@@ -923,7 +1546,7 @@
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
     </row>
-    <row r="8" spans="1:26" ht="13.5" customHeight="1">
+    <row r="8" ht="13.5" customHeight="1" spans="1:26">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -951,7 +1574,7 @@
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
     </row>
-    <row r="9" spans="1:26" ht="13.5" customHeight="1">
+    <row r="9" ht="13.5" customHeight="1" spans="1:26">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -979,7 +1602,7 @@
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
     </row>
-    <row r="10" spans="1:26" ht="13.5" customHeight="1">
+    <row r="10" ht="13.5" customHeight="1" spans="1:18">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -999,7 +1622,7 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:26" ht="13.5" customHeight="1">
+    <row r="11" ht="13.5" customHeight="1" spans="1:18">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1019,7 +1642,7 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:26" ht="13.5" customHeight="1">
+    <row r="12" ht="13.5" customHeight="1" spans="1:18">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1039,7 +1662,7 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:26" ht="13.5" customHeight="1">
+    <row r="13" ht="13.5" customHeight="1" spans="1:18">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1059,7 +1682,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:26" ht="13.5" customHeight="1">
+    <row r="14" ht="13.5" customHeight="1" spans="1:18">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1079,7 +1702,7 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:26" ht="13.5" customHeight="1">
+    <row r="15" ht="13.5" customHeight="1" spans="1:18">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1099,7 +1722,7 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:26" ht="13.5" customHeight="1">
+    <row r="16" ht="13.5" customHeight="1" spans="1:18">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1119,7 +1742,7 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18" ht="13.5" customHeight="1">
+    <row r="17" ht="13.5" customHeight="1" spans="1:18">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1139,7 +1762,7 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18" ht="13.5" customHeight="1">
+    <row r="18" ht="13.5" customHeight="1" spans="1:18">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1159,7 +1782,7 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18" ht="13.5" customHeight="1">
+    <row r="19" ht="13.5" customHeight="1" spans="1:18">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1179,7 +1802,7 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18" ht="13.5" customHeight="1">
+    <row r="20" ht="13.5" customHeight="1" spans="1:18">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1199,7 +1822,7 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18" ht="13.5" customHeight="1">
+    <row r="21" ht="13.5" customHeight="1" spans="1:18">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1219,7 +1842,7 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18" ht="13.5" customHeight="1">
+    <row r="22" ht="13.5" customHeight="1" spans="1:18">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1239,7 +1862,7 @@
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="23" spans="1:18" ht="13.5" customHeight="1">
+    <row r="23" ht="13.5" customHeight="1" spans="1:18">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1259,7 +1882,7 @@
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
     </row>
-    <row r="24" spans="1:18" ht="13.5" customHeight="1">
+    <row r="24" ht="13.5" customHeight="1" spans="1:18">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1279,7 +1902,7 @@
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
     </row>
-    <row r="25" spans="1:18" ht="13.5" customHeight="1">
+    <row r="25" ht="13.5" customHeight="1" spans="1:18">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1299,7 +1922,7 @@
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
     </row>
-    <row r="26" spans="1:18" ht="13.5" customHeight="1">
+    <row r="26" ht="13.5" customHeight="1" spans="1:18">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1319,7 +1942,7 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
     </row>
-    <row r="27" spans="1:18" ht="13.5" customHeight="1">
+    <row r="27" ht="13.5" customHeight="1" spans="1:18">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1339,7 +1962,7 @@
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
     </row>
-    <row r="28" spans="1:18" ht="13.5" customHeight="1">
+    <row r="28" ht="13.5" customHeight="1" spans="1:18">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1359,7 +1982,7 @@
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
     </row>
-    <row r="29" spans="1:18" ht="13.5" customHeight="1">
+    <row r="29" ht="13.5" customHeight="1" spans="1:18">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1379,7 +2002,7 @@
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
     </row>
-    <row r="30" spans="1:18" ht="13.5" customHeight="1">
+    <row r="30" ht="13.5" customHeight="1" spans="1:18">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1399,7 +2022,7 @@
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
     </row>
-    <row r="31" spans="1:18" ht="13.5" customHeight="1">
+    <row r="31" ht="13.5" customHeight="1" spans="1:18">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1419,7 +2042,7 @@
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
     </row>
-    <row r="32" spans="1:18" ht="13.5" customHeight="1">
+    <row r="32" ht="13.5" customHeight="1" spans="1:18">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1439,7 +2062,7 @@
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
     </row>
-    <row r="33" spans="1:18" ht="13.5" customHeight="1">
+    <row r="33" ht="13.5" customHeight="1" spans="1:18">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1459,7 +2082,7 @@
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
     </row>
-    <row r="34" spans="1:18" ht="13.5" customHeight="1">
+    <row r="34" ht="13.5" customHeight="1" spans="1:18">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1479,7 +2102,7 @@
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
     </row>
-    <row r="35" spans="1:18" ht="13.5" customHeight="1">
+    <row r="35" ht="13.5" customHeight="1" spans="1:18">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1499,7 +2122,7 @@
       <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
     </row>
-    <row r="36" spans="1:18" ht="13.5" customHeight="1">
+    <row r="36" ht="13.5" customHeight="1" spans="1:18">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1519,7 +2142,7 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" spans="1:18" ht="13.5" customHeight="1">
+    <row r="37" ht="13.5" customHeight="1" spans="1:18">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1539,7 +2162,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" spans="1:18" ht="13.5" customHeight="1">
+    <row r="38" ht="13.5" customHeight="1" spans="1:18">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1559,7 +2182,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:18" ht="13.5" customHeight="1">
+    <row r="39" ht="13.5" customHeight="1" spans="1:18">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1579,7 +2202,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" spans="1:18" ht="13.5" customHeight="1">
+    <row r="40" ht="13.5" customHeight="1" spans="1:18">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1599,7 +2222,7 @@
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
     </row>
-    <row r="41" spans="1:18" ht="13.5" customHeight="1">
+    <row r="41" ht="13.5" customHeight="1" spans="1:18">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1619,7 +2242,7 @@
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
     </row>
-    <row r="42" spans="1:18" ht="13.5" customHeight="1">
+    <row r="42" ht="13.5" customHeight="1" spans="1:18">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1639,7 +2262,7 @@
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
     </row>
-    <row r="43" spans="1:18" ht="13.5" customHeight="1">
+    <row r="43" ht="13.5" customHeight="1" spans="1:18">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1659,7 +2282,7 @@
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
     </row>
-    <row r="44" spans="1:18" ht="13.5" customHeight="1">
+    <row r="44" ht="13.5" customHeight="1" spans="1:18">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1679,7 +2302,7 @@
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
     </row>
-    <row r="45" spans="1:18" ht="13.5" customHeight="1">
+    <row r="45" ht="13.5" customHeight="1" spans="1:18">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1699,7 +2322,7 @@
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
     </row>
-    <row r="46" spans="1:18" ht="13.5" customHeight="1">
+    <row r="46" ht="13.5" customHeight="1" spans="1:18">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1719,7 +2342,7 @@
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
     </row>
-    <row r="47" spans="1:18" ht="13.5" customHeight="1">
+    <row r="47" ht="13.5" customHeight="1" spans="1:18">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1739,7 +2362,7 @@
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
     </row>
-    <row r="48" spans="1:18" ht="13.5" customHeight="1">
+    <row r="48" ht="13.5" customHeight="1" spans="1:18">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1759,7 +2382,7 @@
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
     </row>
-    <row r="49" spans="1:18" ht="13.5" customHeight="1">
+    <row r="49" ht="13.5" customHeight="1" spans="1:18">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1779,7 +2402,7 @@
       <c r="Q49" s="4"/>
       <c r="R49" s="4"/>
     </row>
-    <row r="50" spans="1:18" ht="13.5" customHeight="1">
+    <row r="50" ht="13.5" customHeight="1" spans="1:18">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -1799,7 +2422,7 @@
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
     </row>
-    <row r="51" spans="1:18" ht="13.5" customHeight="1">
+    <row r="51" ht="13.5" customHeight="1" spans="1:18">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -1819,7 +2442,7 @@
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
     </row>
-    <row r="52" spans="1:18" ht="13.5" customHeight="1">
+    <row r="52" ht="13.5" customHeight="1" spans="1:18">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -1839,7 +2462,7 @@
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
     </row>
-    <row r="53" spans="1:18" ht="13.5" customHeight="1">
+    <row r="53" ht="13.5" customHeight="1" spans="1:18">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -1859,7 +2482,7 @@
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
     </row>
-    <row r="54" spans="1:18" ht="13.5" customHeight="1">
+    <row r="54" ht="13.5" customHeight="1" spans="1:18">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -1879,7 +2502,7 @@
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
     </row>
-    <row r="55" spans="1:18" ht="13.5" customHeight="1">
+    <row r="55" ht="13.5" customHeight="1" spans="1:18">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1899,7 +2522,7 @@
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
     </row>
-    <row r="56" spans="1:18" ht="13.5" customHeight="1">
+    <row r="56" ht="13.5" customHeight="1" spans="1:18">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -1919,7 +2542,7 @@
       <c r="Q56" s="4"/>
       <c r="R56" s="4"/>
     </row>
-    <row r="57" spans="1:18" ht="13.5" customHeight="1">
+    <row r="57" ht="13.5" customHeight="1" spans="1:18">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1939,7 +2562,7 @@
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
     </row>
-    <row r="58" spans="1:18" ht="13.5" customHeight="1">
+    <row r="58" ht="13.5" customHeight="1" spans="1:18">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -1959,7 +2582,7 @@
       <c r="Q58" s="4"/>
       <c r="R58" s="4"/>
     </row>
-    <row r="59" spans="1:18" ht="13.5" customHeight="1">
+    <row r="59" ht="13.5" customHeight="1" spans="1:18">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -1979,7 +2602,7 @@
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
     </row>
-    <row r="60" spans="1:18" ht="13.5" customHeight="1">
+    <row r="60" ht="13.5" customHeight="1" spans="1:18">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -1999,7 +2622,7 @@
       <c r="Q60" s="4"/>
       <c r="R60" s="4"/>
     </row>
-    <row r="61" spans="1:18" ht="13.5" customHeight="1">
+    <row r="61" ht="13.5" customHeight="1" spans="1:18">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2019,7 +2642,7 @@
       <c r="Q61" s="4"/>
       <c r="R61" s="4"/>
     </row>
-    <row r="62" spans="1:18" ht="13.5" customHeight="1">
+    <row r="62" ht="13.5" customHeight="1" spans="1:18">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2039,7 +2662,7 @@
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
     </row>
-    <row r="63" spans="1:18" ht="13.5" customHeight="1">
+    <row r="63" ht="13.5" customHeight="1" spans="1:18">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2059,7 +2682,7 @@
       <c r="Q63" s="4"/>
       <c r="R63" s="4"/>
     </row>
-    <row r="64" spans="1:18" ht="13.5" customHeight="1">
+    <row r="64" ht="13.5" customHeight="1" spans="1:18">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2079,7 +2702,7 @@
       <c r="Q64" s="4"/>
       <c r="R64" s="4"/>
     </row>
-    <row r="65" spans="1:18" ht="13.5" customHeight="1">
+    <row r="65" ht="13.5" customHeight="1" spans="1:18">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2099,7 +2722,7 @@
       <c r="Q65" s="4"/>
       <c r="R65" s="4"/>
     </row>
-    <row r="66" spans="1:18" ht="13.5" customHeight="1">
+    <row r="66" ht="13.5" customHeight="1" spans="1:18">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2119,7 +2742,7 @@
       <c r="Q66" s="4"/>
       <c r="R66" s="4"/>
     </row>
-    <row r="67" spans="1:18" ht="13.5" customHeight="1">
+    <row r="67" ht="13.5" customHeight="1" spans="1:18">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2139,7 +2762,7 @@
       <c r="Q67" s="4"/>
       <c r="R67" s="4"/>
     </row>
-    <row r="68" spans="1:18" ht="13.5" customHeight="1">
+    <row r="68" ht="13.5" customHeight="1" spans="1:18">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2159,7 +2782,7 @@
       <c r="Q68" s="4"/>
       <c r="R68" s="4"/>
     </row>
-    <row r="69" spans="1:18" ht="13.5" customHeight="1">
+    <row r="69" ht="13.5" customHeight="1" spans="1:18">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2179,7 +2802,7 @@
       <c r="Q69" s="4"/>
       <c r="R69" s="4"/>
     </row>
-    <row r="70" spans="1:18" ht="13.5" customHeight="1">
+    <row r="70" ht="13.5" customHeight="1" spans="1:18">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2199,7 +2822,7 @@
       <c r="Q70" s="4"/>
       <c r="R70" s="4"/>
     </row>
-    <row r="71" spans="1:18" ht="13.5" customHeight="1">
+    <row r="71" ht="13.5" customHeight="1" spans="1:18">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2219,7 +2842,7 @@
       <c r="Q71" s="4"/>
       <c r="R71" s="4"/>
     </row>
-    <row r="72" spans="1:18" ht="13.5" customHeight="1">
+    <row r="72" ht="13.5" customHeight="1" spans="1:18">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2239,7 +2862,7 @@
       <c r="Q72" s="4"/>
       <c r="R72" s="4"/>
     </row>
-    <row r="73" spans="1:18" ht="13.5" customHeight="1">
+    <row r="73" ht="13.5" customHeight="1" spans="1:18">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2259,7 +2882,7 @@
       <c r="Q73" s="4"/>
       <c r="R73" s="4"/>
     </row>
-    <row r="74" spans="1:18" ht="13.5" customHeight="1">
+    <row r="74" ht="13.5" customHeight="1" spans="1:18">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2279,7 +2902,7 @@
       <c r="Q74" s="4"/>
       <c r="R74" s="4"/>
     </row>
-    <row r="75" spans="1:18" ht="13.5" customHeight="1">
+    <row r="75" ht="13.5" customHeight="1" spans="1:18">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2299,7 +2922,7 @@
       <c r="Q75" s="4"/>
       <c r="R75" s="4"/>
     </row>
-    <row r="76" spans="1:18" ht="13.5" customHeight="1">
+    <row r="76" ht="13.5" customHeight="1" spans="1:18">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2319,7 +2942,7 @@
       <c r="Q76" s="4"/>
       <c r="R76" s="4"/>
     </row>
-    <row r="77" spans="1:18" ht="13.5" customHeight="1">
+    <row r="77" ht="13.5" customHeight="1" spans="1:18">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2339,7 +2962,7 @@
       <c r="Q77" s="4"/>
       <c r="R77" s="4"/>
     </row>
-    <row r="78" spans="1:18" ht="13.5" customHeight="1">
+    <row r="78" ht="13.5" customHeight="1" spans="1:18">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2359,7 +2982,7 @@
       <c r="Q78" s="4"/>
       <c r="R78" s="4"/>
     </row>
-    <row r="79" spans="1:18" ht="13.5" customHeight="1">
+    <row r="79" ht="13.5" customHeight="1" spans="1:18">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2379,7 +3002,7 @@
       <c r="Q79" s="4"/>
       <c r="R79" s="4"/>
     </row>
-    <row r="80" spans="1:18" ht="13.5" customHeight="1">
+    <row r="80" ht="13.5" customHeight="1" spans="1:18">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2399,7 +3022,7 @@
       <c r="Q80" s="4"/>
       <c r="R80" s="4"/>
     </row>
-    <row r="81" spans="1:18" ht="13.5" customHeight="1">
+    <row r="81" ht="13.5" customHeight="1" spans="1:18">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2419,7 +3042,7 @@
       <c r="Q81" s="4"/>
       <c r="R81" s="4"/>
     </row>
-    <row r="82" spans="1:18" ht="13.5" customHeight="1">
+    <row r="82" ht="13.5" customHeight="1" spans="1:18">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2439,7 +3062,7 @@
       <c r="Q82" s="4"/>
       <c r="R82" s="4"/>
     </row>
-    <row r="83" spans="1:18" ht="13.5" customHeight="1">
+    <row r="83" ht="13.5" customHeight="1" spans="1:18">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2459,7 +3082,7 @@
       <c r="Q83" s="4"/>
       <c r="R83" s="4"/>
     </row>
-    <row r="84" spans="1:18" ht="13.5" customHeight="1">
+    <row r="84" ht="13.5" customHeight="1" spans="1:18">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2479,7 +3102,7 @@
       <c r="Q84" s="4"/>
       <c r="R84" s="4"/>
     </row>
-    <row r="85" spans="1:18" ht="13.5" customHeight="1">
+    <row r="85" ht="13.5" customHeight="1" spans="1:18">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2499,7 +3122,7 @@
       <c r="Q85" s="4"/>
       <c r="R85" s="4"/>
     </row>
-    <row r="86" spans="1:18" ht="13.5" customHeight="1">
+    <row r="86" ht="13.5" customHeight="1" spans="1:18">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2519,7 +3142,7 @@
       <c r="Q86" s="4"/>
       <c r="R86" s="4"/>
     </row>
-    <row r="87" spans="1:18" ht="13.5" customHeight="1">
+    <row r="87" ht="13.5" customHeight="1" spans="1:18">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2539,7 +3162,7 @@
       <c r="Q87" s="4"/>
       <c r="R87" s="4"/>
     </row>
-    <row r="88" spans="1:18" ht="13.5" customHeight="1">
+    <row r="88" ht="13.5" customHeight="1" spans="1:18">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2559,7 +3182,7 @@
       <c r="Q88" s="4"/>
       <c r="R88" s="4"/>
     </row>
-    <row r="89" spans="1:18" ht="13.5" customHeight="1">
+    <row r="89" ht="13.5" customHeight="1" spans="1:18">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2579,7 +3202,7 @@
       <c r="Q89" s="4"/>
       <c r="R89" s="4"/>
     </row>
-    <row r="90" spans="1:18" ht="13.5" customHeight="1">
+    <row r="90" ht="13.5" customHeight="1" spans="1:18">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2599,7 +3222,7 @@
       <c r="Q90" s="4"/>
       <c r="R90" s="4"/>
     </row>
-    <row r="91" spans="1:18" ht="13.5" customHeight="1">
+    <row r="91" ht="13.5" customHeight="1" spans="1:18">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2619,7 +3242,7 @@
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
     </row>
-    <row r="92" spans="1:18" ht="13.5" customHeight="1">
+    <row r="92" ht="13.5" customHeight="1" spans="1:18">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2639,7 +3262,7 @@
       <c r="Q92" s="4"/>
       <c r="R92" s="4"/>
     </row>
-    <row r="93" spans="1:18" ht="13.5" customHeight="1">
+    <row r="93" ht="13.5" customHeight="1" spans="1:18">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -2659,7 +3282,7 @@
       <c r="Q93" s="4"/>
       <c r="R93" s="4"/>
     </row>
-    <row r="94" spans="1:18" ht="13.5" customHeight="1">
+    <row r="94" ht="13.5" customHeight="1" spans="1:18">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -2679,7 +3302,7 @@
       <c r="Q94" s="4"/>
       <c r="R94" s="4"/>
     </row>
-    <row r="95" spans="1:18" ht="13.5" customHeight="1">
+    <row r="95" ht="13.5" customHeight="1" spans="1:18">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -2699,7 +3322,7 @@
       <c r="Q95" s="4"/>
       <c r="R95" s="4"/>
     </row>
-    <row r="96" spans="1:18" ht="13.5" customHeight="1">
+    <row r="96" ht="13.5" customHeight="1" spans="1:18">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -2719,7 +3342,7 @@
       <c r="Q96" s="4"/>
       <c r="R96" s="4"/>
     </row>
-    <row r="97" spans="1:18" ht="13.5" customHeight="1">
+    <row r="97" ht="13.5" customHeight="1" spans="1:18">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -2739,7 +3362,7 @@
       <c r="Q97" s="4"/>
       <c r="R97" s="4"/>
     </row>
-    <row r="98" spans="1:18" ht="13.5" customHeight="1">
+    <row r="98" ht="13.5" customHeight="1" spans="1:18">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -2759,7 +3382,7 @@
       <c r="Q98" s="4"/>
       <c r="R98" s="4"/>
     </row>
-    <row r="99" spans="1:18" ht="13.5" customHeight="1">
+    <row r="99" ht="13.5" customHeight="1" spans="1:18">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -2779,7 +3402,7 @@
       <c r="Q99" s="4"/>
       <c r="R99" s="4"/>
     </row>
-    <row r="100" spans="1:18" ht="13.5" customHeight="1">
+    <row r="100" ht="13.5" customHeight="1" spans="1:18">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -2799,7 +3422,7 @@
       <c r="Q100" s="4"/>
       <c r="R100" s="4"/>
     </row>
-    <row r="101" spans="1:18" ht="13.5" customHeight="1">
+    <row r="101" ht="13.5" customHeight="1" spans="1:18">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -2819,7 +3442,7 @@
       <c r="Q101" s="4"/>
       <c r="R101" s="4"/>
     </row>
-    <row r="102" spans="1:18" ht="13.5" customHeight="1">
+    <row r="102" ht="13.5" customHeight="1" spans="1:18">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -2839,7 +3462,7 @@
       <c r="Q102" s="4"/>
       <c r="R102" s="4"/>
     </row>
-    <row r="103" spans="1:18" ht="13.5" customHeight="1">
+    <row r="103" ht="13.5" customHeight="1" spans="1:18">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -2859,7 +3482,7 @@
       <c r="Q103" s="4"/>
       <c r="R103" s="4"/>
     </row>
-    <row r="104" spans="1:18" ht="13.5" customHeight="1">
+    <row r="104" ht="13.5" customHeight="1" spans="1:18">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -2879,7 +3502,7 @@
       <c r="Q104" s="4"/>
       <c r="R104" s="4"/>
     </row>
-    <row r="105" spans="1:18" ht="13.5" customHeight="1">
+    <row r="105" ht="13.5" customHeight="1" spans="1:18">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -2899,7 +3522,7 @@
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
     </row>
-    <row r="106" spans="1:18" ht="13.5" customHeight="1">
+    <row r="106" ht="13.5" customHeight="1" spans="1:18">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -2919,7 +3542,7 @@
       <c r="Q106" s="4"/>
       <c r="R106" s="4"/>
     </row>
-    <row r="107" spans="1:18" ht="13.5" customHeight="1">
+    <row r="107" ht="13.5" customHeight="1" spans="1:18">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -2939,7 +3562,7 @@
       <c r="Q107" s="4"/>
       <c r="R107" s="4"/>
     </row>
-    <row r="108" spans="1:18" ht="13.5" customHeight="1">
+    <row r="108" ht="13.5" customHeight="1" spans="1:18">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -2959,7 +3582,7 @@
       <c r="Q108" s="4"/>
       <c r="R108" s="4"/>
     </row>
-    <row r="109" spans="1:18" ht="13.5" customHeight="1">
+    <row r="109" ht="13.5" customHeight="1" spans="1:18">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -2979,7 +3602,7 @@
       <c r="Q109" s="4"/>
       <c r="R109" s="4"/>
     </row>
-    <row r="110" spans="1:18" ht="13.5" customHeight="1">
+    <row r="110" ht="13.5" customHeight="1" spans="1:18">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -2999,7 +3622,7 @@
       <c r="Q110" s="4"/>
       <c r="R110" s="4"/>
     </row>
-    <row r="111" spans="1:18" ht="13.5" customHeight="1">
+    <row r="111" ht="13.5" customHeight="1" spans="1:18">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3019,7 +3642,7 @@
       <c r="Q111" s="4"/>
       <c r="R111" s="4"/>
     </row>
-    <row r="112" spans="1:18" ht="13.5" customHeight="1">
+    <row r="112" ht="13.5" customHeight="1" spans="1:18">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3039,7 +3662,7 @@
       <c r="Q112" s="4"/>
       <c r="R112" s="4"/>
     </row>
-    <row r="113" spans="1:18" ht="13.5" customHeight="1">
+    <row r="113" ht="13.5" customHeight="1" spans="1:18">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3059,7 +3682,7 @@
       <c r="Q113" s="4"/>
       <c r="R113" s="4"/>
     </row>
-    <row r="114" spans="1:18" ht="13.5" customHeight="1">
+    <row r="114" ht="13.5" customHeight="1" spans="1:18">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3079,7 +3702,7 @@
       <c r="Q114" s="4"/>
       <c r="R114" s="4"/>
     </row>
-    <row r="115" spans="1:18" ht="13.5" customHeight="1">
+    <row r="115" ht="13.5" customHeight="1" spans="1:18">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3099,7 +3722,7 @@
       <c r="Q115" s="4"/>
       <c r="R115" s="4"/>
     </row>
-    <row r="116" spans="1:18" ht="13.5" customHeight="1">
+    <row r="116" ht="13.5" customHeight="1" spans="1:18">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3119,7 +3742,7 @@
       <c r="Q116" s="4"/>
       <c r="R116" s="4"/>
     </row>
-    <row r="117" spans="1:18" ht="13.5" customHeight="1">
+    <row r="117" ht="13.5" customHeight="1" spans="1:18">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3139,7 +3762,7 @@
       <c r="Q117" s="4"/>
       <c r="R117" s="4"/>
     </row>
-    <row r="118" spans="1:18" ht="13.5" customHeight="1">
+    <row r="118" ht="13.5" customHeight="1" spans="1:18">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3159,7 +3782,7 @@
       <c r="Q118" s="4"/>
       <c r="R118" s="4"/>
     </row>
-    <row r="119" spans="1:18" ht="13.5" customHeight="1">
+    <row r="119" ht="13.5" customHeight="1" spans="1:18">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3179,7 +3802,7 @@
       <c r="Q119" s="4"/>
       <c r="R119" s="4"/>
     </row>
-    <row r="120" spans="1:18" ht="13.5" customHeight="1">
+    <row r="120" ht="13.5" customHeight="1" spans="1:18">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3199,7 +3822,7 @@
       <c r="Q120" s="4"/>
       <c r="R120" s="4"/>
     </row>
-    <row r="121" spans="1:18" ht="13.5" customHeight="1">
+    <row r="121" ht="13.5" customHeight="1" spans="1:18">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3219,7 +3842,7 @@
       <c r="Q121" s="4"/>
       <c r="R121" s="4"/>
     </row>
-    <row r="122" spans="1:18" ht="13.5" customHeight="1">
+    <row r="122" ht="13.5" customHeight="1" spans="1:18">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3239,7 +3862,7 @@
       <c r="Q122" s="4"/>
       <c r="R122" s="4"/>
     </row>
-    <row r="123" spans="1:18" ht="13.5" customHeight="1">
+    <row r="123" ht="13.5" customHeight="1" spans="1:18">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3259,7 +3882,7 @@
       <c r="Q123" s="4"/>
       <c r="R123" s="4"/>
     </row>
-    <row r="124" spans="1:18" ht="13.5" customHeight="1">
+    <row r="124" ht="13.5" customHeight="1" spans="1:18">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3279,7 +3902,7 @@
       <c r="Q124" s="4"/>
       <c r="R124" s="4"/>
     </row>
-    <row r="125" spans="1:18" ht="13.5" customHeight="1">
+    <row r="125" ht="13.5" customHeight="1" spans="1:18">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3299,7 +3922,7 @@
       <c r="Q125" s="4"/>
       <c r="R125" s="4"/>
     </row>
-    <row r="126" spans="1:18" ht="13.5" customHeight="1">
+    <row r="126" ht="13.5" customHeight="1" spans="1:18">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3319,7 +3942,7 @@
       <c r="Q126" s="4"/>
       <c r="R126" s="4"/>
     </row>
-    <row r="127" spans="1:18" ht="13.5" customHeight="1">
+    <row r="127" ht="13.5" customHeight="1" spans="1:18">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3339,7 +3962,7 @@
       <c r="Q127" s="4"/>
       <c r="R127" s="4"/>
     </row>
-    <row r="128" spans="1:18" ht="13.5" customHeight="1">
+    <row r="128" ht="13.5" customHeight="1" spans="1:18">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3359,7 +3982,7 @@
       <c r="Q128" s="4"/>
       <c r="R128" s="4"/>
     </row>
-    <row r="129" spans="1:18" ht="13.5" customHeight="1">
+    <row r="129" ht="13.5" customHeight="1" spans="1:18">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -3379,7 +4002,7 @@
       <c r="Q129" s="4"/>
       <c r="R129" s="4"/>
     </row>
-    <row r="130" spans="1:18" ht="13.5" customHeight="1">
+    <row r="130" ht="13.5" customHeight="1" spans="1:18">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -3399,7 +4022,7 @@
       <c r="Q130" s="4"/>
       <c r="R130" s="4"/>
     </row>
-    <row r="131" spans="1:18" ht="13.5" customHeight="1">
+    <row r="131" ht="13.5" customHeight="1" spans="1:18">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -3419,7 +4042,7 @@
       <c r="Q131" s="4"/>
       <c r="R131" s="4"/>
     </row>
-    <row r="132" spans="1:18" ht="13.5" customHeight="1">
+    <row r="132" ht="13.5" customHeight="1" spans="1:18">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -3439,7 +4062,7 @@
       <c r="Q132" s="4"/>
       <c r="R132" s="4"/>
     </row>
-    <row r="133" spans="1:18" ht="13.5" customHeight="1">
+    <row r="133" ht="13.5" customHeight="1" spans="1:18">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -3459,7 +4082,7 @@
       <c r="Q133" s="4"/>
       <c r="R133" s="4"/>
     </row>
-    <row r="134" spans="1:18" ht="13.5" customHeight="1">
+    <row r="134" ht="13.5" customHeight="1" spans="1:18">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -3479,7 +4102,7 @@
       <c r="Q134" s="4"/>
       <c r="R134" s="4"/>
     </row>
-    <row r="135" spans="1:18" ht="13.5" customHeight="1">
+    <row r="135" ht="13.5" customHeight="1" spans="1:18">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -3499,7 +4122,7 @@
       <c r="Q135" s="4"/>
       <c r="R135" s="4"/>
     </row>
-    <row r="136" spans="1:18" ht="13.5" customHeight="1">
+    <row r="136" ht="13.5" customHeight="1" spans="1:18">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -3519,7 +4142,7 @@
       <c r="Q136" s="4"/>
       <c r="R136" s="4"/>
     </row>
-    <row r="137" spans="1:18" ht="13.5" customHeight="1">
+    <row r="137" ht="13.5" customHeight="1" spans="1:18">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -3539,7 +4162,7 @@
       <c r="Q137" s="4"/>
       <c r="R137" s="4"/>
     </row>
-    <row r="138" spans="1:18" ht="13.5" customHeight="1">
+    <row r="138" ht="13.5" customHeight="1" spans="1:18">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -3559,7 +4182,7 @@
       <c r="Q138" s="4"/>
       <c r="R138" s="4"/>
     </row>
-    <row r="139" spans="1:18" ht="13.5" customHeight="1">
+    <row r="139" ht="13.5" customHeight="1" spans="1:18">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -3579,7 +4202,7 @@
       <c r="Q139" s="4"/>
       <c r="R139" s="4"/>
     </row>
-    <row r="140" spans="1:18" ht="13.5" customHeight="1">
+    <row r="140" ht="13.5" customHeight="1" spans="1:18">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -3599,7 +4222,7 @@
       <c r="Q140" s="4"/>
       <c r="R140" s="4"/>
     </row>
-    <row r="141" spans="1:18" ht="13.5" customHeight="1">
+    <row r="141" ht="13.5" customHeight="1" spans="1:18">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -3619,7 +4242,7 @@
       <c r="Q141" s="4"/>
       <c r="R141" s="4"/>
     </row>
-    <row r="142" spans="1:18" ht="13.5" customHeight="1">
+    <row r="142" ht="13.5" customHeight="1" spans="1:18">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -3639,7 +4262,7 @@
       <c r="Q142" s="4"/>
       <c r="R142" s="4"/>
     </row>
-    <row r="143" spans="1:18" ht="13.5" customHeight="1">
+    <row r="143" ht="13.5" customHeight="1" spans="1:18">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -3659,7 +4282,7 @@
       <c r="Q143" s="4"/>
       <c r="R143" s="4"/>
     </row>
-    <row r="144" spans="1:18" ht="13.5" customHeight="1">
+    <row r="144" ht="13.5" customHeight="1" spans="1:18">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -3679,7 +4302,7 @@
       <c r="Q144" s="4"/>
       <c r="R144" s="4"/>
     </row>
-    <row r="145" spans="1:18" ht="13.5" customHeight="1">
+    <row r="145" ht="13.5" customHeight="1" spans="1:18">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -3699,7 +4322,7 @@
       <c r="Q145" s="4"/>
       <c r="R145" s="4"/>
     </row>
-    <row r="146" spans="1:18" ht="13.5" customHeight="1">
+    <row r="146" ht="13.5" customHeight="1" spans="1:18">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -3719,7 +4342,7 @@
       <c r="Q146" s="4"/>
       <c r="R146" s="4"/>
     </row>
-    <row r="147" spans="1:18" ht="13.5" customHeight="1">
+    <row r="147" ht="13.5" customHeight="1" spans="1:18">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -3739,7 +4362,7 @@
       <c r="Q147" s="4"/>
       <c r="R147" s="4"/>
     </row>
-    <row r="148" spans="1:18" ht="13.5" customHeight="1">
+    <row r="148" ht="13.5" customHeight="1" spans="1:18">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -3759,7 +4382,7 @@
       <c r="Q148" s="4"/>
       <c r="R148" s="4"/>
     </row>
-    <row r="149" spans="1:18" ht="13.5" customHeight="1">
+    <row r="149" ht="13.5" customHeight="1" spans="1:18">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -3779,7 +4402,7 @@
       <c r="Q149" s="4"/>
       <c r="R149" s="4"/>
     </row>
-    <row r="150" spans="1:18" ht="13.5" customHeight="1">
+    <row r="150" ht="13.5" customHeight="1" spans="1:18">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -3799,7 +4422,7 @@
       <c r="Q150" s="4"/>
       <c r="R150" s="4"/>
     </row>
-    <row r="151" spans="1:18" ht="13.5" customHeight="1">
+    <row r="151" ht="13.5" customHeight="1" spans="1:18">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -3819,7 +4442,7 @@
       <c r="Q151" s="4"/>
       <c r="R151" s="4"/>
     </row>
-    <row r="152" spans="1:18" ht="13.5" customHeight="1">
+    <row r="152" ht="13.5" customHeight="1" spans="1:18">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -3839,7 +4462,7 @@
       <c r="Q152" s="4"/>
       <c r="R152" s="4"/>
     </row>
-    <row r="153" spans="1:18" ht="13.5" customHeight="1">
+    <row r="153" ht="13.5" customHeight="1" spans="1:18">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -3859,7 +4482,7 @@
       <c r="Q153" s="4"/>
       <c r="R153" s="4"/>
     </row>
-    <row r="154" spans="1:18" ht="13.5" customHeight="1">
+    <row r="154" ht="13.5" customHeight="1" spans="1:18">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -3879,7 +4502,7 @@
       <c r="Q154" s="4"/>
       <c r="R154" s="4"/>
     </row>
-    <row r="155" spans="1:18" ht="13.5" customHeight="1">
+    <row r="155" ht="13.5" customHeight="1" spans="1:18">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -3899,7 +4522,7 @@
       <c r="Q155" s="4"/>
       <c r="R155" s="4"/>
     </row>
-    <row r="156" spans="1:18" ht="13.5" customHeight="1">
+    <row r="156" ht="13.5" customHeight="1" spans="1:18">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -3919,7 +4542,7 @@
       <c r="Q156" s="4"/>
       <c r="R156" s="4"/>
     </row>
-    <row r="157" spans="1:18" ht="13.5" customHeight="1">
+    <row r="157" ht="13.5" customHeight="1" spans="1:18">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -3939,7 +4562,7 @@
       <c r="Q157" s="4"/>
       <c r="R157" s="4"/>
     </row>
-    <row r="158" spans="1:18" ht="13.5" customHeight="1">
+    <row r="158" ht="13.5" customHeight="1" spans="1:18">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -3959,7 +4582,7 @@
       <c r="Q158" s="4"/>
       <c r="R158" s="4"/>
     </row>
-    <row r="159" spans="1:18" ht="13.5" customHeight="1">
+    <row r="159" ht="13.5" customHeight="1" spans="1:18">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -3979,7 +4602,7 @@
       <c r="Q159" s="4"/>
       <c r="R159" s="4"/>
     </row>
-    <row r="160" spans="1:18" ht="13.5" customHeight="1">
+    <row r="160" ht="13.5" customHeight="1" spans="1:18">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -3999,7 +4622,7 @@
       <c r="Q160" s="4"/>
       <c r="R160" s="4"/>
     </row>
-    <row r="161" spans="1:18" ht="13.5" customHeight="1">
+    <row r="161" ht="13.5" customHeight="1" spans="1:18">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -4019,7 +4642,7 @@
       <c r="Q161" s="4"/>
       <c r="R161" s="4"/>
     </row>
-    <row r="162" spans="1:18" ht="13.5" customHeight="1">
+    <row r="162" ht="13.5" customHeight="1" spans="1:18">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -4039,7 +4662,7 @@
       <c r="Q162" s="4"/>
       <c r="R162" s="4"/>
     </row>
-    <row r="163" spans="1:18" ht="13.5" customHeight="1">
+    <row r="163" ht="13.5" customHeight="1" spans="1:18">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -4059,7 +4682,7 @@
       <c r="Q163" s="4"/>
       <c r="R163" s="4"/>
     </row>
-    <row r="164" spans="1:18" ht="13.5" customHeight="1">
+    <row r="164" ht="13.5" customHeight="1" spans="1:18">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -4079,7 +4702,7 @@
       <c r="Q164" s="4"/>
       <c r="R164" s="4"/>
     </row>
-    <row r="165" spans="1:18" ht="13.5" customHeight="1">
+    <row r="165" ht="13.5" customHeight="1" spans="1:18">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -4099,7 +4722,7 @@
       <c r="Q165" s="4"/>
       <c r="R165" s="4"/>
     </row>
-    <row r="166" spans="1:18" ht="13.5" customHeight="1">
+    <row r="166" ht="13.5" customHeight="1" spans="1:18">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -4119,7 +4742,7 @@
       <c r="Q166" s="4"/>
       <c r="R166" s="4"/>
     </row>
-    <row r="167" spans="1:18" ht="13.5" customHeight="1">
+    <row r="167" ht="13.5" customHeight="1" spans="1:18">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -4139,7 +4762,7 @@
       <c r="Q167" s="4"/>
       <c r="R167" s="4"/>
     </row>
-    <row r="168" spans="1:18" ht="13.5" customHeight="1">
+    <row r="168" ht="13.5" customHeight="1" spans="1:18">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -4159,7 +4782,7 @@
       <c r="Q168" s="4"/>
       <c r="R168" s="4"/>
     </row>
-    <row r="169" spans="1:18" ht="13.5" customHeight="1">
+    <row r="169" ht="13.5" customHeight="1" spans="1:18">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -4179,7 +4802,7 @@
       <c r="Q169" s="4"/>
       <c r="R169" s="4"/>
     </row>
-    <row r="170" spans="1:18" ht="13.5" customHeight="1">
+    <row r="170" ht="13.5" customHeight="1" spans="1:18">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -4199,7 +4822,7 @@
       <c r="Q170" s="4"/>
       <c r="R170" s="4"/>
     </row>
-    <row r="171" spans="1:18" ht="13.5" customHeight="1">
+    <row r="171" ht="13.5" customHeight="1" spans="1:18">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -4219,7 +4842,7 @@
       <c r="Q171" s="4"/>
       <c r="R171" s="4"/>
     </row>
-    <row r="172" spans="1:18" ht="13.5" customHeight="1">
+    <row r="172" ht="13.5" customHeight="1" spans="1:18">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -4239,7 +4862,7 @@
       <c r="Q172" s="4"/>
       <c r="R172" s="4"/>
     </row>
-    <row r="173" spans="1:18" ht="13.5" customHeight="1">
+    <row r="173" ht="13.5" customHeight="1" spans="1:18">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -4259,7 +4882,7 @@
       <c r="Q173" s="4"/>
       <c r="R173" s="4"/>
     </row>
-    <row r="174" spans="1:18" ht="13.5" customHeight="1">
+    <row r="174" ht="13.5" customHeight="1" spans="1:18">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -4279,7 +4902,7 @@
       <c r="Q174" s="4"/>
       <c r="R174" s="4"/>
     </row>
-    <row r="175" spans="1:18" ht="13.5" customHeight="1">
+    <row r="175" ht="13.5" customHeight="1" spans="1:18">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -4299,7 +4922,7 @@
       <c r="Q175" s="4"/>
       <c r="R175" s="4"/>
     </row>
-    <row r="176" spans="1:18" ht="13.5" customHeight="1">
+    <row r="176" ht="13.5" customHeight="1" spans="1:18">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -4319,7 +4942,7 @@
       <c r="Q176" s="4"/>
       <c r="R176" s="4"/>
     </row>
-    <row r="177" spans="1:18" ht="13.5" customHeight="1">
+    <row r="177" ht="13.5" customHeight="1" spans="1:18">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -4339,7 +4962,7 @@
       <c r="Q177" s="4"/>
       <c r="R177" s="4"/>
     </row>
-    <row r="178" spans="1:18" ht="13.5" customHeight="1">
+    <row r="178" ht="13.5" customHeight="1" spans="1:18">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -4359,7 +4982,7 @@
       <c r="Q178" s="4"/>
       <c r="R178" s="4"/>
     </row>
-    <row r="179" spans="1:18" ht="13.5" customHeight="1">
+    <row r="179" ht="13.5" customHeight="1" spans="1:18">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -4379,7 +5002,7 @@
       <c r="Q179" s="4"/>
       <c r="R179" s="4"/>
     </row>
-    <row r="180" spans="1:18" ht="13.5" customHeight="1">
+    <row r="180" ht="13.5" customHeight="1" spans="1:18">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -4399,7 +5022,7 @@
       <c r="Q180" s="4"/>
       <c r="R180" s="4"/>
     </row>
-    <row r="181" spans="1:18" ht="13.5" customHeight="1">
+    <row r="181" ht="13.5" customHeight="1" spans="1:18">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -4419,7 +5042,7 @@
       <c r="Q181" s="4"/>
       <c r="R181" s="4"/>
     </row>
-    <row r="182" spans="1:18" ht="13.5" customHeight="1">
+    <row r="182" ht="13.5" customHeight="1" spans="1:18">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -4439,7 +5062,7 @@
       <c r="Q182" s="4"/>
       <c r="R182" s="4"/>
     </row>
-    <row r="183" spans="1:18" ht="13.5" customHeight="1">
+    <row r="183" ht="13.5" customHeight="1" spans="1:18">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -4459,7 +5082,7 @@
       <c r="Q183" s="4"/>
       <c r="R183" s="4"/>
     </row>
-    <row r="184" spans="1:18" ht="13.5" customHeight="1">
+    <row r="184" ht="13.5" customHeight="1" spans="1:18">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -4479,7 +5102,7 @@
       <c r="Q184" s="4"/>
       <c r="R184" s="4"/>
     </row>
-    <row r="185" spans="1:18" ht="13.5" customHeight="1">
+    <row r="185" ht="13.5" customHeight="1" spans="1:18">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -4499,7 +5122,7 @@
       <c r="Q185" s="4"/>
       <c r="R185" s="4"/>
     </row>
-    <row r="186" spans="1:18" ht="13.5" customHeight="1">
+    <row r="186" ht="13.5" customHeight="1" spans="1:18">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -4519,7 +5142,7 @@
       <c r="Q186" s="4"/>
       <c r="R186" s="4"/>
     </row>
-    <row r="187" spans="1:18" ht="13.5" customHeight="1">
+    <row r="187" ht="13.5" customHeight="1" spans="1:18">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -4539,7 +5162,7 @@
       <c r="Q187" s="4"/>
       <c r="R187" s="4"/>
     </row>
-    <row r="188" spans="1:18" ht="13.5" customHeight="1">
+    <row r="188" ht="13.5" customHeight="1" spans="1:18">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -4559,7 +5182,7 @@
       <c r="Q188" s="4"/>
       <c r="R188" s="4"/>
     </row>
-    <row r="189" spans="1:18" ht="13.5" customHeight="1">
+    <row r="189" ht="13.5" customHeight="1" spans="1:18">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -4579,7 +5202,7 @@
       <c r="Q189" s="4"/>
       <c r="R189" s="4"/>
     </row>
-    <row r="190" spans="1:18" ht="13.5" customHeight="1">
+    <row r="190" ht="13.5" customHeight="1" spans="1:18">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -4599,7 +5222,7 @@
       <c r="Q190" s="4"/>
       <c r="R190" s="4"/>
     </row>
-    <row r="191" spans="1:18" ht="13.5" customHeight="1">
+    <row r="191" ht="13.5" customHeight="1" spans="1:18">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -4619,7 +5242,7 @@
       <c r="Q191" s="4"/>
       <c r="R191" s="4"/>
     </row>
-    <row r="192" spans="1:18" ht="13.5" customHeight="1">
+    <row r="192" ht="13.5" customHeight="1" spans="1:18">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -4639,7 +5262,7 @@
       <c r="Q192" s="4"/>
       <c r="R192" s="4"/>
     </row>
-    <row r="193" spans="1:18" ht="13.5" customHeight="1">
+    <row r="193" ht="13.5" customHeight="1" spans="1:18">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -4659,7 +5282,7 @@
       <c r="Q193" s="4"/>
       <c r="R193" s="4"/>
     </row>
-    <row r="194" spans="1:18" ht="13.5" customHeight="1">
+    <row r="194" ht="13.5" customHeight="1" spans="1:18">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -4679,7 +5302,7 @@
       <c r="Q194" s="4"/>
       <c r="R194" s="4"/>
     </row>
-    <row r="195" spans="1:18" ht="13.5" customHeight="1">
+    <row r="195" ht="13.5" customHeight="1" spans="1:18">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -4699,7 +5322,7 @@
       <c r="Q195" s="4"/>
       <c r="R195" s="4"/>
     </row>
-    <row r="196" spans="1:18" ht="13.5" customHeight="1">
+    <row r="196" ht="13.5" customHeight="1" spans="1:18">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -4719,7 +5342,7 @@
       <c r="Q196" s="4"/>
       <c r="R196" s="4"/>
     </row>
-    <row r="197" spans="1:18" ht="13.5" customHeight="1">
+    <row r="197" ht="13.5" customHeight="1" spans="1:18">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -4739,7 +5362,7 @@
       <c r="Q197" s="4"/>
       <c r="R197" s="4"/>
     </row>
-    <row r="198" spans="1:18" ht="13.5" customHeight="1">
+    <row r="198" ht="13.5" customHeight="1" spans="1:18">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -4759,7 +5382,7 @@
       <c r="Q198" s="4"/>
       <c r="R198" s="4"/>
     </row>
-    <row r="199" spans="1:18" ht="13.5" customHeight="1">
+    <row r="199" ht="13.5" customHeight="1" spans="1:18">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -4779,7 +5402,7 @@
       <c r="Q199" s="4"/>
       <c r="R199" s="4"/>
     </row>
-    <row r="200" spans="1:18" ht="13.5" customHeight="1">
+    <row r="200" ht="13.5" customHeight="1" spans="1:18">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -4799,7 +5422,7 @@
       <c r="Q200" s="4"/>
       <c r="R200" s="4"/>
     </row>
-    <row r="201" spans="1:18" ht="13.5" customHeight="1">
+    <row r="201" ht="13.5" customHeight="1" spans="1:18">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -4819,7 +5442,7 @@
       <c r="Q201" s="4"/>
       <c r="R201" s="4"/>
     </row>
-    <row r="202" spans="1:18" ht="13.5" customHeight="1">
+    <row r="202" ht="13.5" customHeight="1" spans="1:18">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -4839,7 +5462,7 @@
       <c r="Q202" s="4"/>
       <c r="R202" s="4"/>
     </row>
-    <row r="203" spans="1:18" ht="13.5" customHeight="1">
+    <row r="203" ht="13.5" customHeight="1" spans="1:18">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -4859,7 +5482,7 @@
       <c r="Q203" s="4"/>
       <c r="R203" s="4"/>
     </row>
-    <row r="204" spans="1:18" ht="13.5" customHeight="1">
+    <row r="204" ht="13.5" customHeight="1" spans="1:18">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -4879,7 +5502,7 @@
       <c r="Q204" s="4"/>
       <c r="R204" s="4"/>
     </row>
-    <row r="205" spans="1:18" ht="13.5" customHeight="1">
+    <row r="205" ht="13.5" customHeight="1" spans="1:18">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -4899,7 +5522,7 @@
       <c r="Q205" s="4"/>
       <c r="R205" s="4"/>
     </row>
-    <row r="206" spans="1:18" ht="13.5" customHeight="1">
+    <row r="206" ht="13.5" customHeight="1" spans="1:18">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -4919,7 +5542,7 @@
       <c r="Q206" s="4"/>
       <c r="R206" s="4"/>
     </row>
-    <row r="207" spans="1:18" ht="13.5" customHeight="1">
+    <row r="207" ht="13.5" customHeight="1" spans="1:18">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -4939,7 +5562,7 @@
       <c r="Q207" s="4"/>
       <c r="R207" s="4"/>
     </row>
-    <row r="208" spans="1:18" ht="13.5" customHeight="1">
+    <row r="208" ht="13.5" customHeight="1" spans="1:18">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -4959,7 +5582,7 @@
       <c r="Q208" s="4"/>
       <c r="R208" s="4"/>
     </row>
-    <row r="209" spans="1:18" ht="13.5" customHeight="1">
+    <row r="209" ht="13.5" customHeight="1" spans="1:18">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -4979,7 +5602,7 @@
       <c r="Q209" s="4"/>
       <c r="R209" s="4"/>
     </row>
-    <row r="210" spans="1:18" ht="13.5" customHeight="1">
+    <row r="210" ht="13.5" customHeight="1" spans="1:18">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -4999,7 +5622,7 @@
       <c r="Q210" s="4"/>
       <c r="R210" s="4"/>
     </row>
-    <row r="211" spans="1:18" ht="13.5" customHeight="1">
+    <row r="211" ht="13.5" customHeight="1" spans="1:18">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -5019,7 +5642,7 @@
       <c r="Q211" s="4"/>
       <c r="R211" s="4"/>
     </row>
-    <row r="212" spans="1:18" ht="13.5" customHeight="1">
+    <row r="212" ht="13.5" customHeight="1" spans="1:18">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -5039,7 +5662,7 @@
       <c r="Q212" s="4"/>
       <c r="R212" s="4"/>
     </row>
-    <row r="213" spans="1:18" ht="13.5" customHeight="1">
+    <row r="213" ht="13.5" customHeight="1" spans="1:18">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -5059,7 +5682,7 @@
       <c r="Q213" s="4"/>
       <c r="R213" s="4"/>
     </row>
-    <row r="214" spans="1:18" ht="13.5" customHeight="1">
+    <row r="214" ht="13.5" customHeight="1" spans="1:18">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -5079,7 +5702,7 @@
       <c r="Q214" s="4"/>
       <c r="R214" s="4"/>
     </row>
-    <row r="215" spans="1:18" ht="13.5" customHeight="1">
+    <row r="215" ht="13.5" customHeight="1" spans="1:18">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -5099,7 +5722,7 @@
       <c r="Q215" s="4"/>
       <c r="R215" s="4"/>
     </row>
-    <row r="216" spans="1:18" ht="13.5" customHeight="1">
+    <row r="216" ht="13.5" customHeight="1" spans="1:18">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -5119,7 +5742,7 @@
       <c r="Q216" s="4"/>
       <c r="R216" s="4"/>
     </row>
-    <row r="217" spans="1:18" ht="13.5" customHeight="1">
+    <row r="217" ht="13.5" customHeight="1" spans="1:18">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -5139,7 +5762,7 @@
       <c r="Q217" s="4"/>
       <c r="R217" s="4"/>
     </row>
-    <row r="218" spans="1:18" ht="13.5" customHeight="1">
+    <row r="218" ht="13.5" customHeight="1" spans="1:18">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -5159,7 +5782,7 @@
       <c r="Q218" s="4"/>
       <c r="R218" s="4"/>
     </row>
-    <row r="219" spans="1:18" ht="13.5" customHeight="1">
+    <row r="219" ht="13.5" customHeight="1" spans="1:18">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -5179,7 +5802,7 @@
       <c r="Q219" s="4"/>
       <c r="R219" s="4"/>
     </row>
-    <row r="220" spans="1:18" ht="13.5" customHeight="1">
+    <row r="220" ht="13.5" customHeight="1" spans="1:18">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -5199,7 +5822,7 @@
       <c r="Q220" s="4"/>
       <c r="R220" s="4"/>
     </row>
-    <row r="221" spans="1:18" ht="13.5" customHeight="1">
+    <row r="221" ht="13.5" customHeight="1" spans="1:18">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -5219,7 +5842,7 @@
       <c r="Q221" s="4"/>
       <c r="R221" s="4"/>
     </row>
-    <row r="222" spans="1:18" ht="13.5" customHeight="1">
+    <row r="222" ht="13.5" customHeight="1" spans="1:18">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -5239,7 +5862,7 @@
       <c r="Q222" s="4"/>
       <c r="R222" s="4"/>
     </row>
-    <row r="223" spans="1:18" ht="13.5" customHeight="1">
+    <row r="223" ht="13.5" customHeight="1" spans="1:18">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -5259,7 +5882,7 @@
       <c r="Q223" s="4"/>
       <c r="R223" s="4"/>
     </row>
-    <row r="224" spans="1:18" ht="13.5" customHeight="1">
+    <row r="224" ht="13.5" customHeight="1" spans="1:18">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -5279,7 +5902,7 @@
       <c r="Q224" s="4"/>
       <c r="R224" s="4"/>
     </row>
-    <row r="225" spans="1:18" ht="13.5" customHeight="1">
+    <row r="225" ht="13.5" customHeight="1" spans="1:18">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -5299,7 +5922,7 @@
       <c r="Q225" s="4"/>
       <c r="R225" s="4"/>
     </row>
-    <row r="226" spans="1:18" ht="13.5" customHeight="1">
+    <row r="226" ht="13.5" customHeight="1" spans="1:18">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -5319,7 +5942,7 @@
       <c r="Q226" s="4"/>
       <c r="R226" s="4"/>
     </row>
-    <row r="227" spans="1:18" ht="13.5" customHeight="1">
+    <row r="227" ht="13.5" customHeight="1" spans="1:18">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -5339,7 +5962,7 @@
       <c r="Q227" s="4"/>
       <c r="R227" s="4"/>
     </row>
-    <row r="228" spans="1:18" ht="13.5" customHeight="1">
+    <row r="228" ht="13.5" customHeight="1" spans="1:18">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -5359,7 +5982,7 @@
       <c r="Q228" s="4"/>
       <c r="R228" s="4"/>
     </row>
-    <row r="229" spans="1:18" ht="13.5" customHeight="1">
+    <row r="229" ht="13.5" customHeight="1" spans="1:18">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -5379,7 +6002,7 @@
       <c r="Q229" s="4"/>
       <c r="R229" s="4"/>
     </row>
-    <row r="230" spans="1:18" ht="13.5" customHeight="1">
+    <row r="230" ht="13.5" customHeight="1" spans="1:18">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -5399,7 +6022,7 @@
       <c r="Q230" s="4"/>
       <c r="R230" s="4"/>
     </row>
-    <row r="231" spans="1:18" ht="13.5" customHeight="1">
+    <row r="231" ht="13.5" customHeight="1" spans="1:18">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -5419,7 +6042,7 @@
       <c r="Q231" s="4"/>
       <c r="R231" s="4"/>
     </row>
-    <row r="232" spans="1:18" ht="13.5" customHeight="1">
+    <row r="232" ht="13.5" customHeight="1" spans="1:18">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -5439,7 +6062,7 @@
       <c r="Q232" s="4"/>
       <c r="R232" s="4"/>
     </row>
-    <row r="233" spans="1:18" ht="13.5" customHeight="1">
+    <row r="233" ht="13.5" customHeight="1" spans="1:18">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -5459,7 +6082,7 @@
       <c r="Q233" s="4"/>
       <c r="R233" s="4"/>
     </row>
-    <row r="234" spans="1:18" ht="13.5" customHeight="1">
+    <row r="234" ht="13.5" customHeight="1" spans="1:18">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -5479,7 +6102,7 @@
       <c r="Q234" s="4"/>
       <c r="R234" s="4"/>
     </row>
-    <row r="235" spans="1:18" ht="13.5" customHeight="1">
+    <row r="235" ht="13.5" customHeight="1" spans="1:18">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -5499,7 +6122,7 @@
       <c r="Q235" s="4"/>
       <c r="R235" s="4"/>
     </row>
-    <row r="236" spans="1:18" ht="13.5" customHeight="1">
+    <row r="236" ht="13.5" customHeight="1" spans="1:18">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -5519,7 +6142,7 @@
       <c r="Q236" s="4"/>
       <c r="R236" s="4"/>
     </row>
-    <row r="237" spans="1:18" ht="13.5" customHeight="1">
+    <row r="237" ht="13.5" customHeight="1" spans="1:18">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -5539,7 +6162,7 @@
       <c r="Q237" s="4"/>
       <c r="R237" s="4"/>
     </row>
-    <row r="238" spans="1:18" ht="13.5" customHeight="1">
+    <row r="238" ht="13.5" customHeight="1" spans="1:18">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -5559,7 +6182,7 @@
       <c r="Q238" s="4"/>
       <c r="R238" s="4"/>
     </row>
-    <row r="239" spans="1:18" ht="13.5" customHeight="1">
+    <row r="239" ht="13.5" customHeight="1" spans="1:18">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -5579,7 +6202,7 @@
       <c r="Q239" s="4"/>
       <c r="R239" s="4"/>
     </row>
-    <row r="240" spans="1:18" ht="13.5" customHeight="1">
+    <row r="240" ht="13.5" customHeight="1" spans="1:18">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -5599,7 +6222,7 @@
       <c r="Q240" s="4"/>
       <c r="R240" s="4"/>
     </row>
-    <row r="241" spans="1:18" ht="13.5" customHeight="1">
+    <row r="241" ht="13.5" customHeight="1" spans="1:18">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -5619,7 +6242,7 @@
       <c r="Q241" s="4"/>
       <c r="R241" s="4"/>
     </row>
-    <row r="242" spans="1:18" ht="13.5" customHeight="1">
+    <row r="242" ht="13.5" customHeight="1" spans="1:18">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -5639,7 +6262,7 @@
       <c r="Q242" s="4"/>
       <c r="R242" s="4"/>
     </row>
-    <row r="243" spans="1:18" ht="13.5" customHeight="1">
+    <row r="243" ht="13.5" customHeight="1" spans="1:18">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -5659,7 +6282,7 @@
       <c r="Q243" s="4"/>
       <c r="R243" s="4"/>
     </row>
-    <row r="244" spans="1:18" ht="13.5" customHeight="1">
+    <row r="244" ht="13.5" customHeight="1" spans="1:18">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -5679,7 +6302,7 @@
       <c r="Q244" s="4"/>
       <c r="R244" s="4"/>
     </row>
-    <row r="245" spans="1:18" ht="13.5" customHeight="1">
+    <row r="245" ht="13.5" customHeight="1" spans="1:18">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -5699,7 +6322,7 @@
       <c r="Q245" s="4"/>
       <c r="R245" s="4"/>
     </row>
-    <row r="246" spans="1:18" ht="13.5" customHeight="1">
+    <row r="246" ht="13.5" customHeight="1" spans="1:18">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -5719,7 +6342,7 @@
       <c r="Q246" s="4"/>
       <c r="R246" s="4"/>
     </row>
-    <row r="247" spans="1:18" ht="13.5" customHeight="1">
+    <row r="247" ht="13.5" customHeight="1" spans="1:18">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -5739,7 +6362,7 @@
       <c r="Q247" s="4"/>
       <c r="R247" s="4"/>
     </row>
-    <row r="248" spans="1:18" ht="13.5" customHeight="1">
+    <row r="248" ht="13.5" customHeight="1" spans="1:18">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -5759,7 +6382,7 @@
       <c r="Q248" s="4"/>
       <c r="R248" s="4"/>
     </row>
-    <row r="249" spans="1:18" ht="13.5" customHeight="1">
+    <row r="249" ht="13.5" customHeight="1" spans="1:18">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -5779,7 +6402,7 @@
       <c r="Q249" s="4"/>
       <c r="R249" s="4"/>
     </row>
-    <row r="250" spans="1:18" ht="13.5" customHeight="1">
+    <row r="250" ht="13.5" customHeight="1" spans="1:18">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -5799,7 +6422,7 @@
       <c r="Q250" s="4"/>
       <c r="R250" s="4"/>
     </row>
-    <row r="251" spans="1:18" ht="13.5" customHeight="1">
+    <row r="251" ht="13.5" customHeight="1" spans="1:18">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -5819,7 +6442,7 @@
       <c r="Q251" s="4"/>
       <c r="R251" s="4"/>
     </row>
-    <row r="252" spans="1:18" ht="13.5" customHeight="1">
+    <row r="252" ht="13.5" customHeight="1" spans="1:18">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -5839,7 +6462,7 @@
       <c r="Q252" s="4"/>
       <c r="R252" s="4"/>
     </row>
-    <row r="253" spans="1:18" ht="13.5" customHeight="1">
+    <row r="253" ht="13.5" customHeight="1" spans="1:18">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -5859,7 +6482,7 @@
       <c r="Q253" s="4"/>
       <c r="R253" s="4"/>
     </row>
-    <row r="254" spans="1:18" ht="13.5" customHeight="1">
+    <row r="254" ht="13.5" customHeight="1" spans="1:18">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -5879,7 +6502,7 @@
       <c r="Q254" s="4"/>
       <c r="R254" s="4"/>
     </row>
-    <row r="255" spans="1:18" ht="13.5" customHeight="1">
+    <row r="255" ht="13.5" customHeight="1" spans="1:18">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -5899,7 +6522,7 @@
       <c r="Q255" s="4"/>
       <c r="R255" s="4"/>
     </row>
-    <row r="256" spans="1:18" ht="13.5" customHeight="1">
+    <row r="256" ht="13.5" customHeight="1" spans="1:18">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -5919,7 +6542,7 @@
       <c r="Q256" s="4"/>
       <c r="R256" s="4"/>
     </row>
-    <row r="257" spans="1:18" ht="13.5" customHeight="1">
+    <row r="257" ht="13.5" customHeight="1" spans="1:18">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -5939,7 +6562,7 @@
       <c r="Q257" s="4"/>
       <c r="R257" s="4"/>
     </row>
-    <row r="258" spans="1:18" ht="13.5" customHeight="1">
+    <row r="258" ht="13.5" customHeight="1" spans="1:18">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -5959,7 +6582,7 @@
       <c r="Q258" s="4"/>
       <c r="R258" s="4"/>
     </row>
-    <row r="259" spans="1:18" ht="13.5" customHeight="1">
+    <row r="259" ht="13.5" customHeight="1" spans="1:18">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -5979,7 +6602,7 @@
       <c r="Q259" s="4"/>
       <c r="R259" s="4"/>
     </row>
-    <row r="260" spans="1:18" ht="13.5" customHeight="1">
+    <row r="260" ht="13.5" customHeight="1" spans="1:18">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -5999,7 +6622,7 @@
       <c r="Q260" s="4"/>
       <c r="R260" s="4"/>
     </row>
-    <row r="261" spans="1:18" ht="13.5" customHeight="1">
+    <row r="261" ht="13.5" customHeight="1" spans="1:18">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -6019,7 +6642,7 @@
       <c r="Q261" s="4"/>
       <c r="R261" s="4"/>
     </row>
-    <row r="262" spans="1:18" ht="13.5" customHeight="1">
+    <row r="262" ht="13.5" customHeight="1" spans="1:18">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -6039,7 +6662,7 @@
       <c r="Q262" s="4"/>
       <c r="R262" s="4"/>
     </row>
-    <row r="263" spans="1:18" ht="13.5" customHeight="1">
+    <row r="263" ht="13.5" customHeight="1" spans="1:18">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -6059,7 +6682,7 @@
       <c r="Q263" s="4"/>
       <c r="R263" s="4"/>
     </row>
-    <row r="264" spans="1:18" ht="13.5" customHeight="1">
+    <row r="264" ht="13.5" customHeight="1" spans="1:18">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -6079,7 +6702,7 @@
       <c r="Q264" s="4"/>
       <c r="R264" s="4"/>
     </row>
-    <row r="265" spans="1:18" ht="13.5" customHeight="1">
+    <row r="265" ht="13.5" customHeight="1" spans="1:18">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -6099,7 +6722,7 @@
       <c r="Q265" s="4"/>
       <c r="R265" s="4"/>
     </row>
-    <row r="266" spans="1:18" ht="13.5" customHeight="1">
+    <row r="266" ht="13.5" customHeight="1" spans="1:18">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -6119,7 +6742,7 @@
       <c r="Q266" s="4"/>
       <c r="R266" s="4"/>
     </row>
-    <row r="267" spans="1:18" ht="13.5" customHeight="1">
+    <row r="267" ht="13.5" customHeight="1" spans="1:18">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -6139,7 +6762,7 @@
       <c r="Q267" s="4"/>
       <c r="R267" s="4"/>
     </row>
-    <row r="268" spans="1:18" ht="13.5" customHeight="1">
+    <row r="268" ht="13.5" customHeight="1" spans="1:18">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -6159,7 +6782,7 @@
       <c r="Q268" s="4"/>
       <c r="R268" s="4"/>
     </row>
-    <row r="269" spans="1:18" ht="13.5" customHeight="1">
+    <row r="269" ht="13.5" customHeight="1" spans="1:18">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -6179,7 +6802,7 @@
       <c r="Q269" s="4"/>
       <c r="R269" s="4"/>
     </row>
-    <row r="270" spans="1:18" ht="13.5" customHeight="1">
+    <row r="270" ht="13.5" customHeight="1" spans="1:18">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -6199,7 +6822,7 @@
       <c r="Q270" s="4"/>
       <c r="R270" s="4"/>
     </row>
-    <row r="271" spans="1:18" ht="13.5" customHeight="1">
+    <row r="271" ht="13.5" customHeight="1" spans="1:18">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -6219,7 +6842,7 @@
       <c r="Q271" s="4"/>
       <c r="R271" s="4"/>
     </row>
-    <row r="272" spans="1:18" ht="13.5" customHeight="1">
+    <row r="272" ht="13.5" customHeight="1" spans="1:18">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -6239,7 +6862,7 @@
       <c r="Q272" s="4"/>
       <c r="R272" s="4"/>
     </row>
-    <row r="273" spans="1:18" ht="13.5" customHeight="1">
+    <row r="273" ht="13.5" customHeight="1" spans="1:18">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -6259,7 +6882,7 @@
       <c r="Q273" s="4"/>
       <c r="R273" s="4"/>
     </row>
-    <row r="274" spans="1:18" ht="13.5" customHeight="1">
+    <row r="274" ht="13.5" customHeight="1" spans="1:18">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -6279,7 +6902,7 @@
       <c r="Q274" s="4"/>
       <c r="R274" s="4"/>
     </row>
-    <row r="275" spans="1:18" ht="13.5" customHeight="1">
+    <row r="275" ht="13.5" customHeight="1" spans="1:18">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -6299,7 +6922,7 @@
       <c r="Q275" s="4"/>
       <c r="R275" s="4"/>
     </row>
-    <row r="276" spans="1:18" ht="13.5" customHeight="1">
+    <row r="276" ht="13.5" customHeight="1" spans="1:18">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -6319,7 +6942,7 @@
       <c r="Q276" s="4"/>
       <c r="R276" s="4"/>
     </row>
-    <row r="277" spans="1:18" ht="13.5" customHeight="1">
+    <row r="277" ht="13.5" customHeight="1" spans="1:18">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -6339,7 +6962,7 @@
       <c r="Q277" s="4"/>
       <c r="R277" s="4"/>
     </row>
-    <row r="278" spans="1:18" ht="13.5" customHeight="1">
+    <row r="278" ht="13.5" customHeight="1" spans="1:18">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -6359,7 +6982,7 @@
       <c r="Q278" s="4"/>
       <c r="R278" s="4"/>
     </row>
-    <row r="279" spans="1:18" ht="13.5" customHeight="1">
+    <row r="279" ht="13.5" customHeight="1" spans="1:18">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -6379,7 +7002,7 @@
       <c r="Q279" s="4"/>
       <c r="R279" s="4"/>
     </row>
-    <row r="280" spans="1:18" ht="13.5" customHeight="1">
+    <row r="280" ht="13.5" customHeight="1" spans="1:18">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -6399,7 +7022,7 @@
       <c r="Q280" s="4"/>
       <c r="R280" s="4"/>
     </row>
-    <row r="281" spans="1:18" ht="13.5" customHeight="1">
+    <row r="281" ht="13.5" customHeight="1" spans="1:18">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -6419,7 +7042,7 @@
       <c r="Q281" s="4"/>
       <c r="R281" s="4"/>
     </row>
-    <row r="282" spans="1:18" ht="13.5" customHeight="1">
+    <row r="282" ht="13.5" customHeight="1" spans="1:18">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -6439,7 +7062,7 @@
       <c r="Q282" s="4"/>
       <c r="R282" s="4"/>
     </row>
-    <row r="283" spans="1:18" ht="13.5" customHeight="1">
+    <row r="283" ht="13.5" customHeight="1" spans="1:18">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -6459,7 +7082,7 @@
       <c r="Q283" s="4"/>
       <c r="R283" s="4"/>
     </row>
-    <row r="284" spans="1:18" ht="13.5" customHeight="1">
+    <row r="284" ht="13.5" customHeight="1" spans="1:18">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -6479,7 +7102,7 @@
       <c r="Q284" s="4"/>
       <c r="R284" s="4"/>
     </row>
-    <row r="285" spans="1:18" ht="13.5" customHeight="1">
+    <row r="285" ht="13.5" customHeight="1" spans="1:18">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -6499,7 +7122,7 @@
       <c r="Q285" s="4"/>
       <c r="R285" s="4"/>
     </row>
-    <row r="286" spans="1:18" ht="13.5" customHeight="1">
+    <row r="286" ht="13.5" customHeight="1" spans="1:18">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -6519,7 +7142,7 @@
       <c r="Q286" s="4"/>
       <c r="R286" s="4"/>
     </row>
-    <row r="287" spans="1:18" ht="13.5" customHeight="1">
+    <row r="287" ht="13.5" customHeight="1" spans="1:18">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -6539,7 +7162,7 @@
       <c r="Q287" s="4"/>
       <c r="R287" s="4"/>
     </row>
-    <row r="288" spans="1:18" ht="13.5" customHeight="1">
+    <row r="288" ht="13.5" customHeight="1" spans="1:18">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -6559,7 +7182,7 @@
       <c r="Q288" s="4"/>
       <c r="R288" s="4"/>
     </row>
-    <row r="289" spans="1:18" ht="13.5" customHeight="1">
+    <row r="289" ht="13.5" customHeight="1" spans="1:18">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -6579,7 +7202,7 @@
       <c r="Q289" s="4"/>
       <c r="R289" s="4"/>
     </row>
-    <row r="290" spans="1:18" ht="13.5" customHeight="1">
+    <row r="290" ht="13.5" customHeight="1" spans="1:18">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -6599,7 +7222,7 @@
       <c r="Q290" s="4"/>
       <c r="R290" s="4"/>
     </row>
-    <row r="291" spans="1:18" ht="13.5" customHeight="1">
+    <row r="291" ht="13.5" customHeight="1" spans="1:18">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -6619,7 +7242,7 @@
       <c r="Q291" s="4"/>
       <c r="R291" s="4"/>
     </row>
-    <row r="292" spans="1:18" ht="13.5" customHeight="1">
+    <row r="292" ht="13.5" customHeight="1" spans="1:18">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -6639,7 +7262,7 @@
       <c r="Q292" s="4"/>
       <c r="R292" s="4"/>
     </row>
-    <row r="293" spans="1:18" ht="13.5" customHeight="1">
+    <row r="293" ht="13.5" customHeight="1" spans="1:18">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -6659,7 +7282,7 @@
       <c r="Q293" s="4"/>
       <c r="R293" s="4"/>
     </row>
-    <row r="294" spans="1:18" ht="13.5" customHeight="1">
+    <row r="294" ht="13.5" customHeight="1" spans="1:18">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -6679,7 +7302,7 @@
       <c r="Q294" s="4"/>
       <c r="R294" s="4"/>
     </row>
-    <row r="295" spans="1:18" ht="13.5" customHeight="1">
+    <row r="295" ht="13.5" customHeight="1" spans="1:18">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -6699,7 +7322,7 @@
       <c r="Q295" s="4"/>
       <c r="R295" s="4"/>
     </row>
-    <row r="296" spans="1:18" ht="13.5" customHeight="1">
+    <row r="296" ht="13.5" customHeight="1" spans="1:18">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -6719,7 +7342,7 @@
       <c r="Q296" s="4"/>
       <c r="R296" s="4"/>
     </row>
-    <row r="297" spans="1:18" ht="13.5" customHeight="1">
+    <row r="297" ht="13.5" customHeight="1" spans="1:18">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -6739,7 +7362,7 @@
       <c r="Q297" s="4"/>
       <c r="R297" s="4"/>
     </row>
-    <row r="298" spans="1:18" ht="13.5" customHeight="1">
+    <row r="298" ht="13.5" customHeight="1" spans="1:18">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -6759,7 +7382,7 @@
       <c r="Q298" s="4"/>
       <c r="R298" s="4"/>
     </row>
-    <row r="299" spans="1:18" ht="13.5" customHeight="1">
+    <row r="299" ht="13.5" customHeight="1" spans="1:18">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -6779,7 +7402,7 @@
       <c r="Q299" s="4"/>
       <c r="R299" s="4"/>
     </row>
-    <row r="300" spans="1:18" ht="13.5" customHeight="1">
+    <row r="300" ht="13.5" customHeight="1" spans="1:18">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -6799,7 +7422,7 @@
       <c r="Q300" s="4"/>
       <c r="R300" s="4"/>
     </row>
-    <row r="301" spans="1:18" ht="13.5" customHeight="1">
+    <row r="301" ht="13.5" customHeight="1" spans="1:18">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -6819,7 +7442,7 @@
       <c r="Q301" s="4"/>
       <c r="R301" s="4"/>
     </row>
-    <row r="302" spans="1:18" ht="13.5" customHeight="1">
+    <row r="302" ht="13.5" customHeight="1" spans="1:18">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -6839,7 +7462,7 @@
       <c r="Q302" s="4"/>
       <c r="R302" s="4"/>
     </row>
-    <row r="303" spans="1:18" ht="13.5" customHeight="1">
+    <row r="303" ht="13.5" customHeight="1" spans="1:18">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -6859,7 +7482,7 @@
       <c r="Q303" s="4"/>
       <c r="R303" s="4"/>
     </row>
-    <row r="304" spans="1:18" ht="13.5" customHeight="1">
+    <row r="304" ht="13.5" customHeight="1" spans="1:18">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -6879,7 +7502,7 @@
       <c r="Q304" s="4"/>
       <c r="R304" s="4"/>
     </row>
-    <row r="305" spans="1:18" ht="13.5" customHeight="1">
+    <row r="305" ht="13.5" customHeight="1" spans="1:18">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -6899,7 +7522,7 @@
       <c r="Q305" s="4"/>
       <c r="R305" s="4"/>
     </row>
-    <row r="306" spans="1:18" ht="13.5" customHeight="1">
+    <row r="306" ht="13.5" customHeight="1" spans="1:18">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -6919,7 +7542,7 @@
       <c r="Q306" s="4"/>
       <c r="R306" s="4"/>
     </row>
-    <row r="307" spans="1:18" ht="13.5" customHeight="1">
+    <row r="307" ht="13.5" customHeight="1" spans="1:18">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -6939,7 +7562,7 @@
       <c r="Q307" s="4"/>
       <c r="R307" s="4"/>
     </row>
-    <row r="308" spans="1:18" ht="13.5" customHeight="1">
+    <row r="308" ht="13.5" customHeight="1" spans="1:18">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -6959,7 +7582,7 @@
       <c r="Q308" s="4"/>
       <c r="R308" s="4"/>
     </row>
-    <row r="309" spans="1:18" ht="13.5" customHeight="1">
+    <row r="309" ht="13.5" customHeight="1" spans="1:18">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -6979,7 +7602,7 @@
       <c r="Q309" s="4"/>
       <c r="R309" s="4"/>
     </row>
-    <row r="310" spans="1:18" ht="13.5" customHeight="1">
+    <row r="310" ht="13.5" customHeight="1" spans="1:18">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -6999,7 +7622,7 @@
       <c r="Q310" s="4"/>
       <c r="R310" s="4"/>
     </row>
-    <row r="311" spans="1:18" ht="13.5" customHeight="1">
+    <row r="311" ht="13.5" customHeight="1" spans="1:18">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -7019,7 +7642,7 @@
       <c r="Q311" s="4"/>
       <c r="R311" s="4"/>
     </row>
-    <row r="312" spans="1:18" ht="13.5" customHeight="1">
+    <row r="312" ht="13.5" customHeight="1" spans="1:18">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -7039,7 +7662,7 @@
       <c r="Q312" s="4"/>
       <c r="R312" s="4"/>
     </row>
-    <row r="313" spans="1:18" ht="13.5" customHeight="1">
+    <row r="313" ht="13.5" customHeight="1" spans="1:18">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -7059,7 +7682,7 @@
       <c r="Q313" s="4"/>
       <c r="R313" s="4"/>
     </row>
-    <row r="314" spans="1:18" ht="13.5" customHeight="1">
+    <row r="314" ht="13.5" customHeight="1" spans="1:18">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -7079,7 +7702,7 @@
       <c r="Q314" s="4"/>
       <c r="R314" s="4"/>
     </row>
-    <row r="315" spans="1:18" ht="13.5" customHeight="1">
+    <row r="315" ht="13.5" customHeight="1" spans="1:18">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -7099,7 +7722,7 @@
       <c r="Q315" s="4"/>
       <c r="R315" s="4"/>
     </row>
-    <row r="316" spans="1:18" ht="13.5" customHeight="1">
+    <row r="316" ht="13.5" customHeight="1" spans="1:18">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -7119,7 +7742,7 @@
       <c r="Q316" s="4"/>
       <c r="R316" s="4"/>
     </row>
-    <row r="317" spans="1:18" ht="13.5" customHeight="1">
+    <row r="317" ht="13.5" customHeight="1" spans="1:18">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -7139,7 +7762,7 @@
       <c r="Q317" s="4"/>
       <c r="R317" s="4"/>
     </row>
-    <row r="318" spans="1:18" ht="13.5" customHeight="1">
+    <row r="318" ht="13.5" customHeight="1" spans="1:18">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -7159,7 +7782,7 @@
       <c r="Q318" s="4"/>
       <c r="R318" s="4"/>
     </row>
-    <row r="319" spans="1:18" ht="13.5" customHeight="1">
+    <row r="319" ht="13.5" customHeight="1" spans="1:18">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -7179,7 +7802,7 @@
       <c r="Q319" s="4"/>
       <c r="R319" s="4"/>
     </row>
-    <row r="320" spans="1:18" ht="13.5" customHeight="1">
+    <row r="320" ht="13.5" customHeight="1" spans="1:18">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -7199,7 +7822,7 @@
       <c r="Q320" s="4"/>
       <c r="R320" s="4"/>
     </row>
-    <row r="321" spans="1:18" ht="13.5" customHeight="1">
+    <row r="321" ht="13.5" customHeight="1" spans="1:18">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -7219,7 +7842,7 @@
       <c r="Q321" s="4"/>
       <c r="R321" s="4"/>
     </row>
-    <row r="322" spans="1:18" ht="13.5" customHeight="1">
+    <row r="322" ht="13.5" customHeight="1" spans="1:18">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -7239,7 +7862,7 @@
       <c r="Q322" s="4"/>
       <c r="R322" s="4"/>
     </row>
-    <row r="323" spans="1:18" ht="13.5" customHeight="1">
+    <row r="323" ht="13.5" customHeight="1" spans="1:18">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -7259,7 +7882,7 @@
       <c r="Q323" s="4"/>
       <c r="R323" s="4"/>
     </row>
-    <row r="324" spans="1:18" ht="13.5" customHeight="1">
+    <row r="324" ht="13.5" customHeight="1" spans="1:18">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -7279,7 +7902,7 @@
       <c r="Q324" s="4"/>
       <c r="R324" s="4"/>
     </row>
-    <row r="325" spans="1:18" ht="13.5" customHeight="1">
+    <row r="325" ht="13.5" customHeight="1" spans="1:18">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -7299,7 +7922,7 @@
       <c r="Q325" s="4"/>
       <c r="R325" s="4"/>
     </row>
-    <row r="326" spans="1:18" ht="13.5" customHeight="1">
+    <row r="326" ht="13.5" customHeight="1" spans="1:18">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -7319,7 +7942,7 @@
       <c r="Q326" s="4"/>
       <c r="R326" s="4"/>
     </row>
-    <row r="327" spans="1:18" ht="13.5" customHeight="1">
+    <row r="327" ht="13.5" customHeight="1" spans="1:18">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -7339,7 +7962,7 @@
       <c r="Q327" s="4"/>
       <c r="R327" s="4"/>
     </row>
-    <row r="328" spans="1:18" ht="13.5" customHeight="1">
+    <row r="328" ht="13.5" customHeight="1" spans="1:18">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -7359,7 +7982,7 @@
       <c r="Q328" s="4"/>
       <c r="R328" s="4"/>
     </row>
-    <row r="329" spans="1:18" ht="13.5" customHeight="1">
+    <row r="329" ht="13.5" customHeight="1" spans="1:18">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -7379,7 +8002,7 @@
       <c r="Q329" s="4"/>
       <c r="R329" s="4"/>
     </row>
-    <row r="330" spans="1:18" ht="13.5" customHeight="1">
+    <row r="330" ht="13.5" customHeight="1" spans="1:18">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -7399,7 +8022,7 @@
       <c r="Q330" s="4"/>
       <c r="R330" s="4"/>
     </row>
-    <row r="331" spans="1:18" ht="13.5" customHeight="1">
+    <row r="331" ht="13.5" customHeight="1" spans="1:18">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -7419,7 +8042,7 @@
       <c r="Q331" s="4"/>
       <c r="R331" s="4"/>
     </row>
-    <row r="332" spans="1:18" ht="13.5" customHeight="1">
+    <row r="332" ht="13.5" customHeight="1" spans="1:18">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -7439,7 +8062,7 @@
       <c r="Q332" s="4"/>
       <c r="R332" s="4"/>
     </row>
-    <row r="333" spans="1:18" ht="13.5" customHeight="1">
+    <row r="333" ht="13.5" customHeight="1" spans="1:18">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -7459,7 +8082,7 @@
       <c r="Q333" s="4"/>
       <c r="R333" s="4"/>
     </row>
-    <row r="334" spans="1:18" ht="13.5" customHeight="1">
+    <row r="334" ht="13.5" customHeight="1" spans="1:18">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -7479,7 +8102,7 @@
       <c r="Q334" s="4"/>
       <c r="R334" s="4"/>
     </row>
-    <row r="335" spans="1:18" ht="13.5" customHeight="1">
+    <row r="335" ht="13.5" customHeight="1" spans="1:18">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -7499,7 +8122,7 @@
       <c r="Q335" s="4"/>
       <c r="R335" s="4"/>
     </row>
-    <row r="336" spans="1:18" ht="13.5" customHeight="1">
+    <row r="336" ht="13.5" customHeight="1" spans="1:18">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -7519,7 +8142,7 @@
       <c r="Q336" s="4"/>
       <c r="R336" s="4"/>
     </row>
-    <row r="337" spans="1:18" ht="13.5" customHeight="1">
+    <row r="337" ht="13.5" customHeight="1" spans="1:18">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -7539,7 +8162,7 @@
       <c r="Q337" s="4"/>
       <c r="R337" s="4"/>
     </row>
-    <row r="338" spans="1:18" ht="13.5" customHeight="1">
+    <row r="338" ht="13.5" customHeight="1" spans="1:18">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -7559,7 +8182,7 @@
       <c r="Q338" s="4"/>
       <c r="R338" s="4"/>
     </row>
-    <row r="339" spans="1:18" ht="13.5" customHeight="1">
+    <row r="339" ht="13.5" customHeight="1" spans="1:18">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -7579,7 +8202,7 @@
       <c r="Q339" s="4"/>
       <c r="R339" s="4"/>
     </row>
-    <row r="340" spans="1:18" ht="13.5" customHeight="1">
+    <row r="340" ht="13.5" customHeight="1" spans="1:18">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -7599,7 +8222,7 @@
       <c r="Q340" s="4"/>
       <c r="R340" s="4"/>
     </row>
-    <row r="341" spans="1:18" ht="13.5" customHeight="1">
+    <row r="341" ht="13.5" customHeight="1" spans="1:18">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -7619,7 +8242,7 @@
       <c r="Q341" s="4"/>
       <c r="R341" s="4"/>
     </row>
-    <row r="342" spans="1:18" ht="13.5" customHeight="1">
+    <row r="342" ht="13.5" customHeight="1" spans="1:18">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -7639,7 +8262,7 @@
       <c r="Q342" s="4"/>
       <c r="R342" s="4"/>
     </row>
-    <row r="343" spans="1:18" ht="13.5" customHeight="1">
+    <row r="343" ht="13.5" customHeight="1" spans="1:18">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -7659,7 +8282,7 @@
       <c r="Q343" s="4"/>
       <c r="R343" s="4"/>
     </row>
-    <row r="344" spans="1:18" ht="13.5" customHeight="1">
+    <row r="344" ht="13.5" customHeight="1" spans="1:18">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -7679,7 +8302,7 @@
       <c r="Q344" s="4"/>
       <c r="R344" s="4"/>
     </row>
-    <row r="345" spans="1:18" ht="13.5" customHeight="1">
+    <row r="345" ht="13.5" customHeight="1" spans="1:18">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -7699,7 +8322,7 @@
       <c r="Q345" s="4"/>
       <c r="R345" s="4"/>
     </row>
-    <row r="346" spans="1:18" ht="13.5" customHeight="1">
+    <row r="346" ht="13.5" customHeight="1" spans="1:18">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -7719,7 +8342,7 @@
       <c r="Q346" s="4"/>
       <c r="R346" s="4"/>
     </row>
-    <row r="347" spans="1:18" ht="13.5" customHeight="1">
+    <row r="347" ht="13.5" customHeight="1" spans="1:18">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -7739,7 +8362,7 @@
       <c r="Q347" s="4"/>
       <c r="R347" s="4"/>
     </row>
-    <row r="348" spans="1:18" ht="13.5" customHeight="1">
+    <row r="348" ht="13.5" customHeight="1" spans="1:18">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -7759,7 +8382,7 @@
       <c r="Q348" s="4"/>
       <c r="R348" s="4"/>
     </row>
-    <row r="349" spans="1:18" ht="13.5" customHeight="1">
+    <row r="349" ht="13.5" customHeight="1" spans="1:18">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -7779,7 +8402,7 @@
       <c r="Q349" s="4"/>
       <c r="R349" s="4"/>
     </row>
-    <row r="350" spans="1:18" ht="13.5" customHeight="1">
+    <row r="350" ht="13.5" customHeight="1" spans="1:18">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -7799,7 +8422,7 @@
       <c r="Q350" s="4"/>
       <c r="R350" s="4"/>
     </row>
-    <row r="351" spans="1:18" ht="13.5" customHeight="1">
+    <row r="351" ht="13.5" customHeight="1" spans="1:18">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -7819,7 +8442,7 @@
       <c r="Q351" s="4"/>
       <c r="R351" s="4"/>
     </row>
-    <row r="352" spans="1:18" ht="13.5" customHeight="1">
+    <row r="352" ht="13.5" customHeight="1" spans="1:18">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -7839,7 +8462,7 @@
       <c r="Q352" s="4"/>
       <c r="R352" s="4"/>
     </row>
-    <row r="353" spans="1:18" ht="13.5" customHeight="1">
+    <row r="353" ht="13.5" customHeight="1" spans="1:18">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -7859,7 +8482,7 @@
       <c r="Q353" s="4"/>
       <c r="R353" s="4"/>
     </row>
-    <row r="354" spans="1:18" ht="13.5" customHeight="1">
+    <row r="354" ht="13.5" customHeight="1" spans="1:18">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -7879,7 +8502,7 @@
       <c r="Q354" s="4"/>
       <c r="R354" s="4"/>
     </row>
-    <row r="355" spans="1:18" ht="13.5" customHeight="1">
+    <row r="355" ht="13.5" customHeight="1" spans="1:18">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -7899,7 +8522,7 @@
       <c r="Q355" s="4"/>
       <c r="R355" s="4"/>
     </row>
-    <row r="356" spans="1:18" ht="13.5" customHeight="1">
+    <row r="356" ht="13.5" customHeight="1" spans="1:18">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -7919,7 +8542,7 @@
       <c r="Q356" s="4"/>
       <c r="R356" s="4"/>
     </row>
-    <row r="357" spans="1:18" ht="13.5" customHeight="1">
+    <row r="357" ht="13.5" customHeight="1" spans="1:18">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -7939,7 +8562,7 @@
       <c r="Q357" s="4"/>
       <c r="R357" s="4"/>
     </row>
-    <row r="358" spans="1:18" ht="13.5" customHeight="1">
+    <row r="358" ht="13.5" customHeight="1" spans="1:18">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -7959,7 +8582,7 @@
       <c r="Q358" s="4"/>
       <c r="R358" s="4"/>
     </row>
-    <row r="359" spans="1:18" ht="13.5" customHeight="1">
+    <row r="359" ht="13.5" customHeight="1" spans="1:18">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -7979,7 +8602,7 @@
       <c r="Q359" s="4"/>
       <c r="R359" s="4"/>
     </row>
-    <row r="360" spans="1:18" ht="13.5" customHeight="1">
+    <row r="360" ht="13.5" customHeight="1" spans="1:18">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -7999,7 +8622,7 @@
       <c r="Q360" s="4"/>
       <c r="R360" s="4"/>
     </row>
-    <row r="361" spans="1:18" ht="13.5" customHeight="1">
+    <row r="361" ht="13.5" customHeight="1" spans="1:18">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -8019,7 +8642,7 @@
       <c r="Q361" s="4"/>
       <c r="R361" s="4"/>
     </row>
-    <row r="362" spans="1:18" ht="13.5" customHeight="1">
+    <row r="362" ht="13.5" customHeight="1" spans="1:18">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -8039,7 +8662,7 @@
       <c r="Q362" s="4"/>
       <c r="R362" s="4"/>
     </row>
-    <row r="363" spans="1:18" ht="13.5" customHeight="1">
+    <row r="363" ht="13.5" customHeight="1" spans="1:18">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -8059,7 +8682,7 @@
       <c r="Q363" s="4"/>
       <c r="R363" s="4"/>
     </row>
-    <row r="364" spans="1:18" ht="13.5" customHeight="1">
+    <row r="364" ht="13.5" customHeight="1" spans="1:18">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -8079,7 +8702,7 @@
       <c r="Q364" s="4"/>
       <c r="R364" s="4"/>
     </row>
-    <row r="365" spans="1:18" ht="13.5" customHeight="1">
+    <row r="365" ht="13.5" customHeight="1" spans="1:18">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -8099,7 +8722,7 @@
       <c r="Q365" s="4"/>
       <c r="R365" s="4"/>
     </row>
-    <row r="366" spans="1:18" ht="13.5" customHeight="1">
+    <row r="366" ht="13.5" customHeight="1" spans="1:18">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -8119,7 +8742,7 @@
       <c r="Q366" s="4"/>
       <c r="R366" s="4"/>
     </row>
-    <row r="367" spans="1:18" ht="13.5" customHeight="1">
+    <row r="367" ht="13.5" customHeight="1" spans="1:18">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -8139,7 +8762,7 @@
       <c r="Q367" s="4"/>
       <c r="R367" s="4"/>
     </row>
-    <row r="368" spans="1:18" ht="13.5" customHeight="1">
+    <row r="368" ht="13.5" customHeight="1" spans="1:18">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -8159,7 +8782,7 @@
       <c r="Q368" s="4"/>
       <c r="R368" s="4"/>
     </row>
-    <row r="369" spans="1:18" ht="13.5" customHeight="1">
+    <row r="369" ht="13.5" customHeight="1" spans="1:18">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -8179,7 +8802,7 @@
       <c r="Q369" s="4"/>
       <c r="R369" s="4"/>
     </row>
-    <row r="370" spans="1:18" ht="13.5" customHeight="1">
+    <row r="370" ht="13.5" customHeight="1" spans="1:18">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -8199,7 +8822,7 @@
       <c r="Q370" s="4"/>
       <c r="R370" s="4"/>
     </row>
-    <row r="371" spans="1:18" ht="13.5" customHeight="1">
+    <row r="371" ht="13.5" customHeight="1" spans="1:18">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -8219,7 +8842,7 @@
       <c r="Q371" s="4"/>
       <c r="R371" s="4"/>
     </row>
-    <row r="372" spans="1:18" ht="13.5" customHeight="1">
+    <row r="372" ht="13.5" customHeight="1" spans="1:18">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -8239,7 +8862,7 @@
       <c r="Q372" s="4"/>
       <c r="R372" s="4"/>
     </row>
-    <row r="373" spans="1:18" ht="13.5" customHeight="1">
+    <row r="373" ht="13.5" customHeight="1" spans="1:18">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -8259,7 +8882,7 @@
       <c r="Q373" s="4"/>
       <c r="R373" s="4"/>
     </row>
-    <row r="374" spans="1:18" ht="13.5" customHeight="1">
+    <row r="374" ht="13.5" customHeight="1" spans="1:18">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -8279,7 +8902,7 @@
       <c r="Q374" s="4"/>
       <c r="R374" s="4"/>
     </row>
-    <row r="375" spans="1:18" ht="13.5" customHeight="1">
+    <row r="375" ht="13.5" customHeight="1" spans="1:18">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -8299,7 +8922,7 @@
       <c r="Q375" s="4"/>
       <c r="R375" s="4"/>
     </row>
-    <row r="376" spans="1:18" ht="13.5" customHeight="1">
+    <row r="376" ht="13.5" customHeight="1" spans="1:18">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -8319,7 +8942,7 @@
       <c r="Q376" s="4"/>
       <c r="R376" s="4"/>
     </row>
-    <row r="377" spans="1:18" ht="13.5" customHeight="1">
+    <row r="377" ht="13.5" customHeight="1" spans="1:18">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -8339,7 +8962,7 @@
       <c r="Q377" s="4"/>
       <c r="R377" s="4"/>
     </row>
-    <row r="378" spans="1:18" ht="13.5" customHeight="1">
+    <row r="378" ht="13.5" customHeight="1" spans="1:18">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -8359,7 +8982,7 @@
       <c r="Q378" s="4"/>
       <c r="R378" s="4"/>
     </row>
-    <row r="379" spans="1:18" ht="13.5" customHeight="1">
+    <row r="379" ht="13.5" customHeight="1" spans="1:18">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -8379,7 +9002,7 @@
       <c r="Q379" s="4"/>
       <c r="R379" s="4"/>
     </row>
-    <row r="380" spans="1:18" ht="13.5" customHeight="1">
+    <row r="380" ht="13.5" customHeight="1" spans="1:18">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -8399,7 +9022,7 @@
       <c r="Q380" s="4"/>
       <c r="R380" s="4"/>
     </row>
-    <row r="381" spans="1:18" ht="13.5" customHeight="1">
+    <row r="381" ht="13.5" customHeight="1" spans="1:18">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -8419,7 +9042,7 @@
       <c r="Q381" s="4"/>
       <c r="R381" s="4"/>
     </row>
-    <row r="382" spans="1:18" ht="13.5" customHeight="1">
+    <row r="382" ht="13.5" customHeight="1" spans="1:18">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -8439,7 +9062,7 @@
       <c r="Q382" s="4"/>
       <c r="R382" s="4"/>
     </row>
-    <row r="383" spans="1:18" ht="13.5" customHeight="1">
+    <row r="383" ht="13.5" customHeight="1" spans="1:18">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -8459,7 +9082,7 @@
       <c r="Q383" s="4"/>
       <c r="R383" s="4"/>
     </row>
-    <row r="384" spans="1:18" ht="13.5" customHeight="1">
+    <row r="384" ht="13.5" customHeight="1" spans="1:18">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -8479,7 +9102,7 @@
       <c r="Q384" s="4"/>
       <c r="R384" s="4"/>
     </row>
-    <row r="385" spans="1:18" ht="13.5" customHeight="1">
+    <row r="385" ht="13.5" customHeight="1" spans="1:18">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -8499,7 +9122,7 @@
       <c r="Q385" s="4"/>
       <c r="R385" s="4"/>
     </row>
-    <row r="386" spans="1:18" ht="13.5" customHeight="1">
+    <row r="386" ht="13.5" customHeight="1" spans="1:18">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -8519,7 +9142,7 @@
       <c r="Q386" s="4"/>
       <c r="R386" s="4"/>
     </row>
-    <row r="387" spans="1:18" ht="13.5" customHeight="1">
+    <row r="387" ht="13.5" customHeight="1" spans="1:18">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -8539,7 +9162,7 @@
       <c r="Q387" s="4"/>
       <c r="R387" s="4"/>
     </row>
-    <row r="388" spans="1:18" ht="13.5" customHeight="1">
+    <row r="388" ht="13.5" customHeight="1" spans="1:18">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -8559,7 +9182,7 @@
       <c r="Q388" s="4"/>
       <c r="R388" s="4"/>
     </row>
-    <row r="389" spans="1:18" ht="13.5" customHeight="1">
+    <row r="389" ht="13.5" customHeight="1" spans="1:18">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -8579,7 +9202,7 @@
       <c r="Q389" s="4"/>
       <c r="R389" s="4"/>
     </row>
-    <row r="390" spans="1:18" ht="13.5" customHeight="1">
+    <row r="390" ht="13.5" customHeight="1" spans="1:18">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -8599,7 +9222,7 @@
       <c r="Q390" s="4"/>
       <c r="R390" s="4"/>
     </row>
-    <row r="391" spans="1:18" ht="13.5" customHeight="1">
+    <row r="391" ht="13.5" customHeight="1" spans="1:18">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -8619,7 +9242,7 @@
       <c r="Q391" s="4"/>
       <c r="R391" s="4"/>
     </row>
-    <row r="392" spans="1:18" ht="13.5" customHeight="1">
+    <row r="392" ht="13.5" customHeight="1" spans="1:18">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -8639,7 +9262,7 @@
       <c r="Q392" s="4"/>
       <c r="R392" s="4"/>
     </row>
-    <row r="393" spans="1:18" ht="13.5" customHeight="1">
+    <row r="393" ht="13.5" customHeight="1" spans="1:18">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -8659,7 +9282,7 @@
       <c r="Q393" s="4"/>
       <c r="R393" s="4"/>
     </row>
-    <row r="394" spans="1:18" ht="13.5" customHeight="1">
+    <row r="394" ht="13.5" customHeight="1" spans="1:18">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -8679,7 +9302,7 @@
       <c r="Q394" s="4"/>
       <c r="R394" s="4"/>
     </row>
-    <row r="395" spans="1:18" ht="13.5" customHeight="1">
+    <row r="395" ht="13.5" customHeight="1" spans="1:18">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -8699,7 +9322,7 @@
       <c r="Q395" s="4"/>
       <c r="R395" s="4"/>
     </row>
-    <row r="396" spans="1:18" ht="13.5" customHeight="1">
+    <row r="396" ht="13.5" customHeight="1" spans="1:18">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -8719,7 +9342,7 @@
       <c r="Q396" s="4"/>
       <c r="R396" s="4"/>
     </row>
-    <row r="397" spans="1:18" ht="13.5" customHeight="1">
+    <row r="397" ht="13.5" customHeight="1" spans="1:18">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -8739,7 +9362,7 @@
       <c r="Q397" s="4"/>
       <c r="R397" s="4"/>
     </row>
-    <row r="398" spans="1:18" ht="13.5" customHeight="1">
+    <row r="398" ht="13.5" customHeight="1" spans="1:18">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -8759,7 +9382,7 @@
       <c r="Q398" s="4"/>
       <c r="R398" s="4"/>
     </row>
-    <row r="399" spans="1:18" ht="13.5" customHeight="1">
+    <row r="399" ht="13.5" customHeight="1" spans="1:18">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -8779,7 +9402,7 @@
       <c r="Q399" s="4"/>
       <c r="R399" s="4"/>
     </row>
-    <row r="400" spans="1:18" ht="13.5" customHeight="1">
+    <row r="400" ht="13.5" customHeight="1" spans="1:18">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -8799,7 +9422,7 @@
       <c r="Q400" s="4"/>
       <c r="R400" s="4"/>
     </row>
-    <row r="401" spans="1:18" ht="13.5" customHeight="1">
+    <row r="401" ht="13.5" customHeight="1" spans="1:18">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -8819,7 +9442,7 @@
       <c r="Q401" s="4"/>
       <c r="R401" s="4"/>
     </row>
-    <row r="402" spans="1:18" ht="13.5" customHeight="1">
+    <row r="402" ht="13.5" customHeight="1" spans="1:18">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -8839,7 +9462,7 @@
       <c r="Q402" s="4"/>
       <c r="R402" s="4"/>
     </row>
-    <row r="403" spans="1:18" ht="13.5" customHeight="1">
+    <row r="403" ht="13.5" customHeight="1" spans="1:18">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -8859,7 +9482,7 @@
       <c r="Q403" s="4"/>
       <c r="R403" s="4"/>
     </row>
-    <row r="404" spans="1:18" ht="13.5" customHeight="1">
+    <row r="404" ht="13.5" customHeight="1" spans="1:18">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -8879,7 +9502,7 @@
       <c r="Q404" s="4"/>
       <c r="R404" s="4"/>
     </row>
-    <row r="405" spans="1:18" ht="13.5" customHeight="1">
+    <row r="405" ht="13.5" customHeight="1" spans="1:18">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -8899,7 +9522,7 @@
       <c r="Q405" s="4"/>
       <c r="R405" s="4"/>
     </row>
-    <row r="406" spans="1:18" ht="13.5" customHeight="1">
+    <row r="406" ht="13.5" customHeight="1" spans="1:18">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -8919,7 +9542,7 @@
       <c r="Q406" s="4"/>
       <c r="R406" s="4"/>
     </row>
-    <row r="407" spans="1:18" ht="13.5" customHeight="1">
+    <row r="407" ht="13.5" customHeight="1" spans="1:18">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -8939,7 +9562,7 @@
       <c r="Q407" s="4"/>
       <c r="R407" s="4"/>
     </row>
-    <row r="408" spans="1:18" ht="13.5" customHeight="1">
+    <row r="408" ht="13.5" customHeight="1" spans="1:18">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -8959,7 +9582,7 @@
       <c r="Q408" s="4"/>
       <c r="R408" s="4"/>
     </row>
-    <row r="409" spans="1:18" ht="13.5" customHeight="1">
+    <row r="409" ht="13.5" customHeight="1" spans="1:18">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -8979,7 +9602,7 @@
       <c r="Q409" s="4"/>
       <c r="R409" s="4"/>
     </row>
-    <row r="410" spans="1:18" ht="13.5" customHeight="1">
+    <row r="410" ht="13.5" customHeight="1" spans="1:18">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -8999,7 +9622,7 @@
       <c r="Q410" s="4"/>
       <c r="R410" s="4"/>
     </row>
-    <row r="411" spans="1:18" ht="13.5" customHeight="1">
+    <row r="411" ht="13.5" customHeight="1" spans="1:18">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -9019,7 +9642,7 @@
       <c r="Q411" s="4"/>
       <c r="R411" s="4"/>
     </row>
-    <row r="412" spans="1:18" ht="13.5" customHeight="1">
+    <row r="412" ht="13.5" customHeight="1" spans="1:18">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -9039,7 +9662,7 @@
       <c r="Q412" s="4"/>
       <c r="R412" s="4"/>
     </row>
-    <row r="413" spans="1:18" ht="13.5" customHeight="1">
+    <row r="413" ht="13.5" customHeight="1" spans="1:18">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -9059,7 +9682,7 @@
       <c r="Q413" s="4"/>
       <c r="R413" s="4"/>
     </row>
-    <row r="414" spans="1:18" ht="13.5" customHeight="1">
+    <row r="414" ht="13.5" customHeight="1" spans="1:18">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -9079,7 +9702,7 @@
       <c r="Q414" s="4"/>
       <c r="R414" s="4"/>
     </row>
-    <row r="415" spans="1:18" ht="13.5" customHeight="1">
+    <row r="415" ht="13.5" customHeight="1" spans="1:18">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -9099,7 +9722,7 @@
       <c r="Q415" s="4"/>
       <c r="R415" s="4"/>
     </row>
-    <row r="416" spans="1:18" ht="13.5" customHeight="1">
+    <row r="416" ht="13.5" customHeight="1" spans="1:18">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -9119,7 +9742,7 @@
       <c r="Q416" s="4"/>
       <c r="R416" s="4"/>
     </row>
-    <row r="417" spans="1:18" ht="13.5" customHeight="1">
+    <row r="417" ht="13.5" customHeight="1" spans="1:18">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -9139,7 +9762,7 @@
       <c r="Q417" s="4"/>
       <c r="R417" s="4"/>
     </row>
-    <row r="418" spans="1:18" ht="13.5" customHeight="1">
+    <row r="418" ht="13.5" customHeight="1" spans="1:18">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -9159,7 +9782,7 @@
       <c r="Q418" s="4"/>
       <c r="R418" s="4"/>
     </row>
-    <row r="419" spans="1:18" ht="13.5" customHeight="1">
+    <row r="419" ht="13.5" customHeight="1" spans="1:18">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -9179,7 +9802,7 @@
       <c r="Q419" s="4"/>
       <c r="R419" s="4"/>
     </row>
-    <row r="420" spans="1:18" ht="13.5" customHeight="1">
+    <row r="420" ht="13.5" customHeight="1" spans="1:18">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -9199,7 +9822,7 @@
       <c r="Q420" s="4"/>
       <c r="R420" s="4"/>
     </row>
-    <row r="421" spans="1:18" ht="13.5" customHeight="1">
+    <row r="421" ht="13.5" customHeight="1" spans="1:18">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -9219,7 +9842,7 @@
       <c r="Q421" s="4"/>
       <c r="R421" s="4"/>
     </row>
-    <row r="422" spans="1:18" ht="13.5" customHeight="1">
+    <row r="422" ht="13.5" customHeight="1" spans="1:18">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -9239,7 +9862,7 @@
       <c r="Q422" s="4"/>
       <c r="R422" s="4"/>
     </row>
-    <row r="423" spans="1:18" ht="13.5" customHeight="1">
+    <row r="423" ht="13.5" customHeight="1" spans="1:18">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -9259,7 +9882,7 @@
       <c r="Q423" s="4"/>
       <c r="R423" s="4"/>
     </row>
-    <row r="424" spans="1:18" ht="13.5" customHeight="1">
+    <row r="424" ht="13.5" customHeight="1" spans="1:18">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -9279,7 +9902,7 @@
       <c r="Q424" s="4"/>
       <c r="R424" s="4"/>
     </row>
-    <row r="425" spans="1:18" ht="13.5" customHeight="1">
+    <row r="425" ht="13.5" customHeight="1" spans="1:18">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -9299,7 +9922,7 @@
       <c r="Q425" s="4"/>
       <c r="R425" s="4"/>
     </row>
-    <row r="426" spans="1:18" ht="13.5" customHeight="1">
+    <row r="426" ht="13.5" customHeight="1" spans="1:18">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -9319,7 +9942,7 @@
       <c r="Q426" s="4"/>
       <c r="R426" s="4"/>
     </row>
-    <row r="427" spans="1:18" ht="13.5" customHeight="1">
+    <row r="427" ht="13.5" customHeight="1" spans="1:18">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -9339,7 +9962,7 @@
       <c r="Q427" s="4"/>
       <c r="R427" s="4"/>
     </row>
-    <row r="428" spans="1:18" ht="13.5" customHeight="1">
+    <row r="428" ht="13.5" customHeight="1" spans="1:18">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -9359,7 +9982,7 @@
       <c r="Q428" s="4"/>
       <c r="R428" s="4"/>
     </row>
-    <row r="429" spans="1:18" ht="13.5" customHeight="1">
+    <row r="429" ht="13.5" customHeight="1" spans="1:18">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -9379,7 +10002,7 @@
       <c r="Q429" s="4"/>
       <c r="R429" s="4"/>
     </row>
-    <row r="430" spans="1:18" ht="13.5" customHeight="1">
+    <row r="430" ht="13.5" customHeight="1" spans="1:18">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -9399,7 +10022,7 @@
       <c r="Q430" s="4"/>
       <c r="R430" s="4"/>
     </row>
-    <row r="431" spans="1:18" ht="13.5" customHeight="1">
+    <row r="431" ht="13.5" customHeight="1" spans="1:18">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -9419,7 +10042,7 @@
       <c r="Q431" s="4"/>
       <c r="R431" s="4"/>
     </row>
-    <row r="432" spans="1:18" ht="13.5" customHeight="1">
+    <row r="432" ht="13.5" customHeight="1" spans="1:18">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -9439,7 +10062,7 @@
       <c r="Q432" s="4"/>
       <c r="R432" s="4"/>
     </row>
-    <row r="433" spans="1:18" ht="13.5" customHeight="1">
+    <row r="433" ht="13.5" customHeight="1" spans="1:18">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -9459,7 +10082,7 @@
       <c r="Q433" s="4"/>
       <c r="R433" s="4"/>
     </row>
-    <row r="434" spans="1:18" ht="13.5" customHeight="1">
+    <row r="434" ht="13.5" customHeight="1" spans="1:18">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -9479,7 +10102,7 @@
       <c r="Q434" s="4"/>
       <c r="R434" s="4"/>
     </row>
-    <row r="435" spans="1:18" ht="13.5" customHeight="1">
+    <row r="435" ht="13.5" customHeight="1" spans="1:18">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -9499,7 +10122,7 @@
       <c r="Q435" s="4"/>
       <c r="R435" s="4"/>
     </row>
-    <row r="436" spans="1:18" ht="13.5" customHeight="1">
+    <row r="436" ht="13.5" customHeight="1" spans="1:18">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -9519,7 +10142,7 @@
       <c r="Q436" s="4"/>
       <c r="R436" s="4"/>
     </row>
-    <row r="437" spans="1:18" ht="13.5" customHeight="1">
+    <row r="437" ht="13.5" customHeight="1" spans="1:18">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -9539,7 +10162,7 @@
       <c r="Q437" s="4"/>
       <c r="R437" s="4"/>
     </row>
-    <row r="438" spans="1:18" ht="13.5" customHeight="1">
+    <row r="438" ht="13.5" customHeight="1" spans="1:18">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -9559,7 +10182,7 @@
       <c r="Q438" s="4"/>
       <c r="R438" s="4"/>
     </row>
-    <row r="439" spans="1:18" ht="13.5" customHeight="1">
+    <row r="439" ht="13.5" customHeight="1" spans="1:18">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -9579,7 +10202,7 @@
       <c r="Q439" s="4"/>
       <c r="R439" s="4"/>
     </row>
-    <row r="440" spans="1:18" ht="13.5" customHeight="1">
+    <row r="440" ht="13.5" customHeight="1" spans="1:18">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -9599,7 +10222,7 @@
       <c r="Q440" s="4"/>
       <c r="R440" s="4"/>
     </row>
-    <row r="441" spans="1:18" ht="13.5" customHeight="1">
+    <row r="441" ht="13.5" customHeight="1" spans="1:18">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -9619,7 +10242,7 @@
       <c r="Q441" s="4"/>
       <c r="R441" s="4"/>
     </row>
-    <row r="442" spans="1:18" ht="13.5" customHeight="1">
+    <row r="442" ht="13.5" customHeight="1" spans="1:18">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -9639,7 +10262,7 @@
       <c r="Q442" s="4"/>
       <c r="R442" s="4"/>
     </row>
-    <row r="443" spans="1:18" ht="13.5" customHeight="1">
+    <row r="443" ht="13.5" customHeight="1" spans="1:18">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -9659,7 +10282,7 @@
       <c r="Q443" s="4"/>
       <c r="R443" s="4"/>
     </row>
-    <row r="444" spans="1:18" ht="13.5" customHeight="1">
+    <row r="444" ht="13.5" customHeight="1" spans="1:18">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -9679,7 +10302,7 @@
       <c r="Q444" s="4"/>
       <c r="R444" s="4"/>
     </row>
-    <row r="445" spans="1:18" ht="13.5" customHeight="1">
+    <row r="445" ht="13.5" customHeight="1" spans="1:18">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -9699,7 +10322,7 @@
       <c r="Q445" s="4"/>
       <c r="R445" s="4"/>
     </row>
-    <row r="446" spans="1:18" ht="13.5" customHeight="1">
+    <row r="446" ht="13.5" customHeight="1" spans="1:18">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -9719,7 +10342,7 @@
       <c r="Q446" s="4"/>
       <c r="R446" s="4"/>
     </row>
-    <row r="447" spans="1:18" ht="13.5" customHeight="1">
+    <row r="447" ht="13.5" customHeight="1" spans="1:18">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -9739,7 +10362,7 @@
       <c r="Q447" s="4"/>
       <c r="R447" s="4"/>
     </row>
-    <row r="448" spans="1:18" ht="13.5" customHeight="1">
+    <row r="448" ht="13.5" customHeight="1" spans="1:18">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -9759,7 +10382,7 @@
       <c r="Q448" s="4"/>
       <c r="R448" s="4"/>
     </row>
-    <row r="449" spans="1:18" ht="13.5" customHeight="1">
+    <row r="449" ht="13.5" customHeight="1" spans="1:18">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -9779,7 +10402,7 @@
       <c r="Q449" s="4"/>
       <c r="R449" s="4"/>
     </row>
-    <row r="450" spans="1:18" ht="13.5" customHeight="1">
+    <row r="450" ht="13.5" customHeight="1" spans="1:18">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -9799,7 +10422,7 @@
       <c r="Q450" s="4"/>
       <c r="R450" s="4"/>
     </row>
-    <row r="451" spans="1:18" ht="13.5" customHeight="1">
+    <row r="451" ht="13.5" customHeight="1" spans="1:18">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -9819,7 +10442,7 @@
       <c r="Q451" s="4"/>
       <c r="R451" s="4"/>
     </row>
-    <row r="452" spans="1:18" ht="13.5" customHeight="1">
+    <row r="452" ht="13.5" customHeight="1" spans="1:18">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -9839,7 +10462,7 @@
       <c r="Q452" s="4"/>
       <c r="R452" s="4"/>
     </row>
-    <row r="453" spans="1:18" ht="13.5" customHeight="1">
+    <row r="453" ht="13.5" customHeight="1" spans="1:18">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -9859,7 +10482,7 @@
       <c r="Q453" s="4"/>
       <c r="R453" s="4"/>
     </row>
-    <row r="454" spans="1:18" ht="13.5" customHeight="1">
+    <row r="454" ht="13.5" customHeight="1" spans="1:18">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -9879,7 +10502,7 @@
       <c r="Q454" s="4"/>
       <c r="R454" s="4"/>
     </row>
-    <row r="455" spans="1:18" ht="13.5" customHeight="1">
+    <row r="455" ht="13.5" customHeight="1" spans="1:18">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -9899,7 +10522,7 @@
       <c r="Q455" s="4"/>
       <c r="R455" s="4"/>
     </row>
-    <row r="456" spans="1:18" ht="13.5" customHeight="1">
+    <row r="456" ht="13.5" customHeight="1" spans="1:18">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -9919,7 +10542,7 @@
       <c r="Q456" s="4"/>
       <c r="R456" s="4"/>
     </row>
-    <row r="457" spans="1:18" ht="13.5" customHeight="1">
+    <row r="457" ht="13.5" customHeight="1" spans="1:18">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -9939,7 +10562,7 @@
       <c r="Q457" s="4"/>
       <c r="R457" s="4"/>
     </row>
-    <row r="458" spans="1:18" ht="13.5" customHeight="1">
+    <row r="458" ht="13.5" customHeight="1" spans="1:18">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -9959,7 +10582,7 @@
       <c r="Q458" s="4"/>
       <c r="R458" s="4"/>
     </row>
-    <row r="459" spans="1:18" ht="13.5" customHeight="1">
+    <row r="459" ht="13.5" customHeight="1" spans="1:18">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -9979,7 +10602,7 @@
       <c r="Q459" s="4"/>
       <c r="R459" s="4"/>
     </row>
-    <row r="460" spans="1:18" ht="13.5" customHeight="1">
+    <row r="460" ht="13.5" customHeight="1" spans="1:18">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -9999,7 +10622,7 @@
       <c r="Q460" s="4"/>
       <c r="R460" s="4"/>
     </row>
-    <row r="461" spans="1:18" ht="13.5" customHeight="1">
+    <row r="461" ht="13.5" customHeight="1" spans="1:18">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -10019,7 +10642,7 @@
       <c r="Q461" s="4"/>
       <c r="R461" s="4"/>
     </row>
-    <row r="462" spans="1:18" ht="13.5" customHeight="1">
+    <row r="462" ht="13.5" customHeight="1" spans="1:18">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -10039,7 +10662,7 @@
       <c r="Q462" s="4"/>
       <c r="R462" s="4"/>
     </row>
-    <row r="463" spans="1:18" ht="13.5" customHeight="1">
+    <row r="463" ht="13.5" customHeight="1" spans="1:18">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -10059,7 +10682,7 @@
       <c r="Q463" s="4"/>
       <c r="R463" s="4"/>
     </row>
-    <row r="464" spans="1:18" ht="13.5" customHeight="1">
+    <row r="464" ht="13.5" customHeight="1" spans="1:18">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -10079,7 +10702,7 @@
       <c r="Q464" s="4"/>
       <c r="R464" s="4"/>
     </row>
-    <row r="465" spans="1:18" ht="13.5" customHeight="1">
+    <row r="465" ht="13.5" customHeight="1" spans="1:18">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -10099,7 +10722,7 @@
       <c r="Q465" s="4"/>
       <c r="R465" s="4"/>
     </row>
-    <row r="466" spans="1:18" ht="13.5" customHeight="1">
+    <row r="466" ht="13.5" customHeight="1" spans="1:18">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -10119,7 +10742,7 @@
       <c r="Q466" s="4"/>
       <c r="R466" s="4"/>
     </row>
-    <row r="467" spans="1:18" ht="13.5" customHeight="1">
+    <row r="467" ht="13.5" customHeight="1" spans="1:18">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -10139,7 +10762,7 @@
       <c r="Q467" s="4"/>
       <c r="R467" s="4"/>
     </row>
-    <row r="468" spans="1:18" ht="13.5" customHeight="1">
+    <row r="468" ht="13.5" customHeight="1" spans="1:18">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -10159,7 +10782,7 @@
       <c r="Q468" s="4"/>
       <c r="R468" s="4"/>
     </row>
-    <row r="469" spans="1:18" ht="13.5" customHeight="1">
+    <row r="469" ht="13.5" customHeight="1" spans="1:18">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -10179,7 +10802,7 @@
       <c r="Q469" s="4"/>
       <c r="R469" s="4"/>
     </row>
-    <row r="470" spans="1:18" ht="13.5" customHeight="1">
+    <row r="470" ht="13.5" customHeight="1" spans="1:18">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -10199,7 +10822,7 @@
       <c r="Q470" s="4"/>
       <c r="R470" s="4"/>
     </row>
-    <row r="471" spans="1:18" ht="13.5" customHeight="1">
+    <row r="471" ht="13.5" customHeight="1" spans="1:18">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -10219,7 +10842,7 @@
       <c r="Q471" s="4"/>
       <c r="R471" s="4"/>
     </row>
-    <row r="472" spans="1:18" ht="13.5" customHeight="1">
+    <row r="472" ht="13.5" customHeight="1" spans="1:18">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -10239,7 +10862,7 @@
       <c r="Q472" s="4"/>
       <c r="R472" s="4"/>
     </row>
-    <row r="473" spans="1:18" ht="13.5" customHeight="1">
+    <row r="473" ht="13.5" customHeight="1" spans="1:18">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -10259,7 +10882,7 @@
       <c r="Q473" s="4"/>
       <c r="R473" s="4"/>
     </row>
-    <row r="474" spans="1:18" ht="13.5" customHeight="1">
+    <row r="474" ht="13.5" customHeight="1" spans="1:18">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -10279,7 +10902,7 @@
       <c r="Q474" s="4"/>
       <c r="R474" s="4"/>
     </row>
-    <row r="475" spans="1:18" ht="13.5" customHeight="1">
+    <row r="475" ht="13.5" customHeight="1" spans="1:18">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -10299,7 +10922,7 @@
       <c r="Q475" s="4"/>
       <c r="R475" s="4"/>
     </row>
-    <row r="476" spans="1:18" ht="13.5" customHeight="1">
+    <row r="476" ht="13.5" customHeight="1" spans="1:18">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -10319,7 +10942,7 @@
       <c r="Q476" s="4"/>
       <c r="R476" s="4"/>
     </row>
-    <row r="477" spans="1:18" ht="13.5" customHeight="1">
+    <row r="477" ht="13.5" customHeight="1" spans="1:18">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -10339,7 +10962,7 @@
       <c r="Q477" s="4"/>
       <c r="R477" s="4"/>
     </row>
-    <row r="478" spans="1:18" ht="13.5" customHeight="1">
+    <row r="478" ht="13.5" customHeight="1" spans="1:18">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -10359,7 +10982,7 @@
       <c r="Q478" s="4"/>
       <c r="R478" s="4"/>
     </row>
-    <row r="479" spans="1:18" ht="13.5" customHeight="1">
+    <row r="479" ht="13.5" customHeight="1" spans="1:18">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -10379,7 +11002,7 @@
       <c r="Q479" s="4"/>
       <c r="R479" s="4"/>
     </row>
-    <row r="480" spans="1:18" ht="13.5" customHeight="1">
+    <row r="480" ht="13.5" customHeight="1" spans="1:18">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -10399,7 +11022,7 @@
       <c r="Q480" s="4"/>
       <c r="R480" s="4"/>
     </row>
-    <row r="481" spans="1:18" ht="13.5" customHeight="1">
+    <row r="481" ht="13.5" customHeight="1" spans="1:18">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -10419,7 +11042,7 @@
       <c r="Q481" s="4"/>
       <c r="R481" s="4"/>
     </row>
-    <row r="482" spans="1:18" ht="13.5" customHeight="1">
+    <row r="482" ht="13.5" customHeight="1" spans="1:18">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -10439,7 +11062,7 @@
       <c r="Q482" s="4"/>
       <c r="R482" s="4"/>
     </row>
-    <row r="483" spans="1:18" ht="13.5" customHeight="1">
+    <row r="483" ht="13.5" customHeight="1" spans="1:18">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -10459,7 +11082,7 @@
       <c r="Q483" s="4"/>
       <c r="R483" s="4"/>
     </row>
-    <row r="484" spans="1:18" ht="13.5" customHeight="1">
+    <row r="484" ht="13.5" customHeight="1" spans="1:18">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -10479,7 +11102,7 @@
       <c r="Q484" s="4"/>
       <c r="R484" s="4"/>
     </row>
-    <row r="485" spans="1:18" ht="13.5" customHeight="1">
+    <row r="485" ht="13.5" customHeight="1" spans="1:18">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -10499,7 +11122,7 @@
       <c r="Q485" s="4"/>
       <c r="R485" s="4"/>
     </row>
-    <row r="486" spans="1:18" ht="13.5" customHeight="1">
+    <row r="486" ht="13.5" customHeight="1" spans="1:18">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -10519,7 +11142,7 @@
       <c r="Q486" s="4"/>
       <c r="R486" s="4"/>
     </row>
-    <row r="487" spans="1:18" ht="13.5" customHeight="1">
+    <row r="487" ht="13.5" customHeight="1" spans="1:18">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -10539,7 +11162,7 @@
       <c r="Q487" s="4"/>
       <c r="R487" s="4"/>
     </row>
-    <row r="488" spans="1:18" ht="13.5" customHeight="1">
+    <row r="488" ht="13.5" customHeight="1" spans="1:18">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -10559,7 +11182,7 @@
       <c r="Q488" s="4"/>
       <c r="R488" s="4"/>
     </row>
-    <row r="489" spans="1:18" ht="13.5" customHeight="1">
+    <row r="489" ht="13.5" customHeight="1" spans="1:18">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -10579,7 +11202,7 @@
       <c r="Q489" s="4"/>
       <c r="R489" s="4"/>
     </row>
-    <row r="490" spans="1:18" ht="13.5" customHeight="1">
+    <row r="490" ht="13.5" customHeight="1" spans="1:18">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -10599,7 +11222,7 @@
       <c r="Q490" s="4"/>
       <c r="R490" s="4"/>
     </row>
-    <row r="491" spans="1:18" ht="13.5" customHeight="1">
+    <row r="491" ht="13.5" customHeight="1" spans="1:18">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -10619,7 +11242,7 @@
       <c r="Q491" s="4"/>
       <c r="R491" s="4"/>
     </row>
-    <row r="492" spans="1:18" ht="13.5" customHeight="1">
+    <row r="492" ht="13.5" customHeight="1" spans="1:18">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -10639,7 +11262,7 @@
       <c r="Q492" s="4"/>
       <c r="R492" s="4"/>
     </row>
-    <row r="493" spans="1:18" ht="13.5" customHeight="1">
+    <row r="493" ht="13.5" customHeight="1" spans="1:18">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -10659,7 +11282,7 @@
       <c r="Q493" s="4"/>
       <c r="R493" s="4"/>
     </row>
-    <row r="494" spans="1:18" ht="13.5" customHeight="1">
+    <row r="494" ht="13.5" customHeight="1" spans="1:18">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -10679,7 +11302,7 @@
       <c r="Q494" s="4"/>
       <c r="R494" s="4"/>
     </row>
-    <row r="495" spans="1:18" ht="13.5" customHeight="1">
+    <row r="495" ht="13.5" customHeight="1" spans="1:18">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -10699,7 +11322,7 @@
       <c r="Q495" s="4"/>
       <c r="R495" s="4"/>
     </row>
-    <row r="496" spans="1:18" ht="13.5" customHeight="1">
+    <row r="496" ht="13.5" customHeight="1" spans="1:18">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -10719,7 +11342,7 @@
       <c r="Q496" s="4"/>
       <c r="R496" s="4"/>
     </row>
-    <row r="497" spans="1:18" ht="13.5" customHeight="1">
+    <row r="497" ht="13.5" customHeight="1" spans="1:18">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -10739,7 +11362,7 @@
       <c r="Q497" s="4"/>
       <c r="R497" s="4"/>
     </row>
-    <row r="498" spans="1:18" ht="13.5" customHeight="1">
+    <row r="498" ht="13.5" customHeight="1" spans="1:18">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -10759,7 +11382,7 @@
       <c r="Q498" s="4"/>
       <c r="R498" s="4"/>
     </row>
-    <row r="499" spans="1:18" ht="13.5" customHeight="1">
+    <row r="499" ht="13.5" customHeight="1" spans="1:18">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -10779,7 +11402,7 @@
       <c r="Q499" s="4"/>
       <c r="R499" s="4"/>
     </row>
-    <row r="500" spans="1:18" ht="13.5" customHeight="1">
+    <row r="500" ht="13.5" customHeight="1" spans="1:18">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -10799,7 +11422,7 @@
       <c r="Q500" s="4"/>
       <c r="R500" s="4"/>
     </row>
-    <row r="501" spans="1:18" ht="13.5" customHeight="1">
+    <row r="501" ht="13.5" customHeight="1" spans="1:18">
       <c r="A501" s="4"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -10819,7 +11442,7 @@
       <c r="Q501" s="4"/>
       <c r="R501" s="4"/>
     </row>
-    <row r="502" spans="1:18" ht="13.5" customHeight="1">
+    <row r="502" ht="13.5" customHeight="1" spans="1:18">
       <c r="A502" s="4"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -10839,7 +11462,7 @@
       <c r="Q502" s="4"/>
       <c r="R502" s="4"/>
     </row>
-    <row r="503" spans="1:18" ht="13.5" customHeight="1">
+    <row r="503" ht="13.5" customHeight="1" spans="1:18">
       <c r="A503" s="4"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -10859,7 +11482,7 @@
       <c r="Q503" s="4"/>
       <c r="R503" s="4"/>
     </row>
-    <row r="504" spans="1:18" ht="13.5" customHeight="1">
+    <row r="504" ht="13.5" customHeight="1" spans="1:18">
       <c r="A504" s="4"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -10879,7 +11502,7 @@
       <c r="Q504" s="4"/>
       <c r="R504" s="4"/>
     </row>
-    <row r="505" spans="1:18" ht="13.5" customHeight="1">
+    <row r="505" ht="13.5" customHeight="1" spans="1:18">
       <c r="A505" s="4"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -10899,7 +11522,7 @@
       <c r="Q505" s="4"/>
       <c r="R505" s="4"/>
     </row>
-    <row r="506" spans="1:18" ht="13.5" customHeight="1">
+    <row r="506" ht="13.5" customHeight="1" spans="1:18">
       <c r="A506" s="4"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -10919,7 +11542,7 @@
       <c r="Q506" s="4"/>
       <c r="R506" s="4"/>
     </row>
-    <row r="507" spans="1:18" ht="13.5" customHeight="1">
+    <row r="507" ht="13.5" customHeight="1" spans="1:18">
       <c r="A507" s="4"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -10939,7 +11562,7 @@
       <c r="Q507" s="4"/>
       <c r="R507" s="4"/>
     </row>
-    <row r="508" spans="1:18" ht="13.5" customHeight="1">
+    <row r="508" ht="13.5" customHeight="1" spans="1:18">
       <c r="A508" s="4"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -10959,7 +11582,7 @@
       <c r="Q508" s="4"/>
       <c r="R508" s="4"/>
     </row>
-    <row r="509" spans="1:18" ht="13.5" customHeight="1">
+    <row r="509" ht="13.5" customHeight="1" spans="1:18">
       <c r="A509" s="4"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -10979,7 +11602,7 @@
       <c r="Q509" s="4"/>
       <c r="R509" s="4"/>
     </row>
-    <row r="510" spans="1:18" ht="13.5" customHeight="1">
+    <row r="510" ht="13.5" customHeight="1" spans="1:18">
       <c r="A510" s="4"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -10999,7 +11622,7 @@
       <c r="Q510" s="4"/>
       <c r="R510" s="4"/>
     </row>
-    <row r="511" spans="1:18" ht="13.5" customHeight="1">
+    <row r="511" ht="13.5" customHeight="1" spans="1:18">
       <c r="A511" s="4"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -11019,7 +11642,7 @@
       <c r="Q511" s="4"/>
       <c r="R511" s="4"/>
     </row>
-    <row r="512" spans="1:18" ht="13.5" customHeight="1">
+    <row r="512" ht="13.5" customHeight="1" spans="1:18">
       <c r="A512" s="4"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -11039,7 +11662,7 @@
       <c r="Q512" s="4"/>
       <c r="R512" s="4"/>
     </row>
-    <row r="513" spans="1:18" ht="13.5" customHeight="1">
+    <row r="513" ht="13.5" customHeight="1" spans="1:18">
       <c r="A513" s="4"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -11059,7 +11682,7 @@
       <c r="Q513" s="4"/>
       <c r="R513" s="4"/>
     </row>
-    <row r="514" spans="1:18" ht="13.5" customHeight="1">
+    <row r="514" ht="13.5" customHeight="1" spans="1:18">
       <c r="A514" s="4"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -11079,7 +11702,7 @@
       <c r="Q514" s="4"/>
       <c r="R514" s="4"/>
     </row>
-    <row r="515" spans="1:18" ht="13.5" customHeight="1">
+    <row r="515" ht="13.5" customHeight="1" spans="1:18">
       <c r="A515" s="4"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -11099,7 +11722,7 @@
       <c r="Q515" s="4"/>
       <c r="R515" s="4"/>
     </row>
-    <row r="516" spans="1:18" ht="13.5" customHeight="1">
+    <row r="516" ht="13.5" customHeight="1" spans="1:18">
       <c r="A516" s="4"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -11119,7 +11742,7 @@
       <c r="Q516" s="4"/>
       <c r="R516" s="4"/>
     </row>
-    <row r="517" spans="1:18" ht="13.5" customHeight="1">
+    <row r="517" ht="13.5" customHeight="1" spans="1:18">
       <c r="A517" s="4"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -11139,7 +11762,7 @@
       <c r="Q517" s="4"/>
       <c r="R517" s="4"/>
     </row>
-    <row r="518" spans="1:18" ht="13.5" customHeight="1">
+    <row r="518" ht="13.5" customHeight="1" spans="1:18">
       <c r="A518" s="4"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -11159,7 +11782,7 @@
       <c r="Q518" s="4"/>
       <c r="R518" s="4"/>
     </row>
-    <row r="519" spans="1:18" ht="13.5" customHeight="1">
+    <row r="519" ht="13.5" customHeight="1" spans="1:18">
       <c r="A519" s="4"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -11179,7 +11802,7 @@
       <c r="Q519" s="4"/>
       <c r="R519" s="4"/>
     </row>
-    <row r="520" spans="1:18" ht="13.5" customHeight="1">
+    <row r="520" ht="13.5" customHeight="1" spans="1:18">
       <c r="A520" s="4"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -11199,7 +11822,7 @@
       <c r="Q520" s="4"/>
       <c r="R520" s="4"/>
     </row>
-    <row r="521" spans="1:18" ht="13.5" customHeight="1">
+    <row r="521" ht="13.5" customHeight="1" spans="1:18">
       <c r="A521" s="4"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -11219,7 +11842,7 @@
       <c r="Q521" s="4"/>
       <c r="R521" s="4"/>
     </row>
-    <row r="522" spans="1:18" ht="13.5" customHeight="1">
+    <row r="522" ht="13.5" customHeight="1" spans="1:18">
       <c r="A522" s="4"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -11239,7 +11862,7 @@
       <c r="Q522" s="4"/>
       <c r="R522" s="4"/>
     </row>
-    <row r="523" spans="1:18" ht="13.5" customHeight="1">
+    <row r="523" ht="13.5" customHeight="1" spans="1:18">
       <c r="A523" s="4"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -11259,7 +11882,7 @@
       <c r="Q523" s="4"/>
       <c r="R523" s="4"/>
     </row>
-    <row r="524" spans="1:18" ht="13.5" customHeight="1">
+    <row r="524" ht="13.5" customHeight="1" spans="1:18">
       <c r="A524" s="4"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -11279,7 +11902,7 @@
       <c r="Q524" s="4"/>
       <c r="R524" s="4"/>
     </row>
-    <row r="525" spans="1:18" ht="13.5" customHeight="1">
+    <row r="525" ht="13.5" customHeight="1" spans="1:18">
       <c r="A525" s="4"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -11299,7 +11922,7 @@
       <c r="Q525" s="4"/>
       <c r="R525" s="4"/>
     </row>
-    <row r="526" spans="1:18" ht="13.5" customHeight="1">
+    <row r="526" ht="13.5" customHeight="1" spans="1:18">
       <c r="A526" s="4"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -11319,7 +11942,7 @@
       <c r="Q526" s="4"/>
       <c r="R526" s="4"/>
     </row>
-    <row r="527" spans="1:18" ht="13.5" customHeight="1">
+    <row r="527" ht="13.5" customHeight="1" spans="1:18">
       <c r="A527" s="4"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -11339,7 +11962,7 @@
       <c r="Q527" s="4"/>
       <c r="R527" s="4"/>
     </row>
-    <row r="528" spans="1:18" ht="13.5" customHeight="1">
+    <row r="528" ht="13.5" customHeight="1" spans="1:18">
       <c r="A528" s="4"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -11359,7 +11982,7 @@
       <c r="Q528" s="4"/>
       <c r="R528" s="4"/>
     </row>
-    <row r="529" spans="1:18" ht="13.5" customHeight="1">
+    <row r="529" ht="13.5" customHeight="1" spans="1:18">
       <c r="A529" s="4"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -11379,7 +12002,7 @@
       <c r="Q529" s="4"/>
       <c r="R529" s="4"/>
     </row>
-    <row r="530" spans="1:18" ht="13.5" customHeight="1">
+    <row r="530" ht="13.5" customHeight="1" spans="1:18">
       <c r="A530" s="4"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -11399,7 +12022,7 @@
       <c r="Q530" s="4"/>
       <c r="R530" s="4"/>
     </row>
-    <row r="531" spans="1:18" ht="13.5" customHeight="1">
+    <row r="531" ht="13.5" customHeight="1" spans="1:18">
       <c r="A531" s="4"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -11419,7 +12042,7 @@
       <c r="Q531" s="4"/>
       <c r="R531" s="4"/>
     </row>
-    <row r="532" spans="1:18" ht="13.5" customHeight="1">
+    <row r="532" ht="13.5" customHeight="1" spans="1:18">
       <c r="A532" s="4"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -11439,7 +12062,7 @@
       <c r="Q532" s="4"/>
       <c r="R532" s="4"/>
     </row>
-    <row r="533" spans="1:18" ht="13.5" customHeight="1">
+    <row r="533" ht="13.5" customHeight="1" spans="1:18">
       <c r="A533" s="4"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -11459,7 +12082,7 @@
       <c r="Q533" s="4"/>
       <c r="R533" s="4"/>
     </row>
-    <row r="534" spans="1:18" ht="13.5" customHeight="1">
+    <row r="534" ht="13.5" customHeight="1" spans="1:18">
       <c r="A534" s="4"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -11479,7 +12102,7 @@
       <c r="Q534" s="4"/>
       <c r="R534" s="4"/>
     </row>
-    <row r="535" spans="1:18" ht="13.5" customHeight="1">
+    <row r="535" ht="13.5" customHeight="1" spans="1:18">
       <c r="A535" s="4"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
@@ -11499,7 +12122,7 @@
       <c r="Q535" s="4"/>
       <c r="R535" s="4"/>
     </row>
-    <row r="536" spans="1:18" ht="13.5" customHeight="1">
+    <row r="536" ht="13.5" customHeight="1" spans="1:18">
       <c r="A536" s="4"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
@@ -11519,7 +12142,7 @@
       <c r="Q536" s="4"/>
       <c r="R536" s="4"/>
     </row>
-    <row r="537" spans="1:18" ht="13.5" customHeight="1">
+    <row r="537" ht="13.5" customHeight="1" spans="1:18">
       <c r="A537" s="4"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
@@ -11539,7 +12162,7 @@
       <c r="Q537" s="4"/>
       <c r="R537" s="4"/>
     </row>
-    <row r="538" spans="1:18" ht="13.5" customHeight="1">
+    <row r="538" ht="13.5" customHeight="1" spans="1:18">
       <c r="A538" s="4"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
@@ -11559,7 +12182,7 @@
       <c r="Q538" s="4"/>
       <c r="R538" s="4"/>
     </row>
-    <row r="539" spans="1:18" ht="13.5" customHeight="1">
+    <row r="539" ht="13.5" customHeight="1" spans="1:18">
       <c r="A539" s="4"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
@@ -11579,7 +12202,7 @@
       <c r="Q539" s="4"/>
       <c r="R539" s="4"/>
     </row>
-    <row r="540" spans="1:18" ht="13.5" customHeight="1">
+    <row r="540" ht="13.5" customHeight="1" spans="1:18">
       <c r="A540" s="4"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
@@ -11599,7 +12222,7 @@
       <c r="Q540" s="4"/>
       <c r="R540" s="4"/>
     </row>
-    <row r="541" spans="1:18" ht="13.5" customHeight="1">
+    <row r="541" ht="13.5" customHeight="1" spans="1:18">
       <c r="A541" s="4"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
@@ -11619,7 +12242,7 @@
       <c r="Q541" s="4"/>
       <c r="R541" s="4"/>
     </row>
-    <row r="542" spans="1:18" ht="13.5" customHeight="1">
+    <row r="542" ht="13.5" customHeight="1" spans="1:18">
       <c r="A542" s="4"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
@@ -11639,7 +12262,7 @@
       <c r="Q542" s="4"/>
       <c r="R542" s="4"/>
     </row>
-    <row r="543" spans="1:18" ht="13.5" customHeight="1">
+    <row r="543" ht="13.5" customHeight="1" spans="1:18">
       <c r="A543" s="4"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
@@ -11659,7 +12282,7 @@
       <c r="Q543" s="4"/>
       <c r="R543" s="4"/>
     </row>
-    <row r="544" spans="1:18" ht="13.5" customHeight="1">
+    <row r="544" ht="13.5" customHeight="1" spans="1:18">
       <c r="A544" s="4"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
@@ -11679,7 +12302,7 @@
       <c r="Q544" s="4"/>
       <c r="R544" s="4"/>
     </row>
-    <row r="545" spans="1:18" ht="13.5" customHeight="1">
+    <row r="545" ht="13.5" customHeight="1" spans="1:18">
       <c r="A545" s="4"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
@@ -11699,7 +12322,7 @@
       <c r="Q545" s="4"/>
       <c r="R545" s="4"/>
     </row>
-    <row r="546" spans="1:18" ht="13.5" customHeight="1">
+    <row r="546" ht="13.5" customHeight="1" spans="1:18">
       <c r="A546" s="4"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -11719,7 +12342,7 @@
       <c r="Q546" s="4"/>
       <c r="R546" s="4"/>
     </row>
-    <row r="547" spans="1:18" ht="13.5" customHeight="1">
+    <row r="547" ht="13.5" customHeight="1" spans="1:18">
       <c r="A547" s="4"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
@@ -11739,7 +12362,7 @@
       <c r="Q547" s="4"/>
       <c r="R547" s="4"/>
     </row>
-    <row r="548" spans="1:18" ht="13.5" customHeight="1">
+    <row r="548" ht="13.5" customHeight="1" spans="1:18">
       <c r="A548" s="4"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
@@ -11759,7 +12382,7 @@
       <c r="Q548" s="4"/>
       <c r="R548" s="4"/>
     </row>
-    <row r="549" spans="1:18" ht="13.5" customHeight="1">
+    <row r="549" ht="13.5" customHeight="1" spans="1:18">
       <c r="A549" s="4"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
@@ -11779,7 +12402,7 @@
       <c r="Q549" s="4"/>
       <c r="R549" s="4"/>
     </row>
-    <row r="550" spans="1:18" ht="13.5" customHeight="1">
+    <row r="550" ht="13.5" customHeight="1" spans="1:18">
       <c r="A550" s="4"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
@@ -11799,7 +12422,7 @@
       <c r="Q550" s="4"/>
       <c r="R550" s="4"/>
     </row>
-    <row r="551" spans="1:18" ht="13.5" customHeight="1">
+    <row r="551" ht="13.5" customHeight="1" spans="1:18">
       <c r="A551" s="4"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
@@ -11819,7 +12442,7 @@
       <c r="Q551" s="4"/>
       <c r="R551" s="4"/>
     </row>
-    <row r="552" spans="1:18" ht="13.5" customHeight="1">
+    <row r="552" ht="13.5" customHeight="1" spans="1:18">
       <c r="A552" s="4"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
@@ -11839,7 +12462,7 @@
       <c r="Q552" s="4"/>
       <c r="R552" s="4"/>
     </row>
-    <row r="553" spans="1:18" ht="13.5" customHeight="1">
+    <row r="553" ht="13.5" customHeight="1" spans="1:18">
       <c r="A553" s="4"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
@@ -11859,7 +12482,7 @@
       <c r="Q553" s="4"/>
       <c r="R553" s="4"/>
     </row>
-    <row r="554" spans="1:18" ht="13.5" customHeight="1">
+    <row r="554" ht="13.5" customHeight="1" spans="1:18">
       <c r="A554" s="4"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
@@ -11879,7 +12502,7 @@
       <c r="Q554" s="4"/>
       <c r="R554" s="4"/>
     </row>
-    <row r="555" spans="1:18" ht="13.5" customHeight="1">
+    <row r="555" ht="13.5" customHeight="1" spans="1:18">
       <c r="A555" s="4"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
@@ -11899,7 +12522,7 @@
       <c r="Q555" s="4"/>
       <c r="R555" s="4"/>
     </row>
-    <row r="556" spans="1:18" ht="13.5" customHeight="1">
+    <row r="556" ht="13.5" customHeight="1" spans="1:18">
       <c r="A556" s="4"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
@@ -11919,7 +12542,7 @@
       <c r="Q556" s="4"/>
       <c r="R556" s="4"/>
     </row>
-    <row r="557" spans="1:18" ht="13.5" customHeight="1">
+    <row r="557" ht="13.5" customHeight="1" spans="1:18">
       <c r="A557" s="4"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
@@ -11939,7 +12562,7 @@
       <c r="Q557" s="4"/>
       <c r="R557" s="4"/>
     </row>
-    <row r="558" spans="1:18" ht="13.5" customHeight="1">
+    <row r="558" ht="13.5" customHeight="1" spans="1:18">
       <c r="A558" s="4"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
@@ -11959,7 +12582,7 @@
       <c r="Q558" s="4"/>
       <c r="R558" s="4"/>
     </row>
-    <row r="559" spans="1:18" ht="13.5" customHeight="1">
+    <row r="559" ht="13.5" customHeight="1" spans="1:18">
       <c r="A559" s="4"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
@@ -11979,7 +12602,7 @@
       <c r="Q559" s="4"/>
       <c r="R559" s="4"/>
     </row>
-    <row r="560" spans="1:18" ht="13.5" customHeight="1">
+    <row r="560" ht="13.5" customHeight="1" spans="1:18">
       <c r="A560" s="4"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
@@ -11999,7 +12622,7 @@
       <c r="Q560" s="4"/>
       <c r="R560" s="4"/>
     </row>
-    <row r="561" spans="1:18" ht="13.5" customHeight="1">
+    <row r="561" ht="13.5" customHeight="1" spans="1:18">
       <c r="A561" s="4"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
@@ -12019,7 +12642,7 @@
       <c r="Q561" s="4"/>
       <c r="R561" s="4"/>
     </row>
-    <row r="562" spans="1:18" ht="13.5" customHeight="1">
+    <row r="562" ht="13.5" customHeight="1" spans="1:18">
       <c r="A562" s="4"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -12039,7 +12662,7 @@
       <c r="Q562" s="4"/>
       <c r="R562" s="4"/>
     </row>
-    <row r="563" spans="1:18" ht="13.5" customHeight="1">
+    <row r="563" ht="13.5" customHeight="1" spans="1:18">
       <c r="A563" s="4"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
@@ -12059,7 +12682,7 @@
       <c r="Q563" s="4"/>
       <c r="R563" s="4"/>
     </row>
-    <row r="564" spans="1:18" ht="13.5" customHeight="1">
+    <row r="564" ht="13.5" customHeight="1" spans="1:18">
       <c r="A564" s="4"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
@@ -12079,7 +12702,7 @@
       <c r="Q564" s="4"/>
       <c r="R564" s="4"/>
     </row>
-    <row r="565" spans="1:18" ht="13.5" customHeight="1">
+    <row r="565" ht="13.5" customHeight="1" spans="1:18">
       <c r="A565" s="4"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
@@ -12099,7 +12722,7 @@
       <c r="Q565" s="4"/>
       <c r="R565" s="4"/>
     </row>
-    <row r="566" spans="1:18" ht="13.5" customHeight="1">
+    <row r="566" ht="13.5" customHeight="1" spans="1:18">
       <c r="A566" s="4"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
@@ -12119,7 +12742,7 @@
       <c r="Q566" s="4"/>
       <c r="R566" s="4"/>
     </row>
-    <row r="567" spans="1:18" ht="13.5" customHeight="1">
+    <row r="567" ht="13.5" customHeight="1" spans="1:18">
       <c r="A567" s="4"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
@@ -12139,7 +12762,7 @@
       <c r="Q567" s="4"/>
       <c r="R567" s="4"/>
     </row>
-    <row r="568" spans="1:18" ht="13.5" customHeight="1">
+    <row r="568" ht="13.5" customHeight="1" spans="1:18">
       <c r="A568" s="4"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
@@ -12159,7 +12782,7 @@
       <c r="Q568" s="4"/>
       <c r="R568" s="4"/>
     </row>
-    <row r="569" spans="1:18" ht="13.5" customHeight="1">
+    <row r="569" ht="13.5" customHeight="1" spans="1:18">
       <c r="A569" s="4"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
@@ -12179,7 +12802,7 @@
       <c r="Q569" s="4"/>
       <c r="R569" s="4"/>
     </row>
-    <row r="570" spans="1:18" ht="13.5" customHeight="1">
+    <row r="570" ht="13.5" customHeight="1" spans="1:18">
       <c r="A570" s="4"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
@@ -12199,7 +12822,7 @@
       <c r="Q570" s="4"/>
       <c r="R570" s="4"/>
     </row>
-    <row r="571" spans="1:18" ht="13.5" customHeight="1">
+    <row r="571" ht="13.5" customHeight="1" spans="1:18">
       <c r="A571" s="4"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
@@ -12219,7 +12842,7 @@
       <c r="Q571" s="4"/>
       <c r="R571" s="4"/>
     </row>
-    <row r="572" spans="1:18" ht="13.5" customHeight="1">
+    <row r="572" ht="13.5" customHeight="1" spans="1:18">
       <c r="A572" s="4"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
@@ -12239,7 +12862,7 @@
       <c r="Q572" s="4"/>
       <c r="R572" s="4"/>
     </row>
-    <row r="573" spans="1:18" ht="13.5" customHeight="1">
+    <row r="573" ht="13.5" customHeight="1" spans="1:18">
       <c r="A573" s="4"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
@@ -12259,7 +12882,7 @@
       <c r="Q573" s="4"/>
       <c r="R573" s="4"/>
     </row>
-    <row r="574" spans="1:18" ht="13.5" customHeight="1">
+    <row r="574" ht="13.5" customHeight="1" spans="1:18">
       <c r="A574" s="4"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
@@ -12279,7 +12902,7 @@
       <c r="Q574" s="4"/>
       <c r="R574" s="4"/>
     </row>
-    <row r="575" spans="1:18" ht="13.5" customHeight="1">
+    <row r="575" ht="13.5" customHeight="1" spans="1:18">
       <c r="A575" s="4"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
@@ -12299,7 +12922,7 @@
       <c r="Q575" s="4"/>
       <c r="R575" s="4"/>
     </row>
-    <row r="576" spans="1:18" ht="13.5" customHeight="1">
+    <row r="576" ht="13.5" customHeight="1" spans="1:18">
       <c r="A576" s="4"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
@@ -12319,7 +12942,7 @@
       <c r="Q576" s="4"/>
       <c r="R576" s="4"/>
     </row>
-    <row r="577" spans="1:18" ht="13.5" customHeight="1">
+    <row r="577" ht="13.5" customHeight="1" spans="1:18">
       <c r="A577" s="4"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
@@ -12339,7 +12962,7 @@
       <c r="Q577" s="4"/>
       <c r="R577" s="4"/>
     </row>
-    <row r="578" spans="1:18" ht="13.5" customHeight="1">
+    <row r="578" ht="13.5" customHeight="1" spans="1:18">
       <c r="A578" s="4"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
@@ -12359,7 +12982,7 @@
       <c r="Q578" s="4"/>
       <c r="R578" s="4"/>
     </row>
-    <row r="579" spans="1:18" ht="13.5" customHeight="1">
+    <row r="579" ht="13.5" customHeight="1" spans="1:18">
       <c r="A579" s="4"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
@@ -12379,7 +13002,7 @@
       <c r="Q579" s="4"/>
       <c r="R579" s="4"/>
     </row>
-    <row r="580" spans="1:18" ht="13.5" customHeight="1">
+    <row r="580" ht="13.5" customHeight="1" spans="1:18">
       <c r="A580" s="4"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
@@ -12399,7 +13022,7 @@
       <c r="Q580" s="4"/>
       <c r="R580" s="4"/>
     </row>
-    <row r="581" spans="1:18" ht="13.5" customHeight="1">
+    <row r="581" ht="13.5" customHeight="1" spans="1:18">
       <c r="A581" s="4"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
@@ -12419,7 +13042,7 @@
       <c r="Q581" s="4"/>
       <c r="R581" s="4"/>
     </row>
-    <row r="582" spans="1:18" ht="13.5" customHeight="1">
+    <row r="582" ht="13.5" customHeight="1" spans="1:18">
       <c r="A582" s="4"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
@@ -12439,7 +13062,7 @@
       <c r="Q582" s="4"/>
       <c r="R582" s="4"/>
     </row>
-    <row r="583" spans="1:18" ht="13.5" customHeight="1">
+    <row r="583" ht="13.5" customHeight="1" spans="1:18">
       <c r="A583" s="4"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
@@ -12459,7 +13082,7 @@
       <c r="Q583" s="4"/>
       <c r="R583" s="4"/>
     </row>
-    <row r="584" spans="1:18" ht="13.5" customHeight="1">
+    <row r="584" ht="13.5" customHeight="1" spans="1:18">
       <c r="A584" s="4"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
@@ -12479,7 +13102,7 @@
       <c r="Q584" s="4"/>
       <c r="R584" s="4"/>
     </row>
-    <row r="585" spans="1:18" ht="13.5" customHeight="1">
+    <row r="585" ht="13.5" customHeight="1" spans="1:18">
       <c r="A585" s="4"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
@@ -12499,7 +13122,7 @@
       <c r="Q585" s="4"/>
       <c r="R585" s="4"/>
     </row>
-    <row r="586" spans="1:18" ht="13.5" customHeight="1">
+    <row r="586" ht="13.5" customHeight="1" spans="1:18">
       <c r="A586" s="4"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
@@ -12519,7 +13142,7 @@
       <c r="Q586" s="4"/>
       <c r="R586" s="4"/>
     </row>
-    <row r="587" spans="1:18" ht="13.5" customHeight="1">
+    <row r="587" ht="13.5" customHeight="1" spans="1:18">
       <c r="A587" s="4"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
@@ -12539,7 +13162,7 @@
       <c r="Q587" s="4"/>
       <c r="R587" s="4"/>
     </row>
-    <row r="588" spans="1:18" ht="13.5" customHeight="1">
+    <row r="588" ht="13.5" customHeight="1" spans="1:18">
       <c r="A588" s="4"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
@@ -12559,7 +13182,7 @@
       <c r="Q588" s="4"/>
       <c r="R588" s="4"/>
     </row>
-    <row r="589" spans="1:18" ht="13.5" customHeight="1">
+    <row r="589" ht="13.5" customHeight="1" spans="1:18">
       <c r="A589" s="4"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
@@ -12579,7 +13202,7 @@
       <c r="Q589" s="4"/>
       <c r="R589" s="4"/>
     </row>
-    <row r="590" spans="1:18" ht="13.5" customHeight="1">
+    <row r="590" ht="13.5" customHeight="1" spans="1:18">
       <c r="A590" s="4"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
@@ -12599,7 +13222,7 @@
       <c r="Q590" s="4"/>
       <c r="R590" s="4"/>
     </row>
-    <row r="591" spans="1:18" ht="13.5" customHeight="1">
+    <row r="591" ht="13.5" customHeight="1" spans="1:18">
       <c r="A591" s="4"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
@@ -12619,7 +13242,7 @@
       <c r="Q591" s="4"/>
       <c r="R591" s="4"/>
     </row>
-    <row r="592" spans="1:18" ht="13.5" customHeight="1">
+    <row r="592" ht="13.5" customHeight="1" spans="1:18">
       <c r="A592" s="4"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
@@ -12639,7 +13262,7 @@
       <c r="Q592" s="4"/>
       <c r="R592" s="4"/>
     </row>
-    <row r="593" spans="1:18" ht="13.5" customHeight="1">
+    <row r="593" ht="13.5" customHeight="1" spans="1:18">
       <c r="A593" s="4"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
@@ -12659,7 +13282,7 @@
       <c r="Q593" s="4"/>
       <c r="R593" s="4"/>
     </row>
-    <row r="594" spans="1:18" ht="13.5" customHeight="1">
+    <row r="594" ht="13.5" customHeight="1" spans="1:18">
       <c r="A594" s="4"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
@@ -12679,7 +13302,7 @@
       <c r="Q594" s="4"/>
       <c r="R594" s="4"/>
     </row>
-    <row r="595" spans="1:18" ht="13.5" customHeight="1">
+    <row r="595" ht="13.5" customHeight="1" spans="1:18">
       <c r="A595" s="4"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
@@ -12699,7 +13322,7 @@
       <c r="Q595" s="4"/>
       <c r="R595" s="4"/>
     </row>
-    <row r="596" spans="1:18" ht="13.5" customHeight="1">
+    <row r="596" ht="13.5" customHeight="1" spans="1:18">
       <c r="A596" s="4"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
@@ -12719,7 +13342,7 @@
       <c r="Q596" s="4"/>
       <c r="R596" s="4"/>
     </row>
-    <row r="597" spans="1:18" ht="13.5" customHeight="1">
+    <row r="597" ht="13.5" customHeight="1" spans="1:18">
       <c r="A597" s="4"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -12739,7 +13362,7 @@
       <c r="Q597" s="4"/>
       <c r="R597" s="4"/>
     </row>
-    <row r="598" spans="1:18" ht="13.5" customHeight="1">
+    <row r="598" ht="13.5" customHeight="1" spans="1:18">
       <c r="A598" s="4"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
@@ -12759,7 +13382,7 @@
       <c r="Q598" s="4"/>
       <c r="R598" s="4"/>
     </row>
-    <row r="599" spans="1:18" ht="13.5" customHeight="1">
+    <row r="599" ht="13.5" customHeight="1" spans="1:18">
       <c r="A599" s="4"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
@@ -12779,7 +13402,7 @@
       <c r="Q599" s="4"/>
       <c r="R599" s="4"/>
     </row>
-    <row r="600" spans="1:18" ht="13.5" customHeight="1">
+    <row r="600" ht="13.5" customHeight="1" spans="1:18">
       <c r="A600" s="4"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
@@ -12799,7 +13422,7 @@
       <c r="Q600" s="4"/>
       <c r="R600" s="4"/>
     </row>
-    <row r="601" spans="1:18" ht="13.5" customHeight="1">
+    <row r="601" ht="13.5" customHeight="1" spans="1:18">
       <c r="A601" s="4"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
@@ -12819,7 +13442,7 @@
       <c r="Q601" s="4"/>
       <c r="R601" s="4"/>
     </row>
-    <row r="602" spans="1:18" ht="13.5" customHeight="1">
+    <row r="602" ht="13.5" customHeight="1" spans="1:18">
       <c r="A602" s="4"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
@@ -12839,7 +13462,7 @@
       <c r="Q602" s="4"/>
       <c r="R602" s="4"/>
     </row>
-    <row r="603" spans="1:18" ht="13.5" customHeight="1">
+    <row r="603" ht="13.5" customHeight="1" spans="1:18">
       <c r="A603" s="4"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
@@ -12859,7 +13482,7 @@
       <c r="Q603" s="4"/>
       <c r="R603" s="4"/>
     </row>
-    <row r="604" spans="1:18" ht="13.5" customHeight="1">
+    <row r="604" ht="13.5" customHeight="1" spans="1:18">
       <c r="A604" s="4"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
@@ -12879,7 +13502,7 @@
       <c r="Q604" s="4"/>
       <c r="R604" s="4"/>
     </row>
-    <row r="605" spans="1:18" ht="13.5" customHeight="1">
+    <row r="605" ht="13.5" customHeight="1" spans="1:18">
       <c r="A605" s="4"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
@@ -12899,7 +13522,7 @@
       <c r="Q605" s="4"/>
       <c r="R605" s="4"/>
     </row>
-    <row r="606" spans="1:18" ht="13.5" customHeight="1">
+    <row r="606" ht="13.5" customHeight="1" spans="1:18">
       <c r="A606" s="4"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
@@ -12919,7 +13542,7 @@
       <c r="Q606" s="4"/>
       <c r="R606" s="4"/>
     </row>
-    <row r="607" spans="1:18" ht="13.5" customHeight="1">
+    <row r="607" ht="13.5" customHeight="1" spans="1:18">
       <c r="A607" s="4"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
@@ -12939,7 +13562,7 @@
       <c r="Q607" s="4"/>
       <c r="R607" s="4"/>
     </row>
-    <row r="608" spans="1:18" ht="13.5" customHeight="1">
+    <row r="608" ht="13.5" customHeight="1" spans="1:18">
       <c r="A608" s="4"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
@@ -12959,7 +13582,7 @@
       <c r="Q608" s="4"/>
       <c r="R608" s="4"/>
     </row>
-    <row r="609" spans="1:18" ht="13.5" customHeight="1">
+    <row r="609" ht="13.5" customHeight="1" spans="1:18">
       <c r="A609" s="4"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
@@ -12979,7 +13602,7 @@
       <c r="Q609" s="4"/>
       <c r="R609" s="4"/>
     </row>
-    <row r="610" spans="1:18" ht="13.5" customHeight="1">
+    <row r="610" ht="13.5" customHeight="1" spans="1:18">
       <c r="A610" s="4"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
@@ -12999,7 +13622,7 @@
       <c r="Q610" s="4"/>
       <c r="R610" s="4"/>
     </row>
-    <row r="611" spans="1:18" ht="13.5" customHeight="1">
+    <row r="611" ht="13.5" customHeight="1" spans="1:18">
       <c r="A611" s="4"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
@@ -13019,7 +13642,7 @@
       <c r="Q611" s="4"/>
       <c r="R611" s="4"/>
     </row>
-    <row r="612" spans="1:18" ht="13.5" customHeight="1">
+    <row r="612" ht="13.5" customHeight="1" spans="1:18">
       <c r="A612" s="4"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
@@ -13039,7 +13662,7 @@
       <c r="Q612" s="4"/>
       <c r="R612" s="4"/>
     </row>
-    <row r="613" spans="1:18" ht="13.5" customHeight="1">
+    <row r="613" ht="13.5" customHeight="1" spans="1:18">
       <c r="A613" s="4"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
@@ -13059,7 +13682,7 @@
       <c r="Q613" s="4"/>
       <c r="R613" s="4"/>
     </row>
-    <row r="614" spans="1:18" ht="13.5" customHeight="1">
+    <row r="614" ht="13.5" customHeight="1" spans="1:18">
       <c r="A614" s="4"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
@@ -13079,7 +13702,7 @@
       <c r="Q614" s="4"/>
       <c r="R614" s="4"/>
     </row>
-    <row r="615" spans="1:18" ht="13.5" customHeight="1">
+    <row r="615" ht="13.5" customHeight="1" spans="1:18">
       <c r="A615" s="4"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
@@ -13099,7 +13722,7 @@
       <c r="Q615" s="4"/>
       <c r="R615" s="4"/>
     </row>
-    <row r="616" spans="1:18" ht="13.5" customHeight="1">
+    <row r="616" ht="13.5" customHeight="1" spans="1:18">
       <c r="A616" s="4"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
@@ -13119,7 +13742,7 @@
       <c r="Q616" s="4"/>
       <c r="R616" s="4"/>
     </row>
-    <row r="617" spans="1:18" ht="13.5" customHeight="1">
+    <row r="617" ht="13.5" customHeight="1" spans="1:18">
       <c r="A617" s="4"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
@@ -13139,7 +13762,7 @@
       <c r="Q617" s="4"/>
       <c r="R617" s="4"/>
     </row>
-    <row r="618" spans="1:18" ht="13.5" customHeight="1">
+    <row r="618" ht="13.5" customHeight="1" spans="1:18">
       <c r="A618" s="4"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
@@ -13159,7 +13782,7 @@
       <c r="Q618" s="4"/>
       <c r="R618" s="4"/>
     </row>
-    <row r="619" spans="1:18" ht="13.5" customHeight="1">
+    <row r="619" ht="13.5" customHeight="1" spans="1:18">
       <c r="A619" s="4"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
@@ -13179,7 +13802,7 @@
       <c r="Q619" s="4"/>
       <c r="R619" s="4"/>
     </row>
-    <row r="620" spans="1:18" ht="13.5" customHeight="1">
+    <row r="620" ht="13.5" customHeight="1" spans="1:18">
       <c r="A620" s="4"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
@@ -13199,7 +13822,7 @@
       <c r="Q620" s="4"/>
       <c r="R620" s="4"/>
     </row>
-    <row r="621" spans="1:18" ht="13.5" customHeight="1">
+    <row r="621" ht="13.5" customHeight="1" spans="1:18">
       <c r="A621" s="4"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
@@ -13219,7 +13842,7 @@
       <c r="Q621" s="4"/>
       <c r="R621" s="4"/>
     </row>
-    <row r="622" spans="1:18" ht="13.5" customHeight="1">
+    <row r="622" ht="13.5" customHeight="1" spans="1:18">
       <c r="A622" s="4"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
@@ -13239,7 +13862,7 @@
       <c r="Q622" s="4"/>
       <c r="R622" s="4"/>
     </row>
-    <row r="623" spans="1:18" ht="13.5" customHeight="1">
+    <row r="623" ht="13.5" customHeight="1" spans="1:18">
       <c r="A623" s="4"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
@@ -13259,7 +13882,7 @@
       <c r="Q623" s="4"/>
       <c r="R623" s="4"/>
     </row>
-    <row r="624" spans="1:18" ht="13.5" customHeight="1">
+    <row r="624" ht="13.5" customHeight="1" spans="1:18">
       <c r="A624" s="4"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
@@ -13279,7 +13902,7 @@
       <c r="Q624" s="4"/>
       <c r="R624" s="4"/>
     </row>
-    <row r="625" spans="1:18" ht="13.5" customHeight="1">
+    <row r="625" ht="13.5" customHeight="1" spans="1:18">
       <c r="A625" s="4"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
@@ -13299,7 +13922,7 @@
       <c r="Q625" s="4"/>
       <c r="R625" s="4"/>
     </row>
-    <row r="626" spans="1:18" ht="13.5" customHeight="1">
+    <row r="626" ht="13.5" customHeight="1" spans="1:18">
       <c r="A626" s="4"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
@@ -13319,7 +13942,7 @@
       <c r="Q626" s="4"/>
       <c r="R626" s="4"/>
     </row>
-    <row r="627" spans="1:18" ht="13.5" customHeight="1">
+    <row r="627" ht="13.5" customHeight="1" spans="1:18">
       <c r="A627" s="4"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
@@ -13339,7 +13962,7 @@
       <c r="Q627" s="4"/>
       <c r="R627" s="4"/>
     </row>
-    <row r="628" spans="1:18" ht="13.5" customHeight="1">
+    <row r="628" ht="13.5" customHeight="1" spans="1:18">
       <c r="A628" s="4"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
@@ -13359,7 +13982,7 @@
       <c r="Q628" s="4"/>
       <c r="R628" s="4"/>
     </row>
-    <row r="629" spans="1:18" ht="13.5" customHeight="1">
+    <row r="629" ht="13.5" customHeight="1" spans="1:18">
       <c r="A629" s="4"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
@@ -13379,7 +14002,7 @@
       <c r="Q629" s="4"/>
       <c r="R629" s="4"/>
     </row>
-    <row r="630" spans="1:18" ht="13.5" customHeight="1">
+    <row r="630" ht="13.5" customHeight="1" spans="1:18">
       <c r="A630" s="4"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
@@ -13399,7 +14022,7 @@
       <c r="Q630" s="4"/>
       <c r="R630" s="4"/>
     </row>
-    <row r="631" spans="1:18" ht="13.5" customHeight="1">
+    <row r="631" ht="13.5" customHeight="1" spans="1:18">
       <c r="A631" s="4"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
@@ -13419,7 +14042,7 @@
       <c r="Q631" s="4"/>
       <c r="R631" s="4"/>
     </row>
-    <row r="632" spans="1:18" ht="13.5" customHeight="1">
+    <row r="632" ht="13.5" customHeight="1" spans="1:18">
       <c r="A632" s="4"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
@@ -13439,7 +14062,7 @@
       <c r="Q632" s="4"/>
       <c r="R632" s="4"/>
     </row>
-    <row r="633" spans="1:18" ht="13.5" customHeight="1">
+    <row r="633" ht="13.5" customHeight="1" spans="1:18">
       <c r="A633" s="4"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
@@ -13459,7 +14082,7 @@
       <c r="Q633" s="4"/>
       <c r="R633" s="4"/>
     </row>
-    <row r="634" spans="1:18" ht="13.5" customHeight="1">
+    <row r="634" ht="13.5" customHeight="1" spans="1:18">
       <c r="A634" s="4"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
@@ -13479,7 +14102,7 @@
       <c r="Q634" s="4"/>
       <c r="R634" s="4"/>
     </row>
-    <row r="635" spans="1:18" ht="13.5" customHeight="1">
+    <row r="635" ht="13.5" customHeight="1" spans="1:18">
       <c r="A635" s="4"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
@@ -13499,7 +14122,7 @@
       <c r="Q635" s="4"/>
       <c r="R635" s="4"/>
     </row>
-    <row r="636" spans="1:18" ht="13.5" customHeight="1">
+    <row r="636" ht="13.5" customHeight="1" spans="1:18">
       <c r="A636" s="4"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
@@ -13519,7 +14142,7 @@
       <c r="Q636" s="4"/>
       <c r="R636" s="4"/>
     </row>
-    <row r="637" spans="1:18" ht="13.5" customHeight="1">
+    <row r="637" ht="13.5" customHeight="1" spans="1:18">
       <c r="A637" s="4"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
@@ -13539,7 +14162,7 @@
       <c r="Q637" s="4"/>
       <c r="R637" s="4"/>
     </row>
-    <row r="638" spans="1:18" ht="13.5" customHeight="1">
+    <row r="638" ht="13.5" customHeight="1" spans="1:18">
       <c r="A638" s="4"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
@@ -13559,7 +14182,7 @@
       <c r="Q638" s="4"/>
       <c r="R638" s="4"/>
     </row>
-    <row r="639" spans="1:18" ht="13.5" customHeight="1">
+    <row r="639" ht="13.5" customHeight="1" spans="1:18">
       <c r="A639" s="4"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
@@ -13579,7 +14202,7 @@
       <c r="Q639" s="4"/>
       <c r="R639" s="4"/>
     </row>
-    <row r="640" spans="1:18" ht="13.5" customHeight="1">
+    <row r="640" ht="13.5" customHeight="1" spans="1:18">
       <c r="A640" s="4"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
@@ -13599,7 +14222,7 @@
       <c r="Q640" s="4"/>
       <c r="R640" s="4"/>
     </row>
-    <row r="641" spans="1:18" ht="13.5" customHeight="1">
+    <row r="641" ht="13.5" customHeight="1" spans="1:18">
       <c r="A641" s="4"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
@@ -13619,7 +14242,7 @@
       <c r="Q641" s="4"/>
       <c r="R641" s="4"/>
     </row>
-    <row r="642" spans="1:18" ht="13.5" customHeight="1">
+    <row r="642" ht="13.5" customHeight="1" spans="1:18">
       <c r="A642" s="4"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
@@ -13639,7 +14262,7 @@
       <c r="Q642" s="4"/>
       <c r="R642" s="4"/>
     </row>
-    <row r="643" spans="1:18" ht="13.5" customHeight="1">
+    <row r="643" ht="13.5" customHeight="1" spans="1:18">
       <c r="A643" s="4"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
@@ -13659,7 +14282,7 @@
       <c r="Q643" s="4"/>
       <c r="R643" s="4"/>
     </row>
-    <row r="644" spans="1:18" ht="13.5" customHeight="1">
+    <row r="644" ht="13.5" customHeight="1" spans="1:18">
       <c r="A644" s="4"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
@@ -13679,7 +14302,7 @@
       <c r="Q644" s="4"/>
       <c r="R644" s="4"/>
     </row>
-    <row r="645" spans="1:18" ht="13.5" customHeight="1">
+    <row r="645" ht="13.5" customHeight="1" spans="1:18">
       <c r="A645" s="4"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
@@ -13699,7 +14322,7 @@
       <c r="Q645" s="4"/>
       <c r="R645" s="4"/>
     </row>
-    <row r="646" spans="1:18" ht="13.5" customHeight="1">
+    <row r="646" ht="13.5" customHeight="1" spans="1:18">
       <c r="A646" s="4"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
@@ -13719,7 +14342,7 @@
       <c r="Q646" s="4"/>
       <c r="R646" s="4"/>
     </row>
-    <row r="647" spans="1:18" ht="13.5" customHeight="1">
+    <row r="647" ht="13.5" customHeight="1" spans="1:18">
       <c r="A647" s="4"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
@@ -13739,7 +14362,7 @@
       <c r="Q647" s="4"/>
       <c r="R647" s="4"/>
     </row>
-    <row r="648" spans="1:18" ht="13.5" customHeight="1">
+    <row r="648" ht="13.5" customHeight="1" spans="1:18">
       <c r="A648" s="4"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
@@ -13759,7 +14382,7 @@
       <c r="Q648" s="4"/>
       <c r="R648" s="4"/>
     </row>
-    <row r="649" spans="1:18" ht="13.5" customHeight="1">
+    <row r="649" ht="13.5" customHeight="1" spans="1:18">
       <c r="A649" s="4"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
@@ -13779,7 +14402,7 @@
       <c r="Q649" s="4"/>
       <c r="R649" s="4"/>
     </row>
-    <row r="650" spans="1:18" ht="13.5" customHeight="1">
+    <row r="650" ht="13.5" customHeight="1" spans="1:18">
       <c r="A650" s="4"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
@@ -13799,7 +14422,7 @@
       <c r="Q650" s="4"/>
       <c r="R650" s="4"/>
     </row>
-    <row r="651" spans="1:18" ht="13.5" customHeight="1">
+    <row r="651" ht="13.5" customHeight="1" spans="1:18">
       <c r="A651" s="4"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
@@ -13819,7 +14442,7 @@
       <c r="Q651" s="4"/>
       <c r="R651" s="4"/>
     </row>
-    <row r="652" spans="1:18" ht="13.5" customHeight="1">
+    <row r="652" ht="13.5" customHeight="1" spans="1:18">
       <c r="A652" s="4"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
@@ -13839,7 +14462,7 @@
       <c r="Q652" s="4"/>
       <c r="R652" s="4"/>
     </row>
-    <row r="653" spans="1:18" ht="13.5" customHeight="1">
+    <row r="653" ht="13.5" customHeight="1" spans="1:18">
       <c r="A653" s="4"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
@@ -13859,7 +14482,7 @@
       <c r="Q653" s="4"/>
       <c r="R653" s="4"/>
     </row>
-    <row r="654" spans="1:18" ht="13.5" customHeight="1">
+    <row r="654" ht="13.5" customHeight="1" spans="1:18">
       <c r="A654" s="4"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
@@ -13879,7 +14502,7 @@
       <c r="Q654" s="4"/>
       <c r="R654" s="4"/>
     </row>
-    <row r="655" spans="1:18" ht="13.5" customHeight="1">
+    <row r="655" ht="13.5" customHeight="1" spans="1:18">
       <c r="A655" s="4"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
@@ -13899,7 +14522,7 @@
       <c r="Q655" s="4"/>
       <c r="R655" s="4"/>
     </row>
-    <row r="656" spans="1:18" ht="13.5" customHeight="1">
+    <row r="656" ht="13.5" customHeight="1" spans="1:18">
       <c r="A656" s="4"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
@@ -13919,7 +14542,7 @@
       <c r="Q656" s="4"/>
       <c r="R656" s="4"/>
     </row>
-    <row r="657" spans="1:18" ht="13.5" customHeight="1">
+    <row r="657" ht="13.5" customHeight="1" spans="1:18">
       <c r="A657" s="4"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
@@ -13939,7 +14562,7 @@
       <c r="Q657" s="4"/>
       <c r="R657" s="4"/>
     </row>
-    <row r="658" spans="1:18" ht="13.5" customHeight="1">
+    <row r="658" ht="13.5" customHeight="1" spans="1:18">
       <c r="A658" s="4"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
@@ -13959,7 +14582,7 @@
       <c r="Q658" s="4"/>
       <c r="R658" s="4"/>
     </row>
-    <row r="659" spans="1:18" ht="13.5" customHeight="1">
+    <row r="659" ht="13.5" customHeight="1" spans="1:18">
       <c r="A659" s="4"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
@@ -13979,7 +14602,7 @@
       <c r="Q659" s="4"/>
       <c r="R659" s="4"/>
     </row>
-    <row r="660" spans="1:18" ht="13.5" customHeight="1">
+    <row r="660" ht="13.5" customHeight="1" spans="1:18">
       <c r="A660" s="4"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
@@ -13999,7 +14622,7 @@
       <c r="Q660" s="4"/>
       <c r="R660" s="4"/>
     </row>
-    <row r="661" spans="1:18" ht="13.5" customHeight="1">
+    <row r="661" ht="13.5" customHeight="1" spans="1:18">
       <c r="A661" s="4"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
@@ -14019,7 +14642,7 @@
       <c r="Q661" s="4"/>
       <c r="R661" s="4"/>
     </row>
-    <row r="662" spans="1:18" ht="13.5" customHeight="1">
+    <row r="662" ht="13.5" customHeight="1" spans="1:18">
       <c r="A662" s="4"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
@@ -14039,7 +14662,7 @@
       <c r="Q662" s="4"/>
       <c r="R662" s="4"/>
     </row>
-    <row r="663" spans="1:18" ht="13.5" customHeight="1">
+    <row r="663" ht="13.5" customHeight="1" spans="1:18">
       <c r="A663" s="4"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
@@ -14059,7 +14682,7 @@
       <c r="Q663" s="4"/>
       <c r="R663" s="4"/>
     </row>
-    <row r="664" spans="1:18" ht="13.5" customHeight="1">
+    <row r="664" ht="13.5" customHeight="1" spans="1:18">
       <c r="A664" s="4"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
@@ -14079,7 +14702,7 @@
       <c r="Q664" s="4"/>
       <c r="R664" s="4"/>
     </row>
-    <row r="665" spans="1:18" ht="13.5" customHeight="1">
+    <row r="665" ht="13.5" customHeight="1" spans="1:18">
       <c r="A665" s="4"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
@@ -14099,7 +14722,7 @@
       <c r="Q665" s="4"/>
       <c r="R665" s="4"/>
     </row>
-    <row r="666" spans="1:18" ht="13.5" customHeight="1">
+    <row r="666" ht="13.5" customHeight="1" spans="1:18">
       <c r="A666" s="4"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
@@ -14119,7 +14742,7 @@
       <c r="Q666" s="4"/>
       <c r="R666" s="4"/>
     </row>
-    <row r="667" spans="1:18" ht="13.5" customHeight="1">
+    <row r="667" ht="13.5" customHeight="1" spans="1:18">
       <c r="A667" s="4"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
@@ -14139,7 +14762,7 @@
       <c r="Q667" s="4"/>
       <c r="R667" s="4"/>
     </row>
-    <row r="668" spans="1:18" ht="13.5" customHeight="1">
+    <row r="668" ht="13.5" customHeight="1" spans="1:18">
       <c r="A668" s="4"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
@@ -14159,7 +14782,7 @@
       <c r="Q668" s="4"/>
       <c r="R668" s="4"/>
     </row>
-    <row r="669" spans="1:18" ht="13.5" customHeight="1">
+    <row r="669" ht="13.5" customHeight="1" spans="1:18">
       <c r="A669" s="4"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
@@ -14179,7 +14802,7 @@
       <c r="Q669" s="4"/>
       <c r="R669" s="4"/>
     </row>
-    <row r="670" spans="1:18" ht="13.5" customHeight="1">
+    <row r="670" ht="13.5" customHeight="1" spans="1:18">
       <c r="A670" s="4"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
@@ -14199,7 +14822,7 @@
       <c r="Q670" s="4"/>
       <c r="R670" s="4"/>
     </row>
-    <row r="671" spans="1:18" ht="13.5" customHeight="1">
+    <row r="671" ht="13.5" customHeight="1" spans="1:18">
       <c r="A671" s="4"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
@@ -14219,7 +14842,7 @@
       <c r="Q671" s="4"/>
       <c r="R671" s="4"/>
     </row>
-    <row r="672" spans="1:18" ht="13.5" customHeight="1">
+    <row r="672" ht="13.5" customHeight="1" spans="1:18">
       <c r="A672" s="4"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
@@ -14239,7 +14862,7 @@
       <c r="Q672" s="4"/>
       <c r="R672" s="4"/>
     </row>
-    <row r="673" spans="1:18" ht="13.5" customHeight="1">
+    <row r="673" ht="13.5" customHeight="1" spans="1:18">
       <c r="A673" s="4"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
@@ -14259,7 +14882,7 @@
       <c r="Q673" s="4"/>
       <c r="R673" s="4"/>
     </row>
-    <row r="674" spans="1:18" ht="13.5" customHeight="1">
+    <row r="674" ht="13.5" customHeight="1" spans="1:18">
       <c r="A674" s="4"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
@@ -14279,7 +14902,7 @@
       <c r="Q674" s="4"/>
       <c r="R674" s="4"/>
     </row>
-    <row r="675" spans="1:18" ht="13.5" customHeight="1">
+    <row r="675" ht="13.5" customHeight="1" spans="1:18">
       <c r="A675" s="4"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
@@ -14299,7 +14922,7 @@
       <c r="Q675" s="4"/>
       <c r="R675" s="4"/>
     </row>
-    <row r="676" spans="1:18" ht="13.5" customHeight="1">
+    <row r="676" ht="13.5" customHeight="1" spans="1:18">
       <c r="A676" s="4"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
@@ -14319,7 +14942,7 @@
       <c r="Q676" s="4"/>
       <c r="R676" s="4"/>
     </row>
-    <row r="677" spans="1:18" ht="13.5" customHeight="1">
+    <row r="677" ht="13.5" customHeight="1" spans="1:18">
       <c r="A677" s="4"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
@@ -14339,7 +14962,7 @@
       <c r="Q677" s="4"/>
       <c r="R677" s="4"/>
     </row>
-    <row r="678" spans="1:18" ht="13.5" customHeight="1">
+    <row r="678" ht="13.5" customHeight="1" spans="1:18">
       <c r="A678" s="4"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
@@ -14359,7 +14982,7 @@
       <c r="Q678" s="4"/>
       <c r="R678" s="4"/>
     </row>
-    <row r="679" spans="1:18" ht="13.5" customHeight="1">
+    <row r="679" ht="13.5" customHeight="1" spans="1:18">
       <c r="A679" s="4"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
@@ -14379,7 +15002,7 @@
       <c r="Q679" s="4"/>
       <c r="R679" s="4"/>
     </row>
-    <row r="680" spans="1:18" ht="13.5" customHeight="1">
+    <row r="680" ht="13.5" customHeight="1" spans="1:18">
       <c r="A680" s="4"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
@@ -14399,7 +15022,7 @@
       <c r="Q680" s="4"/>
       <c r="R680" s="4"/>
     </row>
-    <row r="681" spans="1:18" ht="13.5" customHeight="1">
+    <row r="681" ht="13.5" customHeight="1" spans="1:18">
       <c r="A681" s="4"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
@@ -14419,7 +15042,7 @@
       <c r="Q681" s="4"/>
       <c r="R681" s="4"/>
     </row>
-    <row r="682" spans="1:18" ht="13.5" customHeight="1">
+    <row r="682" ht="13.5" customHeight="1" spans="1:18">
       <c r="A682" s="4"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
@@ -14439,7 +15062,7 @@
       <c r="Q682" s="4"/>
       <c r="R682" s="4"/>
     </row>
-    <row r="683" spans="1:18" ht="13.5" customHeight="1">
+    <row r="683" ht="13.5" customHeight="1" spans="1:18">
       <c r="A683" s="4"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
@@ -14459,7 +15082,7 @@
       <c r="Q683" s="4"/>
       <c r="R683" s="4"/>
     </row>
-    <row r="684" spans="1:18" ht="13.5" customHeight="1">
+    <row r="684" ht="13.5" customHeight="1" spans="1:18">
       <c r="A684" s="4"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
@@ -14479,7 +15102,7 @@
       <c r="Q684" s="4"/>
       <c r="R684" s="4"/>
     </row>
-    <row r="685" spans="1:18" ht="13.5" customHeight="1">
+    <row r="685" ht="13.5" customHeight="1" spans="1:18">
       <c r="A685" s="4"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
@@ -14499,7 +15122,7 @@
       <c r="Q685" s="4"/>
       <c r="R685" s="4"/>
     </row>
-    <row r="686" spans="1:18" ht="13.5" customHeight="1">
+    <row r="686" ht="13.5" customHeight="1" spans="1:18">
       <c r="A686" s="4"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
@@ -14519,7 +15142,7 @@
       <c r="Q686" s="4"/>
       <c r="R686" s="4"/>
     </row>
-    <row r="687" spans="1:18" ht="13.5" customHeight="1">
+    <row r="687" ht="13.5" customHeight="1" spans="1:18">
       <c r="A687" s="4"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
@@ -14539,7 +15162,7 @@
       <c r="Q687" s="4"/>
       <c r="R687" s="4"/>
     </row>
-    <row r="688" spans="1:18" ht="13.5" customHeight="1">
+    <row r="688" ht="13.5" customHeight="1" spans="1:18">
       <c r="A688" s="4"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
@@ -14559,7 +15182,7 @@
       <c r="Q688" s="4"/>
       <c r="R688" s="4"/>
     </row>
-    <row r="689" spans="1:18" ht="13.5" customHeight="1">
+    <row r="689" ht="13.5" customHeight="1" spans="1:18">
       <c r="A689" s="4"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
@@ -14579,7 +15202,7 @@
       <c r="Q689" s="4"/>
       <c r="R689" s="4"/>
     </row>
-    <row r="690" spans="1:18" ht="13.5" customHeight="1">
+    <row r="690" ht="13.5" customHeight="1" spans="1:18">
       <c r="A690" s="4"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
@@ -14599,7 +15222,7 @@
       <c r="Q690" s="4"/>
       <c r="R690" s="4"/>
     </row>
-    <row r="691" spans="1:18" ht="13.5" customHeight="1">
+    <row r="691" ht="13.5" customHeight="1" spans="1:18">
       <c r="A691" s="4"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
@@ -14619,7 +15242,7 @@
       <c r="Q691" s="4"/>
       <c r="R691" s="4"/>
     </row>
-    <row r="692" spans="1:18" ht="13.5" customHeight="1">
+    <row r="692" ht="13.5" customHeight="1" spans="1:18">
       <c r="A692" s="4"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
@@ -14639,7 +15262,7 @@
       <c r="Q692" s="4"/>
       <c r="R692" s="4"/>
     </row>
-    <row r="693" spans="1:18" ht="13.5" customHeight="1">
+    <row r="693" ht="13.5" customHeight="1" spans="1:18">
       <c r="A693" s="4"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
@@ -14659,7 +15282,7 @@
       <c r="Q693" s="4"/>
       <c r="R693" s="4"/>
     </row>
-    <row r="694" spans="1:18" ht="13.5" customHeight="1">
+    <row r="694" ht="13.5" customHeight="1" spans="1:18">
       <c r="A694" s="4"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
@@ -14679,7 +15302,7 @@
       <c r="Q694" s="4"/>
       <c r="R694" s="4"/>
     </row>
-    <row r="695" spans="1:18" ht="13.5" customHeight="1">
+    <row r="695" ht="13.5" customHeight="1" spans="1:18">
       <c r="A695" s="4"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
@@ -14699,7 +15322,7 @@
       <c r="Q695" s="4"/>
       <c r="R695" s="4"/>
     </row>
-    <row r="696" spans="1:18" ht="13.5" customHeight="1">
+    <row r="696" ht="13.5" customHeight="1" spans="1:18">
       <c r="A696" s="4"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
@@ -14719,7 +15342,7 @@
       <c r="Q696" s="4"/>
       <c r="R696" s="4"/>
     </row>
-    <row r="697" spans="1:18" ht="13.5" customHeight="1">
+    <row r="697" ht="13.5" customHeight="1" spans="1:18">
       <c r="A697" s="4"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
@@ -14739,7 +15362,7 @@
       <c r="Q697" s="4"/>
       <c r="R697" s="4"/>
     </row>
-    <row r="698" spans="1:18" ht="13.5" customHeight="1">
+    <row r="698" ht="13.5" customHeight="1" spans="1:18">
       <c r="A698" s="4"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
@@ -14759,7 +15382,7 @@
       <c r="Q698" s="4"/>
       <c r="R698" s="4"/>
     </row>
-    <row r="699" spans="1:18" ht="13.5" customHeight="1">
+    <row r="699" ht="13.5" customHeight="1" spans="1:18">
       <c r="A699" s="4"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
@@ -14779,7 +15402,7 @@
       <c r="Q699" s="4"/>
       <c r="R699" s="4"/>
     </row>
-    <row r="700" spans="1:18" ht="13.5" customHeight="1">
+    <row r="700" ht="13.5" customHeight="1" spans="1:18">
       <c r="A700" s="4"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
@@ -14799,7 +15422,7 @@
       <c r="Q700" s="4"/>
       <c r="R700" s="4"/>
     </row>
-    <row r="701" spans="1:18" ht="13.5" customHeight="1">
+    <row r="701" ht="13.5" customHeight="1" spans="1:18">
       <c r="A701" s="4"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
@@ -14819,7 +15442,7 @@
       <c r="Q701" s="4"/>
       <c r="R701" s="4"/>
     </row>
-    <row r="702" spans="1:18" ht="13.5" customHeight="1">
+    <row r="702" ht="13.5" customHeight="1" spans="1:18">
       <c r="A702" s="4"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
@@ -14839,7 +15462,7 @@
       <c r="Q702" s="4"/>
       <c r="R702" s="4"/>
     </row>
-    <row r="703" spans="1:18" ht="13.5" customHeight="1">
+    <row r="703" ht="13.5" customHeight="1" spans="1:18">
       <c r="A703" s="4"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
@@ -14859,7 +15482,7 @@
       <c r="Q703" s="4"/>
       <c r="R703" s="4"/>
     </row>
-    <row r="704" spans="1:18" ht="13.5" customHeight="1">
+    <row r="704" ht="13.5" customHeight="1" spans="1:18">
       <c r="A704" s="4"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
@@ -14879,7 +15502,7 @@
       <c r="Q704" s="4"/>
       <c r="R704" s="4"/>
     </row>
-    <row r="705" spans="1:18" ht="13.5" customHeight="1">
+    <row r="705" ht="13.5" customHeight="1" spans="1:18">
       <c r="A705" s="4"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
@@ -14899,7 +15522,7 @@
       <c r="Q705" s="4"/>
       <c r="R705" s="4"/>
     </row>
-    <row r="706" spans="1:18" ht="13.5" customHeight="1">
+    <row r="706" ht="13.5" customHeight="1" spans="1:18">
       <c r="A706" s="4"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
@@ -14919,7 +15542,7 @@
       <c r="Q706" s="4"/>
       <c r="R706" s="4"/>
     </row>
-    <row r="707" spans="1:18" ht="13.5" customHeight="1">
+    <row r="707" ht="13.5" customHeight="1" spans="1:18">
       <c r="A707" s="4"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
@@ -14939,7 +15562,7 @@
       <c r="Q707" s="4"/>
       <c r="R707" s="4"/>
     </row>
-    <row r="708" spans="1:18" ht="13.5" customHeight="1">
+    <row r="708" ht="13.5" customHeight="1" spans="1:18">
       <c r="A708" s="4"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
@@ -14959,7 +15582,7 @@
       <c r="Q708" s="4"/>
       <c r="R708" s="4"/>
     </row>
-    <row r="709" spans="1:18" ht="13.5" customHeight="1">
+    <row r="709" ht="13.5" customHeight="1" spans="1:18">
       <c r="A709" s="4"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
@@ -14979,7 +15602,7 @@
       <c r="Q709" s="4"/>
       <c r="R709" s="4"/>
     </row>
-    <row r="710" spans="1:18" ht="13.5" customHeight="1">
+    <row r="710" ht="13.5" customHeight="1" spans="1:18">
       <c r="A710" s="4"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
@@ -14999,7 +15622,7 @@
       <c r="Q710" s="4"/>
       <c r="R710" s="4"/>
     </row>
-    <row r="711" spans="1:18" ht="13.5" customHeight="1">
+    <row r="711" ht="13.5" customHeight="1" spans="1:18">
       <c r="A711" s="4"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
@@ -15019,7 +15642,7 @@
       <c r="Q711" s="4"/>
       <c r="R711" s="4"/>
     </row>
-    <row r="712" spans="1:18" ht="13.5" customHeight="1">
+    <row r="712" ht="13.5" customHeight="1" spans="1:18">
       <c r="A712" s="4"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
@@ -15039,7 +15662,7 @@
       <c r="Q712" s="4"/>
       <c r="R712" s="4"/>
     </row>
-    <row r="713" spans="1:18" ht="13.5" customHeight="1">
+    <row r="713" ht="13.5" customHeight="1" spans="1:18">
       <c r="A713" s="4"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
@@ -15059,7 +15682,7 @@
       <c r="Q713" s="4"/>
       <c r="R713" s="4"/>
     </row>
-    <row r="714" spans="1:18" ht="13.5" customHeight="1">
+    <row r="714" ht="13.5" customHeight="1" spans="1:18">
       <c r="A714" s="4"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
@@ -15079,7 +15702,7 @@
       <c r="Q714" s="4"/>
       <c r="R714" s="4"/>
     </row>
-    <row r="715" spans="1:18" ht="13.5" customHeight="1">
+    <row r="715" ht="13.5" customHeight="1" spans="1:18">
       <c r="A715" s="4"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
@@ -15099,7 +15722,7 @@
       <c r="Q715" s="4"/>
       <c r="R715" s="4"/>
     </row>
-    <row r="716" spans="1:18" ht="13.5" customHeight="1">
+    <row r="716" ht="13.5" customHeight="1" spans="1:18">
       <c r="A716" s="4"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
@@ -15119,7 +15742,7 @@
       <c r="Q716" s="4"/>
       <c r="R716" s="4"/>
     </row>
-    <row r="717" spans="1:18" ht="13.5" customHeight="1">
+    <row r="717" ht="13.5" customHeight="1" spans="1:18">
       <c r="A717" s="4"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
@@ -15139,7 +15762,7 @@
       <c r="Q717" s="4"/>
       <c r="R717" s="4"/>
     </row>
-    <row r="718" spans="1:18" ht="13.5" customHeight="1">
+    <row r="718" ht="13.5" customHeight="1" spans="1:18">
       <c r="A718" s="4"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
@@ -15159,7 +15782,7 @@
       <c r="Q718" s="4"/>
       <c r="R718" s="4"/>
     </row>
-    <row r="719" spans="1:18" ht="13.5" customHeight="1">
+    <row r="719" ht="13.5" customHeight="1" spans="1:18">
       <c r="A719" s="4"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
@@ -15179,7 +15802,7 @@
       <c r="Q719" s="4"/>
       <c r="R719" s="4"/>
     </row>
-    <row r="720" spans="1:18" ht="13.5" customHeight="1">
+    <row r="720" ht="13.5" customHeight="1" spans="1:18">
       <c r="A720" s="4"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
@@ -15199,7 +15822,7 @@
       <c r="Q720" s="4"/>
       <c r="R720" s="4"/>
     </row>
-    <row r="721" spans="1:18" ht="13.5" customHeight="1">
+    <row r="721" ht="13.5" customHeight="1" spans="1:18">
       <c r="A721" s="4"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
@@ -15219,7 +15842,7 @@
       <c r="Q721" s="4"/>
       <c r="R721" s="4"/>
     </row>
-    <row r="722" spans="1:18" ht="13.5" customHeight="1">
+    <row r="722" ht="13.5" customHeight="1" spans="1:18">
       <c r="A722" s="4"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
@@ -15239,7 +15862,7 @@
       <c r="Q722" s="4"/>
       <c r="R722" s="4"/>
     </row>
-    <row r="723" spans="1:18" ht="13.5" customHeight="1">
+    <row r="723" ht="13.5" customHeight="1" spans="1:18">
       <c r="A723" s="4"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
@@ -15259,7 +15882,7 @@
       <c r="Q723" s="4"/>
       <c r="R723" s="4"/>
     </row>
-    <row r="724" spans="1:18" ht="13.5" customHeight="1">
+    <row r="724" ht="13.5" customHeight="1" spans="1:18">
       <c r="A724" s="4"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
@@ -15279,7 +15902,7 @@
       <c r="Q724" s="4"/>
       <c r="R724" s="4"/>
     </row>
-    <row r="725" spans="1:18" ht="13.5" customHeight="1">
+    <row r="725" ht="13.5" customHeight="1" spans="1:18">
       <c r="A725" s="4"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
@@ -15299,7 +15922,7 @@
       <c r="Q725" s="4"/>
       <c r="R725" s="4"/>
     </row>
-    <row r="726" spans="1:18" ht="13.5" customHeight="1">
+    <row r="726" ht="13.5" customHeight="1" spans="1:18">
       <c r="A726" s="4"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
@@ -15319,7 +15942,7 @@
       <c r="Q726" s="4"/>
       <c r="R726" s="4"/>
     </row>
-    <row r="727" spans="1:18" ht="13.5" customHeight="1">
+    <row r="727" ht="13.5" customHeight="1" spans="1:18">
       <c r="A727" s="4"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
@@ -15339,7 +15962,7 @@
       <c r="Q727" s="4"/>
       <c r="R727" s="4"/>
     </row>
-    <row r="728" spans="1:18" ht="13.5" customHeight="1">
+    <row r="728" ht="13.5" customHeight="1" spans="1:18">
       <c r="A728" s="4"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
@@ -15359,7 +15982,7 @@
       <c r="Q728" s="4"/>
       <c r="R728" s="4"/>
     </row>
-    <row r="729" spans="1:18" ht="13.5" customHeight="1">
+    <row r="729" ht="13.5" customHeight="1" spans="1:18">
       <c r="A729" s="4"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
@@ -15379,7 +16002,7 @@
       <c r="Q729" s="4"/>
       <c r="R729" s="4"/>
     </row>
-    <row r="730" spans="1:18" ht="13.5" customHeight="1">
+    <row r="730" ht="13.5" customHeight="1" spans="1:18">
       <c r="A730" s="4"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
@@ -15399,7 +16022,7 @@
       <c r="Q730" s="4"/>
       <c r="R730" s="4"/>
     </row>
-    <row r="731" spans="1:18" ht="13.5" customHeight="1">
+    <row r="731" ht="13.5" customHeight="1" spans="1:18">
       <c r="A731" s="4"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
@@ -15419,7 +16042,7 @@
       <c r="Q731" s="4"/>
       <c r="R731" s="4"/>
     </row>
-    <row r="732" spans="1:18" ht="13.5" customHeight="1">
+    <row r="732" ht="13.5" customHeight="1" spans="1:18">
       <c r="A732" s="4"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
@@ -15439,7 +16062,7 @@
       <c r="Q732" s="4"/>
       <c r="R732" s="4"/>
     </row>
-    <row r="733" spans="1:18" ht="13.5" customHeight="1">
+    <row r="733" ht="13.5" customHeight="1" spans="1:18">
       <c r="A733" s="4"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
@@ -15459,7 +16082,7 @@
       <c r="Q733" s="4"/>
       <c r="R733" s="4"/>
     </row>
-    <row r="734" spans="1:18" ht="13.5" customHeight="1">
+    <row r="734" ht="13.5" customHeight="1" spans="1:18">
       <c r="A734" s="4"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
@@ -15479,7 +16102,7 @@
       <c r="Q734" s="4"/>
       <c r="R734" s="4"/>
     </row>
-    <row r="735" spans="1:18" ht="13.5" customHeight="1">
+    <row r="735" ht="13.5" customHeight="1" spans="1:18">
       <c r="A735" s="4"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
@@ -15499,7 +16122,7 @@
       <c r="Q735" s="4"/>
       <c r="R735" s="4"/>
     </row>
-    <row r="736" spans="1:18" ht="13.5" customHeight="1">
+    <row r="736" ht="13.5" customHeight="1" spans="1:18">
       <c r="A736" s="4"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
@@ -15519,7 +16142,7 @@
       <c r="Q736" s="4"/>
       <c r="R736" s="4"/>
     </row>
-    <row r="737" spans="1:18" ht="13.5" customHeight="1">
+    <row r="737" ht="13.5" customHeight="1" spans="1:18">
       <c r="A737" s="4"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
@@ -15539,7 +16162,7 @@
       <c r="Q737" s="4"/>
       <c r="R737" s="4"/>
     </row>
-    <row r="738" spans="1:18" ht="13.5" customHeight="1">
+    <row r="738" ht="13.5" customHeight="1" spans="1:18">
       <c r="A738" s="4"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
@@ -15559,7 +16182,7 @@
       <c r="Q738" s="4"/>
       <c r="R738" s="4"/>
     </row>
-    <row r="739" spans="1:18" ht="13.5" customHeight="1">
+    <row r="739" ht="13.5" customHeight="1" spans="1:18">
       <c r="A739" s="4"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
@@ -15579,7 +16202,7 @@
       <c r="Q739" s="4"/>
       <c r="R739" s="4"/>
     </row>
-    <row r="740" spans="1:18" ht="13.5" customHeight="1">
+    <row r="740" ht="13.5" customHeight="1" spans="1:18">
       <c r="A740" s="4"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
@@ -15599,7 +16222,7 @@
       <c r="Q740" s="4"/>
       <c r="R740" s="4"/>
     </row>
-    <row r="741" spans="1:18" ht="13.5" customHeight="1">
+    <row r="741" ht="13.5" customHeight="1" spans="1:18">
       <c r="A741" s="4"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
@@ -15619,7 +16242,7 @@
       <c r="Q741" s="4"/>
       <c r="R741" s="4"/>
     </row>
-    <row r="742" spans="1:18" ht="13.5" customHeight="1">
+    <row r="742" ht="13.5" customHeight="1" spans="1:18">
       <c r="A742" s="4"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
@@ -15639,7 +16262,7 @@
       <c r="Q742" s="4"/>
       <c r="R742" s="4"/>
     </row>
-    <row r="743" spans="1:18" ht="13.5" customHeight="1">
+    <row r="743" ht="13.5" customHeight="1" spans="1:18">
       <c r="A743" s="4"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
@@ -15659,7 +16282,7 @@
       <c r="Q743" s="4"/>
       <c r="R743" s="4"/>
     </row>
-    <row r="744" spans="1:18" ht="13.5" customHeight="1">
+    <row r="744" ht="13.5" customHeight="1" spans="1:18">
       <c r="A744" s="4"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
@@ -15679,7 +16302,7 @@
       <c r="Q744" s="4"/>
       <c r="R744" s="4"/>
     </row>
-    <row r="745" spans="1:18" ht="13.5" customHeight="1">
+    <row r="745" ht="13.5" customHeight="1" spans="1:18">
       <c r="A745" s="4"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
@@ -15699,7 +16322,7 @@
       <c r="Q745" s="4"/>
       <c r="R745" s="4"/>
     </row>
-    <row r="746" spans="1:18" ht="13.5" customHeight="1">
+    <row r="746" ht="13.5" customHeight="1" spans="1:18">
       <c r="A746" s="4"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
@@ -15719,7 +16342,7 @@
       <c r="Q746" s="4"/>
       <c r="R746" s="4"/>
     </row>
-    <row r="747" spans="1:18" ht="13.5" customHeight="1">
+    <row r="747" ht="13.5" customHeight="1" spans="1:18">
       <c r="A747" s="4"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
@@ -15739,7 +16362,7 @@
       <c r="Q747" s="4"/>
       <c r="R747" s="4"/>
     </row>
-    <row r="748" spans="1:18" ht="13.5" customHeight="1">
+    <row r="748" ht="13.5" customHeight="1" spans="1:18">
       <c r="A748" s="4"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
@@ -15759,7 +16382,7 @@
       <c r="Q748" s="4"/>
       <c r="R748" s="4"/>
     </row>
-    <row r="749" spans="1:18" ht="13.5" customHeight="1">
+    <row r="749" ht="13.5" customHeight="1" spans="1:18">
       <c r="A749" s="4"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
@@ -15779,7 +16402,7 @@
       <c r="Q749" s="4"/>
       <c r="R749" s="4"/>
     </row>
-    <row r="750" spans="1:18" ht="13.5" customHeight="1">
+    <row r="750" ht="13.5" customHeight="1" spans="1:18">
       <c r="A750" s="4"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
@@ -15799,7 +16422,7 @@
       <c r="Q750" s="4"/>
       <c r="R750" s="4"/>
     </row>
-    <row r="751" spans="1:18" ht="13.5" customHeight="1">
+    <row r="751" ht="13.5" customHeight="1" spans="1:18">
       <c r="A751" s="4"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
@@ -15819,7 +16442,7 @@
       <c r="Q751" s="4"/>
       <c r="R751" s="4"/>
     </row>
-    <row r="752" spans="1:18" ht="13.5" customHeight="1">
+    <row r="752" ht="13.5" customHeight="1" spans="1:18">
       <c r="A752" s="4"/>
       <c r="B752" s="4"/>
       <c r="C752" s="4"/>
@@ -15839,7 +16462,7 @@
       <c r="Q752" s="4"/>
       <c r="R752" s="4"/>
     </row>
-    <row r="753" spans="1:18" ht="13.5" customHeight="1">
+    <row r="753" ht="13.5" customHeight="1" spans="1:18">
       <c r="A753" s="4"/>
       <c r="B753" s="4"/>
       <c r="C753" s="4"/>
@@ -15859,7 +16482,7 @@
       <c r="Q753" s="4"/>
       <c r="R753" s="4"/>
     </row>
-    <row r="754" spans="1:18" ht="13.5" customHeight="1">
+    <row r="754" ht="13.5" customHeight="1" spans="1:18">
       <c r="A754" s="4"/>
       <c r="B754" s="4"/>
       <c r="C754" s="4"/>
@@ -15879,7 +16502,7 @@
       <c r="Q754" s="4"/>
       <c r="R754" s="4"/>
     </row>
-    <row r="755" spans="1:18" ht="13.5" customHeight="1">
+    <row r="755" ht="13.5" customHeight="1" spans="1:18">
       <c r="A755" s="4"/>
       <c r="B755" s="4"/>
       <c r="C755" s="4"/>
@@ -15899,7 +16522,7 @@
       <c r="Q755" s="4"/>
       <c r="R755" s="4"/>
     </row>
-    <row r="756" spans="1:18" ht="13.5" customHeight="1">
+    <row r="756" ht="13.5" customHeight="1" spans="1:18">
       <c r="A756" s="4"/>
       <c r="B756" s="4"/>
       <c r="C756" s="4"/>
@@ -15919,7 +16542,7 @@
       <c r="Q756" s="4"/>
       <c r="R756" s="4"/>
     </row>
-    <row r="757" spans="1:18" ht="13.5" customHeight="1">
+    <row r="757" ht="13.5" customHeight="1" spans="1:18">
       <c r="A757" s="4"/>
       <c r="B757" s="4"/>
       <c r="C757" s="4"/>
@@ -15939,7 +16562,7 @@
       <c r="Q757" s="4"/>
       <c r="R757" s="4"/>
     </row>
-    <row r="758" spans="1:18" ht="13.5" customHeight="1">
+    <row r="758" ht="13.5" customHeight="1" spans="1:18">
       <c r="A758" s="4"/>
       <c r="B758" s="4"/>
       <c r="C758" s="4"/>
@@ -15959,7 +16582,7 @@
       <c r="Q758" s="4"/>
       <c r="R758" s="4"/>
     </row>
-    <row r="759" spans="1:18" ht="13.5" customHeight="1">
+    <row r="759" ht="13.5" customHeight="1" spans="1:18">
       <c r="A759" s="4"/>
       <c r="B759" s="4"/>
       <c r="C759" s="4"/>
@@ -15979,7 +16602,7 @@
       <c r="Q759" s="4"/>
       <c r="R759" s="4"/>
     </row>
-    <row r="760" spans="1:18" ht="13.5" customHeight="1">
+    <row r="760" ht="13.5" customHeight="1" spans="1:18">
       <c r="A760" s="4"/>
       <c r="B760" s="4"/>
       <c r="C760" s="4"/>
@@ -15999,7 +16622,7 @@
       <c r="Q760" s="4"/>
       <c r="R760" s="4"/>
     </row>
-    <row r="761" spans="1:18" ht="13.5" customHeight="1">
+    <row r="761" ht="13.5" customHeight="1" spans="1:18">
       <c r="A761" s="4"/>
       <c r="B761" s="4"/>
       <c r="C761" s="4"/>
@@ -16019,7 +16642,7 @@
       <c r="Q761" s="4"/>
       <c r="R761" s="4"/>
     </row>
-    <row r="762" spans="1:18" ht="13.5" customHeight="1">
+    <row r="762" ht="13.5" customHeight="1" spans="1:18">
       <c r="A762" s="4"/>
       <c r="B762" s="4"/>
       <c r="C762" s="4"/>
@@ -16039,7 +16662,7 @@
       <c r="Q762" s="4"/>
       <c r="R762" s="4"/>
     </row>
-    <row r="763" spans="1:18" ht="13.5" customHeight="1">
+    <row r="763" ht="13.5" customHeight="1" spans="1:18">
       <c r="A763" s="4"/>
       <c r="B763" s="4"/>
       <c r="C763" s="4"/>
@@ -16059,7 +16682,7 @@
       <c r="Q763" s="4"/>
       <c r="R763" s="4"/>
     </row>
-    <row r="764" spans="1:18" ht="13.5" customHeight="1">
+    <row r="764" ht="13.5" customHeight="1" spans="1:18">
       <c r="A764" s="4"/>
       <c r="B764" s="4"/>
       <c r="C764" s="4"/>
@@ -16079,7 +16702,7 @@
       <c r="Q764" s="4"/>
       <c r="R764" s="4"/>
     </row>
-    <row r="765" spans="1:18" ht="13.5" customHeight="1">
+    <row r="765" ht="13.5" customHeight="1" spans="1:18">
       <c r="A765" s="4"/>
       <c r="B765" s="4"/>
       <c r="C765" s="4"/>
@@ -16099,7 +16722,7 @@
       <c r="Q765" s="4"/>
       <c r="R765" s="4"/>
     </row>
-    <row r="766" spans="1:18" ht="13.5" customHeight="1">
+    <row r="766" ht="13.5" customHeight="1" spans="1:18">
       <c r="A766" s="4"/>
       <c r="B766" s="4"/>
       <c r="C766" s="4"/>
@@ -16119,7 +16742,7 @@
       <c r="Q766" s="4"/>
       <c r="R766" s="4"/>
     </row>
-    <row r="767" spans="1:18" ht="13.5" customHeight="1">
+    <row r="767" ht="13.5" customHeight="1" spans="1:18">
       <c r="A767" s="4"/>
       <c r="B767" s="4"/>
       <c r="C767" s="4"/>
@@ -16139,7 +16762,7 @@
       <c r="Q767" s="4"/>
       <c r="R767" s="4"/>
     </row>
-    <row r="768" spans="1:18" ht="13.5" customHeight="1">
+    <row r="768" ht="13.5" customHeight="1" spans="1:18">
       <c r="A768" s="4"/>
       <c r="B768" s="4"/>
       <c r="C768" s="4"/>
@@ -16159,7 +16782,7 @@
       <c r="Q768" s="4"/>
       <c r="R768" s="4"/>
     </row>
-    <row r="769" spans="1:18" ht="13.5" customHeight="1">
+    <row r="769" ht="13.5" customHeight="1" spans="1:18">
       <c r="A769" s="4"/>
       <c r="B769" s="4"/>
       <c r="C769" s="4"/>
@@ -16179,7 +16802,7 @@
       <c r="Q769" s="4"/>
       <c r="R769" s="4"/>
     </row>
-    <row r="770" spans="1:18" ht="13.5" customHeight="1">
+    <row r="770" ht="13.5" customHeight="1" spans="1:18">
       <c r="A770" s="4"/>
       <c r="B770" s="4"/>
       <c r="C770" s="4"/>
@@ -16199,7 +16822,7 @@
       <c r="Q770" s="4"/>
       <c r="R770" s="4"/>
     </row>
-    <row r="771" spans="1:18" ht="13.5" customHeight="1">
+    <row r="771" ht="13.5" customHeight="1" spans="1:18">
       <c r="A771" s="4"/>
       <c r="B771" s="4"/>
       <c r="C771" s="4"/>
@@ -16219,7 +16842,7 @@
       <c r="Q771" s="4"/>
       <c r="R771" s="4"/>
     </row>
-    <row r="772" spans="1:18" ht="13.5" customHeight="1">
+    <row r="772" ht="13.5" customHeight="1" spans="1:18">
       <c r="A772" s="4"/>
       <c r="B772" s="4"/>
       <c r="C772" s="4"/>
@@ -16239,7 +16862,7 @@
       <c r="Q772" s="4"/>
       <c r="R772" s="4"/>
     </row>
-    <row r="773" spans="1:18" ht="13.5" customHeight="1">
+    <row r="773" ht="13.5" customHeight="1" spans="1:18">
       <c r="A773" s="4"/>
       <c r="B773" s="4"/>
       <c r="C773" s="4"/>
@@ -16259,7 +16882,7 @@
       <c r="Q773" s="4"/>
       <c r="R773" s="4"/>
     </row>
-    <row r="774" spans="1:18" ht="13.5" customHeight="1">
+    <row r="774" ht="13.5" customHeight="1" spans="1:18">
       <c r="A774" s="4"/>
       <c r="B774" s="4"/>
       <c r="C774" s="4"/>
@@ -16279,7 +16902,7 @@
       <c r="Q774" s="4"/>
       <c r="R774" s="4"/>
     </row>
-    <row r="775" spans="1:18" ht="13.5" customHeight="1">
+    <row r="775" ht="13.5" customHeight="1" spans="1:18">
       <c r="A775" s="4"/>
       <c r="B775" s="4"/>
       <c r="C775" s="4"/>
@@ -16299,7 +16922,7 @@
       <c r="Q775" s="4"/>
       <c r="R775" s="4"/>
     </row>
-    <row r="776" spans="1:18" ht="13.5" customHeight="1">
+    <row r="776" ht="13.5" customHeight="1" spans="1:18">
       <c r="A776" s="4"/>
       <c r="B776" s="4"/>
       <c r="C776" s="4"/>
@@ -16319,7 +16942,7 @@
       <c r="Q776" s="4"/>
       <c r="R776" s="4"/>
     </row>
-    <row r="777" spans="1:18" ht="13.5" customHeight="1">
+    <row r="777" ht="13.5" customHeight="1" spans="1:18">
       <c r="A777" s="4"/>
       <c r="B777" s="4"/>
       <c r="C777" s="4"/>
@@ -16339,7 +16962,7 @@
       <c r="Q777" s="4"/>
       <c r="R777" s="4"/>
     </row>
-    <row r="778" spans="1:18" ht="13.5" customHeight="1">
+    <row r="778" ht="13.5" customHeight="1" spans="1:18">
       <c r="A778" s="4"/>
       <c r="B778" s="4"/>
       <c r="C778" s="4"/>
@@ -16359,7 +16982,7 @@
       <c r="Q778" s="4"/>
       <c r="R778" s="4"/>
     </row>
-    <row r="779" spans="1:18" ht="13.5" customHeight="1">
+    <row r="779" ht="13.5" customHeight="1" spans="1:18">
       <c r="A779" s="4"/>
       <c r="B779" s="4"/>
       <c r="C779" s="4"/>
@@ -16379,7 +17002,7 @@
       <c r="Q779" s="4"/>
       <c r="R779" s="4"/>
     </row>
-    <row r="780" spans="1:18" ht="13.5" customHeight="1">
+    <row r="780" ht="13.5" customHeight="1" spans="1:18">
       <c r="A780" s="4"/>
       <c r="B780" s="4"/>
       <c r="C780" s="4"/>
@@ -16399,7 +17022,7 @@
       <c r="Q780" s="4"/>
       <c r="R780" s="4"/>
     </row>
-    <row r="781" spans="1:18" ht="13.5" customHeight="1">
+    <row r="781" ht="13.5" customHeight="1" spans="1:18">
       <c r="A781" s="4"/>
       <c r="B781" s="4"/>
       <c r="C781" s="4"/>
@@ -16419,7 +17042,7 @@
       <c r="Q781" s="4"/>
       <c r="R781" s="4"/>
     </row>
-    <row r="782" spans="1:18" ht="13.5" customHeight="1">
+    <row r="782" ht="13.5" customHeight="1" spans="1:18">
       <c r="A782" s="4"/>
       <c r="B782" s="4"/>
       <c r="C782" s="4"/>
@@ -16439,7 +17062,7 @@
       <c r="Q782" s="4"/>
       <c r="R782" s="4"/>
     </row>
-    <row r="783" spans="1:18" ht="13.5" customHeight="1">
+    <row r="783" ht="13.5" customHeight="1" spans="1:18">
       <c r="A783" s="4"/>
       <c r="B783" s="4"/>
       <c r="C783" s="4"/>
@@ -16459,7 +17082,7 @@
       <c r="Q783" s="4"/>
       <c r="R783" s="4"/>
     </row>
-    <row r="784" spans="1:18" ht="13.5" customHeight="1">
+    <row r="784" ht="13.5" customHeight="1" spans="1:18">
       <c r="A784" s="4"/>
       <c r="B784" s="4"/>
       <c r="C784" s="4"/>
@@ -16479,7 +17102,7 @@
       <c r="Q784" s="4"/>
       <c r="R784" s="4"/>
     </row>
-    <row r="785" spans="1:18" ht="13.5" customHeight="1">
+    <row r="785" ht="13.5" customHeight="1" spans="1:18">
       <c r="A785" s="4"/>
       <c r="B785" s="4"/>
       <c r="C785" s="4"/>
@@ -16499,7 +17122,7 @@
       <c r="Q785" s="4"/>
       <c r="R785" s="4"/>
     </row>
-    <row r="786" spans="1:18" ht="13.5" customHeight="1">
+    <row r="786" ht="13.5" customHeight="1" spans="1:18">
       <c r="A786" s="4"/>
       <c r="B786" s="4"/>
       <c r="C786" s="4"/>
@@ -16519,7 +17142,7 @@
       <c r="Q786" s="4"/>
       <c r="R786" s="4"/>
     </row>
-    <row r="787" spans="1:18" ht="13.5" customHeight="1">
+    <row r="787" ht="13.5" customHeight="1" spans="1:18">
       <c r="A787" s="4"/>
       <c r="B787" s="4"/>
       <c r="C787" s="4"/>
@@ -16539,7 +17162,7 @@
       <c r="Q787" s="4"/>
       <c r="R787" s="4"/>
     </row>
-    <row r="788" spans="1:18" ht="13.5" customHeight="1">
+    <row r="788" ht="13.5" customHeight="1" spans="1:18">
       <c r="A788" s="4"/>
       <c r="B788" s="4"/>
       <c r="C788" s="4"/>
@@ -16559,7 +17182,7 @@
       <c r="Q788" s="4"/>
       <c r="R788" s="4"/>
     </row>
-    <row r="789" spans="1:18" ht="13.5" customHeight="1">
+    <row r="789" ht="13.5" customHeight="1" spans="1:18">
       <c r="A789" s="4"/>
       <c r="B789" s="4"/>
       <c r="C789" s="4"/>
@@ -16579,7 +17202,7 @@
       <c r="Q789" s="4"/>
       <c r="R789" s="4"/>
     </row>
-    <row r="790" spans="1:18" ht="13.5" customHeight="1">
+    <row r="790" ht="13.5" customHeight="1" spans="1:18">
       <c r="A790" s="4"/>
       <c r="B790" s="4"/>
       <c r="C790" s="4"/>
@@ -16599,7 +17222,7 @@
       <c r="Q790" s="4"/>
       <c r="R790" s="4"/>
     </row>
-    <row r="791" spans="1:18" ht="13.5" customHeight="1">
+    <row r="791" ht="13.5" customHeight="1" spans="1:18">
       <c r="A791" s="4"/>
       <c r="B791" s="4"/>
       <c r="C791" s="4"/>
@@ -16619,7 +17242,7 @@
       <c r="Q791" s="4"/>
       <c r="R791" s="4"/>
     </row>
-    <row r="792" spans="1:18" ht="13.5" customHeight="1">
+    <row r="792" ht="13.5" customHeight="1" spans="1:18">
       <c r="A792" s="4"/>
       <c r="B792" s="4"/>
       <c r="C792" s="4"/>
@@ -16639,7 +17262,7 @@
       <c r="Q792" s="4"/>
       <c r="R792" s="4"/>
     </row>
-    <row r="793" spans="1:18" ht="13.5" customHeight="1">
+    <row r="793" ht="13.5" customHeight="1" spans="1:18">
       <c r="A793" s="4"/>
       <c r="B793" s="4"/>
       <c r="C793" s="4"/>
@@ -16659,7 +17282,7 @@
       <c r="Q793" s="4"/>
       <c r="R793" s="4"/>
     </row>
-    <row r="794" spans="1:18" ht="13.5" customHeight="1">
+    <row r="794" ht="13.5" customHeight="1" spans="1:18">
       <c r="A794" s="4"/>
       <c r="B794" s="4"/>
       <c r="C794" s="4"/>
@@ -16679,7 +17302,7 @@
       <c r="Q794" s="4"/>
       <c r="R794" s="4"/>
     </row>
-    <row r="795" spans="1:18" ht="13.5" customHeight="1">
+    <row r="795" ht="13.5" customHeight="1" spans="1:18">
       <c r="A795" s="4"/>
       <c r="B795" s="4"/>
       <c r="C795" s="4"/>
@@ -16699,7 +17322,7 @@
       <c r="Q795" s="4"/>
       <c r="R795" s="4"/>
     </row>
-    <row r="796" spans="1:18" ht="13.5" customHeight="1">
+    <row r="796" ht="13.5" customHeight="1" spans="1:18">
       <c r="A796" s="4"/>
       <c r="B796" s="4"/>
       <c r="C796" s="4"/>
@@ -16719,7 +17342,7 @@
       <c r="Q796" s="4"/>
       <c r="R796" s="4"/>
     </row>
-    <row r="797" spans="1:18" ht="13.5" customHeight="1">
+    <row r="797" ht="13.5" customHeight="1" spans="1:18">
       <c r="A797" s="4"/>
       <c r="B797" s="4"/>
       <c r="C797" s="4"/>
@@ -16739,7 +17362,7 @@
       <c r="Q797" s="4"/>
       <c r="R797" s="4"/>
     </row>
-    <row r="798" spans="1:18" ht="13.5" customHeight="1">
+    <row r="798" ht="13.5" customHeight="1" spans="1:18">
       <c r="A798" s="4"/>
       <c r="B798" s="4"/>
       <c r="C798" s="4"/>
@@ -16759,7 +17382,7 @@
       <c r="Q798" s="4"/>
       <c r="R798" s="4"/>
     </row>
-    <row r="799" spans="1:18" ht="13.5" customHeight="1">
+    <row r="799" ht="13.5" customHeight="1" spans="1:18">
       <c r="A799" s="4"/>
       <c r="B799" s="4"/>
       <c r="C799" s="4"/>
@@ -16779,7 +17402,7 @@
       <c r="Q799" s="4"/>
       <c r="R799" s="4"/>
     </row>
-    <row r="800" spans="1:18" ht="13.5" customHeight="1">
+    <row r="800" ht="13.5" customHeight="1" spans="1:18">
       <c r="A800" s="4"/>
       <c r="B800" s="4"/>
       <c r="C800" s="4"/>
@@ -16799,7 +17422,7 @@
       <c r="Q800" s="4"/>
       <c r="R800" s="4"/>
     </row>
-    <row r="801" spans="1:18" ht="13.5" customHeight="1">
+    <row r="801" ht="13.5" customHeight="1" spans="1:18">
       <c r="A801" s="4"/>
       <c r="B801" s="4"/>
       <c r="C801" s="4"/>
@@ -16819,7 +17442,7 @@
       <c r="Q801" s="4"/>
       <c r="R801" s="4"/>
     </row>
-    <row r="802" spans="1:18" ht="13.5" customHeight="1">
+    <row r="802" ht="13.5" customHeight="1" spans="1:18">
       <c r="A802" s="4"/>
       <c r="B802" s="4"/>
       <c r="C802" s="4"/>
@@ -16839,7 +17462,7 @@
       <c r="Q802" s="4"/>
       <c r="R802" s="4"/>
     </row>
-    <row r="803" spans="1:18" ht="13.5" customHeight="1">
+    <row r="803" ht="13.5" customHeight="1" spans="1:18">
       <c r="A803" s="4"/>
       <c r="B803" s="4"/>
       <c r="C803" s="4"/>
@@ -16859,7 +17482,7 @@
       <c r="Q803" s="4"/>
       <c r="R803" s="4"/>
     </row>
-    <row r="804" spans="1:18" ht="13.5" customHeight="1">
+    <row r="804" ht="13.5" customHeight="1" spans="1:18">
       <c r="A804" s="4"/>
       <c r="B804" s="4"/>
       <c r="C804" s="4"/>
@@ -16879,7 +17502,7 @@
       <c r="Q804" s="4"/>
       <c r="R804" s="4"/>
     </row>
-    <row r="805" spans="1:18" ht="13.5" customHeight="1">
+    <row r="805" ht="13.5" customHeight="1" spans="1:18">
       <c r="A805" s="4"/>
       <c r="B805" s="4"/>
       <c r="C805" s="4"/>
@@ -16899,7 +17522,7 @@
       <c r="Q805" s="4"/>
       <c r="R805" s="4"/>
     </row>
-    <row r="806" spans="1:18" ht="13.5" customHeight="1">
+    <row r="806" ht="13.5" customHeight="1" spans="1:18">
       <c r="A806" s="4"/>
       <c r="B806" s="4"/>
       <c r="C806" s="4"/>
@@ -16919,7 +17542,7 @@
       <c r="Q806" s="4"/>
       <c r="R806" s="4"/>
     </row>
-    <row r="807" spans="1:18" ht="13.5" customHeight="1">
+    <row r="807" ht="13.5" customHeight="1" spans="1:18">
       <c r="A807" s="4"/>
       <c r="B807" s="4"/>
       <c r="C807" s="4"/>
@@ -16939,7 +17562,7 @@
       <c r="Q807" s="4"/>
       <c r="R807" s="4"/>
     </row>
-    <row r="808" spans="1:18" ht="13.5" customHeight="1">
+    <row r="808" ht="13.5" customHeight="1" spans="1:18">
       <c r="A808" s="4"/>
       <c r="B808" s="4"/>
       <c r="C808" s="4"/>
@@ -16959,7 +17582,7 @@
       <c r="Q808" s="4"/>
       <c r="R808" s="4"/>
     </row>
-    <row r="809" spans="1:18" ht="13.5" customHeight="1">
+    <row r="809" ht="13.5" customHeight="1" spans="1:18">
       <c r="A809" s="4"/>
       <c r="B809" s="4"/>
       <c r="C809" s="4"/>
@@ -16979,7 +17602,7 @@
       <c r="Q809" s="4"/>
       <c r="R809" s="4"/>
     </row>
-    <row r="810" spans="1:18" ht="13.5" customHeight="1">
+    <row r="810" ht="13.5" customHeight="1" spans="1:18">
       <c r="A810" s="4"/>
       <c r="B810" s="4"/>
       <c r="C810" s="4"/>
@@ -16999,7 +17622,7 @@
       <c r="Q810" s="4"/>
       <c r="R810" s="4"/>
     </row>
-    <row r="811" spans="1:18" ht="13.5" customHeight="1">
+    <row r="811" ht="13.5" customHeight="1" spans="1:18">
       <c r="A811" s="4"/>
       <c r="B811" s="4"/>
       <c r="C811" s="4"/>
@@ -17019,7 +17642,7 @@
       <c r="Q811" s="4"/>
       <c r="R811" s="4"/>
     </row>
-    <row r="812" spans="1:18" ht="13.5" customHeight="1">
+    <row r="812" ht="13.5" customHeight="1" spans="1:18">
       <c r="A812" s="4"/>
       <c r="B812" s="4"/>
       <c r="C812" s="4"/>
@@ -17039,7 +17662,7 @@
       <c r="Q812" s="4"/>
       <c r="R812" s="4"/>
     </row>
-    <row r="813" spans="1:18" ht="13.5" customHeight="1">
+    <row r="813" ht="13.5" customHeight="1" spans="1:18">
       <c r="A813" s="4"/>
       <c r="B813" s="4"/>
       <c r="C813" s="4"/>
@@ -17059,7 +17682,7 @@
       <c r="Q813" s="4"/>
       <c r="R813" s="4"/>
     </row>
-    <row r="814" spans="1:18" ht="13.5" customHeight="1">
+    <row r="814" ht="13.5" customHeight="1" spans="1:18">
       <c r="A814" s="4"/>
       <c r="B814" s="4"/>
       <c r="C814" s="4"/>
@@ -17079,7 +17702,7 @@
       <c r="Q814" s="4"/>
       <c r="R814" s="4"/>
     </row>
-    <row r="815" spans="1:18" ht="13.5" customHeight="1">
+    <row r="815" ht="13.5" customHeight="1" spans="1:18">
       <c r="A815" s="4"/>
       <c r="B815" s="4"/>
       <c r="C815" s="4"/>
@@ -17099,7 +17722,7 @@
       <c r="Q815" s="4"/>
       <c r="R815" s="4"/>
     </row>
-    <row r="816" spans="1:18" ht="13.5" customHeight="1">
+    <row r="816" ht="13.5" customHeight="1" spans="1:18">
       <c r="A816" s="4"/>
       <c r="B816" s="4"/>
       <c r="C816" s="4"/>
@@ -17119,7 +17742,7 @@
       <c r="Q816" s="4"/>
       <c r="R816" s="4"/>
     </row>
-    <row r="817" spans="1:18" ht="13.5" customHeight="1">
+    <row r="817" ht="13.5" customHeight="1" spans="1:18">
       <c r="A817" s="4"/>
       <c r="B817" s="4"/>
       <c r="C817" s="4"/>
@@ -17139,7 +17762,7 @@
       <c r="Q817" s="4"/>
       <c r="R817" s="4"/>
     </row>
-    <row r="818" spans="1:18" ht="13.5" customHeight="1">
+    <row r="818" ht="13.5" customHeight="1" spans="1:18">
       <c r="A818" s="4"/>
       <c r="B818" s="4"/>
       <c r="C818" s="4"/>
@@ -17159,7 +17782,7 @@
       <c r="Q818" s="4"/>
       <c r="R818" s="4"/>
     </row>
-    <row r="819" spans="1:18" ht="13.5" customHeight="1">
+    <row r="819" ht="13.5" customHeight="1" spans="1:18">
       <c r="A819" s="4"/>
       <c r="B819" s="4"/>
       <c r="C819" s="4"/>
@@ -17179,7 +17802,7 @@
       <c r="Q819" s="4"/>
       <c r="R819" s="4"/>
     </row>
-    <row r="820" spans="1:18" ht="13.5" customHeight="1">
+    <row r="820" ht="13.5" customHeight="1" spans="1:18">
       <c r="A820" s="4"/>
       <c r="B820" s="4"/>
       <c r="C820" s="4"/>
@@ -17199,7 +17822,7 @@
       <c r="Q820" s="4"/>
       <c r="R820" s="4"/>
     </row>
-    <row r="821" spans="1:18" ht="13.5" customHeight="1">
+    <row r="821" ht="13.5" customHeight="1" spans="1:18">
       <c r="A821" s="4"/>
       <c r="B821" s="4"/>
       <c r="C821" s="4"/>
@@ -17219,7 +17842,7 @@
       <c r="Q821" s="4"/>
       <c r="R821" s="4"/>
     </row>
-    <row r="822" spans="1:18" ht="13.5" customHeight="1">
+    <row r="822" ht="13.5" customHeight="1" spans="1:18">
       <c r="A822" s="4"/>
       <c r="B822" s="4"/>
       <c r="C822" s="4"/>
@@ -17239,7 +17862,7 @@
       <c r="Q822" s="4"/>
       <c r="R822" s="4"/>
     </row>
-    <row r="823" spans="1:18" ht="13.5" customHeight="1">
+    <row r="823" ht="13.5" customHeight="1" spans="1:18">
       <c r="A823" s="4"/>
       <c r="B823" s="4"/>
       <c r="C823" s="4"/>
@@ -17259,7 +17882,7 @@
       <c r="Q823" s="4"/>
       <c r="R823" s="4"/>
     </row>
-    <row r="824" spans="1:18" ht="13.5" customHeight="1">
+    <row r="824" ht="13.5" customHeight="1" spans="1:18">
       <c r="A824" s="4"/>
       <c r="B824" s="4"/>
       <c r="C824" s="4"/>
@@ -17279,7 +17902,7 @@
       <c r="Q824" s="4"/>
       <c r="R824" s="4"/>
     </row>
-    <row r="825" spans="1:18" ht="13.5" customHeight="1">
+    <row r="825" ht="13.5" customHeight="1" spans="1:18">
       <c r="A825" s="4"/>
       <c r="B825" s="4"/>
       <c r="C825" s="4"/>
@@ -17299,7 +17922,7 @@
       <c r="Q825" s="4"/>
       <c r="R825" s="4"/>
     </row>
-    <row r="826" spans="1:18" ht="13.5" customHeight="1">
+    <row r="826" ht="13.5" customHeight="1" spans="1:18">
       <c r="A826" s="4"/>
       <c r="B826" s="4"/>
       <c r="C826" s="4"/>
@@ -17319,7 +17942,7 @@
       <c r="Q826" s="4"/>
       <c r="R826" s="4"/>
     </row>
-    <row r="827" spans="1:18" ht="13.5" customHeight="1">
+    <row r="827" ht="13.5" customHeight="1" spans="1:18">
       <c r="A827" s="4"/>
       <c r="B827" s="4"/>
       <c r="C827" s="4"/>
@@ -17339,7 +17962,7 @@
       <c r="Q827" s="4"/>
       <c r="R827" s="4"/>
     </row>
-    <row r="828" spans="1:18" ht="13.5" customHeight="1">
+    <row r="828" ht="13.5" customHeight="1" spans="1:18">
       <c r="A828" s="4"/>
       <c r="B828" s="4"/>
       <c r="C828" s="4"/>
@@ -17359,7 +17982,7 @@
       <c r="Q828" s="4"/>
       <c r="R828" s="4"/>
     </row>
-    <row r="829" spans="1:18" ht="13.5" customHeight="1">
+    <row r="829" ht="13.5" customHeight="1" spans="1:18">
       <c r="A829" s="4"/>
       <c r="B829" s="4"/>
       <c r="C829" s="4"/>
@@ -17379,7 +18002,7 @@
       <c r="Q829" s="4"/>
       <c r="R829" s="4"/>
     </row>
-    <row r="830" spans="1:18" ht="13.5" customHeight="1">
+    <row r="830" ht="13.5" customHeight="1" spans="1:18">
       <c r="A830" s="4"/>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
@@ -17399,7 +18022,7 @@
       <c r="Q830" s="4"/>
       <c r="R830" s="4"/>
     </row>
-    <row r="831" spans="1:18" ht="13.5" customHeight="1">
+    <row r="831" ht="13.5" customHeight="1" spans="1:18">
       <c r="A831" s="4"/>
       <c r="B831" s="4"/>
       <c r="C831" s="4"/>
@@ -17419,7 +18042,7 @@
       <c r="Q831" s="4"/>
       <c r="R831" s="4"/>
     </row>
-    <row r="832" spans="1:18" ht="13.5" customHeight="1">
+    <row r="832" ht="13.5" customHeight="1" spans="1:18">
       <c r="A832" s="4"/>
       <c r="B832" s="4"/>
       <c r="C832" s="4"/>
@@ -17439,7 +18062,7 @@
       <c r="Q832" s="4"/>
       <c r="R832" s="4"/>
     </row>
-    <row r="833" spans="1:18" ht="13.5" customHeight="1">
+    <row r="833" ht="13.5" customHeight="1" spans="1:18">
       <c r="A833" s="4"/>
       <c r="B833" s="4"/>
       <c r="C833" s="4"/>
@@ -17459,7 +18082,7 @@
       <c r="Q833" s="4"/>
       <c r="R833" s="4"/>
     </row>
-    <row r="834" spans="1:18" ht="13.5" customHeight="1">
+    <row r="834" ht="13.5" customHeight="1" spans="1:18">
       <c r="A834" s="4"/>
       <c r="B834" s="4"/>
       <c r="C834" s="4"/>
@@ -17479,7 +18102,7 @@
       <c r="Q834" s="4"/>
       <c r="R834" s="4"/>
     </row>
-    <row r="835" spans="1:18" ht="13.5" customHeight="1">
+    <row r="835" ht="13.5" customHeight="1" spans="1:18">
       <c r="A835" s="4"/>
       <c r="B835" s="4"/>
       <c r="C835" s="4"/>
@@ -17499,7 +18122,7 @@
       <c r="Q835" s="4"/>
       <c r="R835" s="4"/>
     </row>
-    <row r="836" spans="1:18" ht="13.5" customHeight="1">
+    <row r="836" ht="13.5" customHeight="1" spans="1:18">
       <c r="A836" s="4"/>
       <c r="B836" s="4"/>
       <c r="C836" s="4"/>
@@ -17519,7 +18142,7 @@
       <c r="Q836" s="4"/>
       <c r="R836" s="4"/>
     </row>
-    <row r="837" spans="1:18" ht="13.5" customHeight="1">
+    <row r="837" ht="13.5" customHeight="1" spans="1:18">
       <c r="A837" s="4"/>
       <c r="B837" s="4"/>
       <c r="C837" s="4"/>
@@ -17539,7 +18162,7 @@
       <c r="Q837" s="4"/>
       <c r="R837" s="4"/>
     </row>
-    <row r="838" spans="1:18" ht="13.5" customHeight="1">
+    <row r="838" ht="13.5" customHeight="1" spans="1:18">
       <c r="A838" s="4"/>
       <c r="B838" s="4"/>
       <c r="C838" s="4"/>
@@ -17559,7 +18182,7 @@
       <c r="Q838" s="4"/>
       <c r="R838" s="4"/>
     </row>
-    <row r="839" spans="1:18" ht="13.5" customHeight="1">
+    <row r="839" ht="13.5" customHeight="1" spans="1:18">
       <c r="A839" s="4"/>
       <c r="B839" s="4"/>
       <c r="C839" s="4"/>
@@ -17579,7 +18202,7 @@
       <c r="Q839" s="4"/>
       <c r="R839" s="4"/>
     </row>
-    <row r="840" spans="1:18" ht="13.5" customHeight="1">
+    <row r="840" ht="13.5" customHeight="1" spans="1:18">
       <c r="A840" s="4"/>
       <c r="B840" s="4"/>
       <c r="C840" s="4"/>
@@ -17599,7 +18222,7 @@
       <c r="Q840" s="4"/>
       <c r="R840" s="4"/>
     </row>
-    <row r="841" spans="1:18" ht="13.5" customHeight="1">
+    <row r="841" ht="13.5" customHeight="1" spans="1:18">
       <c r="A841" s="4"/>
       <c r="B841" s="4"/>
       <c r="C841" s="4"/>
@@ -17619,7 +18242,7 @@
       <c r="Q841" s="4"/>
       <c r="R841" s="4"/>
     </row>
-    <row r="842" spans="1:18" ht="13.5" customHeight="1">
+    <row r="842" ht="13.5" customHeight="1" spans="1:18">
       <c r="A842" s="4"/>
       <c r="B842" s="4"/>
       <c r="C842" s="4"/>
@@ -17639,7 +18262,7 @@
       <c r="Q842" s="4"/>
       <c r="R842" s="4"/>
     </row>
-    <row r="843" spans="1:18" ht="13.5" customHeight="1">
+    <row r="843" ht="13.5" customHeight="1" spans="1:18">
       <c r="A843" s="4"/>
       <c r="B843" s="4"/>
       <c r="C843" s="4"/>
@@ -17659,7 +18282,7 @@
       <c r="Q843" s="4"/>
       <c r="R843" s="4"/>
     </row>
-    <row r="844" spans="1:18" ht="13.5" customHeight="1">
+    <row r="844" ht="13.5" customHeight="1" spans="1:18">
       <c r="A844" s="4"/>
       <c r="B844" s="4"/>
       <c r="C844" s="4"/>
@@ -17679,7 +18302,7 @@
       <c r="Q844" s="4"/>
       <c r="R844" s="4"/>
     </row>
-    <row r="845" spans="1:18" ht="13.5" customHeight="1">
+    <row r="845" ht="13.5" customHeight="1" spans="1:18">
       <c r="A845" s="4"/>
       <c r="B845" s="4"/>
       <c r="C845" s="4"/>
@@ -17699,7 +18322,7 @@
       <c r="Q845" s="4"/>
       <c r="R845" s="4"/>
     </row>
-    <row r="846" spans="1:18" ht="13.5" customHeight="1">
+    <row r="846" ht="13.5" customHeight="1" spans="1:18">
       <c r="A846" s="4"/>
       <c r="B846" s="4"/>
       <c r="C846" s="4"/>
@@ -17719,7 +18342,7 @@
       <c r="Q846" s="4"/>
       <c r="R846" s="4"/>
     </row>
-    <row r="847" spans="1:18" ht="13.5" customHeight="1">
+    <row r="847" ht="13.5" customHeight="1" spans="1:18">
       <c r="A847" s="4"/>
       <c r="B847" s="4"/>
       <c r="C847" s="4"/>
@@ -17739,7 +18362,7 @@
       <c r="Q847" s="4"/>
       <c r="R847" s="4"/>
     </row>
-    <row r="848" spans="1:18" ht="13.5" customHeight="1">
+    <row r="848" ht="13.5" customHeight="1" spans="1:18">
       <c r="A848" s="4"/>
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
@@ -17759,7 +18382,7 @@
       <c r="Q848" s="4"/>
       <c r="R848" s="4"/>
     </row>
-    <row r="849" spans="1:18" ht="13.5" customHeight="1">
+    <row r="849" ht="13.5" customHeight="1" spans="1:18">
       <c r="A849" s="4"/>
       <c r="B849" s="4"/>
       <c r="C849" s="4"/>
@@ -17779,7 +18402,7 @@
       <c r="Q849" s="4"/>
       <c r="R849" s="4"/>
     </row>
-    <row r="850" spans="1:18" ht="13.5" customHeight="1">
+    <row r="850" ht="13.5" customHeight="1" spans="1:18">
       <c r="A850" s="4"/>
       <c r="B850" s="4"/>
       <c r="C850" s="4"/>
@@ -17799,7 +18422,7 @@
       <c r="Q850" s="4"/>
       <c r="R850" s="4"/>
     </row>
-    <row r="851" spans="1:18" ht="13.5" customHeight="1">
+    <row r="851" ht="13.5" customHeight="1" spans="1:18">
       <c r="A851" s="4"/>
       <c r="B851" s="4"/>
       <c r="C851" s="4"/>
@@ -17819,7 +18442,7 @@
       <c r="Q851" s="4"/>
       <c r="R851" s="4"/>
     </row>
-    <row r="852" spans="1:18" ht="13.5" customHeight="1">
+    <row r="852" ht="13.5" customHeight="1" spans="1:18">
       <c r="A852" s="4"/>
       <c r="B852" s="4"/>
       <c r="C852" s="4"/>
@@ -17839,7 +18462,7 @@
       <c r="Q852" s="4"/>
       <c r="R852" s="4"/>
     </row>
-    <row r="853" spans="1:18" ht="13.5" customHeight="1">
+    <row r="853" ht="13.5" customHeight="1" spans="1:18">
       <c r="A853" s="4"/>
       <c r="B853" s="4"/>
       <c r="C853" s="4"/>
@@ -17859,7 +18482,7 @@
       <c r="Q853" s="4"/>
       <c r="R853" s="4"/>
     </row>
-    <row r="854" spans="1:18" ht="13.5" customHeight="1">
+    <row r="854" ht="13.5" customHeight="1" spans="1:18">
       <c r="A854" s="4"/>
       <c r="B854" s="4"/>
       <c r="C854" s="4"/>
@@ -17879,7 +18502,7 @@
       <c r="Q854" s="4"/>
       <c r="R854" s="4"/>
     </row>
-    <row r="855" spans="1:18" ht="13.5" customHeight="1">
+    <row r="855" ht="13.5" customHeight="1" spans="1:18">
       <c r="A855" s="4"/>
       <c r="B855" s="4"/>
       <c r="C855" s="4"/>
@@ -17899,7 +18522,7 @@
       <c r="Q855" s="4"/>
       <c r="R855" s="4"/>
     </row>
-    <row r="856" spans="1:18" ht="13.5" customHeight="1">
+    <row r="856" ht="13.5" customHeight="1" spans="1:18">
       <c r="A856" s="4"/>
       <c r="B856" s="4"/>
       <c r="C856" s="4"/>
@@ -17919,7 +18542,7 @@
       <c r="Q856" s="4"/>
       <c r="R856" s="4"/>
     </row>
-    <row r="857" spans="1:18" ht="13.5" customHeight="1">
+    <row r="857" ht="13.5" customHeight="1" spans="1:18">
       <c r="A857" s="4"/>
       <c r="B857" s="4"/>
       <c r="C857" s="4"/>
@@ -17939,7 +18562,7 @@
       <c r="Q857" s="4"/>
       <c r="R857" s="4"/>
     </row>
-    <row r="858" spans="1:18" ht="13.5" customHeight="1">
+    <row r="858" ht="13.5" customHeight="1" spans="1:18">
       <c r="A858" s="4"/>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
@@ -17959,7 +18582,7 @@
       <c r="Q858" s="4"/>
       <c r="R858" s="4"/>
     </row>
-    <row r="859" spans="1:18" ht="13.5" customHeight="1">
+    <row r="859" ht="13.5" customHeight="1" spans="1:18">
       <c r="A859" s="4"/>
       <c r="B859" s="4"/>
       <c r="C859" s="4"/>
@@ -17979,7 +18602,7 @@
       <c r="Q859" s="4"/>
       <c r="R859" s="4"/>
     </row>
-    <row r="860" spans="1:18" ht="13.5" customHeight="1">
+    <row r="860" ht="13.5" customHeight="1" spans="1:18">
       <c r="A860" s="4"/>
       <c r="B860" s="4"/>
       <c r="C860" s="4"/>
@@ -17999,7 +18622,7 @@
       <c r="Q860" s="4"/>
       <c r="R860" s="4"/>
     </row>
-    <row r="861" spans="1:18" ht="13.5" customHeight="1">
+    <row r="861" ht="13.5" customHeight="1" spans="1:18">
       <c r="A861" s="4"/>
       <c r="B861" s="4"/>
       <c r="C861" s="4"/>
@@ -18019,7 +18642,7 @@
       <c r="Q861" s="4"/>
       <c r="R861" s="4"/>
     </row>
-    <row r="862" spans="1:18" ht="13.5" customHeight="1">
+    <row r="862" ht="13.5" customHeight="1" spans="1:18">
       <c r="A862" s="4"/>
       <c r="B862" s="4"/>
       <c r="C862" s="4"/>
@@ -18039,7 +18662,7 @@
       <c r="Q862" s="4"/>
       <c r="R862" s="4"/>
     </row>
-    <row r="863" spans="1:18" ht="13.5" customHeight="1">
+    <row r="863" ht="13.5" customHeight="1" spans="1:18">
       <c r="A863" s="4"/>
       <c r="B863" s="4"/>
       <c r="C863" s="4"/>
@@ -18059,7 +18682,7 @@
       <c r="Q863" s="4"/>
       <c r="R863" s="4"/>
     </row>
-    <row r="864" spans="1:18" ht="13.5" customHeight="1">
+    <row r="864" ht="13.5" customHeight="1" spans="1:18">
       <c r="A864" s="4"/>
       <c r="B864" s="4"/>
       <c r="C864" s="4"/>
@@ -18079,7 +18702,7 @@
       <c r="Q864" s="4"/>
       <c r="R864" s="4"/>
     </row>
-    <row r="865" spans="1:18" ht="13.5" customHeight="1">
+    <row r="865" ht="13.5" customHeight="1" spans="1:18">
       <c r="A865" s="4"/>
       <c r="B865" s="4"/>
       <c r="C865" s="4"/>
@@ -18099,7 +18722,7 @@
       <c r="Q865" s="4"/>
       <c r="R865" s="4"/>
     </row>
-    <row r="866" spans="1:18" ht="13.5" customHeight="1">
+    <row r="866" ht="13.5" customHeight="1" spans="1:18">
       <c r="A866" s="4"/>
       <c r="B866" s="4"/>
       <c r="C866" s="4"/>
@@ -18119,7 +18742,7 @@
       <c r="Q866" s="4"/>
       <c r="R866" s="4"/>
     </row>
-    <row r="867" spans="1:18" ht="13.5" customHeight="1">
+    <row r="867" ht="13.5" customHeight="1" spans="1:18">
       <c r="A867" s="4"/>
       <c r="B867" s="4"/>
       <c r="C867" s="4"/>
@@ -18139,7 +18762,7 @@
       <c r="Q867" s="4"/>
       <c r="R867" s="4"/>
     </row>
-    <row r="868" spans="1:18" ht="13.5" customHeight="1">
+    <row r="868" ht="13.5" customHeight="1" spans="1:18">
       <c r="A868" s="4"/>
       <c r="B868" s="4"/>
       <c r="C868" s="4"/>
@@ -18159,7 +18782,7 @@
       <c r="Q868" s="4"/>
       <c r="R868" s="4"/>
     </row>
-    <row r="869" spans="1:18" ht="13.5" customHeight="1">
+    <row r="869" ht="13.5" customHeight="1" spans="1:18">
       <c r="A869" s="4"/>
       <c r="B869" s="4"/>
       <c r="C869" s="4"/>
@@ -18179,7 +18802,7 @@
       <c r="Q869" s="4"/>
       <c r="R869" s="4"/>
     </row>
-    <row r="870" spans="1:18" ht="13.5" customHeight="1">
+    <row r="870" ht="13.5" customHeight="1" spans="1:18">
       <c r="A870" s="4"/>
       <c r="B870" s="4"/>
       <c r="C870" s="4"/>
@@ -18199,7 +18822,7 @@
       <c r="Q870" s="4"/>
       <c r="R870" s="4"/>
     </row>
-    <row r="871" spans="1:18" ht="13.5" customHeight="1">
+    <row r="871" ht="13.5" customHeight="1" spans="1:18">
       <c r="A871" s="4"/>
       <c r="B871" s="4"/>
       <c r="C871" s="4"/>
@@ -18219,7 +18842,7 @@
       <c r="Q871" s="4"/>
       <c r="R871" s="4"/>
     </row>
-    <row r="872" spans="1:18" ht="13.5" customHeight="1">
+    <row r="872" ht="13.5" customHeight="1" spans="1:18">
       <c r="A872" s="4"/>
       <c r="B872" s="4"/>
       <c r="C872" s="4"/>
@@ -18239,7 +18862,7 @@
       <c r="Q872" s="4"/>
       <c r="R872" s="4"/>
     </row>
-    <row r="873" spans="1:18" ht="13.5" customHeight="1">
+    <row r="873" ht="13.5" customHeight="1" spans="1:18">
       <c r="A873" s="4"/>
       <c r="B873" s="4"/>
       <c r="C873" s="4"/>
@@ -18259,7 +18882,7 @@
       <c r="Q873" s="4"/>
       <c r="R873" s="4"/>
     </row>
-    <row r="874" spans="1:18" ht="13.5" customHeight="1">
+    <row r="874" ht="13.5" customHeight="1" spans="1:18">
       <c r="A874" s="4"/>
       <c r="B874" s="4"/>
       <c r="C874" s="4"/>
@@ -18279,7 +18902,7 @@
       <c r="Q874" s="4"/>
       <c r="R874" s="4"/>
     </row>
-    <row r="875" spans="1:18" ht="13.5" customHeight="1">
+    <row r="875" ht="13.5" customHeight="1" spans="1:18">
       <c r="A875" s="4"/>
       <c r="B875" s="4"/>
       <c r="C875" s="4"/>
@@ -18299,7 +18922,7 @@
       <c r="Q875" s="4"/>
       <c r="R875" s="4"/>
     </row>
-    <row r="876" spans="1:18" ht="13.5" customHeight="1">
+    <row r="876" ht="13.5" customHeight="1" spans="1:18">
       <c r="A876" s="4"/>
       <c r="B876" s="4"/>
       <c r="C876" s="4"/>
@@ -18319,7 +18942,7 @@
       <c r="Q876" s="4"/>
       <c r="R876" s="4"/>
     </row>
-    <row r="877" spans="1:18" ht="13.5" customHeight="1">
+    <row r="877" ht="13.5" customHeight="1" spans="1:18">
       <c r="A877" s="4"/>
       <c r="B877" s="4"/>
       <c r="C877" s="4"/>
@@ -18339,7 +18962,7 @@
       <c r="Q877" s="4"/>
       <c r="R877" s="4"/>
     </row>
-    <row r="878" spans="1:18" ht="13.5" customHeight="1">
+    <row r="878" ht="13.5" customHeight="1" spans="1:18">
       <c r="A878" s="4"/>
       <c r="B878" s="4"/>
       <c r="C878" s="4"/>
@@ -18359,7 +18982,7 @@
       <c r="Q878" s="4"/>
       <c r="R878" s="4"/>
     </row>
-    <row r="879" spans="1:18" ht="13.5" customHeight="1">
+    <row r="879" ht="13.5" customHeight="1" spans="1:18">
       <c r="A879" s="4"/>
       <c r="B879" s="4"/>
       <c r="C879" s="4"/>
@@ -18379,7 +19002,7 @@
       <c r="Q879" s="4"/>
       <c r="R879" s="4"/>
     </row>
-    <row r="880" spans="1:18" ht="13.5" customHeight="1">
+    <row r="880" ht="13.5" customHeight="1" spans="1:18">
       <c r="A880" s="4"/>
       <c r="B880" s="4"/>
       <c r="C880" s="4"/>
@@ -18399,7 +19022,7 @@
       <c r="Q880" s="4"/>
       <c r="R880" s="4"/>
     </row>
-    <row r="881" spans="1:18" ht="13.5" customHeight="1">
+    <row r="881" ht="13.5" customHeight="1" spans="1:18">
       <c r="A881" s="4"/>
       <c r="B881" s="4"/>
       <c r="C881" s="4"/>
@@ -18419,7 +19042,7 @@
       <c r="Q881" s="4"/>
       <c r="R881" s="4"/>
     </row>
-    <row r="882" spans="1:18" ht="13.5" customHeight="1">
+    <row r="882" ht="13.5" customHeight="1" spans="1:18">
       <c r="A882" s="4"/>
       <c r="B882" s="4"/>
       <c r="C882" s="4"/>
@@ -18439,7 +19062,7 @@
       <c r="Q882" s="4"/>
       <c r="R882" s="4"/>
     </row>
-    <row r="883" spans="1:18" ht="13.5" customHeight="1">
+    <row r="883" ht="13.5" customHeight="1" spans="1:18">
       <c r="A883" s="4"/>
       <c r="B883" s="4"/>
       <c r="C883" s="4"/>
@@ -18459,7 +19082,7 @@
       <c r="Q883" s="4"/>
       <c r="R883" s="4"/>
     </row>
-    <row r="884" spans="1:18" ht="13.5" customHeight="1">
+    <row r="884" ht="13.5" customHeight="1" spans="1:18">
       <c r="A884" s="4"/>
       <c r="B884" s="4"/>
       <c r="C884" s="4"/>
@@ -18479,7 +19102,7 @@
       <c r="Q884" s="4"/>
       <c r="R884" s="4"/>
     </row>
-    <row r="885" spans="1:18" ht="13.5" customHeight="1">
+    <row r="885" ht="13.5" customHeight="1" spans="1:18">
       <c r="A885" s="4"/>
       <c r="B885" s="4"/>
       <c r="C885" s="4"/>
@@ -18499,7 +19122,7 @@
       <c r="Q885" s="4"/>
       <c r="R885" s="4"/>
     </row>
-    <row r="886" spans="1:18" ht="13.5" customHeight="1">
+    <row r="886" ht="13.5" customHeight="1" spans="1:18">
       <c r="A886" s="4"/>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
@@ -18519,7 +19142,7 @@
       <c r="Q886" s="4"/>
       <c r="R886" s="4"/>
     </row>
-    <row r="887" spans="1:18" ht="13.5" customHeight="1">
+    <row r="887" ht="13.5" customHeight="1" spans="1:18">
       <c r="A887" s="4"/>
       <c r="B887" s="4"/>
       <c r="C887" s="4"/>
@@ -18539,7 +19162,7 @@
       <c r="Q887" s="4"/>
       <c r="R887" s="4"/>
     </row>
-    <row r="888" spans="1:18" ht="13.5" customHeight="1">
+    <row r="888" ht="13.5" customHeight="1" spans="1:18">
       <c r="A888" s="4"/>
       <c r="B888" s="4"/>
       <c r="C888" s="4"/>
@@ -18559,7 +19182,7 @@
       <c r="Q888" s="4"/>
       <c r="R888" s="4"/>
     </row>
-    <row r="889" spans="1:18" ht="13.5" customHeight="1">
+    <row r="889" ht="13.5" customHeight="1" spans="1:18">
       <c r="A889" s="4"/>
       <c r="B889" s="4"/>
       <c r="C889" s="4"/>
@@ -18579,7 +19202,7 @@
       <c r="Q889" s="4"/>
       <c r="R889" s="4"/>
     </row>
-    <row r="890" spans="1:18" ht="13.5" customHeight="1">
+    <row r="890" ht="13.5" customHeight="1" spans="1:18">
       <c r="A890" s="4"/>
       <c r="B890" s="4"/>
       <c r="C890" s="4"/>
@@ -18599,7 +19222,7 @@
       <c r="Q890" s="4"/>
       <c r="R890" s="4"/>
     </row>
-    <row r="891" spans="1:18" ht="13.5" customHeight="1">
+    <row r="891" ht="13.5" customHeight="1" spans="1:18">
       <c r="A891" s="4"/>
       <c r="B891" s="4"/>
       <c r="C891" s="4"/>
@@ -18619,7 +19242,7 @@
       <c r="Q891" s="4"/>
       <c r="R891" s="4"/>
     </row>
-    <row r="892" spans="1:18" ht="13.5" customHeight="1">
+    <row r="892" ht="13.5" customHeight="1" spans="1:18">
       <c r="A892" s="4"/>
       <c r="B892" s="4"/>
       <c r="C892" s="4"/>
@@ -18639,7 +19262,7 @@
       <c r="Q892" s="4"/>
       <c r="R892" s="4"/>
     </row>
-    <row r="893" spans="1:18" ht="13.5" customHeight="1">
+    <row r="893" ht="13.5" customHeight="1" spans="1:18">
       <c r="A893" s="4"/>
       <c r="B893" s="4"/>
       <c r="C893" s="4"/>
@@ -18659,7 +19282,7 @@
       <c r="Q893" s="4"/>
       <c r="R893" s="4"/>
     </row>
-    <row r="894" spans="1:18" ht="13.5" customHeight="1">
+    <row r="894" ht="13.5" customHeight="1" spans="1:18">
       <c r="A894" s="4"/>
       <c r="B894" s="4"/>
       <c r="C894" s="4"/>
@@ -18679,7 +19302,7 @@
       <c r="Q894" s="4"/>
       <c r="R894" s="4"/>
     </row>
-    <row r="895" spans="1:18" ht="13.5" customHeight="1">
+    <row r="895" ht="13.5" customHeight="1" spans="1:18">
       <c r="A895" s="4"/>
       <c r="B895" s="4"/>
       <c r="C895" s="4"/>
@@ -18699,7 +19322,7 @@
       <c r="Q895" s="4"/>
       <c r="R895" s="4"/>
     </row>
-    <row r="896" spans="1:18" ht="13.5" customHeight="1">
+    <row r="896" ht="13.5" customHeight="1" spans="1:18">
       <c r="A896" s="4"/>
       <c r="B896" s="4"/>
       <c r="C896" s="4"/>
@@ -18719,7 +19342,7 @@
       <c r="Q896" s="4"/>
       <c r="R896" s="4"/>
     </row>
-    <row r="897" spans="1:18" ht="13.5" customHeight="1">
+    <row r="897" ht="13.5" customHeight="1" spans="1:18">
       <c r="A897" s="4"/>
       <c r="B897" s="4"/>
       <c r="C897" s="4"/>
@@ -18739,7 +19362,7 @@
       <c r="Q897" s="4"/>
       <c r="R897" s="4"/>
     </row>
-    <row r="898" spans="1:18" ht="13.5" customHeight="1">
+    <row r="898" ht="13.5" customHeight="1" spans="1:18">
       <c r="A898" s="4"/>
       <c r="B898" s="4"/>
       <c r="C898" s="4"/>
@@ -18759,7 +19382,7 @@
       <c r="Q898" s="4"/>
       <c r="R898" s="4"/>
     </row>
-    <row r="899" spans="1:18" ht="13.5" customHeight="1">
+    <row r="899" ht="13.5" customHeight="1" spans="1:18">
       <c r="A899" s="4"/>
       <c r="B899" s="4"/>
       <c r="C899" s="4"/>
@@ -18779,7 +19402,7 @@
       <c r="Q899" s="4"/>
       <c r="R899" s="4"/>
     </row>
-    <row r="900" spans="1:18" ht="13.5" customHeight="1">
+    <row r="900" ht="13.5" customHeight="1" spans="1:18">
       <c r="A900" s="4"/>
       <c r="B900" s="4"/>
       <c r="C900" s="4"/>
@@ -18799,7 +19422,7 @@
       <c r="Q900" s="4"/>
       <c r="R900" s="4"/>
     </row>
-    <row r="901" spans="1:18" ht="13.5" customHeight="1">
+    <row r="901" ht="13.5" customHeight="1" spans="1:18">
       <c r="A901" s="4"/>
       <c r="B901" s="4"/>
       <c r="C901" s="4"/>
@@ -18819,7 +19442,7 @@
       <c r="Q901" s="4"/>
       <c r="R901" s="4"/>
     </row>
-    <row r="902" spans="1:18" ht="13.5" customHeight="1">
+    <row r="902" ht="13.5" customHeight="1" spans="1:18">
       <c r="A902" s="4"/>
       <c r="B902" s="4"/>
       <c r="C902" s="4"/>
@@ -18839,7 +19462,7 @@
       <c r="Q902" s="4"/>
       <c r="R902" s="4"/>
     </row>
-    <row r="903" spans="1:18" ht="13.5" customHeight="1">
+    <row r="903" ht="13.5" customHeight="1" spans="1:18">
       <c r="A903" s="4"/>
       <c r="B903" s="4"/>
       <c r="C903" s="4"/>
@@ -18859,7 +19482,7 @@
       <c r="Q903" s="4"/>
       <c r="R903" s="4"/>
     </row>
-    <row r="904" spans="1:18" ht="13.5" customHeight="1">
+    <row r="904" ht="13.5" customHeight="1" spans="1:18">
       <c r="A904" s="4"/>
       <c r="B904" s="4"/>
       <c r="C904" s="4"/>
@@ -18879,7 +19502,7 @@
       <c r="Q904" s="4"/>
       <c r="R904" s="4"/>
     </row>
-    <row r="905" spans="1:18" ht="13.5" customHeight="1">
+    <row r="905" ht="13.5" customHeight="1" spans="1:18">
       <c r="A905" s="4"/>
       <c r="B905" s="4"/>
       <c r="C905" s="4"/>
@@ -18899,7 +19522,7 @@
       <c r="Q905" s="4"/>
       <c r="R905" s="4"/>
     </row>
-    <row r="906" spans="1:18" ht="13.5" customHeight="1">
+    <row r="906" ht="13.5" customHeight="1" spans="1:18">
       <c r="A906" s="4"/>
       <c r="B906" s="4"/>
       <c r="C906" s="4"/>
@@ -18919,7 +19542,7 @@
       <c r="Q906" s="4"/>
       <c r="R906" s="4"/>
     </row>
-    <row r="907" spans="1:18" ht="13.5" customHeight="1">
+    <row r="907" ht="13.5" customHeight="1" spans="1:18">
       <c r="A907" s="4"/>
       <c r="B907" s="4"/>
       <c r="C907" s="4"/>
@@ -18939,7 +19562,7 @@
       <c r="Q907" s="4"/>
       <c r="R907" s="4"/>
     </row>
-    <row r="908" spans="1:18" ht="13.5" customHeight="1">
+    <row r="908" ht="13.5" customHeight="1" spans="1:18">
       <c r="A908" s="4"/>
       <c r="B908" s="4"/>
       <c r="C908" s="4"/>
@@ -18959,7 +19582,7 @@
       <c r="Q908" s="4"/>
       <c r="R908" s="4"/>
     </row>
-    <row r="909" spans="1:18" ht="13.5" customHeight="1">
+    <row r="909" ht="13.5" customHeight="1" spans="1:18">
       <c r="A909" s="4"/>
       <c r="B909" s="4"/>
       <c r="C909" s="4"/>
@@ -18979,7 +19602,7 @@
       <c r="Q909" s="4"/>
       <c r="R909" s="4"/>
     </row>
-    <row r="910" spans="1:18" ht="13.5" customHeight="1">
+    <row r="910" ht="13.5" customHeight="1" spans="1:18">
       <c r="A910" s="4"/>
       <c r="B910" s="4"/>
       <c r="C910" s="4"/>
@@ -18999,7 +19622,7 @@
       <c r="Q910" s="4"/>
       <c r="R910" s="4"/>
     </row>
-    <row r="911" spans="1:18" ht="13.5" customHeight="1">
+    <row r="911" ht="13.5" customHeight="1" spans="1:18">
       <c r="A911" s="4"/>
       <c r="B911" s="4"/>
       <c r="C911" s="4"/>
@@ -19019,7 +19642,7 @@
       <c r="Q911" s="4"/>
       <c r="R911" s="4"/>
     </row>
-    <row r="912" spans="1:18" ht="13.5" customHeight="1">
+    <row r="912" ht="13.5" customHeight="1" spans="1:18">
       <c r="A912" s="4"/>
       <c r="B912" s="4"/>
       <c r="C912" s="4"/>
@@ -19039,7 +19662,7 @@
       <c r="Q912" s="4"/>
       <c r="R912" s="4"/>
     </row>
-    <row r="913" spans="1:18" ht="13.5" customHeight="1">
+    <row r="913" ht="13.5" customHeight="1" spans="1:18">
       <c r="A913" s="4"/>
       <c r="B913" s="4"/>
       <c r="C913" s="4"/>
@@ -19059,7 +19682,7 @@
       <c r="Q913" s="4"/>
       <c r="R913" s="4"/>
     </row>
-    <row r="914" spans="1:18" ht="13.5" customHeight="1">
+    <row r="914" ht="13.5" customHeight="1" spans="1:18">
       <c r="A914" s="4"/>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
@@ -19079,7 +19702,7 @@
       <c r="Q914" s="4"/>
       <c r="R914" s="4"/>
     </row>
-    <row r="915" spans="1:18" ht="13.5" customHeight="1">
+    <row r="915" ht="13.5" customHeight="1" spans="1:18">
       <c r="A915" s="4"/>
       <c r="B915" s="4"/>
       <c r="C915" s="4"/>
@@ -19099,7 +19722,7 @@
       <c r="Q915" s="4"/>
       <c r="R915" s="4"/>
     </row>
-    <row r="916" spans="1:18" ht="13.5" customHeight="1">
+    <row r="916" ht="13.5" customHeight="1" spans="1:18">
       <c r="A916" s="4"/>
       <c r="B916" s="4"/>
       <c r="C916" s="4"/>
@@ -19119,7 +19742,7 @@
       <c r="Q916" s="4"/>
       <c r="R916" s="4"/>
     </row>
-    <row r="917" spans="1:18" ht="13.5" customHeight="1">
+    <row r="917" ht="13.5" customHeight="1" spans="1:18">
       <c r="A917" s="4"/>
       <c r="B917" s="4"/>
       <c r="C917" s="4"/>
@@ -19139,7 +19762,7 @@
       <c r="Q917" s="4"/>
       <c r="R917" s="4"/>
     </row>
-    <row r="918" spans="1:18" ht="13.5" customHeight="1">
+    <row r="918" ht="13.5" customHeight="1" spans="1:18">
       <c r="A918" s="4"/>
       <c r="B918" s="4"/>
       <c r="C918" s="4"/>
@@ -19159,7 +19782,7 @@
       <c r="Q918" s="4"/>
       <c r="R918" s="4"/>
     </row>
-    <row r="919" spans="1:18" ht="13.5" customHeight="1">
+    <row r="919" ht="13.5" customHeight="1" spans="1:18">
       <c r="A919" s="4"/>
       <c r="B919" s="4"/>
       <c r="C919" s="4"/>
@@ -19179,7 +19802,7 @@
       <c r="Q919" s="4"/>
       <c r="R919" s="4"/>
     </row>
-    <row r="920" spans="1:18" ht="13.5" customHeight="1">
+    <row r="920" ht="13.5" customHeight="1" spans="1:18">
       <c r="A920" s="4"/>
       <c r="B920" s="4"/>
       <c r="C920" s="4"/>
@@ -19199,7 +19822,7 @@
       <c r="Q920" s="4"/>
       <c r="R920" s="4"/>
     </row>
-    <row r="921" spans="1:18" ht="13.5" customHeight="1">
+    <row r="921" ht="13.5" customHeight="1" spans="1:18">
       <c r="A921" s="4"/>
       <c r="B921" s="4"/>
       <c r="C921" s="4"/>
@@ -19219,7 +19842,7 @@
       <c r="Q921" s="4"/>
       <c r="R921" s="4"/>
     </row>
-    <row r="922" spans="1:18" ht="13.5" customHeight="1">
+    <row r="922" ht="13.5" customHeight="1" spans="1:18">
       <c r="A922" s="4"/>
       <c r="B922" s="4"/>
       <c r="C922" s="4"/>
@@ -19239,7 +19862,7 @@
       <c r="Q922" s="4"/>
       <c r="R922" s="4"/>
     </row>
-    <row r="923" spans="1:18" ht="13.5" customHeight="1">
+    <row r="923" ht="13.5" customHeight="1" spans="1:18">
       <c r="A923" s="4"/>
       <c r="B923" s="4"/>
       <c r="C923" s="4"/>
@@ -19259,7 +19882,7 @@
       <c r="Q923" s="4"/>
       <c r="R923" s="4"/>
     </row>
-    <row r="924" spans="1:18" ht="13.5" customHeight="1">
+    <row r="924" ht="13.5" customHeight="1" spans="1:18">
       <c r="A924" s="4"/>
       <c r="B924" s="4"/>
       <c r="C924" s="4"/>
@@ -19279,7 +19902,7 @@
       <c r="Q924" s="4"/>
       <c r="R924" s="4"/>
     </row>
-    <row r="925" spans="1:18" ht="13.5" customHeight="1">
+    <row r="925" ht="13.5" customHeight="1" spans="1:18">
       <c r="A925" s="4"/>
       <c r="B925" s="4"/>
       <c r="C925" s="4"/>
@@ -19299,7 +19922,7 @@
       <c r="Q925" s="4"/>
       <c r="R925" s="4"/>
     </row>
-    <row r="926" spans="1:18" ht="13.5" customHeight="1">
+    <row r="926" ht="13.5" customHeight="1" spans="1:18">
       <c r="A926" s="4"/>
       <c r="B926" s="4"/>
       <c r="C926" s="4"/>
@@ -19319,7 +19942,7 @@
       <c r="Q926" s="4"/>
       <c r="R926" s="4"/>
     </row>
-    <row r="927" spans="1:18" ht="13.5" customHeight="1">
+    <row r="927" ht="13.5" customHeight="1" spans="1:18">
       <c r="A927" s="4"/>
       <c r="B927" s="4"/>
       <c r="C927" s="4"/>
@@ -19339,7 +19962,7 @@
       <c r="Q927" s="4"/>
       <c r="R927" s="4"/>
     </row>
-    <row r="928" spans="1:18" ht="13.5" customHeight="1">
+    <row r="928" ht="13.5" customHeight="1" spans="1:18">
       <c r="A928" s="4"/>
       <c r="B928" s="4"/>
       <c r="C928" s="4"/>
@@ -19359,7 +19982,7 @@
       <c r="Q928" s="4"/>
       <c r="R928" s="4"/>
     </row>
-    <row r="929" spans="1:18" ht="13.5" customHeight="1">
+    <row r="929" ht="13.5" customHeight="1" spans="1:18">
       <c r="A929" s="4"/>
       <c r="B929" s="4"/>
       <c r="C929" s="4"/>
@@ -19379,7 +20002,7 @@
       <c r="Q929" s="4"/>
       <c r="R929" s="4"/>
     </row>
-    <row r="930" spans="1:18" ht="13.5" customHeight="1">
+    <row r="930" ht="13.5" customHeight="1" spans="1:18">
       <c r="A930" s="4"/>
       <c r="B930" s="4"/>
       <c r="C930" s="4"/>
@@ -19399,7 +20022,7 @@
       <c r="Q930" s="4"/>
       <c r="R930" s="4"/>
     </row>
-    <row r="931" spans="1:18" ht="13.5" customHeight="1">
+    <row r="931" ht="13.5" customHeight="1" spans="1:18">
       <c r="A931" s="4"/>
       <c r="B931" s="4"/>
       <c r="C931" s="4"/>
@@ -19419,7 +20042,7 @@
       <c r="Q931" s="4"/>
       <c r="R931" s="4"/>
     </row>
-    <row r="932" spans="1:18" ht="13.5" customHeight="1">
+    <row r="932" ht="13.5" customHeight="1" spans="1:18">
       <c r="A932" s="4"/>
       <c r="B932" s="4"/>
       <c r="C932" s="4"/>
@@ -19439,7 +20062,7 @@
       <c r="Q932" s="4"/>
       <c r="R932" s="4"/>
     </row>
-    <row r="933" spans="1:18" ht="13.5" customHeight="1">
+    <row r="933" ht="13.5" customHeight="1" spans="1:18">
       <c r="A933" s="4"/>
       <c r="B933" s="4"/>
       <c r="C933" s="4"/>
@@ -19459,7 +20082,7 @@
       <c r="Q933" s="4"/>
       <c r="R933" s="4"/>
     </row>
-    <row r="934" spans="1:18" ht="13.5" customHeight="1">
+    <row r="934" ht="13.5" customHeight="1" spans="1:18">
       <c r="A934" s="4"/>
       <c r="B934" s="4"/>
       <c r="C934" s="4"/>
@@ -19479,7 +20102,7 @@
       <c r="Q934" s="4"/>
       <c r="R934" s="4"/>
     </row>
-    <row r="935" spans="1:18" ht="13.5" customHeight="1">
+    <row r="935" ht="13.5" customHeight="1" spans="1:18">
       <c r="A935" s="4"/>
       <c r="B935" s="4"/>
       <c r="C935" s="4"/>
@@ -19499,7 +20122,7 @@
       <c r="Q935" s="4"/>
       <c r="R935" s="4"/>
     </row>
-    <row r="936" spans="1:18" ht="13.5" customHeight="1">
+    <row r="936" ht="13.5" customHeight="1" spans="1:18">
       <c r="A936" s="4"/>
       <c r="B936" s="4"/>
       <c r="C936" s="4"/>
@@ -19519,7 +20142,7 @@
       <c r="Q936" s="4"/>
       <c r="R936" s="4"/>
     </row>
-    <row r="937" spans="1:18" ht="13.5" customHeight="1">
+    <row r="937" ht="13.5" customHeight="1" spans="1:18">
       <c r="A937" s="4"/>
       <c r="B937" s="4"/>
       <c r="C937" s="4"/>
@@ -19539,7 +20162,7 @@
       <c r="Q937" s="4"/>
       <c r="R937" s="4"/>
     </row>
-    <row r="938" spans="1:18" ht="13.5" customHeight="1">
+    <row r="938" ht="13.5" customHeight="1" spans="1:18">
       <c r="A938" s="4"/>
       <c r="B938" s="4"/>
       <c r="C938" s="4"/>
@@ -19559,7 +20182,7 @@
       <c r="Q938" s="4"/>
       <c r="R938" s="4"/>
     </row>
-    <row r="939" spans="1:18" ht="13.5" customHeight="1">
+    <row r="939" ht="13.5" customHeight="1" spans="1:18">
       <c r="A939" s="4"/>
       <c r="B939" s="4"/>
       <c r="C939" s="4"/>
@@ -19579,7 +20202,7 @@
       <c r="Q939" s="4"/>
       <c r="R939" s="4"/>
     </row>
-    <row r="940" spans="1:18" ht="13.5" customHeight="1">
+    <row r="940" ht="13.5" customHeight="1" spans="1:18">
       <c r="A940" s="4"/>
       <c r="B940" s="4"/>
       <c r="C940" s="4"/>
@@ -19599,7 +20222,7 @@
       <c r="Q940" s="4"/>
       <c r="R940" s="4"/>
     </row>
-    <row r="941" spans="1:18" ht="13.5" customHeight="1">
+    <row r="941" ht="13.5" customHeight="1" spans="1:18">
       <c r="A941" s="4"/>
       <c r="B941" s="4"/>
       <c r="C941" s="4"/>
@@ -19619,7 +20242,7 @@
       <c r="Q941" s="4"/>
       <c r="R941" s="4"/>
     </row>
-    <row r="942" spans="1:18" ht="13.5" customHeight="1">
+    <row r="942" ht="13.5" customHeight="1" spans="1:18">
       <c r="A942" s="4"/>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
@@ -19639,7 +20262,7 @@
       <c r="Q942" s="4"/>
       <c r="R942" s="4"/>
     </row>
-    <row r="943" spans="1:18" ht="13.5" customHeight="1">
+    <row r="943" ht="13.5" customHeight="1" spans="1:18">
       <c r="A943" s="4"/>
       <c r="B943" s="4"/>
       <c r="C943" s="4"/>
@@ -19659,7 +20282,7 @@
       <c r="Q943" s="4"/>
       <c r="R943" s="4"/>
     </row>
-    <row r="944" spans="1:18" ht="13.5" customHeight="1">
+    <row r="944" ht="13.5" customHeight="1" spans="1:18">
       <c r="A944" s="4"/>
       <c r="B944" s="4"/>
       <c r="C944" s="4"/>
@@ -19679,7 +20302,7 @@
       <c r="Q944" s="4"/>
       <c r="R944" s="4"/>
     </row>
-    <row r="945" spans="1:18" ht="13.5" customHeight="1">
+    <row r="945" ht="13.5" customHeight="1" spans="1:18">
       <c r="A945" s="4"/>
       <c r="B945" s="4"/>
       <c r="C945" s="4"/>
@@ -19699,7 +20322,7 @@
       <c r="Q945" s="4"/>
       <c r="R945" s="4"/>
     </row>
-    <row r="946" spans="1:18" ht="13.5" customHeight="1">
+    <row r="946" ht="13.5" customHeight="1" spans="1:18">
       <c r="A946" s="4"/>
       <c r="B946" s="4"/>
       <c r="C946" s="4"/>
@@ -19719,7 +20342,7 @@
       <c r="Q946" s="4"/>
       <c r="R946" s="4"/>
     </row>
-    <row r="947" spans="1:18" ht="13.5" customHeight="1">
+    <row r="947" ht="13.5" customHeight="1" spans="1:18">
       <c r="A947" s="4"/>
       <c r="B947" s="4"/>
       <c r="C947" s="4"/>
@@ -19739,7 +20362,7 @@
       <c r="Q947" s="4"/>
       <c r="R947" s="4"/>
     </row>
-    <row r="948" spans="1:18" ht="13.5" customHeight="1">
+    <row r="948" ht="13.5" customHeight="1" spans="1:18">
       <c r="A948" s="4"/>
       <c r="B948" s="4"/>
       <c r="C948" s="4"/>
@@ -19759,7 +20382,7 @@
       <c r="Q948" s="4"/>
       <c r="R948" s="4"/>
     </row>
-    <row r="949" spans="1:18" ht="13.5" customHeight="1">
+    <row r="949" ht="13.5" customHeight="1" spans="1:18">
       <c r="A949" s="4"/>
       <c r="B949" s="4"/>
       <c r="C949" s="4"/>
@@ -19779,7 +20402,7 @@
       <c r="Q949" s="4"/>
       <c r="R949" s="4"/>
     </row>
-    <row r="950" spans="1:18" ht="13.5" customHeight="1">
+    <row r="950" ht="13.5" customHeight="1" spans="1:18">
       <c r="A950" s="4"/>
       <c r="B950" s="4"/>
       <c r="C950" s="4"/>
@@ -19799,7 +20422,7 @@
       <c r="Q950" s="4"/>
       <c r="R950" s="4"/>
     </row>
-    <row r="951" spans="1:18" ht="13.5" customHeight="1">
+    <row r="951" ht="13.5" customHeight="1" spans="1:18">
       <c r="A951" s="4"/>
       <c r="B951" s="4"/>
       <c r="C951" s="4"/>
@@ -19819,7 +20442,7 @@
       <c r="Q951" s="4"/>
       <c r="R951" s="4"/>
     </row>
-    <row r="952" spans="1:18" ht="13.5" customHeight="1">
+    <row r="952" ht="13.5" customHeight="1" spans="1:18">
       <c r="A952" s="4"/>
       <c r="B952" s="4"/>
       <c r="C952" s="4"/>
@@ -19839,7 +20462,7 @@
       <c r="Q952" s="4"/>
       <c r="R952" s="4"/>
     </row>
-    <row r="953" spans="1:18" ht="13.5" customHeight="1">
+    <row r="953" ht="13.5" customHeight="1" spans="1:18">
       <c r="A953" s="4"/>
       <c r="B953" s="4"/>
       <c r="C953" s="4"/>
@@ -19859,7 +20482,7 @@
       <c r="Q953" s="4"/>
       <c r="R953" s="4"/>
     </row>
-    <row r="954" spans="1:18" ht="13.5" customHeight="1">
+    <row r="954" ht="13.5" customHeight="1" spans="1:18">
       <c r="A954" s="4"/>
       <c r="B954" s="4"/>
       <c r="C954" s="4"/>
@@ -19879,7 +20502,7 @@
       <c r="Q954" s="4"/>
       <c r="R954" s="4"/>
     </row>
-    <row r="955" spans="1:18" ht="13.5" customHeight="1">
+    <row r="955" ht="13.5" customHeight="1" spans="1:18">
       <c r="A955" s="4"/>
       <c r="B955" s="4"/>
       <c r="C955" s="4"/>
@@ -19899,7 +20522,7 @@
       <c r="Q955" s="4"/>
       <c r="R955" s="4"/>
     </row>
-    <row r="956" spans="1:18" ht="13.5" customHeight="1">
+    <row r="956" ht="13.5" customHeight="1" spans="1:18">
       <c r="A956" s="4"/>
       <c r="B956" s="4"/>
       <c r="C956" s="4"/>
@@ -19919,7 +20542,7 @@
       <c r="Q956" s="4"/>
       <c r="R956" s="4"/>
     </row>
-    <row r="957" spans="1:18" ht="13.5" customHeight="1">
+    <row r="957" ht="13.5" customHeight="1" spans="1:18">
       <c r="A957" s="4"/>
       <c r="B957" s="4"/>
       <c r="C957" s="4"/>
@@ -19939,7 +20562,7 @@
       <c r="Q957" s="4"/>
       <c r="R957" s="4"/>
     </row>
-    <row r="958" spans="1:18" ht="13.5" customHeight="1">
+    <row r="958" ht="13.5" customHeight="1" spans="1:18">
       <c r="A958" s="4"/>
       <c r="B958" s="4"/>
       <c r="C958" s="4"/>
@@ -19959,7 +20582,7 @@
       <c r="Q958" s="4"/>
       <c r="R958" s="4"/>
     </row>
-    <row r="959" spans="1:18" ht="13.5" customHeight="1">
+    <row r="959" ht="13.5" customHeight="1" spans="1:18">
       <c r="A959" s="4"/>
       <c r="B959" s="4"/>
       <c r="C959" s="4"/>
@@ -19979,7 +20602,7 @@
       <c r="Q959" s="4"/>
       <c r="R959" s="4"/>
     </row>
-    <row r="960" spans="1:18" ht="13.5" customHeight="1">
+    <row r="960" ht="13.5" customHeight="1" spans="1:18">
       <c r="A960" s="4"/>
       <c r="B960" s="4"/>
       <c r="C960" s="4"/>
@@ -19999,7 +20622,7 @@
       <c r="Q960" s="4"/>
       <c r="R960" s="4"/>
     </row>
-    <row r="961" spans="1:18" ht="13.5" customHeight="1">
+    <row r="961" ht="13.5" customHeight="1" spans="1:18">
       <c r="A961" s="4"/>
       <c r="B961" s="4"/>
       <c r="C961" s="4"/>
@@ -20019,7 +20642,7 @@
       <c r="Q961" s="4"/>
       <c r="R961" s="4"/>
     </row>
-    <row r="962" spans="1:18" ht="13.5" customHeight="1">
+    <row r="962" ht="13.5" customHeight="1" spans="1:18">
       <c r="A962" s="4"/>
       <c r="B962" s="4"/>
       <c r="C962" s="4"/>
@@ -20039,7 +20662,7 @@
       <c r="Q962" s="4"/>
       <c r="R962" s="4"/>
     </row>
-    <row r="963" spans="1:18" ht="13.5" customHeight="1">
+    <row r="963" ht="13.5" customHeight="1" spans="1:18">
       <c r="A963" s="4"/>
       <c r="B963" s="4"/>
       <c r="C963" s="4"/>
@@ -20059,7 +20682,7 @@
       <c r="Q963" s="4"/>
       <c r="R963" s="4"/>
     </row>
-    <row r="964" spans="1:18" ht="13.5" customHeight="1">
+    <row r="964" ht="13.5" customHeight="1" spans="1:18">
       <c r="A964" s="4"/>
       <c r="B964" s="4"/>
       <c r="C964" s="4"/>
@@ -20079,7 +20702,7 @@
       <c r="Q964" s="4"/>
       <c r="R964" s="4"/>
     </row>
-    <row r="965" spans="1:18" ht="13.5" customHeight="1">
+    <row r="965" ht="13.5" customHeight="1" spans="1:18">
       <c r="A965" s="4"/>
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
@@ -20099,7 +20722,7 @@
       <c r="Q965" s="4"/>
       <c r="R965" s="4"/>
     </row>
-    <row r="966" spans="1:18" ht="13.5" customHeight="1">
+    <row r="966" ht="13.5" customHeight="1" spans="1:18">
       <c r="A966" s="4"/>
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
@@ -20119,7 +20742,7 @@
       <c r="Q966" s="4"/>
       <c r="R966" s="4"/>
     </row>
-    <row r="967" spans="1:18" ht="13.5" customHeight="1">
+    <row r="967" ht="13.5" customHeight="1" spans="1:18">
       <c r="A967" s="4"/>
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
@@ -20139,7 +20762,7 @@
       <c r="Q967" s="4"/>
       <c r="R967" s="4"/>
     </row>
-    <row r="968" spans="1:18" ht="13.5" customHeight="1">
+    <row r="968" ht="13.5" customHeight="1" spans="1:18">
       <c r="A968" s="4"/>
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
@@ -20159,7 +20782,7 @@
       <c r="Q968" s="4"/>
       <c r="R968" s="4"/>
     </row>
-    <row r="969" spans="1:18" ht="13.5" customHeight="1">
+    <row r="969" ht="13.5" customHeight="1" spans="1:18">
       <c r="A969" s="4"/>
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
@@ -20179,7 +20802,7 @@
       <c r="Q969" s="4"/>
       <c r="R969" s="4"/>
     </row>
-    <row r="970" spans="1:18" ht="13.5" customHeight="1">
+    <row r="970" ht="13.5" customHeight="1" spans="1:18">
       <c r="A970" s="4"/>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
@@ -20199,7 +20822,7 @@
       <c r="Q970" s="4"/>
       <c r="R970" s="4"/>
     </row>
-    <row r="971" spans="1:18" ht="13.5" customHeight="1">
+    <row r="971" ht="13.5" customHeight="1" spans="1:18">
       <c r="A971" s="4"/>
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
@@ -20219,7 +20842,7 @@
       <c r="Q971" s="4"/>
       <c r="R971" s="4"/>
     </row>
-    <row r="972" spans="1:18" ht="13.5" customHeight="1">
+    <row r="972" ht="13.5" customHeight="1" spans="1:18">
       <c r="A972" s="4"/>
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
@@ -20239,7 +20862,7 @@
       <c r="Q972" s="4"/>
       <c r="R972" s="4"/>
     </row>
-    <row r="973" spans="1:18" ht="13.5" customHeight="1">
+    <row r="973" ht="13.5" customHeight="1" spans="1:18">
       <c r="A973" s="4"/>
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
@@ -20259,7 +20882,7 @@
       <c r="Q973" s="4"/>
       <c r="R973" s="4"/>
     </row>
-    <row r="974" spans="1:18" ht="13.5" customHeight="1">
+    <row r="974" ht="13.5" customHeight="1" spans="1:18">
       <c r="A974" s="4"/>
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
@@ -20279,7 +20902,7 @@
       <c r="Q974" s="4"/>
       <c r="R974" s="4"/>
     </row>
-    <row r="975" spans="1:18" ht="13.5" customHeight="1">
+    <row r="975" ht="13.5" customHeight="1" spans="1:18">
       <c r="A975" s="4"/>
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
@@ -20299,7 +20922,7 @@
       <c r="Q975" s="4"/>
       <c r="R975" s="4"/>
     </row>
-    <row r="976" spans="1:18" ht="13.5" customHeight="1">
+    <row r="976" ht="13.5" customHeight="1" spans="1:18">
       <c r="A976" s="4"/>
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
@@ -20319,7 +20942,7 @@
       <c r="Q976" s="4"/>
       <c r="R976" s="4"/>
     </row>
-    <row r="977" spans="1:18" ht="13.5" customHeight="1">
+    <row r="977" ht="13.5" customHeight="1" spans="1:18">
       <c r="A977" s="4"/>
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
@@ -20339,7 +20962,7 @@
       <c r="Q977" s="4"/>
       <c r="R977" s="4"/>
     </row>
-    <row r="978" spans="1:18" ht="13.5" customHeight="1">
+    <row r="978" ht="13.5" customHeight="1" spans="1:18">
       <c r="A978" s="4"/>
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
@@ -20359,7 +20982,7 @@
       <c r="Q978" s="4"/>
       <c r="R978" s="4"/>
     </row>
-    <row r="979" spans="1:18" ht="13.5" customHeight="1">
+    <row r="979" ht="13.5" customHeight="1" spans="1:18">
       <c r="A979" s="4"/>
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
@@ -20379,7 +21002,7 @@
       <c r="Q979" s="4"/>
       <c r="R979" s="4"/>
     </row>
-    <row r="980" spans="1:18" ht="13.5" customHeight="1">
+    <row r="980" ht="13.5" customHeight="1" spans="1:18">
       <c r="A980" s="4"/>
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
@@ -20399,7 +21022,7 @@
       <c r="Q980" s="4"/>
       <c r="R980" s="4"/>
     </row>
-    <row r="981" spans="1:18" ht="13.5" customHeight="1">
+    <row r="981" ht="13.5" customHeight="1" spans="1:18">
       <c r="A981" s="4"/>
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
@@ -20419,7 +21042,7 @@
       <c r="Q981" s="4"/>
       <c r="R981" s="4"/>
     </row>
-    <row r="982" spans="1:18" ht="13.5" customHeight="1">
+    <row r="982" ht="13.5" customHeight="1" spans="1:18">
       <c r="A982" s="4"/>
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
@@ -20439,7 +21062,7 @@
       <c r="Q982" s="4"/>
       <c r="R982" s="4"/>
     </row>
-    <row r="983" spans="1:18" ht="13.5" customHeight="1">
+    <row r="983" ht="13.5" customHeight="1" spans="1:18">
       <c r="A983" s="4"/>
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
@@ -20459,7 +21082,7 @@
       <c r="Q983" s="4"/>
       <c r="R983" s="4"/>
     </row>
-    <row r="984" spans="1:18" ht="13.5" customHeight="1">
+    <row r="984" ht="13.5" customHeight="1" spans="1:18">
       <c r="A984" s="4"/>
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
@@ -20479,7 +21102,7 @@
       <c r="Q984" s="4"/>
       <c r="R984" s="4"/>
     </row>
-    <row r="985" spans="1:18" ht="13.5" customHeight="1">
+    <row r="985" ht="13.5" customHeight="1" spans="1:18">
       <c r="A985" s="4"/>
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
@@ -20499,7 +21122,7 @@
       <c r="Q985" s="4"/>
       <c r="R985" s="4"/>
     </row>
-    <row r="986" spans="1:18" ht="13.5" customHeight="1">
+    <row r="986" ht="13.5" customHeight="1" spans="1:18">
       <c r="A986" s="4"/>
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
@@ -20519,7 +21142,7 @@
       <c r="Q986" s="4"/>
       <c r="R986" s="4"/>
     </row>
-    <row r="987" spans="1:18" ht="13.5" customHeight="1">
+    <row r="987" ht="13.5" customHeight="1" spans="1:18">
       <c r="A987" s="4"/>
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
@@ -20539,7 +21162,7 @@
       <c r="Q987" s="4"/>
       <c r="R987" s="4"/>
     </row>
-    <row r="988" spans="1:18" ht="13.5" customHeight="1">
+    <row r="988" ht="13.5" customHeight="1" spans="1:18">
       <c r="A988" s="4"/>
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
@@ -20559,7 +21182,7 @@
       <c r="Q988" s="4"/>
       <c r="R988" s="4"/>
     </row>
-    <row r="989" spans="1:18" ht="13.5" customHeight="1">
+    <row r="989" ht="13.5" customHeight="1" spans="1:18">
       <c r="A989" s="4"/>
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
@@ -20579,7 +21202,7 @@
       <c r="Q989" s="4"/>
       <c r="R989" s="4"/>
     </row>
-    <row r="990" spans="1:18" ht="13.5" customHeight="1">
+    <row r="990" ht="13.5" customHeight="1" spans="1:18">
       <c r="A990" s="4"/>
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
@@ -20599,7 +21222,7 @@
       <c r="Q990" s="4"/>
       <c r="R990" s="4"/>
     </row>
-    <row r="991" spans="1:18" ht="13.5" customHeight="1">
+    <row r="991" ht="13.5" customHeight="1" spans="1:18">
       <c r="A991" s="4"/>
       <c r="B991" s="4"/>
       <c r="C991" s="4"/>
@@ -20619,7 +21242,7 @@
       <c r="Q991" s="4"/>
       <c r="R991" s="4"/>
     </row>
-    <row r="992" spans="1:18" ht="13.5" customHeight="1">
+    <row r="992" ht="13.5" customHeight="1" spans="1:18">
       <c r="A992" s="4"/>
       <c r="B992" s="4"/>
       <c r="C992" s="4"/>
@@ -20639,7 +21262,7 @@
       <c r="Q992" s="4"/>
       <c r="R992" s="4"/>
     </row>
-    <row r="993" spans="1:18" ht="13.5" customHeight="1">
+    <row r="993" ht="13.5" customHeight="1" spans="1:18">
       <c r="A993" s="4"/>
       <c r="B993" s="4"/>
       <c r="C993" s="4"/>
@@ -20659,7 +21282,7 @@
       <c r="Q993" s="4"/>
       <c r="R993" s="4"/>
     </row>
-    <row r="994" spans="1:18" ht="13.5" customHeight="1">
+    <row r="994" ht="13.5" customHeight="1" spans="1:18">
       <c r="A994" s="4"/>
       <c r="B994" s="4"/>
       <c r="C994" s="4"/>
@@ -20679,7 +21302,7 @@
       <c r="Q994" s="4"/>
       <c r="R994" s="4"/>
     </row>
-    <row r="995" spans="1:18" ht="13.5" customHeight="1">
+    <row r="995" ht="13.5" customHeight="1" spans="1:18">
       <c r="A995" s="4"/>
       <c r="B995" s="4"/>
       <c r="C995" s="4"/>
@@ -20699,7 +21322,7 @@
       <c r="Q995" s="4"/>
       <c r="R995" s="4"/>
     </row>
-    <row r="996" spans="1:18" ht="13.5" customHeight="1">
+    <row r="996" ht="13.5" customHeight="1" spans="1:18">
       <c r="A996" s="4"/>
       <c r="B996" s="4"/>
       <c r="C996" s="4"/>
@@ -20719,7 +21342,7 @@
       <c r="Q996" s="4"/>
       <c r="R996" s="4"/>
     </row>
-    <row r="997" spans="1:18" ht="13.5" customHeight="1">
+    <row r="997" ht="13.5" customHeight="1" spans="1:18">
       <c r="A997" s="4"/>
       <c r="B997" s="4"/>
       <c r="C997" s="4"/>
@@ -20739,7 +21362,7 @@
       <c r="Q997" s="4"/>
       <c r="R997" s="4"/>
     </row>
-    <row r="998" spans="1:18" ht="13.5" customHeight="1">
+    <row r="998" ht="13.5" customHeight="1" spans="1:18">
       <c r="A998" s="4"/>
       <c r="B998" s="4"/>
       <c r="C998" s="4"/>
@@ -20762,5 +21385,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>